--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91C6228-939D-4236-B9D7-CCCD2351EF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC11D4E-9CB6-48F7-8F4F-8A3EFE2444FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,10 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -349,1242 +353,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.18357200000000001</v>
+        <v>0.20014299999999999</v>
       </c>
       <c r="B1">
-        <v>0.18604399999999999</v>
+        <v>0.201714</v>
       </c>
       <c r="C1">
-        <v>0.18849099999999999</v>
+        <v>0.20338500000000001</v>
       </c>
       <c r="D1">
-        <v>0.189997</v>
+        <v>0.20743</v>
       </c>
       <c r="E1">
-        <v>0.19217100000000001</v>
+        <v>0.210482</v>
       </c>
       <c r="F1">
-        <v>0.193634</v>
+        <v>0.21307300000000001</v>
       </c>
       <c r="G1">
-        <v>0.194249</v>
+        <v>0.215361</v>
       </c>
       <c r="H1">
-        <v>0.196158</v>
+        <v>0.21770900000000001</v>
       </c>
       <c r="I1">
-        <v>0.19721900000000001</v>
+        <v>0.22001100000000001</v>
       </c>
       <c r="J1">
-        <v>0.19936200000000001</v>
+        <v>0.220716</v>
       </c>
       <c r="K1">
-        <v>0.20069400000000001</v>
+        <v>0.22278999999999999</v>
       </c>
       <c r="L1">
-        <v>0.203764</v>
+        <v>0.224472</v>
       </c>
       <c r="M1">
-        <v>0.20727699999999999</v>
+        <v>0.22745199999999999</v>
       </c>
       <c r="N1">
-        <v>0.209754</v>
+        <v>0.23051199999999999</v>
       </c>
       <c r="O1">
-        <v>0.21176400000000001</v>
+        <v>0.23377800000000001</v>
       </c>
       <c r="P1">
-        <v>0.21374899999999999</v>
+        <v>0.23646</v>
       </c>
       <c r="Q1">
-        <v>0.216943</v>
+        <v>0.238431</v>
       </c>
       <c r="R1">
-        <v>0.221999</v>
+        <v>0.23975099999999999</v>
       </c>
       <c r="S1">
-        <v>0.223968</v>
+        <v>0.240897</v>
       </c>
       <c r="T1">
-        <v>0.224716</v>
+        <v>0.23660900000000001</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.185972</v>
+        <v>0.20213900000000001</v>
       </c>
       <c r="B2">
-        <v>0.18826799999999999</v>
+        <v>0.20371800000000001</v>
       </c>
       <c r="C2">
-        <v>0.19075</v>
+        <v>0.20533699999999999</v>
       </c>
       <c r="D2">
-        <v>0.19220699999999999</v>
+        <v>0.20932600000000001</v>
       </c>
       <c r="E2">
-        <v>0.19417400000000001</v>
+        <v>0.212538</v>
       </c>
       <c r="F2">
-        <v>0.19553899999999999</v>
+        <v>0.215195</v>
       </c>
       <c r="G2">
-        <v>0.19623599999999999</v>
+        <v>0.217193</v>
       </c>
       <c r="H2">
-        <v>0.19823399999999999</v>
+        <v>0.219614</v>
       </c>
       <c r="I2">
-        <v>0.199381</v>
+        <v>0.22188099999999999</v>
       </c>
       <c r="J2">
-        <v>0.20161699999999999</v>
+        <v>0.222552</v>
       </c>
       <c r="K2">
-        <v>0.203071</v>
+        <v>0.224609</v>
       </c>
       <c r="L2">
-        <v>0.20596400000000001</v>
+        <v>0.226464</v>
       </c>
       <c r="M2">
-        <v>0.20934700000000001</v>
+        <v>0.229545</v>
       </c>
       <c r="N2">
-        <v>0.21193500000000001</v>
+        <v>0.23247100000000001</v>
       </c>
       <c r="O2">
-        <v>0.21399199999999999</v>
+        <v>0.23577000000000001</v>
       </c>
       <c r="P2">
-        <v>0.216145</v>
+        <v>0.23802899999999999</v>
       </c>
       <c r="Q2">
-        <v>0.21929799999999999</v>
+        <v>0.239788</v>
       </c>
       <c r="R2">
-        <v>0.224188</v>
+        <v>0.241095</v>
       </c>
       <c r="S2">
-        <v>0.22622200000000001</v>
+        <v>0.24244399999999999</v>
       </c>
       <c r="T2">
-        <v>0.22694700000000001</v>
+        <v>0.238398</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.18771299999999999</v>
+        <v>0.205009</v>
       </c>
       <c r="B3">
-        <v>0.190086</v>
+        <v>0.20652100000000001</v>
       </c>
       <c r="C3">
-        <v>0.19278500000000001</v>
+        <v>0.20799599999999999</v>
       </c>
       <c r="D3">
-        <v>0.19422700000000001</v>
+        <v>0.21218000000000001</v>
       </c>
       <c r="E3">
-        <v>0.19622600000000001</v>
+        <v>0.21532999999999999</v>
       </c>
       <c r="F3">
-        <v>0.19744700000000001</v>
+        <v>0.218142</v>
       </c>
       <c r="G3">
-        <v>0.19816600000000001</v>
+        <v>0.22004399999999999</v>
       </c>
       <c r="H3">
-        <v>0.20012099999999999</v>
+        <v>0.22201000000000001</v>
       </c>
       <c r="I3">
-        <v>0.20119600000000001</v>
+        <v>0.22412899999999999</v>
       </c>
       <c r="J3">
-        <v>0.20344300000000001</v>
+        <v>0.224803</v>
       </c>
       <c r="K3">
-        <v>0.20504</v>
+        <v>0.22700899999999999</v>
       </c>
       <c r="L3">
-        <v>0.207755</v>
+        <v>0.22889899999999999</v>
       </c>
       <c r="M3">
-        <v>0.21100099999999999</v>
+        <v>0.23198099999999999</v>
       </c>
       <c r="N3">
-        <v>0.21376200000000001</v>
+        <v>0.23452899999999999</v>
       </c>
       <c r="O3">
-        <v>0.215702</v>
+        <v>0.237985</v>
       </c>
       <c r="P3">
-        <v>0.21773200000000001</v>
+        <v>0.24038100000000001</v>
       </c>
       <c r="Q3">
-        <v>0.22064</v>
+        <v>0.242398</v>
       </c>
       <c r="R3">
-        <v>0.225746</v>
+        <v>0.24382400000000001</v>
       </c>
       <c r="S3">
-        <v>0.227878</v>
+        <v>0.245224</v>
       </c>
       <c r="T3">
-        <v>0.228661</v>
+        <v>0.24074899999999999</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.18957499999999999</v>
+        <v>0.206759</v>
       </c>
       <c r="B4">
-        <v>0.19190299999999999</v>
+        <v>0.20826700000000001</v>
       </c>
       <c r="C4">
-        <v>0.194435</v>
+        <v>0.20974599999999999</v>
       </c>
       <c r="D4">
-        <v>0.195996</v>
+        <v>0.21376400000000001</v>
       </c>
       <c r="E4">
-        <v>0.19796800000000001</v>
+        <v>0.21698899999999999</v>
       </c>
       <c r="F4">
-        <v>0.19910600000000001</v>
+        <v>0.21971399999999999</v>
       </c>
       <c r="G4">
-        <v>0.199766</v>
+        <v>0.22182499999999999</v>
       </c>
       <c r="H4">
-        <v>0.201788</v>
+        <v>0.224354</v>
       </c>
       <c r="I4">
-        <v>0.20288100000000001</v>
+        <v>0.226636</v>
       </c>
       <c r="J4">
-        <v>0.205097</v>
+        <v>0.227491</v>
       </c>
       <c r="K4">
-        <v>0.20680100000000001</v>
+        <v>0.230046</v>
       </c>
       <c r="L4">
-        <v>0.20947099999999999</v>
+        <v>0.23169400000000001</v>
       </c>
       <c r="M4">
-        <v>0.212759</v>
+        <v>0.234683</v>
       </c>
       <c r="N4">
-        <v>0.21562799999999999</v>
+        <v>0.23721300000000001</v>
       </c>
       <c r="O4">
-        <v>0.21762999999999999</v>
+        <v>0.240894</v>
       </c>
       <c r="P4">
-        <v>0.21959799999999999</v>
+        <v>0.24312900000000001</v>
       </c>
       <c r="Q4">
-        <v>0.22240099999999999</v>
+        <v>0.24580299999999999</v>
       </c>
       <c r="R4">
-        <v>0.22762399999999999</v>
+        <v>0.24792</v>
       </c>
       <c r="S4">
-        <v>0.22944999999999999</v>
+        <v>0.24896599999999999</v>
       </c>
       <c r="T4">
-        <v>0.23024500000000001</v>
+        <v>0.24504000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.19189500000000001</v>
+        <v>0.209509</v>
       </c>
       <c r="B5">
-        <v>0.19430800000000001</v>
+        <v>0.211031</v>
       </c>
       <c r="C5">
-        <v>0.196797</v>
+        <v>0.21276200000000001</v>
       </c>
       <c r="D5">
-        <v>0.198269</v>
+        <v>0.21687999999999999</v>
       </c>
       <c r="E5">
-        <v>0.200013</v>
+        <v>0.21999299999999999</v>
       </c>
       <c r="F5">
-        <v>0.20108200000000001</v>
+        <v>0.22266</v>
       </c>
       <c r="G5">
-        <v>0.20188500000000001</v>
+        <v>0.22486100000000001</v>
       </c>
       <c r="H5">
-        <v>0.203712</v>
+        <v>0.227466</v>
       </c>
       <c r="I5">
-        <v>0.204848</v>
+        <v>0.22955300000000001</v>
       </c>
       <c r="J5">
-        <v>0.20693600000000001</v>
+        <v>0.230154</v>
       </c>
       <c r="K5">
-        <v>0.208509</v>
+        <v>0.23277200000000001</v>
       </c>
       <c r="L5">
-        <v>0.21130499999999999</v>
+        <v>0.23414099999999999</v>
       </c>
       <c r="M5">
-        <v>0.21460599999999999</v>
+        <v>0.23713200000000001</v>
       </c>
       <c r="N5">
-        <v>0.21736900000000001</v>
+        <v>0.23986099999999999</v>
       </c>
       <c r="O5">
-        <v>0.21918799999999999</v>
+        <v>0.243616</v>
       </c>
       <c r="P5">
-        <v>0.22120200000000001</v>
+        <v>0.24629000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.22354299999999999</v>
+        <v>0.24856</v>
       </c>
       <c r="R5">
-        <v>0.22869300000000001</v>
+        <v>0.24953600000000001</v>
       </c>
       <c r="S5">
-        <v>0.230652</v>
+        <v>0.25165199999999999</v>
       </c>
       <c r="T5">
-        <v>0.23077600000000001</v>
+        <v>0.24865799999999999</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.19395499999999999</v>
+        <v>0.21221300000000001</v>
       </c>
       <c r="B6">
-        <v>0.19643099999999999</v>
+        <v>0.21373500000000001</v>
       </c>
       <c r="C6">
-        <v>0.198911</v>
+        <v>0.2155</v>
       </c>
       <c r="D6">
-        <v>0.20026099999999999</v>
+        <v>0.21970100000000001</v>
       </c>
       <c r="E6">
-        <v>0.20205899999999999</v>
+        <v>0.22270100000000001</v>
       </c>
       <c r="F6">
-        <v>0.20296800000000001</v>
+        <v>0.22564799999999999</v>
       </c>
       <c r="G6">
-        <v>0.203879</v>
+        <v>0.22802500000000001</v>
       </c>
       <c r="H6">
-        <v>0.20538899999999999</v>
+        <v>0.23039799999999999</v>
       </c>
       <c r="I6">
-        <v>0.206564</v>
+        <v>0.23246900000000001</v>
       </c>
       <c r="J6">
-        <v>0.20848700000000001</v>
+        <v>0.232844</v>
       </c>
       <c r="K6">
-        <v>0.21029200000000001</v>
+        <v>0.23579800000000001</v>
       </c>
       <c r="L6">
-        <v>0.21366499999999999</v>
+        <v>0.23771300000000001</v>
       </c>
       <c r="M6">
-        <v>0.217222</v>
+        <v>0.24016199999999999</v>
       </c>
       <c r="N6">
-        <v>0.219995</v>
+        <v>0.24308299999999999</v>
       </c>
       <c r="O6">
-        <v>0.22172</v>
+        <v>0.24629200000000001</v>
       </c>
       <c r="P6">
-        <v>0.22365099999999999</v>
+        <v>0.24849399999999999</v>
       </c>
       <c r="Q6">
-        <v>0.22611100000000001</v>
+        <v>0.25055300000000003</v>
       </c>
       <c r="R6">
-        <v>0.23108000000000001</v>
+        <v>0.25098700000000002</v>
       </c>
       <c r="S6">
-        <v>0.23224400000000001</v>
+        <v>0.25321300000000002</v>
       </c>
       <c r="T6">
-        <v>0.23345099999999999</v>
+        <v>0.25090899999999999</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.19621</v>
+        <v>0.21688399999999999</v>
       </c>
       <c r="B7">
-        <v>0.198432</v>
+        <v>0.21862799999999999</v>
       </c>
       <c r="C7">
-        <v>0.201047</v>
+        <v>0.22043499999999999</v>
       </c>
       <c r="D7">
-        <v>0.20227500000000001</v>
+        <v>0.22450300000000001</v>
       </c>
       <c r="E7">
-        <v>0.20389399999999999</v>
+        <v>0.22746</v>
       </c>
       <c r="F7">
-        <v>0.20488200000000001</v>
+        <v>0.23002</v>
       </c>
       <c r="G7">
-        <v>0.20569999999999999</v>
+        <v>0.232324</v>
       </c>
       <c r="H7">
-        <v>0.20708799999999999</v>
+        <v>0.23485700000000001</v>
       </c>
       <c r="I7">
-        <v>0.208311</v>
+        <v>0.23722699999999999</v>
       </c>
       <c r="J7">
-        <v>0.21029800000000001</v>
+        <v>0.23786199999999999</v>
       </c>
       <c r="K7">
-        <v>0.212115</v>
+        <v>0.24055000000000001</v>
       </c>
       <c r="L7">
-        <v>0.21540000000000001</v>
+        <v>0.24235100000000001</v>
       </c>
       <c r="M7">
-        <v>0.21895200000000001</v>
+        <v>0.245195</v>
       </c>
       <c r="N7">
-        <v>0.22185199999999999</v>
+        <v>0.248363</v>
       </c>
       <c r="O7">
-        <v>0.224047</v>
+        <v>0.25238500000000003</v>
       </c>
       <c r="P7">
-        <v>0.225968</v>
+        <v>0.25488</v>
       </c>
       <c r="Q7">
-        <v>0.228297</v>
+        <v>0.25753999999999999</v>
       </c>
       <c r="R7">
-        <v>0.23244999999999999</v>
+        <v>0.25855099999999998</v>
       </c>
       <c r="S7">
-        <v>0.233736</v>
+        <v>0.260851</v>
       </c>
       <c r="T7">
-        <v>0.234954</v>
+        <v>0.25609100000000001</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.19777500000000001</v>
+        <v>0.21951999999999999</v>
       </c>
       <c r="B8">
-        <v>0.19994899999999999</v>
+        <v>0.22140399999999999</v>
       </c>
       <c r="C8">
-        <v>0.20269699999999999</v>
+        <v>0.223188</v>
       </c>
       <c r="D8">
-        <v>0.20413100000000001</v>
+        <v>0.22744200000000001</v>
       </c>
       <c r="E8">
-        <v>0.20553299999999999</v>
+        <v>0.23044799999999999</v>
       </c>
       <c r="F8">
-        <v>0.20663400000000001</v>
+        <v>0.233211</v>
       </c>
       <c r="G8">
-        <v>0.20760300000000001</v>
+        <v>0.235621</v>
       </c>
       <c r="H8">
-        <v>0.209063</v>
+        <v>0.238291</v>
       </c>
       <c r="I8">
-        <v>0.21024799999999999</v>
+        <v>0.24065800000000001</v>
       </c>
       <c r="J8">
-        <v>0.212482</v>
+        <v>0.241228</v>
       </c>
       <c r="K8">
-        <v>0.214196</v>
+        <v>0.244204</v>
       </c>
       <c r="L8">
-        <v>0.21745400000000001</v>
+        <v>0.24621899999999999</v>
       </c>
       <c r="M8">
-        <v>0.220912</v>
+        <v>0.24899099999999999</v>
       </c>
       <c r="N8">
-        <v>0.22397500000000001</v>
+        <v>0.25195800000000002</v>
       </c>
       <c r="O8">
-        <v>0.22641</v>
+        <v>0.256436</v>
       </c>
       <c r="P8">
-        <v>0.228413</v>
+        <v>0.25910699999999998</v>
       </c>
       <c r="Q8">
-        <v>0.23102700000000001</v>
+        <v>0.26182</v>
       </c>
       <c r="R8">
-        <v>0.23469699999999999</v>
+        <v>0.26346999999999998</v>
       </c>
       <c r="S8">
-        <v>0.235433</v>
+        <v>0.26547300000000001</v>
       </c>
       <c r="T8">
-        <v>0.23566100000000001</v>
+        <v>0.26217600000000002</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.203628</v>
+        <v>0.22182299999999999</v>
       </c>
       <c r="B9">
-        <v>0.20611499999999999</v>
+        <v>0.22397400000000001</v>
       </c>
       <c r="C9">
-        <v>0.20891699999999999</v>
+        <v>0.22584399999999999</v>
       </c>
       <c r="D9">
-        <v>0.210425</v>
+        <v>0.230242</v>
       </c>
       <c r="E9">
-        <v>0.21198700000000001</v>
+        <v>0.23331299999999999</v>
       </c>
       <c r="F9">
-        <v>0.21322199999999999</v>
+        <v>0.23603299999999999</v>
       </c>
       <c r="G9">
-        <v>0.2145</v>
+        <v>0.23889199999999999</v>
       </c>
       <c r="H9">
-        <v>0.21582200000000001</v>
+        <v>0.241894</v>
       </c>
       <c r="I9">
-        <v>0.217116</v>
+        <v>0.24415500000000001</v>
       </c>
       <c r="J9">
-        <v>0.218781</v>
+        <v>0.245146</v>
       </c>
       <c r="K9">
-        <v>0.22073499999999999</v>
+        <v>0.24815599999999999</v>
       </c>
       <c r="L9">
-        <v>0.22400800000000001</v>
+        <v>0.25063000000000002</v>
       </c>
       <c r="M9">
-        <v>0.22747700000000001</v>
+        <v>0.253772</v>
       </c>
       <c r="N9">
-        <v>0.23062299999999999</v>
+        <v>0.25747199999999998</v>
       </c>
       <c r="O9">
-        <v>0.23308400000000001</v>
+        <v>0.26248500000000002</v>
       </c>
       <c r="P9">
-        <v>0.234705</v>
+        <v>0.265233</v>
       </c>
       <c r="Q9">
-        <v>0.23727400000000001</v>
+        <v>0.267903</v>
       </c>
       <c r="R9">
-        <v>0.241033</v>
+        <v>0.26947300000000002</v>
       </c>
       <c r="S9">
-        <v>0.24108499999999999</v>
+        <v>0.27248800000000001</v>
       </c>
       <c r="T9">
-        <v>0.238958</v>
+        <v>0.26932899999999999</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.20416699999999999</v>
+        <v>0.22430900000000001</v>
       </c>
       <c r="B10">
-        <v>0.20648</v>
+        <v>0.22652</v>
       </c>
       <c r="C10">
-        <v>0.20949999999999999</v>
+        <v>0.22858600000000001</v>
       </c>
       <c r="D10">
-        <v>0.21121400000000001</v>
+        <v>0.233039</v>
       </c>
       <c r="E10">
-        <v>0.212724</v>
+        <v>0.23580400000000001</v>
       </c>
       <c r="F10">
-        <v>0.21401300000000001</v>
+        <v>0.238457</v>
       </c>
       <c r="G10">
-        <v>0.21515100000000001</v>
+        <v>0.240923</v>
       </c>
       <c r="H10">
-        <v>0.216447</v>
+        <v>0.24382499999999999</v>
       </c>
       <c r="I10">
-        <v>0.21787999999999999</v>
+        <v>0.24630099999999999</v>
       </c>
       <c r="J10">
-        <v>0.21988099999999999</v>
+        <v>0.24735399999999999</v>
       </c>
       <c r="K10">
-        <v>0.22209799999999999</v>
+        <v>0.25037500000000001</v>
       </c>
       <c r="L10">
-        <v>0.22542699999999999</v>
+        <v>0.25324799999999997</v>
       </c>
       <c r="M10">
-        <v>0.22856599999999999</v>
+        <v>0.25647999999999999</v>
       </c>
       <c r="N10">
-        <v>0.23138300000000001</v>
+        <v>0.26041900000000001</v>
       </c>
       <c r="O10">
-        <v>0.23392299999999999</v>
+        <v>0.26555499999999999</v>
       </c>
       <c r="P10">
-        <v>0.235626</v>
+        <v>0.269262</v>
       </c>
       <c r="Q10">
-        <v>0.23835200000000001</v>
+        <v>0.271507</v>
       </c>
       <c r="R10">
-        <v>0.24230099999999999</v>
+        <v>0.27300600000000003</v>
       </c>
       <c r="S10">
-        <v>0.24249200000000001</v>
+        <v>0.27684799999999998</v>
       </c>
       <c r="T10">
-        <v>0.239617</v>
+        <v>0.27488000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.207012</v>
+        <v>0.227578</v>
       </c>
       <c r="B11">
-        <v>0.209206</v>
+        <v>0.230152</v>
       </c>
       <c r="C11">
-        <v>0.21235699999999999</v>
+        <v>0.232798</v>
       </c>
       <c r="D11">
-        <v>0.21412100000000001</v>
+        <v>0.23751800000000001</v>
       </c>
       <c r="E11">
-        <v>0.21523999999999999</v>
+        <v>0.240366</v>
       </c>
       <c r="F11">
-        <v>0.21629899999999999</v>
+        <v>0.243036</v>
       </c>
       <c r="G11">
-        <v>0.21790200000000001</v>
+        <v>0.246112</v>
       </c>
       <c r="H11">
-        <v>0.219281</v>
+        <v>0.248695</v>
       </c>
       <c r="I11">
-        <v>0.220771</v>
+        <v>0.25120100000000001</v>
       </c>
       <c r="J11">
-        <v>0.223306</v>
+        <v>0.25286999999999998</v>
       </c>
       <c r="K11">
-        <v>0.225607</v>
+        <v>0.25687599999999999</v>
       </c>
       <c r="L11">
-        <v>0.22923199999999999</v>
+        <v>0.26033000000000001</v>
       </c>
       <c r="M11">
-        <v>0.23268</v>
+        <v>0.26325799999999999</v>
       </c>
       <c r="N11">
-        <v>0.23635100000000001</v>
+        <v>0.26684999999999998</v>
       </c>
       <c r="O11">
-        <v>0.23913599999999999</v>
+        <v>0.270984</v>
       </c>
       <c r="P11">
-        <v>0.24082600000000001</v>
+        <v>0.27390300000000001</v>
       </c>
       <c r="Q11">
-        <v>0.243975</v>
+        <v>0.27659400000000001</v>
       </c>
       <c r="R11">
-        <v>0.24811900000000001</v>
+        <v>0.27884799999999998</v>
       </c>
       <c r="S11">
-        <v>0.248587</v>
+        <v>0.28229100000000001</v>
       </c>
       <c r="T11">
-        <v>0.24558199999999999</v>
+        <v>0.27881400000000001</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.210481</v>
+        <v>0.23125100000000001</v>
       </c>
       <c r="B12">
-        <v>0.21282100000000001</v>
+        <v>0.23363600000000001</v>
       </c>
       <c r="C12">
-        <v>0.21604499999999999</v>
+        <v>0.236707</v>
       </c>
       <c r="D12">
-        <v>0.217699</v>
+        <v>0.24131900000000001</v>
       </c>
       <c r="E12">
-        <v>0.21853400000000001</v>
+        <v>0.24440300000000001</v>
       </c>
       <c r="F12">
-        <v>0.21987499999999999</v>
+        <v>0.24710499999999999</v>
       </c>
       <c r="G12">
-        <v>0.221416</v>
+        <v>0.25009199999999998</v>
       </c>
       <c r="H12">
-        <v>0.222882</v>
+        <v>0.25242100000000001</v>
       </c>
       <c r="I12">
-        <v>0.22443399999999999</v>
+        <v>0.255305</v>
       </c>
       <c r="J12">
-        <v>0.22731999999999999</v>
+        <v>0.25759900000000002</v>
       </c>
       <c r="K12">
-        <v>0.22942199999999999</v>
+        <v>0.26155499999999998</v>
       </c>
       <c r="L12">
-        <v>0.23327700000000001</v>
+        <v>0.26441799999999999</v>
       </c>
       <c r="M12">
-        <v>0.23685899999999999</v>
+        <v>0.26803300000000002</v>
       </c>
       <c r="N12">
-        <v>0.24041999999999999</v>
+        <v>0.27238000000000001</v>
       </c>
       <c r="O12">
-        <v>0.24310000000000001</v>
+        <v>0.27712999999999999</v>
       </c>
       <c r="P12">
-        <v>0.24493799999999999</v>
+        <v>0.279752</v>
       </c>
       <c r="Q12">
-        <v>0.24715100000000001</v>
+        <v>0.28237000000000001</v>
       </c>
       <c r="R12">
-        <v>0.25125500000000001</v>
+        <v>0.284356</v>
       </c>
       <c r="S12">
-        <v>0.25156800000000001</v>
+        <v>0.288412</v>
       </c>
       <c r="T12">
-        <v>0.24698400000000001</v>
+        <v>0.28333799999999998</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.213646</v>
+        <v>0.232875</v>
       </c>
       <c r="B13">
-        <v>0.21570300000000001</v>
+        <v>0.234987</v>
       </c>
       <c r="C13">
-        <v>0.21872800000000001</v>
+        <v>0.23797299999999999</v>
       </c>
       <c r="D13">
-        <v>0.220417</v>
+        <v>0.24247099999999999</v>
       </c>
       <c r="E13">
-        <v>0.22090499999999999</v>
+        <v>0.24609200000000001</v>
       </c>
       <c r="F13">
-        <v>0.22248699999999999</v>
+        <v>0.24933</v>
       </c>
       <c r="G13">
-        <v>0.224333</v>
+        <v>0.252498</v>
       </c>
       <c r="H13">
-        <v>0.22572999999999999</v>
+        <v>0.25516100000000003</v>
       </c>
       <c r="I13">
-        <v>0.227025</v>
+        <v>0.25926100000000002</v>
       </c>
       <c r="J13">
-        <v>0.230078</v>
+        <v>0.26204499999999997</v>
       </c>
       <c r="K13">
-        <v>0.232325</v>
+        <v>0.26521800000000001</v>
       </c>
       <c r="L13">
-        <v>0.23560400000000001</v>
+        <v>0.26909300000000003</v>
       </c>
       <c r="M13">
-        <v>0.23885799999999999</v>
+        <v>0.27277299999999999</v>
       </c>
       <c r="N13">
-        <v>0.24201900000000001</v>
+        <v>0.278115</v>
       </c>
       <c r="O13">
-        <v>0.244591</v>
+        <v>0.28410800000000003</v>
       </c>
       <c r="P13">
-        <v>0.24663099999999999</v>
+        <v>0.288468</v>
       </c>
       <c r="Q13">
-        <v>0.24759500000000001</v>
+        <v>0.29004000000000002</v>
       </c>
       <c r="R13">
-        <v>0.25118000000000001</v>
+        <v>0.291742</v>
       </c>
       <c r="S13">
-        <v>0.25164900000000001</v>
+        <v>0.29261199999999998</v>
       </c>
       <c r="T13">
-        <v>0.24718499999999999</v>
+        <v>0.28690300000000002</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.21765699999999999</v>
+        <v>0.23880999999999999</v>
       </c>
       <c r="B14">
-        <v>0.22012200000000001</v>
+        <v>0.24144699999999999</v>
       </c>
       <c r="C14">
-        <v>0.22308900000000001</v>
+        <v>0.244033</v>
       </c>
       <c r="D14">
-        <v>0.224603</v>
+        <v>0.24876200000000001</v>
       </c>
       <c r="E14">
-        <v>0.22522500000000001</v>
+        <v>0.25297399999999998</v>
       </c>
       <c r="F14">
-        <v>0.22692799999999999</v>
+        <v>0.25515500000000002</v>
       </c>
       <c r="G14">
-        <v>0.228432</v>
+        <v>0.25889499999999999</v>
       </c>
       <c r="H14">
-        <v>0.229488</v>
+        <v>0.26160299999999997</v>
       </c>
       <c r="I14">
-        <v>0.23075999999999999</v>
+        <v>0.26573799999999997</v>
       </c>
       <c r="J14">
-        <v>0.234128</v>
+        <v>0.268428</v>
       </c>
       <c r="K14">
-        <v>0.23621600000000001</v>
+        <v>0.27198299999999997</v>
       </c>
       <c r="L14">
-        <v>0.23957200000000001</v>
+        <v>0.27611599999999997</v>
       </c>
       <c r="M14">
-        <v>0.24266499999999999</v>
+        <v>0.27884799999999998</v>
       </c>
       <c r="N14">
-        <v>0.246363</v>
+        <v>0.28503899999999999</v>
       </c>
       <c r="O14">
-        <v>0.24887799999999999</v>
+        <v>0.29080299999999998</v>
       </c>
       <c r="P14">
-        <v>0.25042799999999998</v>
+        <v>0.295734</v>
       </c>
       <c r="Q14">
-        <v>0.25158599999999998</v>
+        <v>0.29719200000000001</v>
       </c>
       <c r="R14">
-        <v>0.25659399999999999</v>
+        <v>0.299149</v>
       </c>
       <c r="S14">
-        <v>0.25587500000000002</v>
+        <v>0.30298000000000003</v>
       </c>
       <c r="T14">
-        <v>0.24948799999999999</v>
+        <v>0.29822799999999999</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.217085</v>
+        <v>0.24391499999999999</v>
       </c>
       <c r="B15">
-        <v>0.219472</v>
+        <v>0.24601100000000001</v>
       </c>
       <c r="C15">
-        <v>0.22189</v>
+        <v>0.24887899999999999</v>
       </c>
       <c r="D15">
-        <v>0.223357</v>
+        <v>0.25364399999999998</v>
       </c>
       <c r="E15">
-        <v>0.22357299999999999</v>
+        <v>0.25894699999999998</v>
       </c>
       <c r="F15">
-        <v>0.22545100000000001</v>
+        <v>0.26094099999999998</v>
       </c>
       <c r="G15">
-        <v>0.227186</v>
+        <v>0.26462000000000002</v>
       </c>
       <c r="H15">
-        <v>0.228412</v>
+        <v>0.26732299999999998</v>
       </c>
       <c r="I15">
-        <v>0.229848</v>
+        <v>0.27144000000000001</v>
       </c>
       <c r="J15">
-        <v>0.232876</v>
+        <v>0.27478999999999998</v>
       </c>
       <c r="K15">
-        <v>0.23385700000000001</v>
+        <v>0.27773500000000001</v>
       </c>
       <c r="L15">
-        <v>0.23699300000000001</v>
+        <v>0.281719</v>
       </c>
       <c r="M15">
-        <v>0.23993600000000001</v>
+        <v>0.28403400000000001</v>
       </c>
       <c r="N15">
-        <v>0.24396999999999999</v>
+        <v>0.290715</v>
       </c>
       <c r="O15">
-        <v>0.24624099999999999</v>
+        <v>0.29483599999999999</v>
       </c>
       <c r="P15">
-        <v>0.24812300000000001</v>
+        <v>0.29891699999999999</v>
       </c>
       <c r="Q15">
-        <v>0.24892700000000001</v>
+        <v>0.30074299999999998</v>
       </c>
       <c r="R15">
-        <v>0.25240000000000001</v>
+        <v>0.30429899999999999</v>
       </c>
       <c r="S15">
-        <v>0.25394299999999997</v>
+        <v>0.30680299999999999</v>
       </c>
       <c r="T15">
-        <v>0.248443</v>
+        <v>0.29866399999999999</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.22176899999999999</v>
+        <v>0.23960699999999999</v>
       </c>
       <c r="B16">
-        <v>0.22461</v>
+        <v>0.24104300000000001</v>
       </c>
       <c r="C16">
-        <v>0.22711100000000001</v>
+        <v>0.24406700000000001</v>
       </c>
       <c r="D16">
-        <v>0.228522</v>
+        <v>0.24859000000000001</v>
       </c>
       <c r="E16">
-        <v>0.22911200000000001</v>
+        <v>0.25324400000000002</v>
       </c>
       <c r="F16">
-        <v>0.230907</v>
+        <v>0.25592700000000002</v>
       </c>
       <c r="G16">
-        <v>0.23272300000000001</v>
+        <v>0.259274</v>
       </c>
       <c r="H16">
-        <v>0.23419300000000001</v>
+        <v>0.263046</v>
       </c>
       <c r="I16">
-        <v>0.23596400000000001</v>
+        <v>0.26747100000000001</v>
       </c>
       <c r="J16">
-        <v>0.23843600000000001</v>
+        <v>0.27036700000000002</v>
       </c>
       <c r="K16">
-        <v>0.24008399999999999</v>
+        <v>0.27317900000000001</v>
       </c>
       <c r="L16">
-        <v>0.244029</v>
+        <v>0.27713199999999999</v>
       </c>
       <c r="M16">
-        <v>0.24674699999999999</v>
+        <v>0.27849699999999999</v>
       </c>
       <c r="N16">
-        <v>0.249469</v>
+        <v>0.28573900000000002</v>
       </c>
       <c r="O16">
-        <v>0.25175900000000001</v>
+        <v>0.29022500000000001</v>
       </c>
       <c r="P16">
-        <v>0.252996</v>
+        <v>0.29489500000000002</v>
       </c>
       <c r="Q16">
-        <v>0.25475999999999999</v>
+        <v>0.29670800000000003</v>
       </c>
       <c r="R16">
-        <v>0.25780999999999998</v>
+        <v>0.301593</v>
       </c>
       <c r="S16">
-        <v>0.25960299999999997</v>
+        <v>0.30367100000000002</v>
       </c>
       <c r="T16">
-        <v>0.25187300000000001</v>
+        <v>0.296151</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.22024099999999999</v>
+        <v>0.241117</v>
       </c>
       <c r="B17">
-        <v>0.223272</v>
+        <v>0.24332400000000001</v>
       </c>
       <c r="C17">
-        <v>0.22601399999999999</v>
+        <v>0.246588</v>
       </c>
       <c r="D17">
-        <v>0.22783600000000001</v>
+        <v>0.252139</v>
       </c>
       <c r="E17">
-        <v>0.228883</v>
+        <v>0.25807400000000003</v>
       </c>
       <c r="F17">
-        <v>0.230632</v>
+        <v>0.260967</v>
       </c>
       <c r="G17">
-        <v>0.23286799999999999</v>
+        <v>0.26369799999999999</v>
       </c>
       <c r="H17">
-        <v>0.234959</v>
+        <v>0.26752199999999998</v>
       </c>
       <c r="I17">
-        <v>0.23675199999999999</v>
+        <v>0.27295599999999998</v>
       </c>
       <c r="J17">
-        <v>0.23889199999999999</v>
+        <v>0.27639900000000001</v>
       </c>
       <c r="K17">
-        <v>0.240341</v>
+        <v>0.27804000000000001</v>
       </c>
       <c r="L17">
-        <v>0.24469399999999999</v>
+        <v>0.28069100000000002</v>
       </c>
       <c r="M17">
-        <v>0.246811</v>
+        <v>0.28234300000000001</v>
       </c>
       <c r="N17">
-        <v>0.24998999999999999</v>
+        <v>0.291848</v>
       </c>
       <c r="O17">
-        <v>0.252581</v>
+        <v>0.29811900000000002</v>
       </c>
       <c r="P17">
-        <v>0.25351800000000002</v>
+        <v>0.30451699999999998</v>
       </c>
       <c r="Q17">
-        <v>0.25558700000000001</v>
+        <v>0.30453400000000003</v>
       </c>
       <c r="R17">
-        <v>0.25939000000000001</v>
+        <v>0.3085</v>
       </c>
       <c r="S17">
-        <v>0.26142300000000002</v>
+        <v>0.31217</v>
       </c>
       <c r="T17">
-        <v>0.251612</v>
+        <v>0.30206499999999997</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.22819900000000001</v>
+        <v>0.23300100000000001</v>
       </c>
       <c r="B18">
-        <v>0.23122100000000001</v>
+        <v>0.23505200000000001</v>
       </c>
       <c r="C18">
-        <v>0.23499700000000001</v>
+        <v>0.23888899999999999</v>
       </c>
       <c r="D18">
-        <v>0.236985</v>
+        <v>0.24426100000000001</v>
       </c>
       <c r="E18">
-        <v>0.23749700000000001</v>
+        <v>0.24962599999999999</v>
       </c>
       <c r="F18">
-        <v>0.23865500000000001</v>
+        <v>0.25345699999999999</v>
       </c>
       <c r="G18">
-        <v>0.24071999999999999</v>
+        <v>0.25611200000000001</v>
       </c>
       <c r="H18">
-        <v>0.243564</v>
+        <v>0.25935900000000001</v>
       </c>
       <c r="I18">
-        <v>0.244336</v>
+        <v>0.26600400000000002</v>
       </c>
       <c r="J18">
-        <v>0.24727099999999999</v>
+        <v>0.27083699999999999</v>
       </c>
       <c r="K18">
-        <v>0.24799199999999999</v>
+        <v>0.27218399999999998</v>
       </c>
       <c r="L18">
-        <v>0.25221199999999999</v>
+        <v>0.27564100000000002</v>
       </c>
       <c r="M18">
-        <v>0.252919</v>
+        <v>0.27890799999999999</v>
       </c>
       <c r="N18">
-        <v>0.25673400000000002</v>
+        <v>0.28825899999999999</v>
       </c>
       <c r="O18">
-        <v>0.26159300000000002</v>
+        <v>0.29478399999999999</v>
       </c>
       <c r="P18">
-        <v>0.26344200000000001</v>
+        <v>0.30580200000000002</v>
       </c>
       <c r="Q18">
-        <v>0.26442199999999999</v>
+        <v>0.30808600000000003</v>
       </c>
       <c r="R18">
-        <v>0.26844699999999999</v>
+        <v>0.312639</v>
       </c>
       <c r="S18">
-        <v>0.271339</v>
+        <v>0.31319999999999998</v>
       </c>
       <c r="T18">
-        <v>0.25817800000000002</v>
+        <v>0.30616300000000002</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.223528</v>
+        <v>0.215864</v>
       </c>
       <c r="B19">
-        <v>0.227295</v>
+        <v>0.21863099999999999</v>
       </c>
       <c r="C19">
-        <v>0.22839699999999999</v>
+        <v>0.222798</v>
       </c>
       <c r="D19">
-        <v>0.23033699999999999</v>
+        <v>0.22831899999999999</v>
       </c>
       <c r="E19">
-        <v>0.230597</v>
+        <v>0.23380200000000001</v>
       </c>
       <c r="F19">
-        <v>0.23042599999999999</v>
+        <v>0.23675199999999999</v>
       </c>
       <c r="G19">
-        <v>0.23305500000000001</v>
+        <v>0.23860100000000001</v>
       </c>
       <c r="H19">
-        <v>0.234459</v>
+        <v>0.24005899999999999</v>
       </c>
       <c r="I19">
-        <v>0.235933</v>
+        <v>0.245728</v>
       </c>
       <c r="J19">
-        <v>0.23771999999999999</v>
+        <v>0.25165900000000002</v>
       </c>
       <c r="K19">
-        <v>0.23652300000000001</v>
+        <v>0.25243599999999999</v>
       </c>
       <c r="L19">
-        <v>0.239149</v>
+        <v>0.25621699999999997</v>
       </c>
       <c r="M19">
-        <v>0.24088799999999999</v>
+        <v>0.26170500000000002</v>
       </c>
       <c r="N19">
-        <v>0.245614</v>
+        <v>0.26689299999999999</v>
       </c>
       <c r="O19">
-        <v>0.25068499999999999</v>
+        <v>0.27444099999999999</v>
       </c>
       <c r="P19">
-        <v>0.25113200000000002</v>
+        <v>0.279557</v>
       </c>
       <c r="Q19">
-        <v>0.25196099999999999</v>
+        <v>0.28298499999999999</v>
       </c>
       <c r="R19">
-        <v>0.25561899999999999</v>
+        <v>0.289269</v>
       </c>
       <c r="S19">
-        <v>0.25871</v>
+        <v>0.290329</v>
       </c>
       <c r="T19">
-        <v>0.25050800000000001</v>
+        <v>0.28025099999999997</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.20244400000000001</v>
+        <v>0.174175</v>
       </c>
       <c r="B20">
-        <v>0.20527799999999999</v>
+        <v>0.17885599999999999</v>
       </c>
       <c r="C20">
-        <v>0.206535</v>
+        <v>0.18156700000000001</v>
       </c>
       <c r="D20">
-        <v>0.209594</v>
+        <v>0.18892500000000001</v>
       </c>
       <c r="E20">
-        <v>0.21096500000000001</v>
+        <v>0.188495</v>
       </c>
       <c r="F20">
-        <v>0.209646</v>
+        <v>0.18920600000000001</v>
       </c>
       <c r="G20">
-        <v>0.21204100000000001</v>
+        <v>0.19247</v>
       </c>
       <c r="H20">
-        <v>0.211593</v>
+        <v>0.195462</v>
       </c>
       <c r="I20">
-        <v>0.217086</v>
+        <v>0.19634299999999999</v>
       </c>
       <c r="J20">
-        <v>0.21918099999999999</v>
+        <v>0.20397799999999999</v>
       </c>
       <c r="K20">
-        <v>0.218253</v>
+        <v>0.202569</v>
       </c>
       <c r="L20">
-        <v>0.21778800000000001</v>
+        <v>0.202099</v>
       </c>
       <c r="M20">
-        <v>0.22250200000000001</v>
+        <v>0.204792</v>
       </c>
       <c r="N20">
-        <v>0.22386400000000001</v>
+        <v>0.20866699999999999</v>
       </c>
       <c r="O20">
-        <v>0.232409</v>
+        <v>0.21423900000000001</v>
       </c>
       <c r="P20">
-        <v>0.23206599999999999</v>
+        <v>0.216248</v>
       </c>
       <c r="Q20">
-        <v>0.229516</v>
+        <v>0.21902099999999999</v>
       </c>
       <c r="R20">
-        <v>0.22594400000000001</v>
+        <v>0.22492999999999999</v>
       </c>
       <c r="S20">
-        <v>0.23097200000000001</v>
+        <v>0.22952</v>
       </c>
       <c r="T20">
-        <v>0.22154199999999999</v>
+        <v>0.221917</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC11D4E-9CB6-48F7-8F4F-8A3EFE2444FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A21A6B-0B8F-4DA0-A71A-0695DCCAA809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,10 +22,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -353,1242 +349,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.20014299999999999</v>
+        <v>0.285271</v>
       </c>
       <c r="B1">
-        <v>0.201714</v>
+        <v>0.28644799999999998</v>
       </c>
       <c r="C1">
-        <v>0.20338500000000001</v>
+        <v>0.28771400000000003</v>
       </c>
       <c r="D1">
-        <v>0.20743</v>
+        <v>0.28714499999999998</v>
       </c>
       <c r="E1">
-        <v>0.210482</v>
+        <v>0.28677200000000003</v>
       </c>
       <c r="F1">
-        <v>0.21307300000000001</v>
+        <v>0.28777399999999997</v>
       </c>
       <c r="G1">
-        <v>0.215361</v>
+        <v>0.28812900000000002</v>
       </c>
       <c r="H1">
-        <v>0.21770900000000001</v>
+        <v>0.288383</v>
       </c>
       <c r="I1">
-        <v>0.22001100000000001</v>
+        <v>0.28819899999999998</v>
       </c>
       <c r="J1">
-        <v>0.220716</v>
+        <v>0.28898800000000002</v>
       </c>
       <c r="K1">
-        <v>0.22278999999999999</v>
+        <v>0.28989399999999999</v>
       </c>
       <c r="L1">
-        <v>0.224472</v>
+        <v>0.28755700000000001</v>
       </c>
       <c r="M1">
-        <v>0.22745199999999999</v>
+        <v>0.28765800000000002</v>
       </c>
       <c r="N1">
-        <v>0.23051199999999999</v>
+        <v>0.286358</v>
       </c>
       <c r="O1">
-        <v>0.23377800000000001</v>
+        <v>0.28708299999999998</v>
       </c>
       <c r="P1">
-        <v>0.23646</v>
+        <v>0.282808</v>
       </c>
       <c r="Q1">
-        <v>0.238431</v>
+        <v>0.27735100000000001</v>
       </c>
       <c r="R1">
-        <v>0.23975099999999999</v>
+        <v>0.26554</v>
       </c>
       <c r="S1">
-        <v>0.240897</v>
+        <v>0.24798899999999999</v>
       </c>
       <c r="T1">
-        <v>0.23660900000000001</v>
+        <v>0.23005200000000001</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.20213900000000001</v>
+        <v>0.28513699999999997</v>
       </c>
       <c r="B2">
-        <v>0.20371800000000001</v>
+        <v>0.28561599999999998</v>
       </c>
       <c r="C2">
-        <v>0.20533699999999999</v>
+        <v>0.286999</v>
       </c>
       <c r="D2">
-        <v>0.20932600000000001</v>
+        <v>0.285605</v>
       </c>
       <c r="E2">
-        <v>0.212538</v>
+        <v>0.28603600000000001</v>
       </c>
       <c r="F2">
-        <v>0.215195</v>
+        <v>0.28710999999999998</v>
       </c>
       <c r="G2">
-        <v>0.217193</v>
+        <v>0.287545</v>
       </c>
       <c r="H2">
-        <v>0.219614</v>
+        <v>0.28844399999999998</v>
       </c>
       <c r="I2">
-        <v>0.22188099999999999</v>
+        <v>0.288323</v>
       </c>
       <c r="J2">
-        <v>0.222552</v>
+        <v>0.28950399999999998</v>
       </c>
       <c r="K2">
-        <v>0.224609</v>
+        <v>0.28955199999999998</v>
       </c>
       <c r="L2">
-        <v>0.226464</v>
+        <v>0.28747</v>
       </c>
       <c r="M2">
-        <v>0.229545</v>
+        <v>0.28773799999999999</v>
       </c>
       <c r="N2">
-        <v>0.23247100000000001</v>
+        <v>0.28653899999999999</v>
       </c>
       <c r="O2">
-        <v>0.23577000000000001</v>
+        <v>0.285105</v>
       </c>
       <c r="P2">
-        <v>0.23802899999999999</v>
+        <v>0.28181699999999998</v>
       </c>
       <c r="Q2">
-        <v>0.239788</v>
+        <v>0.27672099999999999</v>
       </c>
       <c r="R2">
-        <v>0.241095</v>
+        <v>0.26585399999999998</v>
       </c>
       <c r="S2">
-        <v>0.24244399999999999</v>
+        <v>0.24820600000000001</v>
       </c>
       <c r="T2">
-        <v>0.238398</v>
+        <v>0.23309099999999999</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.205009</v>
+        <v>0.28768500000000002</v>
       </c>
       <c r="B3">
-        <v>0.20652100000000001</v>
+        <v>0.28885300000000003</v>
       </c>
       <c r="C3">
-        <v>0.20799599999999999</v>
+        <v>0.29048600000000002</v>
       </c>
       <c r="D3">
-        <v>0.21218000000000001</v>
+        <v>0.28913</v>
       </c>
       <c r="E3">
-        <v>0.21532999999999999</v>
+        <v>0.28966399999999998</v>
       </c>
       <c r="F3">
-        <v>0.218142</v>
+        <v>0.29021799999999998</v>
       </c>
       <c r="G3">
-        <v>0.22004399999999999</v>
+        <v>0.29111300000000001</v>
       </c>
       <c r="H3">
-        <v>0.22201000000000001</v>
+        <v>0.29227700000000001</v>
       </c>
       <c r="I3">
-        <v>0.22412899999999999</v>
+        <v>0.29049399999999997</v>
       </c>
       <c r="J3">
-        <v>0.224803</v>
+        <v>0.29186000000000001</v>
       </c>
       <c r="K3">
-        <v>0.22700899999999999</v>
+        <v>0.29100700000000002</v>
       </c>
       <c r="L3">
-        <v>0.22889899999999999</v>
+        <v>0.28890500000000002</v>
       </c>
       <c r="M3">
-        <v>0.23198099999999999</v>
+        <v>0.28943600000000003</v>
       </c>
       <c r="N3">
-        <v>0.23452899999999999</v>
+        <v>0.28963</v>
       </c>
       <c r="O3">
-        <v>0.237985</v>
+        <v>0.28840399999999999</v>
       </c>
       <c r="P3">
-        <v>0.24038100000000001</v>
+        <v>0.28449600000000003</v>
       </c>
       <c r="Q3">
-        <v>0.242398</v>
+        <v>0.28029700000000002</v>
       </c>
       <c r="R3">
-        <v>0.24382400000000001</v>
+        <v>0.27023599999999998</v>
       </c>
       <c r="S3">
-        <v>0.245224</v>
+        <v>0.25101400000000001</v>
       </c>
       <c r="T3">
-        <v>0.24074899999999999</v>
+        <v>0.236151</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.206759</v>
+        <v>0.28641899999999998</v>
       </c>
       <c r="B4">
-        <v>0.20826700000000001</v>
+        <v>0.285831</v>
       </c>
       <c r="C4">
-        <v>0.20974599999999999</v>
+        <v>0.287497</v>
       </c>
       <c r="D4">
-        <v>0.21376400000000001</v>
+        <v>0.28612900000000002</v>
       </c>
       <c r="E4">
-        <v>0.21698899999999999</v>
+        <v>0.28695100000000001</v>
       </c>
       <c r="F4">
-        <v>0.21971399999999999</v>
+        <v>0.28752100000000003</v>
       </c>
       <c r="G4">
-        <v>0.22182499999999999</v>
+        <v>0.28872799999999998</v>
       </c>
       <c r="H4">
-        <v>0.224354</v>
+        <v>0.28993999999999998</v>
       </c>
       <c r="I4">
-        <v>0.226636</v>
+        <v>0.28842499999999999</v>
       </c>
       <c r="J4">
-        <v>0.227491</v>
+        <v>0.29013499999999998</v>
       </c>
       <c r="K4">
-        <v>0.230046</v>
+        <v>0.28819099999999997</v>
       </c>
       <c r="L4">
-        <v>0.23169400000000001</v>
+        <v>0.28636099999999998</v>
       </c>
       <c r="M4">
-        <v>0.234683</v>
+        <v>0.28722999999999999</v>
       </c>
       <c r="N4">
-        <v>0.23721300000000001</v>
+        <v>0.28684599999999999</v>
       </c>
       <c r="O4">
-        <v>0.240894</v>
+        <v>0.284966</v>
       </c>
       <c r="P4">
-        <v>0.24312900000000001</v>
+        <v>0.280279</v>
       </c>
       <c r="Q4">
-        <v>0.24580299999999999</v>
+        <v>0.27693800000000002</v>
       </c>
       <c r="R4">
-        <v>0.24792</v>
+        <v>0.26744600000000002</v>
       </c>
       <c r="S4">
-        <v>0.24896599999999999</v>
+        <v>0.248498</v>
       </c>
       <c r="T4">
-        <v>0.24504000000000001</v>
+        <v>0.234847</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.209509</v>
+        <v>0.29377500000000001</v>
       </c>
       <c r="B5">
-        <v>0.211031</v>
+        <v>0.29330299999999998</v>
       </c>
       <c r="C5">
-        <v>0.21276200000000001</v>
+        <v>0.29570999999999997</v>
       </c>
       <c r="D5">
-        <v>0.21687999999999999</v>
+        <v>0.294435</v>
       </c>
       <c r="E5">
-        <v>0.21999299999999999</v>
+        <v>0.29437099999999999</v>
       </c>
       <c r="F5">
-        <v>0.22266</v>
+        <v>0.29512300000000002</v>
       </c>
       <c r="G5">
-        <v>0.22486100000000001</v>
+        <v>0.295572</v>
       </c>
       <c r="H5">
-        <v>0.227466</v>
+        <v>0.29664800000000002</v>
       </c>
       <c r="I5">
-        <v>0.22955300000000001</v>
+        <v>0.29514400000000002</v>
       </c>
       <c r="J5">
-        <v>0.230154</v>
+        <v>0.297545</v>
       </c>
       <c r="K5">
-        <v>0.23277200000000001</v>
+        <v>0.29452499999999998</v>
       </c>
       <c r="L5">
-        <v>0.23414099999999999</v>
+        <v>0.29177199999999998</v>
       </c>
       <c r="M5">
-        <v>0.23713200000000001</v>
+        <v>0.289327</v>
       </c>
       <c r="N5">
-        <v>0.23986099999999999</v>
+        <v>0.288443</v>
       </c>
       <c r="O5">
-        <v>0.243616</v>
+        <v>0.28731000000000001</v>
       </c>
       <c r="P5">
-        <v>0.24629000000000001</v>
+        <v>0.28415000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.24856</v>
+        <v>0.28181600000000001</v>
       </c>
       <c r="R5">
-        <v>0.24953600000000001</v>
+        <v>0.27170499999999997</v>
       </c>
       <c r="S5">
-        <v>0.25165199999999999</v>
+        <v>0.25147000000000003</v>
       </c>
       <c r="T5">
-        <v>0.24865799999999999</v>
+        <v>0.23599300000000001</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.21221300000000001</v>
+        <v>0.29425499999999999</v>
       </c>
       <c r="B6">
-        <v>0.21373500000000001</v>
+        <v>0.29415400000000003</v>
       </c>
       <c r="C6">
-        <v>0.2155</v>
+        <v>0.29577700000000001</v>
       </c>
       <c r="D6">
-        <v>0.21970100000000001</v>
+        <v>0.29397299999999998</v>
       </c>
       <c r="E6">
-        <v>0.22270100000000001</v>
+        <v>0.29424800000000001</v>
       </c>
       <c r="F6">
-        <v>0.22564799999999999</v>
+        <v>0.29423100000000002</v>
       </c>
       <c r="G6">
-        <v>0.22802500000000001</v>
+        <v>0.29481499999999999</v>
       </c>
       <c r="H6">
-        <v>0.23039799999999999</v>
+        <v>0.29641000000000001</v>
       </c>
       <c r="I6">
-        <v>0.23246900000000001</v>
+        <v>0.29489599999999999</v>
       </c>
       <c r="J6">
-        <v>0.232844</v>
+        <v>0.29758600000000002</v>
       </c>
       <c r="K6">
-        <v>0.23579800000000001</v>
+        <v>0.29550599999999999</v>
       </c>
       <c r="L6">
-        <v>0.23771300000000001</v>
+        <v>0.29296100000000003</v>
       </c>
       <c r="M6">
-        <v>0.24016199999999999</v>
+        <v>0.29162900000000003</v>
       </c>
       <c r="N6">
-        <v>0.24308299999999999</v>
+        <v>0.29049399999999997</v>
       </c>
       <c r="O6">
-        <v>0.24629200000000001</v>
+        <v>0.28846899999999998</v>
       </c>
       <c r="P6">
-        <v>0.24849399999999999</v>
+        <v>0.28594900000000001</v>
       </c>
       <c r="Q6">
-        <v>0.25055300000000003</v>
+        <v>0.28239399999999998</v>
       </c>
       <c r="R6">
-        <v>0.25098700000000002</v>
+        <v>0.27173799999999998</v>
       </c>
       <c r="S6">
-        <v>0.25321300000000002</v>
+        <v>0.25258700000000001</v>
       </c>
       <c r="T6">
-        <v>0.25090899999999999</v>
+        <v>0.23438700000000001</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.21688399999999999</v>
+        <v>0.29424800000000001</v>
       </c>
       <c r="B7">
-        <v>0.21862799999999999</v>
+        <v>0.29421900000000001</v>
       </c>
       <c r="C7">
-        <v>0.22043499999999999</v>
+        <v>0.29666599999999999</v>
       </c>
       <c r="D7">
-        <v>0.22450300000000001</v>
+        <v>0.29484700000000003</v>
       </c>
       <c r="E7">
-        <v>0.22746</v>
+        <v>0.29517700000000002</v>
       </c>
       <c r="F7">
-        <v>0.23002</v>
+        <v>0.29551500000000003</v>
       </c>
       <c r="G7">
-        <v>0.232324</v>
+        <v>0.29626799999999998</v>
       </c>
       <c r="H7">
-        <v>0.23485700000000001</v>
+        <v>0.298454</v>
       </c>
       <c r="I7">
-        <v>0.23722699999999999</v>
+        <v>0.29726399999999997</v>
       </c>
       <c r="J7">
-        <v>0.23786199999999999</v>
+        <v>0.30030699999999999</v>
       </c>
       <c r="K7">
-        <v>0.24055000000000001</v>
+        <v>0.29861300000000002</v>
       </c>
       <c r="L7">
-        <v>0.24235100000000001</v>
+        <v>0.29663200000000001</v>
       </c>
       <c r="M7">
-        <v>0.245195</v>
+        <v>0.29622500000000002</v>
       </c>
       <c r="N7">
-        <v>0.248363</v>
+        <v>0.29555300000000001</v>
       </c>
       <c r="O7">
-        <v>0.25238500000000003</v>
+        <v>0.29283500000000001</v>
       </c>
       <c r="P7">
-        <v>0.25488</v>
+        <v>0.29189500000000002</v>
       </c>
       <c r="Q7">
-        <v>0.25753999999999999</v>
+        <v>0.28994500000000001</v>
       </c>
       <c r="R7">
-        <v>0.25855099999999998</v>
+        <v>0.27658500000000003</v>
       </c>
       <c r="S7">
-        <v>0.260851</v>
+        <v>0.25795099999999999</v>
       </c>
       <c r="T7">
-        <v>0.25609100000000001</v>
+        <v>0.24050099999999999</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.21951999999999999</v>
+        <v>0.28993200000000002</v>
       </c>
       <c r="B8">
-        <v>0.22140399999999999</v>
+        <v>0.290572</v>
       </c>
       <c r="C8">
-        <v>0.223188</v>
+        <v>0.292543</v>
       </c>
       <c r="D8">
-        <v>0.22744200000000001</v>
+        <v>0.29068899999999998</v>
       </c>
       <c r="E8">
-        <v>0.23044799999999999</v>
+        <v>0.29105199999999998</v>
       </c>
       <c r="F8">
-        <v>0.233211</v>
+        <v>0.29142400000000002</v>
       </c>
       <c r="G8">
-        <v>0.235621</v>
+        <v>0.29227700000000001</v>
       </c>
       <c r="H8">
-        <v>0.238291</v>
+        <v>0.29465000000000002</v>
       </c>
       <c r="I8">
-        <v>0.24065800000000001</v>
+        <v>0.29344999999999999</v>
       </c>
       <c r="J8">
-        <v>0.241228</v>
+        <v>0.297072</v>
       </c>
       <c r="K8">
-        <v>0.244204</v>
+        <v>0.29573700000000003</v>
       </c>
       <c r="L8">
-        <v>0.24621899999999999</v>
+        <v>0.293684</v>
       </c>
       <c r="M8">
-        <v>0.24899099999999999</v>
+        <v>0.293435</v>
       </c>
       <c r="N8">
-        <v>0.25195800000000002</v>
+        <v>0.29318499999999997</v>
       </c>
       <c r="O8">
-        <v>0.256436</v>
+        <v>0.290821</v>
       </c>
       <c r="P8">
-        <v>0.25910699999999998</v>
+        <v>0.289574</v>
       </c>
       <c r="Q8">
-        <v>0.26182</v>
+        <v>0.286744</v>
       </c>
       <c r="R8">
-        <v>0.26346999999999998</v>
+        <v>0.273449</v>
       </c>
       <c r="S8">
-        <v>0.26547300000000001</v>
+        <v>0.25528400000000001</v>
       </c>
       <c r="T8">
-        <v>0.26217600000000002</v>
+        <v>0.238737</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.22182299999999999</v>
+        <v>0.28606799999999999</v>
       </c>
       <c r="B9">
-        <v>0.22397400000000001</v>
+        <v>0.28715200000000002</v>
       </c>
       <c r="C9">
-        <v>0.22584399999999999</v>
+        <v>0.28795399999999999</v>
       </c>
       <c r="D9">
-        <v>0.230242</v>
+        <v>0.286719</v>
       </c>
       <c r="E9">
-        <v>0.23331299999999999</v>
+        <v>0.28747200000000001</v>
       </c>
       <c r="F9">
-        <v>0.23603299999999999</v>
+        <v>0.287906</v>
       </c>
       <c r="G9">
-        <v>0.23889199999999999</v>
+        <v>0.28927999999999998</v>
       </c>
       <c r="H9">
-        <v>0.241894</v>
+        <v>0.29076999999999997</v>
       </c>
       <c r="I9">
-        <v>0.24415500000000001</v>
+        <v>0.28991</v>
       </c>
       <c r="J9">
-        <v>0.245146</v>
+        <v>0.29133599999999998</v>
       </c>
       <c r="K9">
-        <v>0.24815599999999999</v>
+        <v>0.288381</v>
       </c>
       <c r="L9">
-        <v>0.25063000000000002</v>
+        <v>0.286269</v>
       </c>
       <c r="M9">
-        <v>0.253772</v>
+        <v>0.28711300000000001</v>
       </c>
       <c r="N9">
-        <v>0.25747199999999998</v>
+        <v>0.28761100000000001</v>
       </c>
       <c r="O9">
-        <v>0.26248500000000002</v>
+        <v>0.28594999999999998</v>
       </c>
       <c r="P9">
-        <v>0.265233</v>
+        <v>0.28559499999999999</v>
       </c>
       <c r="Q9">
-        <v>0.267903</v>
+        <v>0.28326299999999999</v>
       </c>
       <c r="R9">
-        <v>0.26947300000000002</v>
+        <v>0.270843</v>
       </c>
       <c r="S9">
-        <v>0.27248800000000001</v>
+        <v>0.25423400000000002</v>
       </c>
       <c r="T9">
-        <v>0.26932899999999999</v>
+        <v>0.23207</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.22430900000000001</v>
+        <v>0.28249999999999997</v>
       </c>
       <c r="B10">
-        <v>0.22652</v>
+        <v>0.28375099999999998</v>
       </c>
       <c r="C10">
-        <v>0.22858600000000001</v>
+        <v>0.28506300000000001</v>
       </c>
       <c r="D10">
-        <v>0.233039</v>
+        <v>0.28417500000000001</v>
       </c>
       <c r="E10">
-        <v>0.23580400000000001</v>
+        <v>0.28503699999999998</v>
       </c>
       <c r="F10">
-        <v>0.238457</v>
+        <v>0.28591699999999998</v>
       </c>
       <c r="G10">
-        <v>0.240923</v>
+        <v>0.28760000000000002</v>
       </c>
       <c r="H10">
-        <v>0.24382499999999999</v>
+        <v>0.28808</v>
       </c>
       <c r="I10">
-        <v>0.24630099999999999</v>
+        <v>0.28797499999999998</v>
       </c>
       <c r="J10">
-        <v>0.24735399999999999</v>
+        <v>0.28788000000000002</v>
       </c>
       <c r="K10">
-        <v>0.25037500000000001</v>
+        <v>0.28384700000000002</v>
       </c>
       <c r="L10">
-        <v>0.25324799999999997</v>
+        <v>0.28238000000000002</v>
       </c>
       <c r="M10">
-        <v>0.25647999999999999</v>
+        <v>0.28205200000000002</v>
       </c>
       <c r="N10">
-        <v>0.26041900000000001</v>
+        <v>0.28339799999999998</v>
       </c>
       <c r="O10">
-        <v>0.26555499999999999</v>
+        <v>0.28214499999999998</v>
       </c>
       <c r="P10">
-        <v>0.269262</v>
+        <v>0.28207300000000002</v>
       </c>
       <c r="Q10">
-        <v>0.271507</v>
+        <v>0.28023900000000002</v>
       </c>
       <c r="R10">
-        <v>0.27300600000000003</v>
+        <v>0.26923599999999998</v>
       </c>
       <c r="S10">
-        <v>0.27684799999999998</v>
+        <v>0.25397199999999998</v>
       </c>
       <c r="T10">
-        <v>0.27488000000000001</v>
+        <v>0.23227700000000001</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.227578</v>
+        <v>0.29473700000000003</v>
       </c>
       <c r="B11">
-        <v>0.230152</v>
+        <v>0.29665900000000001</v>
       </c>
       <c r="C11">
-        <v>0.232798</v>
+        <v>0.29906899999999997</v>
       </c>
       <c r="D11">
-        <v>0.23751800000000001</v>
+        <v>0.29637200000000002</v>
       </c>
       <c r="E11">
-        <v>0.240366</v>
+        <v>0.295601</v>
       </c>
       <c r="F11">
-        <v>0.243036</v>
+        <v>0.29682799999999998</v>
       </c>
       <c r="G11">
-        <v>0.246112</v>
+        <v>0.29741000000000001</v>
       </c>
       <c r="H11">
-        <v>0.248695</v>
+        <v>0.29673899999999998</v>
       </c>
       <c r="I11">
-        <v>0.25120100000000001</v>
+        <v>0.296873</v>
       </c>
       <c r="J11">
-        <v>0.25286999999999998</v>
+        <v>0.29742600000000002</v>
       </c>
       <c r="K11">
-        <v>0.25687599999999999</v>
+        <v>0.29340699999999997</v>
       </c>
       <c r="L11">
-        <v>0.26033000000000001</v>
+        <v>0.29179899999999998</v>
       </c>
       <c r="M11">
-        <v>0.26325799999999999</v>
+        <v>0.29266199999999998</v>
       </c>
       <c r="N11">
-        <v>0.26684999999999998</v>
+        <v>0.29244100000000001</v>
       </c>
       <c r="O11">
-        <v>0.270984</v>
+        <v>0.292466</v>
       </c>
       <c r="P11">
-        <v>0.27390300000000001</v>
+        <v>0.28786499999999998</v>
       </c>
       <c r="Q11">
-        <v>0.27659400000000001</v>
+        <v>0.28275299999999998</v>
       </c>
       <c r="R11">
-        <v>0.27884799999999998</v>
+        <v>0.27177699999999999</v>
       </c>
       <c r="S11">
-        <v>0.28229100000000001</v>
+        <v>0.25594699999999998</v>
       </c>
       <c r="T11">
-        <v>0.27881400000000001</v>
+        <v>0.23913000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.23125100000000001</v>
+        <v>0.295819</v>
       </c>
       <c r="B12">
-        <v>0.23363600000000001</v>
+        <v>0.29598000000000002</v>
       </c>
       <c r="C12">
-        <v>0.236707</v>
+        <v>0.29923699999999998</v>
       </c>
       <c r="D12">
-        <v>0.24131900000000001</v>
+        <v>0.29718299999999997</v>
       </c>
       <c r="E12">
-        <v>0.24440300000000001</v>
+        <v>0.29636099999999999</v>
       </c>
       <c r="F12">
-        <v>0.24710499999999999</v>
+        <v>0.29782500000000001</v>
       </c>
       <c r="G12">
-        <v>0.25009199999999998</v>
+        <v>0.29877700000000001</v>
       </c>
       <c r="H12">
-        <v>0.25242100000000001</v>
+        <v>0.29865900000000001</v>
       </c>
       <c r="I12">
-        <v>0.255305</v>
+        <v>0.29984100000000002</v>
       </c>
       <c r="J12">
-        <v>0.25759900000000002</v>
+        <v>0.30063400000000001</v>
       </c>
       <c r="K12">
-        <v>0.26155499999999998</v>
+        <v>0.29675400000000002</v>
       </c>
       <c r="L12">
-        <v>0.26441799999999999</v>
+        <v>0.29546099999999997</v>
       </c>
       <c r="M12">
-        <v>0.26803300000000002</v>
+        <v>0.29748400000000003</v>
       </c>
       <c r="N12">
-        <v>0.27238000000000001</v>
+        <v>0.297487</v>
       </c>
       <c r="O12">
-        <v>0.27712999999999999</v>
+        <v>0.295713</v>
       </c>
       <c r="P12">
-        <v>0.279752</v>
+        <v>0.29214400000000001</v>
       </c>
       <c r="Q12">
-        <v>0.28237000000000001</v>
+        <v>0.285244</v>
       </c>
       <c r="R12">
-        <v>0.284356</v>
+        <v>0.27394099999999999</v>
       </c>
       <c r="S12">
-        <v>0.288412</v>
+        <v>0.25935599999999998</v>
       </c>
       <c r="T12">
-        <v>0.28333799999999998</v>
+        <v>0.236678</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.232875</v>
+        <v>0.28338099999999999</v>
       </c>
       <c r="B13">
-        <v>0.234987</v>
+        <v>0.28358299999999997</v>
       </c>
       <c r="C13">
-        <v>0.23797299999999999</v>
+        <v>0.28754299999999999</v>
       </c>
       <c r="D13">
-        <v>0.24247099999999999</v>
+        <v>0.28623700000000002</v>
       </c>
       <c r="E13">
-        <v>0.24609200000000001</v>
+        <v>0.28536600000000001</v>
       </c>
       <c r="F13">
-        <v>0.24933</v>
+        <v>0.286972</v>
       </c>
       <c r="G13">
-        <v>0.252498</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="H13">
-        <v>0.25516100000000003</v>
+        <v>0.28676400000000002</v>
       </c>
       <c r="I13">
-        <v>0.25926100000000002</v>
+        <v>0.28804800000000003</v>
       </c>
       <c r="J13">
-        <v>0.26204499999999997</v>
+        <v>0.289381</v>
       </c>
       <c r="K13">
-        <v>0.26521800000000001</v>
+        <v>0.28573799999999999</v>
       </c>
       <c r="L13">
-        <v>0.26909300000000003</v>
+        <v>0.284827</v>
       </c>
       <c r="M13">
-        <v>0.27277299999999999</v>
+        <v>0.284779</v>
       </c>
       <c r="N13">
-        <v>0.278115</v>
+        <v>0.284798</v>
       </c>
       <c r="O13">
-        <v>0.28410800000000003</v>
+        <v>0.28245199999999998</v>
       </c>
       <c r="P13">
-        <v>0.288468</v>
+        <v>0.27821000000000001</v>
       </c>
       <c r="Q13">
-        <v>0.29004000000000002</v>
+        <v>0.27199099999999998</v>
       </c>
       <c r="R13">
-        <v>0.291742</v>
+        <v>0.26266400000000001</v>
       </c>
       <c r="S13">
-        <v>0.29261199999999998</v>
+        <v>0.250025</v>
       </c>
       <c r="T13">
-        <v>0.28690300000000002</v>
+        <v>0.226606</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.23880999999999999</v>
+        <v>0.29100199999999998</v>
       </c>
       <c r="B14">
-        <v>0.24144699999999999</v>
+        <v>0.29162500000000002</v>
       </c>
       <c r="C14">
-        <v>0.244033</v>
+        <v>0.29374400000000001</v>
       </c>
       <c r="D14">
-        <v>0.24876200000000001</v>
+        <v>0.29277700000000001</v>
       </c>
       <c r="E14">
-        <v>0.25297399999999998</v>
+        <v>0.292294</v>
       </c>
       <c r="F14">
-        <v>0.25515500000000002</v>
+        <v>0.29181099999999999</v>
       </c>
       <c r="G14">
-        <v>0.25889499999999999</v>
+        <v>0.29476999999999998</v>
       </c>
       <c r="H14">
-        <v>0.26160299999999997</v>
+        <v>0.29279500000000003</v>
       </c>
       <c r="I14">
-        <v>0.26573799999999997</v>
+        <v>0.29510799999999998</v>
       </c>
       <c r="J14">
-        <v>0.268428</v>
+        <v>0.29700900000000002</v>
       </c>
       <c r="K14">
-        <v>0.27198299999999997</v>
+        <v>0.29347400000000001</v>
       </c>
       <c r="L14">
-        <v>0.27611599999999997</v>
+        <v>0.29296899999999998</v>
       </c>
       <c r="M14">
-        <v>0.27884799999999998</v>
+        <v>0.29383900000000002</v>
       </c>
       <c r="N14">
-        <v>0.28503899999999999</v>
+        <v>0.29435899999999998</v>
       </c>
       <c r="O14">
-        <v>0.29080299999999998</v>
+        <v>0.29278799999999999</v>
       </c>
       <c r="P14">
-        <v>0.295734</v>
+        <v>0.287024</v>
       </c>
       <c r="Q14">
-        <v>0.29719200000000001</v>
+        <v>0.281138</v>
       </c>
       <c r="R14">
-        <v>0.299149</v>
+        <v>0.27082899999999999</v>
       </c>
       <c r="S14">
-        <v>0.30298000000000003</v>
+        <v>0.25753599999999999</v>
       </c>
       <c r="T14">
-        <v>0.29822799999999999</v>
+        <v>0.23056299999999999</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.24391499999999999</v>
+        <v>0.27374500000000002</v>
       </c>
       <c r="B15">
-        <v>0.24601100000000001</v>
+        <v>0.27443800000000002</v>
       </c>
       <c r="C15">
-        <v>0.24887899999999999</v>
+        <v>0.27674599999999999</v>
       </c>
       <c r="D15">
-        <v>0.25364399999999998</v>
+        <v>0.27570899999999998</v>
       </c>
       <c r="E15">
-        <v>0.25894699999999998</v>
+        <v>0.27518999999999999</v>
       </c>
       <c r="F15">
-        <v>0.26094099999999998</v>
+        <v>0.27518999999999999</v>
       </c>
       <c r="G15">
-        <v>0.26462000000000002</v>
+        <v>0.27901199999999998</v>
       </c>
       <c r="H15">
-        <v>0.26732299999999998</v>
+        <v>0.27741700000000002</v>
       </c>
       <c r="I15">
-        <v>0.27144000000000001</v>
+        <v>0.27999200000000002</v>
       </c>
       <c r="J15">
-        <v>0.27478999999999998</v>
+        <v>0.28268799999999999</v>
       </c>
       <c r="K15">
-        <v>0.27773500000000001</v>
+        <v>0.27941300000000002</v>
       </c>
       <c r="L15">
-        <v>0.281719</v>
+        <v>0.27886699999999998</v>
       </c>
       <c r="M15">
-        <v>0.28403400000000001</v>
+        <v>0.280061</v>
       </c>
       <c r="N15">
-        <v>0.290715</v>
+        <v>0.280775</v>
       </c>
       <c r="O15">
-        <v>0.29483599999999999</v>
+        <v>0.279636</v>
       </c>
       <c r="P15">
-        <v>0.29891699999999999</v>
+        <v>0.27507599999999999</v>
       </c>
       <c r="Q15">
-        <v>0.30074299999999998</v>
+        <v>0.269372</v>
       </c>
       <c r="R15">
-        <v>0.30429899999999999</v>
+        <v>0.26188499999999998</v>
       </c>
       <c r="S15">
-        <v>0.30680299999999999</v>
+        <v>0.251859</v>
       </c>
       <c r="T15">
-        <v>0.29866399999999999</v>
+        <v>0.22723299999999999</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.23960699999999999</v>
+        <v>0.25981500000000002</v>
       </c>
       <c r="B16">
-        <v>0.24104300000000001</v>
+        <v>0.25812499999999999</v>
       </c>
       <c r="C16">
-        <v>0.24406700000000001</v>
+        <v>0.26080399999999998</v>
       </c>
       <c r="D16">
-        <v>0.24859000000000001</v>
+        <v>0.25966099999999998</v>
       </c>
       <c r="E16">
-        <v>0.25324400000000002</v>
+        <v>0.25966099999999998</v>
       </c>
       <c r="F16">
-        <v>0.25592700000000002</v>
+        <v>0.25966099999999998</v>
       </c>
       <c r="G16">
-        <v>0.259274</v>
+        <v>0.26542100000000002</v>
       </c>
       <c r="H16">
-        <v>0.263046</v>
+        <v>0.26424300000000001</v>
       </c>
       <c r="I16">
-        <v>0.26747100000000001</v>
+        <v>0.26794400000000002</v>
       </c>
       <c r="J16">
-        <v>0.27036700000000002</v>
+        <v>0.26674799999999999</v>
       </c>
       <c r="K16">
-        <v>0.27317900000000001</v>
+        <v>0.26375500000000002</v>
       </c>
       <c r="L16">
-        <v>0.27713199999999999</v>
+        <v>0.263156</v>
       </c>
       <c r="M16">
-        <v>0.27849699999999999</v>
+        <v>0.26606000000000002</v>
       </c>
       <c r="N16">
-        <v>0.28573900000000002</v>
+        <v>0.268349</v>
       </c>
       <c r="O16">
-        <v>0.29022500000000001</v>
+        <v>0.26771899999999998</v>
       </c>
       <c r="P16">
-        <v>0.29489500000000002</v>
+        <v>0.26393699999999998</v>
       </c>
       <c r="Q16">
-        <v>0.29670800000000003</v>
+        <v>0.25825900000000002</v>
       </c>
       <c r="R16">
-        <v>0.301593</v>
+        <v>0.25282199999999999</v>
       </c>
       <c r="S16">
-        <v>0.30367100000000002</v>
+        <v>0.24057500000000001</v>
       </c>
       <c r="T16">
-        <v>0.296151</v>
+        <v>0.212314</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.241117</v>
+        <v>0.22789599999999999</v>
       </c>
       <c r="B17">
-        <v>0.24332400000000001</v>
+        <v>0.22667000000000001</v>
       </c>
       <c r="C17">
-        <v>0.246588</v>
+        <v>0.229404</v>
       </c>
       <c r="D17">
-        <v>0.252139</v>
+        <v>0.22878000000000001</v>
       </c>
       <c r="E17">
-        <v>0.25807400000000003</v>
+        <v>0.22878000000000001</v>
       </c>
       <c r="F17">
-        <v>0.260967</v>
+        <v>0.22878000000000001</v>
       </c>
       <c r="G17">
-        <v>0.26369799999999999</v>
+        <v>0.23540900000000001</v>
       </c>
       <c r="H17">
-        <v>0.26752199999999998</v>
+        <v>0.23411699999999999</v>
       </c>
       <c r="I17">
-        <v>0.27295599999999998</v>
+        <v>0.23347000000000001</v>
       </c>
       <c r="J17">
-        <v>0.27639900000000001</v>
+        <v>0.23347000000000001</v>
       </c>
       <c r="K17">
-        <v>0.27804000000000001</v>
+        <v>0.23153099999999999</v>
       </c>
       <c r="L17">
-        <v>0.28069100000000002</v>
+        <v>0.23088400000000001</v>
       </c>
       <c r="M17">
-        <v>0.28234300000000001</v>
+        <v>0.23486699999999999</v>
       </c>
       <c r="N17">
-        <v>0.291848</v>
+        <v>0.23352300000000001</v>
       </c>
       <c r="O17">
-        <v>0.29811900000000002</v>
+        <v>0.23352300000000001</v>
       </c>
       <c r="P17">
-        <v>0.30451699999999998</v>
+        <v>0.230159</v>
       </c>
       <c r="Q17">
-        <v>0.30453400000000003</v>
+        <v>0.22544600000000001</v>
       </c>
       <c r="R17">
-        <v>0.3085</v>
+        <v>0.22339400000000001</v>
       </c>
       <c r="S17">
-        <v>0.31217</v>
+        <v>0.21374799999999999</v>
       </c>
       <c r="T17">
-        <v>0.30206499999999997</v>
+        <v>0.19524</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.23300100000000001</v>
+        <v>0.21079100000000001</v>
       </c>
       <c r="B18">
-        <v>0.23505200000000001</v>
+        <v>0.21008499999999999</v>
       </c>
       <c r="C18">
-        <v>0.23888899999999999</v>
+        <v>0.208673</v>
       </c>
       <c r="D18">
-        <v>0.24426100000000001</v>
+        <v>0.208673</v>
       </c>
       <c r="E18">
-        <v>0.24962599999999999</v>
+        <v>0.208673</v>
       </c>
       <c r="F18">
-        <v>0.25345699999999999</v>
+        <v>0.208673</v>
       </c>
       <c r="G18">
-        <v>0.25611200000000001</v>
+        <v>0.211423</v>
       </c>
       <c r="H18">
-        <v>0.25935900000000001</v>
+        <v>0.209978</v>
       </c>
       <c r="I18">
-        <v>0.26600400000000002</v>
+        <v>0.209978</v>
       </c>
       <c r="J18">
-        <v>0.27083699999999999</v>
+        <v>0.209978</v>
       </c>
       <c r="K18">
-        <v>0.27218399999999998</v>
+        <v>0.20780999999999999</v>
       </c>
       <c r="L18">
-        <v>0.27564100000000002</v>
+        <v>0.20708799999999999</v>
       </c>
       <c r="M18">
-        <v>0.27890799999999999</v>
+        <v>0.21073500000000001</v>
       </c>
       <c r="N18">
-        <v>0.28825899999999999</v>
+        <v>0.20999499999999999</v>
       </c>
       <c r="O18">
-        <v>0.29478399999999999</v>
+        <v>0.20999499999999999</v>
       </c>
       <c r="P18">
-        <v>0.30580200000000002</v>
+        <v>0.206292</v>
       </c>
       <c r="Q18">
-        <v>0.30808600000000003</v>
+        <v>0.201844</v>
       </c>
       <c r="R18">
-        <v>0.312639</v>
+        <v>0.201791</v>
       </c>
       <c r="S18">
-        <v>0.31319999999999998</v>
+        <v>0.19569900000000001</v>
       </c>
       <c r="T18">
-        <v>0.30616300000000002</v>
+        <v>0.18464800000000001</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.215864</v>
+        <v>0.15674099999999999</v>
       </c>
       <c r="B19">
-        <v>0.21863099999999999</v>
+        <v>0.15674099999999999</v>
       </c>
       <c r="C19">
-        <v>0.222798</v>
+        <v>0.15590200000000001</v>
       </c>
       <c r="D19">
-        <v>0.22831899999999999</v>
+        <v>0.15590200000000001</v>
       </c>
       <c r="E19">
-        <v>0.23380200000000001</v>
+        <v>0.15590200000000001</v>
       </c>
       <c r="F19">
-        <v>0.23675199999999999</v>
+        <v>0.15590200000000001</v>
       </c>
       <c r="G19">
-        <v>0.23860100000000001</v>
+        <v>0.16114700000000001</v>
       </c>
       <c r="H19">
-        <v>0.24005899999999999</v>
+        <v>0.16114700000000001</v>
       </c>
       <c r="I19">
-        <v>0.245728</v>
+        <v>0.16114700000000001</v>
       </c>
       <c r="J19">
-        <v>0.25165900000000002</v>
+        <v>0.16114700000000001</v>
       </c>
       <c r="K19">
-        <v>0.25243599999999999</v>
+        <v>0.159413</v>
       </c>
       <c r="L19">
-        <v>0.25621699999999997</v>
+        <v>0.15854599999999999</v>
       </c>
       <c r="M19">
-        <v>0.26170500000000002</v>
+        <v>0.15854599999999999</v>
       </c>
       <c r="N19">
-        <v>0.26689299999999999</v>
+        <v>0.15854599999999999</v>
       </c>
       <c r="O19">
-        <v>0.27444099999999999</v>
+        <v>0.15854599999999999</v>
       </c>
       <c r="P19">
-        <v>0.279557</v>
+        <v>0.15681</v>
       </c>
       <c r="Q19">
-        <v>0.28298499999999999</v>
+        <v>0.15507499999999999</v>
       </c>
       <c r="R19">
-        <v>0.289269</v>
+        <v>0.153338</v>
       </c>
       <c r="S19">
-        <v>0.290329</v>
+        <v>0.149862</v>
       </c>
       <c r="T19">
-        <v>0.28025099999999997</v>
+        <v>0.14357300000000001</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.174175</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="B20">
-        <v>0.17885599999999999</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="C20">
-        <v>0.18156700000000001</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="D20">
-        <v>0.18892500000000001</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="E20">
-        <v>0.188495</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="F20">
-        <v>0.18920600000000001</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="G20">
-        <v>0.19247</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="H20">
-        <v>0.195462</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="I20">
-        <v>0.19634299999999999</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="J20">
-        <v>0.20397799999999999</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="K20">
-        <v>0.202569</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="L20">
-        <v>0.202099</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="M20">
-        <v>0.204792</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="N20">
-        <v>0.20866699999999999</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="O20">
-        <v>0.21423900000000001</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="P20">
-        <v>0.216248</v>
+        <v>9.0495000000000006E-2</v>
       </c>
       <c r="Q20">
-        <v>0.21902099999999999</v>
+        <v>8.9039999999999994E-2</v>
       </c>
       <c r="R20">
-        <v>0.22492999999999999</v>
+        <v>8.7584999999999996E-2</v>
       </c>
       <c r="S20">
-        <v>0.22952</v>
+        <v>8.6127999999999996E-2</v>
       </c>
       <c r="T20">
-        <v>0.221917</v>
+        <v>8.3211999999999994E-2</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A21A6B-0B8F-4DA0-A71A-0695DCCAA809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA26963A-CD8C-4DCF-915C-82F782D2CB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA26963A-CD8C-4DCF-915C-82F782D2CB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A62D88D-D02B-4229-A0FB-384F5DF0C632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,1242 +349,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.285271</v>
+        <v>0.25622</v>
       </c>
       <c r="B1">
-        <v>0.28644799999999998</v>
+        <v>0.25780799999999998</v>
       </c>
       <c r="C1">
-        <v>0.28771400000000003</v>
+        <v>0.25949</v>
       </c>
       <c r="D1">
-        <v>0.28714499999999998</v>
+        <v>0.25909399999999999</v>
       </c>
       <c r="E1">
-        <v>0.28677200000000003</v>
+        <v>0.25615300000000002</v>
       </c>
       <c r="F1">
-        <v>0.28777399999999997</v>
+        <v>0.25410199999999999</v>
       </c>
       <c r="G1">
-        <v>0.28812900000000002</v>
+        <v>0.25580599999999998</v>
       </c>
       <c r="H1">
-        <v>0.288383</v>
+        <v>0.25604700000000002</v>
       </c>
       <c r="I1">
-        <v>0.28819899999999998</v>
+        <v>0.25464999999999999</v>
       </c>
       <c r="J1">
-        <v>0.28898800000000002</v>
+        <v>0.25421100000000002</v>
       </c>
       <c r="K1">
-        <v>0.28989399999999999</v>
+        <v>0.25347599999999998</v>
       </c>
       <c r="L1">
-        <v>0.28755700000000001</v>
+        <v>0.25579099999999999</v>
       </c>
       <c r="M1">
-        <v>0.28765800000000002</v>
+        <v>0.254832</v>
       </c>
       <c r="N1">
-        <v>0.286358</v>
+        <v>0.25522800000000001</v>
       </c>
       <c r="O1">
-        <v>0.28708299999999998</v>
+        <v>0.25219000000000003</v>
       </c>
       <c r="P1">
-        <v>0.282808</v>
+        <v>0.25472800000000001</v>
       </c>
       <c r="Q1">
-        <v>0.27735100000000001</v>
+        <v>0.25354199999999999</v>
       </c>
       <c r="R1">
-        <v>0.26554</v>
+        <v>0.26287300000000002</v>
       </c>
       <c r="S1">
-        <v>0.24798899999999999</v>
+        <v>0.25548700000000002</v>
       </c>
       <c r="T1">
-        <v>0.23005200000000001</v>
+        <v>0.24960199999999999</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.28513699999999997</v>
+        <v>0.252444</v>
       </c>
       <c r="B2">
-        <v>0.28561599999999998</v>
+        <v>0.25410199999999999</v>
       </c>
       <c r="C2">
-        <v>0.286999</v>
+        <v>0.25586399999999998</v>
       </c>
       <c r="D2">
-        <v>0.285605</v>
+        <v>0.255471</v>
       </c>
       <c r="E2">
-        <v>0.28603600000000001</v>
+        <v>0.25279200000000002</v>
       </c>
       <c r="F2">
-        <v>0.28710999999999998</v>
+        <v>0.25070399999999998</v>
       </c>
       <c r="G2">
-        <v>0.287545</v>
+        <v>0.25389299999999998</v>
       </c>
       <c r="H2">
-        <v>0.28844399999999998</v>
+        <v>0.25282900000000003</v>
       </c>
       <c r="I2">
-        <v>0.288323</v>
+        <v>0.25176100000000001</v>
       </c>
       <c r="J2">
-        <v>0.28950399999999998</v>
+        <v>0.25171100000000002</v>
       </c>
       <c r="K2">
-        <v>0.28955199999999998</v>
+        <v>0.25101400000000001</v>
       </c>
       <c r="L2">
-        <v>0.28747</v>
+        <v>0.25351699999999999</v>
       </c>
       <c r="M2">
-        <v>0.28773799999999999</v>
+        <v>0.251363</v>
       </c>
       <c r="N2">
-        <v>0.28653899999999999</v>
+        <v>0.250529</v>
       </c>
       <c r="O2">
-        <v>0.285105</v>
+        <v>0.247423</v>
       </c>
       <c r="P2">
-        <v>0.28181699999999998</v>
+        <v>0.25035400000000002</v>
       </c>
       <c r="Q2">
-        <v>0.27672099999999999</v>
+        <v>0.25131999999999999</v>
       </c>
       <c r="R2">
-        <v>0.26585399999999998</v>
+        <v>0.25935599999999998</v>
       </c>
       <c r="S2">
-        <v>0.24820600000000001</v>
+        <v>0.25236999999999998</v>
       </c>
       <c r="T2">
-        <v>0.23309099999999999</v>
+        <v>0.250552</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.28768500000000002</v>
+        <v>0.26042900000000002</v>
       </c>
       <c r="B3">
-        <v>0.28885300000000003</v>
+        <v>0.26330599999999998</v>
       </c>
       <c r="C3">
-        <v>0.29048600000000002</v>
+        <v>0.26413599999999998</v>
       </c>
       <c r="D3">
-        <v>0.28913</v>
+        <v>0.26385700000000001</v>
       </c>
       <c r="E3">
-        <v>0.28966399999999998</v>
+        <v>0.26100200000000001</v>
       </c>
       <c r="F3">
-        <v>0.29021799999999998</v>
+        <v>0.25891700000000001</v>
       </c>
       <c r="G3">
-        <v>0.29111300000000001</v>
+        <v>0.26015100000000002</v>
       </c>
       <c r="H3">
-        <v>0.29227700000000001</v>
+        <v>0.257608</v>
       </c>
       <c r="I3">
-        <v>0.29049399999999997</v>
+        <v>0.25658900000000001</v>
       </c>
       <c r="J3">
-        <v>0.29186000000000001</v>
+        <v>0.25686900000000001</v>
       </c>
       <c r="K3">
-        <v>0.29100700000000002</v>
+        <v>0.25649499999999997</v>
       </c>
       <c r="L3">
-        <v>0.28890500000000002</v>
+        <v>0.258162</v>
       </c>
       <c r="M3">
-        <v>0.28943600000000003</v>
+        <v>0.25641199999999997</v>
       </c>
       <c r="N3">
-        <v>0.28963</v>
+        <v>0.25634299999999999</v>
       </c>
       <c r="O3">
-        <v>0.28840399999999999</v>
+        <v>0.25351099999999999</v>
       </c>
       <c r="P3">
-        <v>0.28449600000000003</v>
+        <v>0.25611699999999998</v>
       </c>
       <c r="Q3">
-        <v>0.28029700000000002</v>
+        <v>0.25965700000000003</v>
       </c>
       <c r="R3">
-        <v>0.27023599999999998</v>
+        <v>0.26896100000000001</v>
       </c>
       <c r="S3">
-        <v>0.25101400000000001</v>
+        <v>0.26194699999999999</v>
       </c>
       <c r="T3">
-        <v>0.236151</v>
+        <v>0.25992599999999999</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.28641899999999998</v>
+        <v>0.25921699999999998</v>
       </c>
       <c r="B4">
-        <v>0.285831</v>
+        <v>0.26233000000000001</v>
       </c>
       <c r="C4">
-        <v>0.287497</v>
+        <v>0.26365699999999997</v>
       </c>
       <c r="D4">
-        <v>0.28612900000000002</v>
+        <v>0.262187</v>
       </c>
       <c r="E4">
-        <v>0.28695100000000001</v>
+        <v>0.25924599999999998</v>
       </c>
       <c r="F4">
-        <v>0.28752100000000003</v>
+        <v>0.257135</v>
       </c>
       <c r="G4">
-        <v>0.28872799999999998</v>
+        <v>0.257241</v>
       </c>
       <c r="H4">
-        <v>0.28993999999999998</v>
+        <v>0.25500699999999998</v>
       </c>
       <c r="I4">
-        <v>0.28842499999999999</v>
+        <v>0.25436199999999998</v>
       </c>
       <c r="J4">
-        <v>0.29013499999999998</v>
+        <v>0.25511499999999998</v>
       </c>
       <c r="K4">
-        <v>0.28819099999999997</v>
+        <v>0.25522299999999998</v>
       </c>
       <c r="L4">
-        <v>0.28636099999999998</v>
+        <v>0.25715100000000002</v>
       </c>
       <c r="M4">
-        <v>0.28722999999999999</v>
+        <v>0.25539899999999999</v>
       </c>
       <c r="N4">
-        <v>0.28684599999999999</v>
+        <v>0.25548300000000002</v>
       </c>
       <c r="O4">
-        <v>0.284966</v>
+        <v>0.25316</v>
       </c>
       <c r="P4">
-        <v>0.280279</v>
+        <v>0.256299</v>
       </c>
       <c r="Q4">
-        <v>0.27693800000000002</v>
+        <v>0.26129799999999997</v>
       </c>
       <c r="R4">
-        <v>0.26744600000000002</v>
+        <v>0.27082899999999999</v>
       </c>
       <c r="S4">
-        <v>0.248498</v>
+        <v>0.26188600000000001</v>
       </c>
       <c r="T4">
-        <v>0.234847</v>
+        <v>0.256693</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.29377500000000001</v>
+        <v>0.26035599999999998</v>
       </c>
       <c r="B5">
-        <v>0.29330299999999998</v>
+        <v>0.26389800000000002</v>
       </c>
       <c r="C5">
-        <v>0.29570999999999997</v>
+        <v>0.26587899999999998</v>
       </c>
       <c r="D5">
-        <v>0.294435</v>
+        <v>0.26433200000000001</v>
       </c>
       <c r="E5">
-        <v>0.29437099999999999</v>
+        <v>0.261625</v>
       </c>
       <c r="F5">
-        <v>0.29512300000000002</v>
+        <v>0.25814199999999998</v>
       </c>
       <c r="G5">
-        <v>0.295572</v>
+        <v>0.25834000000000001</v>
       </c>
       <c r="H5">
-        <v>0.29664800000000002</v>
+        <v>0.25600200000000001</v>
       </c>
       <c r="I5">
-        <v>0.29514400000000002</v>
+        <v>0.255415</v>
       </c>
       <c r="J5">
-        <v>0.297545</v>
+        <v>0.25648700000000002</v>
       </c>
       <c r="K5">
-        <v>0.29452499999999998</v>
+        <v>0.254992</v>
       </c>
       <c r="L5">
-        <v>0.29177199999999998</v>
+        <v>0.25787700000000002</v>
       </c>
       <c r="M5">
-        <v>0.289327</v>
+        <v>0.25657099999999999</v>
       </c>
       <c r="N5">
-        <v>0.288443</v>
+        <v>0.25568299999999999</v>
       </c>
       <c r="O5">
-        <v>0.28731000000000001</v>
+        <v>0.25355100000000003</v>
       </c>
       <c r="P5">
-        <v>0.28415000000000001</v>
+        <v>0.25499500000000003</v>
       </c>
       <c r="Q5">
-        <v>0.28181600000000001</v>
+        <v>0.25856499999999999</v>
       </c>
       <c r="R5">
-        <v>0.27170499999999997</v>
+        <v>0.27107100000000001</v>
       </c>
       <c r="S5">
-        <v>0.25147000000000003</v>
+        <v>0.26149899999999998</v>
       </c>
       <c r="T5">
-        <v>0.23599300000000001</v>
+        <v>0.26299600000000001</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.29425499999999999</v>
+        <v>0.25996799999999998</v>
       </c>
       <c r="B6">
-        <v>0.29415400000000003</v>
+        <v>0.26249699999999998</v>
       </c>
       <c r="C6">
-        <v>0.29577700000000001</v>
+        <v>0.26515699999999998</v>
       </c>
       <c r="D6">
-        <v>0.29397299999999998</v>
+        <v>0.26353100000000002</v>
       </c>
       <c r="E6">
-        <v>0.29424800000000001</v>
+        <v>0.26109199999999999</v>
       </c>
       <c r="F6">
-        <v>0.29423100000000002</v>
+        <v>0.25743300000000002</v>
       </c>
       <c r="G6">
-        <v>0.29481499999999999</v>
+        <v>0.25773299999999999</v>
       </c>
       <c r="H6">
-        <v>0.29641000000000001</v>
+        <v>0.255274</v>
       </c>
       <c r="I6">
-        <v>0.29489599999999999</v>
+        <v>0.25474999999999998</v>
       </c>
       <c r="J6">
-        <v>0.29758600000000002</v>
+        <v>0.25456400000000001</v>
       </c>
       <c r="K6">
-        <v>0.29550599999999999</v>
+        <v>0.25316</v>
       </c>
       <c r="L6">
-        <v>0.29296100000000003</v>
+        <v>0.25711000000000001</v>
       </c>
       <c r="M6">
-        <v>0.29162900000000003</v>
+        <v>0.25585000000000002</v>
       </c>
       <c r="N6">
-        <v>0.29049399999999997</v>
+        <v>0.25652700000000001</v>
       </c>
       <c r="O6">
-        <v>0.28846899999999998</v>
+        <v>0.25359599999999999</v>
       </c>
       <c r="P6">
-        <v>0.28594900000000001</v>
+        <v>0.25775599999999999</v>
       </c>
       <c r="Q6">
-        <v>0.28239399999999998</v>
+        <v>0.25752599999999998</v>
       </c>
       <c r="R6">
-        <v>0.27173799999999998</v>
+        <v>0.268843</v>
       </c>
       <c r="S6">
-        <v>0.25258700000000001</v>
+        <v>0.26267600000000002</v>
       </c>
       <c r="T6">
-        <v>0.23438700000000001</v>
+        <v>0.25623899999999999</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.29424800000000001</v>
+        <v>0.25516299999999997</v>
       </c>
       <c r="B7">
-        <v>0.29421900000000001</v>
+        <v>0.25791999999999998</v>
       </c>
       <c r="C7">
-        <v>0.29666599999999999</v>
+        <v>0.26083299999999998</v>
       </c>
       <c r="D7">
-        <v>0.29484700000000003</v>
+        <v>0.25955499999999998</v>
       </c>
       <c r="E7">
-        <v>0.29517700000000002</v>
+        <v>0.25742399999999999</v>
       </c>
       <c r="F7">
-        <v>0.29551500000000003</v>
+        <v>0.25358700000000001</v>
       </c>
       <c r="G7">
-        <v>0.29626799999999998</v>
+        <v>0.25397199999999998</v>
       </c>
       <c r="H7">
-        <v>0.298454</v>
+        <v>0.251392</v>
       </c>
       <c r="I7">
-        <v>0.29726399999999997</v>
+        <v>0.250913</v>
       </c>
       <c r="J7">
-        <v>0.30030699999999999</v>
+        <v>0.25087100000000001</v>
       </c>
       <c r="K7">
-        <v>0.29861300000000002</v>
+        <v>0.24956100000000001</v>
       </c>
       <c r="L7">
-        <v>0.29663200000000001</v>
+        <v>0.24928800000000001</v>
       </c>
       <c r="M7">
-        <v>0.29622500000000002</v>
+        <v>0.24893000000000001</v>
       </c>
       <c r="N7">
-        <v>0.29555300000000001</v>
+        <v>0.25017400000000001</v>
       </c>
       <c r="O7">
-        <v>0.29283500000000001</v>
+        <v>0.24817800000000001</v>
       </c>
       <c r="P7">
-        <v>0.29189500000000002</v>
+        <v>0.25192300000000001</v>
       </c>
       <c r="Q7">
-        <v>0.28994500000000001</v>
+        <v>0.25023299999999998</v>
       </c>
       <c r="R7">
-        <v>0.27658500000000003</v>
+        <v>0.26255699999999998</v>
       </c>
       <c r="S7">
-        <v>0.25795099999999999</v>
+        <v>0.26039400000000001</v>
       </c>
       <c r="T7">
-        <v>0.24050099999999999</v>
+        <v>0.25627299999999997</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.28993200000000002</v>
+        <v>0.25264799999999998</v>
       </c>
       <c r="B8">
-        <v>0.290572</v>
+        <v>0.25572400000000001</v>
       </c>
       <c r="C8">
-        <v>0.292543</v>
+        <v>0.25944099999999998</v>
       </c>
       <c r="D8">
-        <v>0.29068899999999998</v>
+        <v>0.25809399999999999</v>
       </c>
       <c r="E8">
-        <v>0.29105199999999998</v>
+        <v>0.25585000000000002</v>
       </c>
       <c r="F8">
-        <v>0.29142400000000002</v>
+        <v>0.25225700000000001</v>
       </c>
       <c r="G8">
-        <v>0.29227700000000001</v>
+        <v>0.25322800000000001</v>
       </c>
       <c r="H8">
-        <v>0.29465000000000002</v>
+        <v>0.25050699999999998</v>
       </c>
       <c r="I8">
-        <v>0.29344999999999999</v>
+        <v>0.25012099999999998</v>
       </c>
       <c r="J8">
-        <v>0.297072</v>
+        <v>0.25033</v>
       </c>
       <c r="K8">
-        <v>0.29573700000000003</v>
+        <v>0.24670400000000001</v>
       </c>
       <c r="L8">
-        <v>0.293684</v>
+        <v>0.248665</v>
       </c>
       <c r="M8">
-        <v>0.293435</v>
+        <v>0.248421</v>
       </c>
       <c r="N8">
-        <v>0.29318499999999997</v>
+        <v>0.24721000000000001</v>
       </c>
       <c r="O8">
-        <v>0.290821</v>
+        <v>0.245311</v>
       </c>
       <c r="P8">
-        <v>0.289574</v>
+        <v>0.25023299999999998</v>
       </c>
       <c r="Q8">
-        <v>0.286744</v>
+        <v>0.251359</v>
       </c>
       <c r="R8">
-        <v>0.273449</v>
+        <v>0.26825100000000002</v>
       </c>
       <c r="S8">
-        <v>0.25528400000000001</v>
+        <v>0.25905299999999998</v>
       </c>
       <c r="T8">
-        <v>0.238737</v>
+        <v>0.25096099999999999</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.28606799999999999</v>
+        <v>0.25423899999999999</v>
       </c>
       <c r="B9">
-        <v>0.28715200000000002</v>
+        <v>0.25575599999999998</v>
       </c>
       <c r="C9">
-        <v>0.28795399999999999</v>
+        <v>0.25779299999999999</v>
       </c>
       <c r="D9">
-        <v>0.286719</v>
+        <v>0.25639400000000001</v>
       </c>
       <c r="E9">
-        <v>0.28747200000000001</v>
+        <v>0.25406200000000001</v>
       </c>
       <c r="F9">
-        <v>0.287906</v>
+        <v>0.25033</v>
       </c>
       <c r="G9">
-        <v>0.28927999999999998</v>
+        <v>0.25141799999999997</v>
       </c>
       <c r="H9">
-        <v>0.29076999999999997</v>
+        <v>0.24859000000000001</v>
       </c>
       <c r="I9">
-        <v>0.28991</v>
+        <v>0.24826899999999999</v>
       </c>
       <c r="J9">
-        <v>0.29133599999999998</v>
+        <v>0.25061</v>
       </c>
       <c r="K9">
-        <v>0.288381</v>
+        <v>0.24743799999999999</v>
       </c>
       <c r="L9">
-        <v>0.286269</v>
+        <v>0.249889</v>
       </c>
       <c r="M9">
-        <v>0.28711300000000001</v>
+        <v>0.25030000000000002</v>
       </c>
       <c r="N9">
-        <v>0.28761100000000001</v>
+        <v>0.249196</v>
       </c>
       <c r="O9">
-        <v>0.28594999999999998</v>
+        <v>0.247562</v>
       </c>
       <c r="P9">
-        <v>0.28559499999999999</v>
+        <v>0.25112899999999999</v>
       </c>
       <c r="Q9">
-        <v>0.28326299999999999</v>
+        <v>0.25363000000000002</v>
       </c>
       <c r="R9">
-        <v>0.270843</v>
+        <v>0.27103699999999997</v>
       </c>
       <c r="S9">
-        <v>0.25423400000000002</v>
+        <v>0.25643300000000002</v>
       </c>
       <c r="T9">
-        <v>0.23207</v>
+        <v>0.25375599999999998</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.28249999999999997</v>
+        <v>0.250857</v>
       </c>
       <c r="B10">
-        <v>0.28375099999999998</v>
+        <v>0.25303999999999999</v>
       </c>
       <c r="C10">
-        <v>0.28506300000000001</v>
+        <v>0.255301</v>
       </c>
       <c r="D10">
-        <v>0.28417500000000001</v>
+        <v>0.25382700000000002</v>
       </c>
       <c r="E10">
-        <v>0.28503699999999998</v>
+        <v>0.25137100000000001</v>
       </c>
       <c r="F10">
-        <v>0.28591699999999998</v>
+        <v>0.24743799999999999</v>
       </c>
       <c r="G10">
-        <v>0.28760000000000002</v>
+        <v>0.249198</v>
       </c>
       <c r="H10">
-        <v>0.28808</v>
+        <v>0.24621499999999999</v>
       </c>
       <c r="I10">
-        <v>0.28797499999999998</v>
+        <v>0.246506</v>
       </c>
       <c r="J10">
-        <v>0.28788000000000002</v>
+        <v>0.24978500000000001</v>
       </c>
       <c r="K10">
-        <v>0.28384700000000002</v>
+        <v>0.246591</v>
       </c>
       <c r="L10">
-        <v>0.28238000000000002</v>
+        <v>0.25083800000000001</v>
       </c>
       <c r="M10">
-        <v>0.28205200000000002</v>
+        <v>0.25150499999999998</v>
       </c>
       <c r="N10">
-        <v>0.28339799999999998</v>
+        <v>0.25057299999999999</v>
       </c>
       <c r="O10">
-        <v>0.28214499999999998</v>
+        <v>0.249361</v>
       </c>
       <c r="P10">
-        <v>0.28207300000000002</v>
+        <v>0.25536599999999998</v>
       </c>
       <c r="Q10">
-        <v>0.28023900000000002</v>
+        <v>0.26054300000000002</v>
       </c>
       <c r="R10">
-        <v>0.26923599999999998</v>
+        <v>0.286192</v>
       </c>
       <c r="S10">
-        <v>0.25397199999999998</v>
+        <v>0.27553699999999998</v>
       </c>
       <c r="T10">
-        <v>0.23227700000000001</v>
+        <v>0.26702900000000002</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.29473700000000003</v>
+        <v>0.24815400000000001</v>
       </c>
       <c r="B11">
-        <v>0.29665900000000001</v>
+        <v>0.25074200000000002</v>
       </c>
       <c r="C11">
-        <v>0.29906899999999997</v>
+        <v>0.253438</v>
       </c>
       <c r="D11">
-        <v>0.29637200000000002</v>
+        <v>0.251836</v>
       </c>
       <c r="E11">
-        <v>0.295601</v>
+        <v>0.249165</v>
       </c>
       <c r="F11">
-        <v>0.29682799999999998</v>
+        <v>0.245424</v>
       </c>
       <c r="G11">
-        <v>0.29741000000000001</v>
+        <v>0.24759</v>
       </c>
       <c r="H11">
-        <v>0.29673899999999998</v>
+        <v>0.24434</v>
       </c>
       <c r="I11">
-        <v>0.296873</v>
+        <v>0.24492</v>
       </c>
       <c r="J11">
-        <v>0.29742600000000002</v>
+        <v>0.249666</v>
       </c>
       <c r="K11">
-        <v>0.29340699999999997</v>
+        <v>0.24707000000000001</v>
       </c>
       <c r="L11">
-        <v>0.29179899999999998</v>
+        <v>0.25067800000000001</v>
       </c>
       <c r="M11">
-        <v>0.29266199999999998</v>
+        <v>0.252967</v>
       </c>
       <c r="N11">
-        <v>0.29244100000000001</v>
+        <v>0.25357600000000002</v>
       </c>
       <c r="O11">
-        <v>0.292466</v>
+        <v>0.254469</v>
       </c>
       <c r="P11">
-        <v>0.28786499999999998</v>
+        <v>0.26502700000000001</v>
       </c>
       <c r="Q11">
-        <v>0.28275299999999998</v>
+        <v>0.26271800000000001</v>
       </c>
       <c r="R11">
-        <v>0.27177699999999999</v>
+        <v>0.28963</v>
       </c>
       <c r="S11">
-        <v>0.25594699999999998</v>
+        <v>0.28517399999999998</v>
       </c>
       <c r="T11">
-        <v>0.23913000000000001</v>
+        <v>0.260071</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.295819</v>
+        <v>0.265152</v>
       </c>
       <c r="B12">
-        <v>0.29598000000000002</v>
+        <v>0.26915499999999998</v>
       </c>
       <c r="C12">
-        <v>0.29923699999999998</v>
+        <v>0.27338699999999999</v>
       </c>
       <c r="D12">
-        <v>0.29718299999999997</v>
+        <v>0.27149899999999999</v>
       </c>
       <c r="E12">
-        <v>0.29636099999999999</v>
+        <v>0.26960899999999999</v>
       </c>
       <c r="F12">
-        <v>0.29782500000000001</v>
+        <v>0.26582800000000001</v>
       </c>
       <c r="G12">
-        <v>0.29877700000000001</v>
+        <v>0.26953500000000002</v>
       </c>
       <c r="H12">
-        <v>0.29865900000000001</v>
+        <v>0.26632499999999998</v>
       </c>
       <c r="I12">
-        <v>0.29984100000000002</v>
+        <v>0.26890700000000001</v>
       </c>
       <c r="J12">
-        <v>0.30063400000000001</v>
+        <v>0.271704</v>
       </c>
       <c r="K12">
-        <v>0.29675400000000002</v>
+        <v>0.27065299999999998</v>
       </c>
       <c r="L12">
-        <v>0.29546099999999997</v>
+        <v>0.26656200000000002</v>
       </c>
       <c r="M12">
-        <v>0.29748400000000003</v>
+        <v>0.27038800000000002</v>
       </c>
       <c r="N12">
-        <v>0.297487</v>
+        <v>0.27453300000000003</v>
       </c>
       <c r="O12">
-        <v>0.295713</v>
+        <v>0.27393400000000001</v>
       </c>
       <c r="P12">
-        <v>0.29214400000000001</v>
+        <v>0.29131499999999999</v>
       </c>
       <c r="Q12">
-        <v>0.285244</v>
+        <v>0.29317100000000001</v>
       </c>
       <c r="R12">
-        <v>0.27394099999999999</v>
+        <v>0.30975799999999998</v>
       </c>
       <c r="S12">
-        <v>0.25935599999999998</v>
+        <v>0.30110599999999998</v>
       </c>
       <c r="T12">
-        <v>0.236678</v>
+        <v>0.266594</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.28338099999999999</v>
+        <v>0.276669</v>
       </c>
       <c r="B13">
-        <v>0.28358299999999997</v>
+        <v>0.27595700000000001</v>
       </c>
       <c r="C13">
-        <v>0.28754299999999999</v>
+        <v>0.28195300000000001</v>
       </c>
       <c r="D13">
-        <v>0.28623700000000002</v>
+        <v>0.27976699999999999</v>
       </c>
       <c r="E13">
-        <v>0.28536600000000001</v>
+        <v>0.27758100000000002</v>
       </c>
       <c r="F13">
-        <v>0.286972</v>
+        <v>0.27466400000000002</v>
       </c>
       <c r="G13">
-        <v>0.28899999999999998</v>
+        <v>0.28096500000000002</v>
       </c>
       <c r="H13">
-        <v>0.28676400000000002</v>
+        <v>0.27722799999999997</v>
       </c>
       <c r="I13">
-        <v>0.28804800000000003</v>
+        <v>0.27423599999999998</v>
       </c>
       <c r="J13">
-        <v>0.289381</v>
+        <v>0.27859800000000001</v>
       </c>
       <c r="K13">
-        <v>0.28573799999999999</v>
+        <v>0.27948699999999999</v>
       </c>
       <c r="L13">
-        <v>0.284827</v>
+        <v>0.27474700000000002</v>
       </c>
       <c r="M13">
-        <v>0.284779</v>
+        <v>0.280692</v>
       </c>
       <c r="N13">
-        <v>0.284798</v>
+        <v>0.27825100000000003</v>
       </c>
       <c r="O13">
-        <v>0.28245199999999998</v>
+        <v>0.27975299999999997</v>
       </c>
       <c r="P13">
-        <v>0.27821000000000001</v>
+        <v>0.294985</v>
       </c>
       <c r="Q13">
-        <v>0.27199099999999998</v>
+        <v>0.30500100000000002</v>
       </c>
       <c r="R13">
-        <v>0.26266400000000001</v>
+        <v>0.32328099999999999</v>
       </c>
       <c r="S13">
-        <v>0.250025</v>
+        <v>0.32261800000000002</v>
       </c>
       <c r="T13">
-        <v>0.226606</v>
+        <v>0.292902</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.29100199999999998</v>
+        <v>0.280692</v>
       </c>
       <c r="B14">
-        <v>0.29162500000000002</v>
+        <v>0.27987800000000002</v>
       </c>
       <c r="C14">
-        <v>0.29374400000000001</v>
+        <v>0.28814499999999998</v>
       </c>
       <c r="D14">
-        <v>0.29277700000000001</v>
+        <v>0.28562900000000002</v>
       </c>
       <c r="E14">
-        <v>0.292294</v>
+        <v>0.28395100000000001</v>
       </c>
       <c r="F14">
-        <v>0.29181099999999999</v>
+        <v>0.28059299999999998</v>
       </c>
       <c r="G14">
-        <v>0.29476999999999998</v>
+        <v>0.27975299999999997</v>
       </c>
       <c r="H14">
-        <v>0.29279500000000003</v>
+        <v>0.27555000000000002</v>
       </c>
       <c r="I14">
-        <v>0.29510799999999998</v>
+        <v>0.27302599999999999</v>
       </c>
       <c r="J14">
-        <v>0.29700900000000002</v>
+        <v>0.27050099999999999</v>
       </c>
       <c r="K14">
-        <v>0.29347400000000001</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="L14">
-        <v>0.29296899999999998</v>
+        <v>0.269515</v>
       </c>
       <c r="M14">
-        <v>0.29383900000000002</v>
+        <v>0.276974</v>
       </c>
       <c r="N14">
-        <v>0.29435899999999998</v>
+        <v>0.27426499999999998</v>
       </c>
       <c r="O14">
-        <v>0.29278799999999999</v>
+        <v>0.27890700000000002</v>
       </c>
       <c r="P14">
-        <v>0.287024</v>
+        <v>0.28645700000000002</v>
       </c>
       <c r="Q14">
-        <v>0.281138</v>
+        <v>0.30181599999999997</v>
       </c>
       <c r="R14">
-        <v>0.27082899999999999</v>
+        <v>0.32827899999999999</v>
       </c>
       <c r="S14">
-        <v>0.25753599999999999</v>
+        <v>0.30760100000000001</v>
       </c>
       <c r="T14">
-        <v>0.23056299999999999</v>
+        <v>0.28547800000000001</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.27374500000000002</v>
+        <v>0.24978500000000001</v>
       </c>
       <c r="B15">
-        <v>0.27443800000000002</v>
+        <v>0.24978500000000001</v>
       </c>
       <c r="C15">
-        <v>0.27674599999999999</v>
+        <v>0.259127</v>
       </c>
       <c r="D15">
-        <v>0.27570899999999998</v>
+        <v>0.25629099999999999</v>
       </c>
       <c r="E15">
-        <v>0.27518999999999999</v>
+        <v>0.25440000000000002</v>
       </c>
       <c r="F15">
-        <v>0.27518999999999999</v>
+        <v>0.25156099999999998</v>
       </c>
       <c r="G15">
-        <v>0.27901199999999998</v>
+        <v>0.25156099999999998</v>
       </c>
       <c r="H15">
-        <v>0.27741700000000002</v>
+        <v>0.24777199999999999</v>
       </c>
       <c r="I15">
-        <v>0.27999200000000002</v>
+        <v>0.24492700000000001</v>
       </c>
       <c r="J15">
-        <v>0.28268799999999999</v>
+        <v>0.24207999999999999</v>
       </c>
       <c r="K15">
-        <v>0.27941300000000002</v>
+        <v>0.24607699999999999</v>
       </c>
       <c r="L15">
-        <v>0.27886699999999998</v>
+        <v>0.24310200000000001</v>
       </c>
       <c r="M15">
-        <v>0.280061</v>
+        <v>0.25313000000000002</v>
       </c>
       <c r="N15">
-        <v>0.280775</v>
+        <v>0.25001400000000001</v>
       </c>
       <c r="O15">
-        <v>0.279636</v>
+        <v>0.25730900000000001</v>
       </c>
       <c r="P15">
-        <v>0.27507599999999999</v>
+        <v>0.26991399999999999</v>
       </c>
       <c r="Q15">
-        <v>0.269372</v>
+        <v>0.27440700000000001</v>
       </c>
       <c r="R15">
-        <v>0.26188499999999998</v>
+        <v>0.282806</v>
       </c>
       <c r="S15">
-        <v>0.251859</v>
+        <v>0.26670899999999997</v>
       </c>
       <c r="T15">
-        <v>0.22723299999999999</v>
+        <v>0.25264999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.25981500000000002</v>
+        <v>0.26573000000000002</v>
       </c>
       <c r="B16">
-        <v>0.25812499999999999</v>
+        <v>0.26573000000000002</v>
       </c>
       <c r="C16">
-        <v>0.26080399999999998</v>
+        <v>0.28814699999999999</v>
       </c>
       <c r="D16">
-        <v>0.25966099999999998</v>
+        <v>0.28547800000000001</v>
       </c>
       <c r="E16">
-        <v>0.25966099999999998</v>
+        <v>0.28414200000000001</v>
       </c>
       <c r="F16">
-        <v>0.25966099999999998</v>
+        <v>0.28013100000000002</v>
       </c>
       <c r="G16">
-        <v>0.26542100000000002</v>
+        <v>0.28013100000000002</v>
       </c>
       <c r="H16">
-        <v>0.26424300000000001</v>
+        <v>0.27477099999999999</v>
       </c>
       <c r="I16">
-        <v>0.26794400000000002</v>
+        <v>0.27074300000000001</v>
       </c>
       <c r="J16">
-        <v>0.26674799999999999</v>
+        <v>0.269399</v>
       </c>
       <c r="K16">
-        <v>0.26375500000000002</v>
+        <v>0.29115400000000002</v>
       </c>
       <c r="L16">
-        <v>0.263156</v>
+        <v>0.28821799999999997</v>
       </c>
       <c r="M16">
-        <v>0.26606000000000002</v>
+        <v>0.322351</v>
       </c>
       <c r="N16">
-        <v>0.268349</v>
+        <v>0.31745400000000001</v>
       </c>
       <c r="O16">
-        <v>0.26771899999999998</v>
+        <v>0.36419099999999999</v>
       </c>
       <c r="P16">
-        <v>0.26393699999999998</v>
+        <v>0.36045300000000002</v>
       </c>
       <c r="Q16">
-        <v>0.25825900000000002</v>
+        <v>0.43845800000000001</v>
       </c>
       <c r="R16">
-        <v>0.25282199999999999</v>
+        <v>0.717306</v>
       </c>
       <c r="S16">
-        <v>0.24057500000000001</v>
+        <v>0.69817499999999999</v>
       </c>
       <c r="T16">
-        <v>0.212314</v>
+        <v>0.64263300000000001</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.22789599999999999</v>
+        <v>0.187279</v>
       </c>
       <c r="B17">
-        <v>0.22667000000000001</v>
+        <v>0.187279</v>
       </c>
       <c r="C17">
-        <v>0.229404</v>
+        <v>0.207313</v>
       </c>
       <c r="D17">
-        <v>0.22878000000000001</v>
+        <v>0.20578399999999999</v>
       </c>
       <c r="E17">
-        <v>0.22878000000000001</v>
+        <v>0.20425499999999999</v>
       </c>
       <c r="F17">
-        <v>0.22878000000000001</v>
+        <v>0.20272399999999999</v>
       </c>
       <c r="G17">
-        <v>0.23540900000000001</v>
+        <v>0.20272399999999999</v>
       </c>
       <c r="H17">
-        <v>0.23411699999999999</v>
+        <v>0.199659</v>
       </c>
       <c r="I17">
-        <v>0.23347000000000001</v>
+        <v>0.195053</v>
       </c>
       <c r="J17">
-        <v>0.23347000000000001</v>
+        <v>0.19351499999999999</v>
       </c>
       <c r="K17">
-        <v>0.23153099999999999</v>
+        <v>0.216643</v>
       </c>
       <c r="L17">
-        <v>0.23088400000000001</v>
+        <v>0.216643</v>
       </c>
       <c r="M17">
-        <v>0.23486699999999999</v>
+        <v>0.25786500000000001</v>
       </c>
       <c r="N17">
-        <v>0.23352300000000001</v>
+        <v>0.253853</v>
       </c>
       <c r="O17">
-        <v>0.23352300000000001</v>
+        <v>0.32283600000000001</v>
       </c>
       <c r="P17">
-        <v>0.230159</v>
+        <v>0.32034699999999999</v>
       </c>
       <c r="Q17">
-        <v>0.22544600000000001</v>
+        <v>0.30529299999999998</v>
       </c>
       <c r="R17">
-        <v>0.22339400000000001</v>
+        <v>0.57596499999999995</v>
       </c>
       <c r="S17">
-        <v>0.21374799999999999</v>
+        <v>0.56107899999999999</v>
       </c>
       <c r="T17">
-        <v>0.19524</v>
+        <v>0.50049399999999999</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.21079100000000001</v>
+        <v>0.113483</v>
       </c>
       <c r="B18">
-        <v>0.21008499999999999</v>
+        <v>0.113483</v>
       </c>
       <c r="C18">
-        <v>0.208673</v>
+        <v>0.113483</v>
       </c>
       <c r="D18">
-        <v>0.208673</v>
+        <v>0.113483</v>
       </c>
       <c r="E18">
-        <v>0.208673</v>
+        <v>0.111651</v>
       </c>
       <c r="F18">
-        <v>0.208673</v>
+        <v>0.111651</v>
       </c>
       <c r="G18">
-        <v>0.211423</v>
+        <v>0.111651</v>
       </c>
       <c r="H18">
-        <v>0.209978</v>
+        <v>0.109816</v>
       </c>
       <c r="I18">
-        <v>0.209978</v>
+        <v>0.106142</v>
       </c>
       <c r="J18">
-        <v>0.209978</v>
+        <v>0.10430200000000001</v>
       </c>
       <c r="K18">
-        <v>0.20780999999999999</v>
+        <v>0.125917</v>
       </c>
       <c r="L18">
-        <v>0.20708799999999999</v>
+        <v>0.125917</v>
       </c>
       <c r="M18">
-        <v>0.21073500000000001</v>
+        <v>0.17094400000000001</v>
       </c>
       <c r="N18">
-        <v>0.20999499999999999</v>
+        <v>0.168076</v>
       </c>
       <c r="O18">
-        <v>0.20999499999999999</v>
+        <v>0.41955100000000001</v>
       </c>
       <c r="P18">
-        <v>0.206292</v>
+        <v>0.41549700000000001</v>
       </c>
       <c r="Q18">
-        <v>0.201844</v>
+        <v>0.39460400000000001</v>
       </c>
       <c r="R18">
-        <v>0.201791</v>
+        <v>0.37254199999999998</v>
       </c>
       <c r="S18">
-        <v>0.19569900000000001</v>
+        <v>0.358653</v>
       </c>
       <c r="T18">
-        <v>0.18464800000000001</v>
+        <v>0.31867200000000001</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.15674099999999999</v>
+        <v>0.201546</v>
       </c>
       <c r="B19">
-        <v>0.15674099999999999</v>
+        <v>0.201546</v>
       </c>
       <c r="C19">
-        <v>0.15590200000000001</v>
+        <v>0.201546</v>
       </c>
       <c r="D19">
-        <v>0.15590200000000001</v>
+        <v>0.201546</v>
       </c>
       <c r="E19">
-        <v>0.15590200000000001</v>
+        <v>0.192965</v>
       </c>
       <c r="F19">
-        <v>0.15590200000000001</v>
+        <v>0.192965</v>
       </c>
       <c r="G19">
-        <v>0.16114700000000001</v>
+        <v>0.192965</v>
       </c>
       <c r="H19">
-        <v>0.16114700000000001</v>
+        <v>0.192965</v>
       </c>
       <c r="I19">
-        <v>0.16114700000000001</v>
+        <v>0.192965</v>
       </c>
       <c r="J19">
-        <v>0.16114700000000001</v>
+        <v>0.192965</v>
       </c>
       <c r="K19">
-        <v>0.159413</v>
+        <v>0.192965</v>
       </c>
       <c r="L19">
-        <v>0.15854599999999999</v>
+        <v>0.192965</v>
       </c>
       <c r="M19">
-        <v>0.15854599999999999</v>
+        <v>0.192965</v>
       </c>
       <c r="N19">
-        <v>0.15854599999999999</v>
+        <v>0.18398500000000001</v>
       </c>
       <c r="O19">
-        <v>0.15854599999999999</v>
+        <v>0.18398500000000001</v>
       </c>
       <c r="P19">
-        <v>0.15681</v>
+        <v>0.18398500000000001</v>
       </c>
       <c r="Q19">
-        <v>0.15507499999999999</v>
+        <v>0.18398500000000001</v>
       </c>
       <c r="R19">
-        <v>0.153338</v>
+        <v>0.18398500000000001</v>
       </c>
       <c r="S19">
-        <v>0.149862</v>
+        <v>0.174544</v>
       </c>
       <c r="T19">
-        <v>0.14357300000000001</v>
+        <v>0.15393299999999999</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="B20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>9.0495000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>8.9039999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>8.7584999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>8.6127999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>8.3211999999999994E-2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A62D88D-D02B-4229-A0FB-384F5DF0C632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7007686C-ED5C-449E-AC15-964252A270A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,1242 +349,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.25622</v>
+        <v>0.16613900000000001</v>
       </c>
       <c r="B1">
-        <v>0.25780799999999998</v>
+        <v>0.16697100000000001</v>
       </c>
       <c r="C1">
-        <v>0.25949</v>
+        <v>0.16869999999999999</v>
       </c>
       <c r="D1">
-        <v>0.25909399999999999</v>
+        <v>0.168575</v>
       </c>
       <c r="E1">
-        <v>0.25615300000000002</v>
+        <v>0.17061000000000001</v>
       </c>
       <c r="F1">
-        <v>0.25410199999999999</v>
+        <v>0.170982</v>
       </c>
       <c r="G1">
-        <v>0.25580599999999998</v>
+        <v>0.17006599999999999</v>
       </c>
       <c r="H1">
-        <v>0.25604700000000002</v>
+        <v>0.17006399999999999</v>
       </c>
       <c r="I1">
-        <v>0.25464999999999999</v>
+        <v>0.17069999999999999</v>
       </c>
       <c r="J1">
-        <v>0.25421100000000002</v>
+        <v>0.168235</v>
       </c>
       <c r="K1">
-        <v>0.25347599999999998</v>
+        <v>0.16919799999999999</v>
       </c>
       <c r="L1">
-        <v>0.25579099999999999</v>
+        <v>0.16574800000000001</v>
       </c>
       <c r="M1">
-        <v>0.254832</v>
+        <v>0.16589899999999999</v>
       </c>
       <c r="N1">
-        <v>0.25522800000000001</v>
+        <v>0.16335</v>
       </c>
       <c r="O1">
-        <v>0.25219000000000003</v>
+        <v>0.16105700000000001</v>
       </c>
       <c r="P1">
-        <v>0.25472800000000001</v>
+        <v>0.16069</v>
       </c>
       <c r="Q1">
-        <v>0.25354199999999999</v>
+        <v>0.16025</v>
       </c>
       <c r="R1">
-        <v>0.26287300000000002</v>
+        <v>0.16017300000000001</v>
       </c>
       <c r="S1">
-        <v>0.25548700000000002</v>
+        <v>0.16069</v>
       </c>
       <c r="T1">
-        <v>0.24960199999999999</v>
+        <v>0.16029299999999999</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.252444</v>
+        <v>0.16758999999999999</v>
       </c>
       <c r="B2">
-        <v>0.25410199999999999</v>
+        <v>0.16825200000000001</v>
       </c>
       <c r="C2">
-        <v>0.25586399999999998</v>
+        <v>0.17018800000000001</v>
       </c>
       <c r="D2">
-        <v>0.255471</v>
+        <v>0.16963400000000001</v>
       </c>
       <c r="E2">
-        <v>0.25279200000000002</v>
+        <v>0.171518</v>
       </c>
       <c r="F2">
-        <v>0.25070399999999998</v>
+        <v>0.17177799999999999</v>
       </c>
       <c r="G2">
-        <v>0.25389299999999998</v>
+        <v>0.17099700000000001</v>
       </c>
       <c r="H2">
-        <v>0.25282900000000003</v>
+        <v>0.170738</v>
       </c>
       <c r="I2">
-        <v>0.25176100000000001</v>
+        <v>0.17144699999999999</v>
       </c>
       <c r="J2">
-        <v>0.25171100000000002</v>
+        <v>0.16910800000000001</v>
       </c>
       <c r="K2">
-        <v>0.25101400000000001</v>
+        <v>0.17041300000000001</v>
       </c>
       <c r="L2">
-        <v>0.25351699999999999</v>
+        <v>0.167434</v>
       </c>
       <c r="M2">
-        <v>0.251363</v>
+        <v>0.16788500000000001</v>
       </c>
       <c r="N2">
-        <v>0.250529</v>
+        <v>0.16583899999999999</v>
       </c>
       <c r="O2">
-        <v>0.247423</v>
+        <v>0.163022</v>
       </c>
       <c r="P2">
-        <v>0.25035400000000002</v>
+        <v>0.162185</v>
       </c>
       <c r="Q2">
-        <v>0.25131999999999999</v>
+        <v>0.161438</v>
       </c>
       <c r="R2">
-        <v>0.25935599999999998</v>
+        <v>0.16188900000000001</v>
       </c>
       <c r="S2">
-        <v>0.25236999999999998</v>
+        <v>0.16220999999999999</v>
       </c>
       <c r="T2">
-        <v>0.250552</v>
+        <v>0.16103100000000001</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.26042900000000002</v>
+        <v>0.16969300000000001</v>
       </c>
       <c r="B3">
-        <v>0.26330599999999998</v>
+        <v>0.17027700000000001</v>
       </c>
       <c r="C3">
-        <v>0.26413599999999998</v>
+        <v>0.17135800000000001</v>
       </c>
       <c r="D3">
-        <v>0.26385700000000001</v>
+        <v>0.17065</v>
       </c>
       <c r="E3">
-        <v>0.26100200000000001</v>
+        <v>0.17205599999999999</v>
       </c>
       <c r="F3">
-        <v>0.25891700000000001</v>
+        <v>0.17266200000000001</v>
       </c>
       <c r="G3">
-        <v>0.26015100000000002</v>
+        <v>0.17147899999999999</v>
       </c>
       <c r="H3">
-        <v>0.257608</v>
+        <v>0.171349</v>
       </c>
       <c r="I3">
-        <v>0.25658900000000001</v>
+        <v>0.17211299999999999</v>
       </c>
       <c r="J3">
-        <v>0.25686900000000001</v>
+        <v>0.17015</v>
       </c>
       <c r="K3">
-        <v>0.25649499999999997</v>
+        <v>0.171177</v>
       </c>
       <c r="L3">
-        <v>0.258162</v>
+        <v>0.16894899999999999</v>
       </c>
       <c r="M3">
-        <v>0.25641199999999997</v>
+        <v>0.169041</v>
       </c>
       <c r="N3">
-        <v>0.25634299999999999</v>
+        <v>0.16666600000000001</v>
       </c>
       <c r="O3">
-        <v>0.25351099999999999</v>
+        <v>0.164746</v>
       </c>
       <c r="P3">
-        <v>0.25611699999999998</v>
+        <v>0.163691</v>
       </c>
       <c r="Q3">
-        <v>0.25965700000000003</v>
+        <v>0.16264400000000001</v>
       </c>
       <c r="R3">
-        <v>0.26896100000000001</v>
+        <v>0.161887</v>
       </c>
       <c r="S3">
-        <v>0.26194699999999999</v>
+        <v>0.16215399999999999</v>
       </c>
       <c r="T3">
-        <v>0.25992599999999999</v>
+        <v>0.160635</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.25921699999999998</v>
+        <v>0.17050799999999999</v>
       </c>
       <c r="B4">
-        <v>0.26233000000000001</v>
+        <v>0.171185</v>
       </c>
       <c r="C4">
-        <v>0.26365699999999997</v>
+        <v>0.17268800000000001</v>
       </c>
       <c r="D4">
-        <v>0.262187</v>
+        <v>0.17192499999999999</v>
       </c>
       <c r="E4">
-        <v>0.25924599999999998</v>
+        <v>0.17316400000000001</v>
       </c>
       <c r="F4">
-        <v>0.257135</v>
+        <v>0.17407900000000001</v>
       </c>
       <c r="G4">
-        <v>0.257241</v>
+        <v>0.17245099999999999</v>
       </c>
       <c r="H4">
-        <v>0.25500699999999998</v>
+        <v>0.17272999999999999</v>
       </c>
       <c r="I4">
-        <v>0.25436199999999998</v>
+        <v>0.17305699999999999</v>
       </c>
       <c r="J4">
-        <v>0.25511499999999998</v>
+        <v>0.171318</v>
       </c>
       <c r="K4">
-        <v>0.25522299999999998</v>
+        <v>0.17264199999999999</v>
       </c>
       <c r="L4">
-        <v>0.25715100000000002</v>
+        <v>0.170933</v>
       </c>
       <c r="M4">
-        <v>0.25539899999999999</v>
+        <v>0.170817</v>
       </c>
       <c r="N4">
-        <v>0.25548300000000002</v>
+        <v>0.167878</v>
       </c>
       <c r="O4">
-        <v>0.25316</v>
+        <v>0.16616600000000001</v>
       </c>
       <c r="P4">
-        <v>0.256299</v>
+        <v>0.164522</v>
       </c>
       <c r="Q4">
-        <v>0.26129799999999997</v>
+        <v>0.16378000000000001</v>
       </c>
       <c r="R4">
-        <v>0.27082899999999999</v>
+        <v>0.16406599999999999</v>
       </c>
       <c r="S4">
-        <v>0.26188600000000001</v>
+        <v>0.16375400000000001</v>
       </c>
       <c r="T4">
-        <v>0.256693</v>
+        <v>0.162911</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.26035599999999998</v>
+        <v>0.170323</v>
       </c>
       <c r="B5">
-        <v>0.26389800000000002</v>
+        <v>0.17121</v>
       </c>
       <c r="C5">
-        <v>0.26587899999999998</v>
+        <v>0.17286499999999999</v>
       </c>
       <c r="D5">
-        <v>0.26433200000000001</v>
+        <v>0.17263000000000001</v>
       </c>
       <c r="E5">
-        <v>0.261625</v>
+        <v>0.17382300000000001</v>
       </c>
       <c r="F5">
-        <v>0.25814199999999998</v>
+        <v>0.17457900000000001</v>
       </c>
       <c r="G5">
-        <v>0.25834000000000001</v>
+        <v>0.17339199999999999</v>
       </c>
       <c r="H5">
-        <v>0.25600200000000001</v>
+        <v>0.17435700000000001</v>
       </c>
       <c r="I5">
-        <v>0.255415</v>
+        <v>0.174569</v>
       </c>
       <c r="J5">
-        <v>0.25648700000000002</v>
+        <v>0.17259099999999999</v>
       </c>
       <c r="K5">
-        <v>0.254992</v>
+        <v>0.172823</v>
       </c>
       <c r="L5">
-        <v>0.25787700000000002</v>
+        <v>0.17149900000000001</v>
       </c>
       <c r="M5">
-        <v>0.25657099999999999</v>
+        <v>0.17060700000000001</v>
       </c>
       <c r="N5">
-        <v>0.25568299999999999</v>
+        <v>0.16708799999999999</v>
       </c>
       <c r="O5">
-        <v>0.25355100000000003</v>
+        <v>0.16547400000000001</v>
       </c>
       <c r="P5">
-        <v>0.25499500000000003</v>
+        <v>0.16401299999999999</v>
       </c>
       <c r="Q5">
-        <v>0.25856499999999999</v>
+        <v>0.16380900000000001</v>
       </c>
       <c r="R5">
-        <v>0.27107100000000001</v>
+        <v>0.16356499999999999</v>
       </c>
       <c r="S5">
-        <v>0.26149899999999998</v>
+        <v>0.16259699999999999</v>
       </c>
       <c r="T5">
-        <v>0.26299600000000001</v>
+        <v>0.161886</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.25996799999999998</v>
+        <v>0.17088999999999999</v>
       </c>
       <c r="B6">
-        <v>0.26249699999999998</v>
+        <v>0.17219899999999999</v>
       </c>
       <c r="C6">
-        <v>0.26515699999999998</v>
+        <v>0.174403</v>
       </c>
       <c r="D6">
-        <v>0.26353100000000002</v>
+        <v>0.174182</v>
       </c>
       <c r="E6">
-        <v>0.26109199999999999</v>
+        <v>0.174898</v>
       </c>
       <c r="F6">
-        <v>0.25743300000000002</v>
+        <v>0.175983</v>
       </c>
       <c r="G6">
-        <v>0.25773299999999999</v>
+        <v>0.174679</v>
       </c>
       <c r="H6">
-        <v>0.255274</v>
+        <v>0.175509</v>
       </c>
       <c r="I6">
-        <v>0.25474999999999998</v>
+        <v>0.17593200000000001</v>
       </c>
       <c r="J6">
-        <v>0.25456400000000001</v>
+        <v>0.17452599999999999</v>
       </c>
       <c r="K6">
-        <v>0.25316</v>
+        <v>0.17489499999999999</v>
       </c>
       <c r="L6">
-        <v>0.25711000000000001</v>
+        <v>0.17302600000000001</v>
       </c>
       <c r="M6">
-        <v>0.25585000000000002</v>
+        <v>0.17107700000000001</v>
       </c>
       <c r="N6">
-        <v>0.25652700000000001</v>
+        <v>0.167656</v>
       </c>
       <c r="O6">
-        <v>0.25359599999999999</v>
+        <v>0.166376</v>
       </c>
       <c r="P6">
-        <v>0.25775599999999999</v>
+        <v>0.16428300000000001</v>
       </c>
       <c r="Q6">
-        <v>0.25752599999999998</v>
+        <v>0.16458600000000001</v>
       </c>
       <c r="R6">
-        <v>0.268843</v>
+        <v>0.16480400000000001</v>
       </c>
       <c r="S6">
-        <v>0.26267600000000002</v>
+        <v>0.16352800000000001</v>
       </c>
       <c r="T6">
-        <v>0.25623899999999999</v>
+        <v>0.16322600000000001</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.25516299999999997</v>
+        <v>0.173017</v>
       </c>
       <c r="B7">
-        <v>0.25791999999999998</v>
+        <v>0.17537800000000001</v>
       </c>
       <c r="C7">
-        <v>0.26083299999999998</v>
+        <v>0.177428</v>
       </c>
       <c r="D7">
-        <v>0.25955499999999998</v>
+        <v>0.177343</v>
       </c>
       <c r="E7">
-        <v>0.25742399999999999</v>
+        <v>0.17758199999999999</v>
       </c>
       <c r="F7">
-        <v>0.25358700000000001</v>
+        <v>0.17916899999999999</v>
       </c>
       <c r="G7">
-        <v>0.25397199999999998</v>
+        <v>0.17838799999999999</v>
       </c>
       <c r="H7">
-        <v>0.251392</v>
+        <v>0.178956</v>
       </c>
       <c r="I7">
-        <v>0.250913</v>
+        <v>0.18049499999999999</v>
       </c>
       <c r="J7">
-        <v>0.25087100000000001</v>
+        <v>0.18010200000000001</v>
       </c>
       <c r="K7">
-        <v>0.24956100000000001</v>
+        <v>0.18088599999999999</v>
       </c>
       <c r="L7">
-        <v>0.24928800000000001</v>
+        <v>0.17940900000000001</v>
       </c>
       <c r="M7">
-        <v>0.24893000000000001</v>
+        <v>0.177344</v>
       </c>
       <c r="N7">
-        <v>0.25017400000000001</v>
+        <v>0.17346700000000001</v>
       </c>
       <c r="O7">
-        <v>0.24817800000000001</v>
+        <v>0.17286899999999999</v>
       </c>
       <c r="P7">
-        <v>0.25192300000000001</v>
+        <v>0.170567</v>
       </c>
       <c r="Q7">
-        <v>0.25023299999999998</v>
+        <v>0.17205899999999999</v>
       </c>
       <c r="R7">
-        <v>0.26255699999999998</v>
+        <v>0.17283799999999999</v>
       </c>
       <c r="S7">
-        <v>0.26039400000000001</v>
+        <v>0.17169300000000001</v>
       </c>
       <c r="T7">
-        <v>0.25627299999999997</v>
+        <v>0.17230500000000001</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.25264799999999998</v>
+        <v>0.173987</v>
       </c>
       <c r="B8">
-        <v>0.25572400000000001</v>
+        <v>0.17585600000000001</v>
       </c>
       <c r="C8">
-        <v>0.25944099999999998</v>
+        <v>0.17674400000000001</v>
       </c>
       <c r="D8">
-        <v>0.25809399999999999</v>
+        <v>0.176812</v>
       </c>
       <c r="E8">
-        <v>0.25585000000000002</v>
+        <v>0.17693</v>
       </c>
       <c r="F8">
-        <v>0.25225700000000001</v>
+        <v>0.178759</v>
       </c>
       <c r="G8">
-        <v>0.25322800000000001</v>
+        <v>0.17827799999999999</v>
       </c>
       <c r="H8">
-        <v>0.25050699999999998</v>
+        <v>0.17929899999999999</v>
       </c>
       <c r="I8">
-        <v>0.25012099999999998</v>
+        <v>0.18113299999999999</v>
       </c>
       <c r="J8">
-        <v>0.25033</v>
+        <v>0.18168000000000001</v>
       </c>
       <c r="K8">
-        <v>0.24670400000000001</v>
+        <v>0.182308</v>
       </c>
       <c r="L8">
-        <v>0.248665</v>
+        <v>0.180481</v>
       </c>
       <c r="M8">
-        <v>0.248421</v>
+        <v>0.178674</v>
       </c>
       <c r="N8">
-        <v>0.24721000000000001</v>
+        <v>0.17494399999999999</v>
       </c>
       <c r="O8">
-        <v>0.245311</v>
+        <v>0.17402100000000001</v>
       </c>
       <c r="P8">
-        <v>0.25023299999999998</v>
+        <v>0.17177300000000001</v>
       </c>
       <c r="Q8">
-        <v>0.251359</v>
+        <v>0.17138200000000001</v>
       </c>
       <c r="R8">
-        <v>0.26825100000000002</v>
+        <v>0.17211000000000001</v>
       </c>
       <c r="S8">
-        <v>0.25905299999999998</v>
+        <v>0.17042399999999999</v>
       </c>
       <c r="T8">
-        <v>0.25096099999999999</v>
+        <v>0.17247799999999999</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.25423899999999999</v>
+        <v>0.17402000000000001</v>
       </c>
       <c r="B9">
-        <v>0.25575599999999998</v>
+        <v>0.175451</v>
       </c>
       <c r="C9">
-        <v>0.25779299999999999</v>
+        <v>0.17643500000000001</v>
       </c>
       <c r="D9">
-        <v>0.25639400000000001</v>
+        <v>0.17701800000000001</v>
       </c>
       <c r="E9">
-        <v>0.25406200000000001</v>
+        <v>0.17657400000000001</v>
       </c>
       <c r="F9">
-        <v>0.25033</v>
+        <v>0.177729</v>
       </c>
       <c r="G9">
-        <v>0.25141799999999997</v>
+        <v>0.17790500000000001</v>
       </c>
       <c r="H9">
-        <v>0.24859000000000001</v>
+        <v>0.17885200000000001</v>
       </c>
       <c r="I9">
-        <v>0.24826899999999999</v>
+        <v>0.179753</v>
       </c>
       <c r="J9">
-        <v>0.25061</v>
+        <v>0.18092900000000001</v>
       </c>
       <c r="K9">
-        <v>0.24743799999999999</v>
+        <v>0.182171</v>
       </c>
       <c r="L9">
-        <v>0.249889</v>
+        <v>0.18035100000000001</v>
       </c>
       <c r="M9">
-        <v>0.25030000000000002</v>
+        <v>0.17882100000000001</v>
       </c>
       <c r="N9">
-        <v>0.249196</v>
+        <v>0.17501700000000001</v>
       </c>
       <c r="O9">
-        <v>0.247562</v>
+        <v>0.174318</v>
       </c>
       <c r="P9">
-        <v>0.25112899999999999</v>
+        <v>0.17253599999999999</v>
       </c>
       <c r="Q9">
-        <v>0.25363000000000002</v>
+        <v>0.17136000000000001</v>
       </c>
       <c r="R9">
-        <v>0.27103699999999997</v>
+        <v>0.174567</v>
       </c>
       <c r="S9">
-        <v>0.25643300000000002</v>
+        <v>0.17179</v>
       </c>
       <c r="T9">
-        <v>0.25375599999999998</v>
+        <v>0.172014</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.250857</v>
+        <v>0.181649</v>
       </c>
       <c r="B10">
-        <v>0.25303999999999999</v>
+        <v>0.18212200000000001</v>
       </c>
       <c r="C10">
-        <v>0.255301</v>
+        <v>0.18273600000000001</v>
       </c>
       <c r="D10">
-        <v>0.25382700000000002</v>
+        <v>0.18296799999999999</v>
       </c>
       <c r="E10">
-        <v>0.25137100000000001</v>
+        <v>0.18359600000000001</v>
       </c>
       <c r="F10">
-        <v>0.24743799999999999</v>
+        <v>0.18496199999999999</v>
       </c>
       <c r="G10">
-        <v>0.249198</v>
+        <v>0.183203</v>
       </c>
       <c r="H10">
-        <v>0.24621499999999999</v>
+        <v>0.18354200000000001</v>
       </c>
       <c r="I10">
-        <v>0.246506</v>
+        <v>0.184445</v>
       </c>
       <c r="J10">
-        <v>0.24978500000000001</v>
+        <v>0.185616</v>
       </c>
       <c r="K10">
-        <v>0.246591</v>
+        <v>0.18601699999999999</v>
       </c>
       <c r="L10">
-        <v>0.25083800000000001</v>
+        <v>0.18341299999999999</v>
       </c>
       <c r="M10">
-        <v>0.25150499999999998</v>
+        <v>0.180811</v>
       </c>
       <c r="N10">
-        <v>0.25057299999999999</v>
+        <v>0.17711499999999999</v>
       </c>
       <c r="O10">
-        <v>0.249361</v>
+        <v>0.175812</v>
       </c>
       <c r="P10">
-        <v>0.25536599999999998</v>
+        <v>0.175286</v>
       </c>
       <c r="Q10">
-        <v>0.26054300000000002</v>
+        <v>0.174261</v>
       </c>
       <c r="R10">
-        <v>0.286192</v>
+        <v>0.17754600000000001</v>
       </c>
       <c r="S10">
-        <v>0.27553699999999998</v>
+        <v>0.17655899999999999</v>
       </c>
       <c r="T10">
-        <v>0.26702900000000002</v>
+        <v>0.17641799999999999</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.24815400000000001</v>
+        <v>0.184002</v>
       </c>
       <c r="B11">
-        <v>0.25074200000000002</v>
+        <v>0.18321100000000001</v>
       </c>
       <c r="C11">
-        <v>0.253438</v>
+        <v>0.18412100000000001</v>
       </c>
       <c r="D11">
-        <v>0.251836</v>
+        <v>0.18310699999999999</v>
       </c>
       <c r="E11">
-        <v>0.249165</v>
+        <v>0.183478</v>
       </c>
       <c r="F11">
-        <v>0.245424</v>
+        <v>0.18450900000000001</v>
       </c>
       <c r="G11">
-        <v>0.24759</v>
+        <v>0.18401999999999999</v>
       </c>
       <c r="H11">
-        <v>0.24434</v>
+        <v>0.18328900000000001</v>
       </c>
       <c r="I11">
-        <v>0.24492</v>
+        <v>0.184337</v>
       </c>
       <c r="J11">
-        <v>0.249666</v>
+        <v>0.18595800000000001</v>
       </c>
       <c r="K11">
-        <v>0.24707000000000001</v>
+        <v>0.18553900000000001</v>
       </c>
       <c r="L11">
-        <v>0.25067800000000001</v>
+        <v>0.18357699999999999</v>
       </c>
       <c r="M11">
-        <v>0.252967</v>
+        <v>0.18187800000000001</v>
       </c>
       <c r="N11">
-        <v>0.25357600000000002</v>
+        <v>0.17769399999999999</v>
       </c>
       <c r="O11">
-        <v>0.254469</v>
+        <v>0.176174</v>
       </c>
       <c r="P11">
-        <v>0.26502700000000001</v>
+        <v>0.177288</v>
       </c>
       <c r="Q11">
-        <v>0.26271800000000001</v>
+        <v>0.17484</v>
       </c>
       <c r="R11">
-        <v>0.28963</v>
+        <v>0.17602799999999999</v>
       </c>
       <c r="S11">
-        <v>0.28517399999999998</v>
+        <v>0.17500299999999999</v>
       </c>
       <c r="T11">
-        <v>0.260071</v>
+        <v>0.174789</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.265152</v>
+        <v>0.17954100000000001</v>
       </c>
       <c r="B12">
-        <v>0.26915499999999998</v>
+        <v>0.178505</v>
       </c>
       <c r="C12">
-        <v>0.27338699999999999</v>
+        <v>0.17901400000000001</v>
       </c>
       <c r="D12">
-        <v>0.27149899999999999</v>
+        <v>0.17849100000000001</v>
       </c>
       <c r="E12">
-        <v>0.26960899999999999</v>
+        <v>0.179313</v>
       </c>
       <c r="F12">
-        <v>0.26582800000000001</v>
+        <v>0.181169</v>
       </c>
       <c r="G12">
-        <v>0.26953500000000002</v>
+        <v>0.18038899999999999</v>
       </c>
       <c r="H12">
-        <v>0.26632499999999998</v>
+        <v>0.18053900000000001</v>
       </c>
       <c r="I12">
-        <v>0.26890700000000001</v>
+        <v>0.181312</v>
       </c>
       <c r="J12">
-        <v>0.271704</v>
+        <v>0.183055</v>
       </c>
       <c r="K12">
-        <v>0.27065299999999998</v>
+        <v>0.181279</v>
       </c>
       <c r="L12">
-        <v>0.26656200000000002</v>
+        <v>0.178702</v>
       </c>
       <c r="M12">
-        <v>0.27038800000000002</v>
+        <v>0.177841</v>
       </c>
       <c r="N12">
-        <v>0.27453300000000003</v>
+        <v>0.17349500000000001</v>
       </c>
       <c r="O12">
-        <v>0.27393400000000001</v>
+        <v>0.172623</v>
       </c>
       <c r="P12">
-        <v>0.29131499999999999</v>
+        <v>0.173707</v>
       </c>
       <c r="Q12">
-        <v>0.29317100000000001</v>
+        <v>0.170823</v>
       </c>
       <c r="R12">
-        <v>0.30975799999999998</v>
+        <v>0.17338999999999999</v>
       </c>
       <c r="S12">
-        <v>0.30110599999999998</v>
+        <v>0.17408799999999999</v>
       </c>
       <c r="T12">
-        <v>0.266594</v>
+        <v>0.17411299999999999</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.276669</v>
+        <v>0.18137300000000001</v>
       </c>
       <c r="B13">
-        <v>0.27595700000000001</v>
+        <v>0.17884800000000001</v>
       </c>
       <c r="C13">
-        <v>0.28195300000000001</v>
+        <v>0.17922299999999999</v>
       </c>
       <c r="D13">
-        <v>0.27976699999999999</v>
+        <v>0.179118</v>
       </c>
       <c r="E13">
-        <v>0.27758100000000002</v>
+        <v>0.18026800000000001</v>
       </c>
       <c r="F13">
-        <v>0.27466400000000002</v>
+        <v>0.18214900000000001</v>
       </c>
       <c r="G13">
-        <v>0.28096500000000002</v>
+        <v>0.18082999999999999</v>
       </c>
       <c r="H13">
-        <v>0.27722799999999997</v>
+        <v>0.18051600000000001</v>
       </c>
       <c r="I13">
-        <v>0.27423599999999998</v>
+        <v>0.182647</v>
       </c>
       <c r="J13">
-        <v>0.27859800000000001</v>
+        <v>0.18069199999999999</v>
       </c>
       <c r="K13">
-        <v>0.27948699999999999</v>
+        <v>0.179754</v>
       </c>
       <c r="L13">
-        <v>0.27474700000000002</v>
+        <v>0.177759</v>
       </c>
       <c r="M13">
-        <v>0.280692</v>
+        <v>0.175068</v>
       </c>
       <c r="N13">
-        <v>0.27825100000000003</v>
+        <v>0.170982</v>
       </c>
       <c r="O13">
-        <v>0.27975299999999997</v>
+        <v>0.17106199999999999</v>
       </c>
       <c r="P13">
-        <v>0.294985</v>
+        <v>0.17238899999999999</v>
       </c>
       <c r="Q13">
-        <v>0.30500100000000002</v>
+        <v>0.17019599999999999</v>
       </c>
       <c r="R13">
-        <v>0.32328099999999999</v>
+        <v>0.17131199999999999</v>
       </c>
       <c r="S13">
-        <v>0.32261800000000002</v>
+        <v>0.17168800000000001</v>
       </c>
       <c r="T13">
-        <v>0.292902</v>
+        <v>0.168985</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.280692</v>
+        <v>0.17490800000000001</v>
       </c>
       <c r="B14">
-        <v>0.27987800000000002</v>
+        <v>0.17253399999999999</v>
       </c>
       <c r="C14">
-        <v>0.28814499999999998</v>
+        <v>0.17350599999999999</v>
       </c>
       <c r="D14">
-        <v>0.28562900000000002</v>
+        <v>0.174209</v>
       </c>
       <c r="E14">
-        <v>0.28395100000000001</v>
+        <v>0.176175</v>
       </c>
       <c r="F14">
-        <v>0.28059299999999998</v>
+        <v>0.177566</v>
       </c>
       <c r="G14">
-        <v>0.27975299999999997</v>
+        <v>0.17662700000000001</v>
       </c>
       <c r="H14">
-        <v>0.27555000000000002</v>
+        <v>0.177207</v>
       </c>
       <c r="I14">
-        <v>0.27302599999999999</v>
+        <v>0.17944199999999999</v>
       </c>
       <c r="J14">
-        <v>0.27050099999999999</v>
+        <v>0.176539</v>
       </c>
       <c r="K14">
-        <v>0.27300000000000002</v>
+        <v>0.17192099999999999</v>
       </c>
       <c r="L14">
-        <v>0.269515</v>
+        <v>0.168933</v>
       </c>
       <c r="M14">
-        <v>0.276974</v>
+        <v>0.166853</v>
       </c>
       <c r="N14">
-        <v>0.27426499999999998</v>
+        <v>0.16314899999999999</v>
       </c>
       <c r="O14">
-        <v>0.27890700000000002</v>
+        <v>0.164016</v>
       </c>
       <c r="P14">
-        <v>0.28645700000000002</v>
+        <v>0.167217</v>
       </c>
       <c r="Q14">
-        <v>0.30181599999999997</v>
+        <v>0.16601199999999999</v>
       </c>
       <c r="R14">
-        <v>0.32827899999999999</v>
+        <v>0.16456399999999999</v>
       </c>
       <c r="S14">
-        <v>0.30760100000000001</v>
+        <v>0.164052</v>
       </c>
       <c r="T14">
-        <v>0.28547800000000001</v>
+        <v>0.163077</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.24978500000000001</v>
+        <v>0.18417700000000001</v>
       </c>
       <c r="B15">
-        <v>0.24978500000000001</v>
+        <v>0.181672</v>
       </c>
       <c r="C15">
-        <v>0.259127</v>
+        <v>0.18427299999999999</v>
       </c>
       <c r="D15">
-        <v>0.25629099999999999</v>
+        <v>0.183507</v>
       </c>
       <c r="E15">
-        <v>0.25440000000000002</v>
+        <v>0.18418899999999999</v>
       </c>
       <c r="F15">
-        <v>0.25156099999999998</v>
+        <v>0.18568499999999999</v>
       </c>
       <c r="G15">
-        <v>0.25156099999999998</v>
+        <v>0.18541199999999999</v>
       </c>
       <c r="H15">
-        <v>0.24777199999999999</v>
+        <v>0.18365400000000001</v>
       </c>
       <c r="I15">
-        <v>0.24492700000000001</v>
+        <v>0.18440000000000001</v>
       </c>
       <c r="J15">
-        <v>0.24207999999999999</v>
+        <v>0.182059</v>
       </c>
       <c r="K15">
-        <v>0.24607699999999999</v>
+        <v>0.177284</v>
       </c>
       <c r="L15">
-        <v>0.24310200000000001</v>
+        <v>0.17541000000000001</v>
       </c>
       <c r="M15">
-        <v>0.25313000000000002</v>
+        <v>0.174175</v>
       </c>
       <c r="N15">
-        <v>0.25001400000000001</v>
+        <v>0.171569</v>
       </c>
       <c r="O15">
-        <v>0.25730900000000001</v>
+        <v>0.17444399999999999</v>
       </c>
       <c r="P15">
-        <v>0.26991399999999999</v>
+        <v>0.179282</v>
       </c>
       <c r="Q15">
-        <v>0.27440700000000001</v>
+        <v>0.18024399999999999</v>
       </c>
       <c r="R15">
-        <v>0.282806</v>
+        <v>0.18082799999999999</v>
       </c>
       <c r="S15">
-        <v>0.26670899999999997</v>
+        <v>0.177375</v>
       </c>
       <c r="T15">
-        <v>0.25264999999999999</v>
+        <v>0.17672399999999999</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.26573000000000002</v>
+        <v>0.18728900000000001</v>
       </c>
       <c r="B16">
-        <v>0.26573000000000002</v>
+        <v>0.184696</v>
       </c>
       <c r="C16">
-        <v>0.28814699999999999</v>
+        <v>0.187334</v>
       </c>
       <c r="D16">
-        <v>0.28547800000000001</v>
+        <v>0.18754799999999999</v>
       </c>
       <c r="E16">
-        <v>0.28414200000000001</v>
+        <v>0.189996</v>
       </c>
       <c r="F16">
-        <v>0.28013100000000002</v>
+        <v>0.190278</v>
       </c>
       <c r="G16">
-        <v>0.28013100000000002</v>
+        <v>0.19097900000000001</v>
       </c>
       <c r="H16">
-        <v>0.27477099999999999</v>
+        <v>0.187834</v>
       </c>
       <c r="I16">
-        <v>0.27074300000000001</v>
+        <v>0.184389</v>
       </c>
       <c r="J16">
-        <v>0.269399</v>
+        <v>0.18007300000000001</v>
       </c>
       <c r="K16">
-        <v>0.29115400000000002</v>
+        <v>0.175624</v>
       </c>
       <c r="L16">
-        <v>0.28821799999999997</v>
+        <v>0.17242399999999999</v>
       </c>
       <c r="M16">
-        <v>0.322351</v>
+        <v>0.17227700000000001</v>
       </c>
       <c r="N16">
-        <v>0.31745400000000001</v>
+        <v>0.170573</v>
       </c>
       <c r="O16">
-        <v>0.36419099999999999</v>
+        <v>0.17291899999999999</v>
       </c>
       <c r="P16">
-        <v>0.36045300000000002</v>
+        <v>0.177898</v>
       </c>
       <c r="Q16">
-        <v>0.43845800000000001</v>
+        <v>0.17699000000000001</v>
       </c>
       <c r="R16">
-        <v>0.717306</v>
+        <v>0.18001500000000001</v>
       </c>
       <c r="S16">
-        <v>0.69817499999999999</v>
+        <v>0.17394699999999999</v>
       </c>
       <c r="T16">
-        <v>0.64263300000000001</v>
+        <v>0.17563999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.187279</v>
+        <v>0.179759</v>
       </c>
       <c r="B17">
-        <v>0.187279</v>
+        <v>0.177532</v>
       </c>
       <c r="C17">
-        <v>0.207313</v>
+        <v>0.17838000000000001</v>
       </c>
       <c r="D17">
-        <v>0.20578399999999999</v>
+        <v>0.17905399999999999</v>
       </c>
       <c r="E17">
-        <v>0.20425499999999999</v>
+        <v>0.182807</v>
       </c>
       <c r="F17">
-        <v>0.20272399999999999</v>
+        <v>0.18444099999999999</v>
       </c>
       <c r="G17">
-        <v>0.20272399999999999</v>
+        <v>0.18620800000000001</v>
       </c>
       <c r="H17">
-        <v>0.199659</v>
+        <v>0.18343799999999999</v>
       </c>
       <c r="I17">
-        <v>0.195053</v>
+        <v>0.180006</v>
       </c>
       <c r="J17">
-        <v>0.19351499999999999</v>
+        <v>0.17605199999999999</v>
       </c>
       <c r="K17">
-        <v>0.216643</v>
+        <v>0.17189499999999999</v>
       </c>
       <c r="L17">
-        <v>0.216643</v>
+        <v>0.168818</v>
       </c>
       <c r="M17">
-        <v>0.25786500000000001</v>
+        <v>0.170154</v>
       </c>
       <c r="N17">
-        <v>0.253853</v>
+        <v>0.16639499999999999</v>
       </c>
       <c r="O17">
-        <v>0.32283600000000001</v>
+        <v>0.170651</v>
       </c>
       <c r="P17">
-        <v>0.32034699999999999</v>
+        <v>0.17978</v>
       </c>
       <c r="Q17">
-        <v>0.30529299999999998</v>
+        <v>0.175342</v>
       </c>
       <c r="R17">
-        <v>0.57596499999999995</v>
+        <v>0.17113600000000001</v>
       </c>
       <c r="S17">
-        <v>0.56107899999999999</v>
+        <v>0.16633200000000001</v>
       </c>
       <c r="T17">
-        <v>0.50049399999999999</v>
+        <v>0.17033699999999999</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.113483</v>
+        <v>0.18624199999999999</v>
       </c>
       <c r="B18">
-        <v>0.113483</v>
+        <v>0.18398600000000001</v>
       </c>
       <c r="C18">
-        <v>0.113483</v>
+        <v>0.18732699999999999</v>
       </c>
       <c r="D18">
-        <v>0.113483</v>
+        <v>0.19053200000000001</v>
       </c>
       <c r="E18">
-        <v>0.111651</v>
+        <v>0.193745</v>
       </c>
       <c r="F18">
-        <v>0.111651</v>
+        <v>0.192577</v>
       </c>
       <c r="G18">
-        <v>0.111651</v>
+        <v>0.19738600000000001</v>
       </c>
       <c r="H18">
-        <v>0.109816</v>
+        <v>0.19495199999999999</v>
       </c>
       <c r="I18">
-        <v>0.106142</v>
+        <v>0.191584</v>
       </c>
       <c r="J18">
-        <v>0.10430200000000001</v>
+        <v>0.187968</v>
       </c>
       <c r="K18">
-        <v>0.125917</v>
+        <v>0.183918</v>
       </c>
       <c r="L18">
-        <v>0.125917</v>
+        <v>0.18132100000000001</v>
       </c>
       <c r="M18">
-        <v>0.17094400000000001</v>
+        <v>0.17908299999999999</v>
       </c>
       <c r="N18">
-        <v>0.168076</v>
+        <v>0.175036</v>
       </c>
       <c r="O18">
-        <v>0.41955100000000001</v>
+        <v>0.17749899999999999</v>
       </c>
       <c r="P18">
-        <v>0.41549700000000001</v>
+        <v>0.187254</v>
       </c>
       <c r="Q18">
-        <v>0.39460400000000001</v>
+        <v>0.18277099999999999</v>
       </c>
       <c r="R18">
-        <v>0.37254199999999998</v>
+        <v>0.178782</v>
       </c>
       <c r="S18">
-        <v>0.358653</v>
+        <v>0.17389099999999999</v>
       </c>
       <c r="T18">
-        <v>0.31867200000000001</v>
+        <v>0.16769600000000001</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.201546</v>
+        <v>0.17171500000000001</v>
       </c>
       <c r="B19">
-        <v>0.201546</v>
+        <v>0.17013800000000001</v>
       </c>
       <c r="C19">
-        <v>0.201546</v>
+        <v>0.17508499999999999</v>
       </c>
       <c r="D19">
-        <v>0.201546</v>
+        <v>0.17980199999999999</v>
       </c>
       <c r="E19">
-        <v>0.192965</v>
+        <v>0.18471399999999999</v>
       </c>
       <c r="F19">
-        <v>0.192965</v>
+        <v>0.18355399999999999</v>
       </c>
       <c r="G19">
-        <v>0.192965</v>
+        <v>0.19031500000000001</v>
       </c>
       <c r="H19">
-        <v>0.192965</v>
+        <v>0.18837499999999999</v>
       </c>
       <c r="I19">
-        <v>0.192965</v>
+        <v>0.18482799999999999</v>
       </c>
       <c r="J19">
-        <v>0.192965</v>
+        <v>0.181808</v>
       </c>
       <c r="K19">
-        <v>0.192965</v>
+        <v>0.17860000000000001</v>
       </c>
       <c r="L19">
-        <v>0.192965</v>
+        <v>0.176562</v>
       </c>
       <c r="M19">
-        <v>0.192965</v>
+        <v>0.17458399999999999</v>
       </c>
       <c r="N19">
-        <v>0.18398500000000001</v>
+        <v>0.17075299999999999</v>
       </c>
       <c r="O19">
-        <v>0.18398500000000001</v>
+        <v>0.17577300000000001</v>
       </c>
       <c r="P19">
-        <v>0.18398500000000001</v>
+        <v>0.18207599999999999</v>
       </c>
       <c r="Q19">
-        <v>0.18398500000000001</v>
+        <v>0.17765600000000001</v>
       </c>
       <c r="R19">
-        <v>0.18398500000000001</v>
+        <v>0.17394100000000001</v>
       </c>
       <c r="S19">
-        <v>0.174544</v>
+        <v>0.16939199999999999</v>
       </c>
       <c r="T19">
-        <v>0.15393299999999999</v>
+        <v>0.16358900000000001</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0</v>
+        <v>0.16586300000000001</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.16420699999999999</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.17268</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.18195800000000001</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>0.19275900000000001</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>0.191223</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>0.206037</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>0.20393500000000001</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.20077300000000001</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>0.19775499999999999</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>0.19494500000000001</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>0.19353899999999999</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>0.19170899999999999</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>0.18771699999999999</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>0.204343</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>0.22800899999999999</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>0.22181999999999999</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>0.21857099999999999</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>0.21432799999999999</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>0.20757500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7007686C-ED5C-449E-AC15-964252A270A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C7C32-ECA6-462B-8C84-ED0F8BB462F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,1242 +349,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.16613900000000001</v>
+        <v>0.13115499999999999</v>
       </c>
       <c r="B1">
-        <v>0.16697100000000001</v>
+        <v>0.131435</v>
       </c>
       <c r="C1">
-        <v>0.16869999999999999</v>
+        <v>0.128385</v>
       </c>
       <c r="D1">
-        <v>0.168575</v>
+        <v>0.12818299999999999</v>
       </c>
       <c r="E1">
-        <v>0.17061000000000001</v>
+        <v>0.12562499999999999</v>
       </c>
       <c r="F1">
-        <v>0.170982</v>
+        <v>0.12212199999999999</v>
       </c>
       <c r="G1">
-        <v>0.17006599999999999</v>
+        <v>0.118257</v>
       </c>
       <c r="H1">
-        <v>0.17006399999999999</v>
+        <v>0.117072</v>
       </c>
       <c r="I1">
-        <v>0.17069999999999999</v>
+        <v>0.11175499999999999</v>
       </c>
       <c r="J1">
-        <v>0.168235</v>
+        <v>0.106253</v>
       </c>
       <c r="K1">
-        <v>0.16919799999999999</v>
+        <v>0.101923</v>
       </c>
       <c r="L1">
-        <v>0.16574800000000001</v>
+        <v>9.1844999999999996E-2</v>
       </c>
       <c r="M1">
-        <v>0.16589899999999999</v>
+        <v>8.4185999999999997E-2</v>
       </c>
       <c r="N1">
-        <v>0.16335</v>
+        <v>7.7727000000000004E-2</v>
       </c>
       <c r="O1">
-        <v>0.16105700000000001</v>
+        <v>7.3246000000000006E-2</v>
       </c>
       <c r="P1">
-        <v>0.16069</v>
+        <v>6.6646999999999998E-2</v>
       </c>
       <c r="Q1">
-        <v>0.16025</v>
+        <v>5.1582000000000003E-2</v>
       </c>
       <c r="R1">
-        <v>0.16017300000000001</v>
+        <v>3.0883000000000001E-2</v>
       </c>
       <c r="S1">
-        <v>0.16069</v>
+        <v>0.124391</v>
       </c>
       <c r="T1">
-        <v>0.16029299999999999</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.16758999999999999</v>
+        <v>0.13359699999999999</v>
       </c>
       <c r="B2">
-        <v>0.16825200000000001</v>
+        <v>0.13400599999999999</v>
       </c>
       <c r="C2">
-        <v>0.17018800000000001</v>
+        <v>0.13126699999999999</v>
       </c>
       <c r="D2">
-        <v>0.16963400000000001</v>
+        <v>0.13061300000000001</v>
       </c>
       <c r="E2">
-        <v>0.171518</v>
+        <v>0.12659400000000001</v>
       </c>
       <c r="F2">
-        <v>0.17177799999999999</v>
+        <v>0.12256</v>
       </c>
       <c r="G2">
-        <v>0.17099700000000001</v>
+        <v>0.11859699999999999</v>
       </c>
       <c r="H2">
-        <v>0.170738</v>
+        <v>0.116566</v>
       </c>
       <c r="I2">
-        <v>0.17144699999999999</v>
+        <v>0.111931</v>
       </c>
       <c r="J2">
-        <v>0.16910800000000001</v>
+        <v>0.107139</v>
       </c>
       <c r="K2">
-        <v>0.17041300000000001</v>
+        <v>0.102336</v>
       </c>
       <c r="L2">
-        <v>0.167434</v>
+        <v>9.2462000000000003E-2</v>
       </c>
       <c r="M2">
-        <v>0.16788500000000001</v>
+        <v>8.5751999999999995E-2</v>
       </c>
       <c r="N2">
-        <v>0.16583899999999999</v>
+        <v>7.8516000000000002E-2</v>
       </c>
       <c r="O2">
-        <v>0.163022</v>
+        <v>7.2931999999999997E-2</v>
       </c>
       <c r="P2">
-        <v>0.162185</v>
+        <v>6.5568000000000001E-2</v>
       </c>
       <c r="Q2">
-        <v>0.161438</v>
+        <v>5.1156E-2</v>
       </c>
       <c r="R2">
-        <v>0.16188900000000001</v>
+        <v>3.0733E-2</v>
       </c>
       <c r="S2">
-        <v>0.16220999999999999</v>
+        <v>0.12300800000000001</v>
       </c>
       <c r="T2">
-        <v>0.16103100000000001</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.16969300000000001</v>
+        <v>0.13300899999999999</v>
       </c>
       <c r="B3">
-        <v>0.17027700000000001</v>
+        <v>0.133158</v>
       </c>
       <c r="C3">
-        <v>0.17135800000000001</v>
+        <v>0.13031200000000001</v>
       </c>
       <c r="D3">
-        <v>0.17065</v>
+        <v>0.12970400000000001</v>
       </c>
       <c r="E3">
-        <v>0.17205599999999999</v>
+        <v>0.12612100000000001</v>
       </c>
       <c r="F3">
-        <v>0.17266200000000001</v>
+        <v>0.122174</v>
       </c>
       <c r="G3">
-        <v>0.17147899999999999</v>
+        <v>0.117077</v>
       </c>
       <c r="H3">
-        <v>0.171349</v>
+        <v>0.115769</v>
       </c>
       <c r="I3">
-        <v>0.17211299999999999</v>
+        <v>0.111887</v>
       </c>
       <c r="J3">
-        <v>0.17015</v>
+        <v>0.106965</v>
       </c>
       <c r="K3">
-        <v>0.171177</v>
+        <v>0.102344</v>
       </c>
       <c r="L3">
-        <v>0.16894899999999999</v>
+        <v>9.2979999999999993E-2</v>
       </c>
       <c r="M3">
-        <v>0.169041</v>
+        <v>8.5539000000000004E-2</v>
       </c>
       <c r="N3">
-        <v>0.16666600000000001</v>
+        <v>7.7709E-2</v>
       </c>
       <c r="O3">
-        <v>0.164746</v>
+        <v>7.3654999999999998E-2</v>
       </c>
       <c r="P3">
-        <v>0.163691</v>
+        <v>6.8163000000000001E-2</v>
       </c>
       <c r="Q3">
-        <v>0.16264400000000001</v>
+        <v>5.2863E-2</v>
       </c>
       <c r="R3">
-        <v>0.161887</v>
+        <v>3.4133999999999998E-2</v>
       </c>
       <c r="S3">
-        <v>0.16215399999999999</v>
+        <v>0.12300800000000001</v>
       </c>
       <c r="T3">
-        <v>0.160635</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.17050799999999999</v>
+        <v>0.132051</v>
       </c>
       <c r="B4">
-        <v>0.171185</v>
+        <v>0.13305900000000001</v>
       </c>
       <c r="C4">
-        <v>0.17268800000000001</v>
+        <v>0.13018199999999999</v>
       </c>
       <c r="D4">
-        <v>0.17192499999999999</v>
+        <v>0.129579</v>
       </c>
       <c r="E4">
-        <v>0.17316400000000001</v>
+        <v>0.12507299999999999</v>
       </c>
       <c r="F4">
-        <v>0.17407900000000001</v>
+        <v>0.120991</v>
       </c>
       <c r="G4">
-        <v>0.17245099999999999</v>
+        <v>0.11633300000000001</v>
       </c>
       <c r="H4">
-        <v>0.17272999999999999</v>
+        <v>0.113862</v>
       </c>
       <c r="I4">
-        <v>0.17305699999999999</v>
+        <v>0.110753</v>
       </c>
       <c r="J4">
-        <v>0.171318</v>
+        <v>0.10556699999999999</v>
       </c>
       <c r="K4">
-        <v>0.17264199999999999</v>
+        <v>0.101036</v>
       </c>
       <c r="L4">
-        <v>0.170933</v>
+        <v>9.1856999999999994E-2</v>
       </c>
       <c r="M4">
-        <v>0.170817</v>
+        <v>8.5481000000000001E-2</v>
       </c>
       <c r="N4">
-        <v>0.167878</v>
+        <v>7.5638999999999998E-2</v>
       </c>
       <c r="O4">
-        <v>0.16616600000000001</v>
+        <v>7.1233000000000005E-2</v>
       </c>
       <c r="P4">
-        <v>0.164522</v>
+        <v>6.6725000000000007E-2</v>
       </c>
       <c r="Q4">
-        <v>0.16378000000000001</v>
+        <v>5.2047000000000003E-2</v>
       </c>
       <c r="R4">
-        <v>0.16406599999999999</v>
+        <v>3.3626999999999997E-2</v>
       </c>
       <c r="S4">
-        <v>0.16375400000000001</v>
+        <v>0.121598</v>
       </c>
       <c r="T4">
-        <v>0.162911</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.170323</v>
+        <v>0.128244</v>
       </c>
       <c r="B5">
-        <v>0.17121</v>
+        <v>0.12921199999999999</v>
       </c>
       <c r="C5">
-        <v>0.17286499999999999</v>
+        <v>0.12692400000000001</v>
       </c>
       <c r="D5">
-        <v>0.17263000000000001</v>
+        <v>0.12554799999999999</v>
       </c>
       <c r="E5">
-        <v>0.17382300000000001</v>
+        <v>0.12179</v>
       </c>
       <c r="F5">
-        <v>0.17457900000000001</v>
+        <v>0.11823699999999999</v>
       </c>
       <c r="G5">
-        <v>0.17339199999999999</v>
+        <v>0.113564</v>
       </c>
       <c r="H5">
-        <v>0.17435700000000001</v>
+        <v>0.11102099999999999</v>
       </c>
       <c r="I5">
-        <v>0.174569</v>
+        <v>0.10851</v>
       </c>
       <c r="J5">
-        <v>0.17259099999999999</v>
+        <v>0.10312200000000001</v>
       </c>
       <c r="K5">
-        <v>0.172823</v>
+        <v>9.8204E-2</v>
       </c>
       <c r="L5">
-        <v>0.17149900000000001</v>
+        <v>8.9446999999999999E-2</v>
       </c>
       <c r="M5">
-        <v>0.17060700000000001</v>
+        <v>8.3731E-2</v>
       </c>
       <c r="N5">
-        <v>0.16708799999999999</v>
+        <v>7.4958999999999998E-2</v>
       </c>
       <c r="O5">
-        <v>0.16547400000000001</v>
+        <v>7.2523000000000004E-2</v>
       </c>
       <c r="P5">
-        <v>0.16401299999999999</v>
+        <v>6.9056999999999993E-2</v>
       </c>
       <c r="Q5">
-        <v>0.16380900000000001</v>
+        <v>5.0244999999999998E-2</v>
       </c>
       <c r="R5">
-        <v>0.16356499999999999</v>
+        <v>3.2443E-2</v>
       </c>
       <c r="S5">
-        <v>0.16259699999999999</v>
+        <v>0.118731</v>
       </c>
       <c r="T5">
-        <v>0.161886</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.17088999999999999</v>
+        <v>0.12686700000000001</v>
       </c>
       <c r="B6">
-        <v>0.17219899999999999</v>
+        <v>0.12735099999999999</v>
       </c>
       <c r="C6">
-        <v>0.174403</v>
+        <v>0.12546299999999999</v>
       </c>
       <c r="D6">
-        <v>0.174182</v>
+        <v>0.124851</v>
       </c>
       <c r="E6">
-        <v>0.174898</v>
+        <v>0.12078999999999999</v>
       </c>
       <c r="F6">
-        <v>0.175983</v>
+        <v>0.11649</v>
       </c>
       <c r="G6">
-        <v>0.174679</v>
+        <v>0.111665</v>
       </c>
       <c r="H6">
-        <v>0.175509</v>
+        <v>0.110192</v>
       </c>
       <c r="I6">
-        <v>0.17593200000000001</v>
+        <v>0.10680000000000001</v>
       </c>
       <c r="J6">
-        <v>0.17452599999999999</v>
+        <v>0.10179299999999999</v>
       </c>
       <c r="K6">
-        <v>0.17489499999999999</v>
+        <v>9.7928000000000001E-2</v>
       </c>
       <c r="L6">
-        <v>0.17302600000000001</v>
+        <v>9.0295E-2</v>
       </c>
       <c r="M6">
-        <v>0.17107700000000001</v>
+        <v>8.2007999999999998E-2</v>
       </c>
       <c r="N6">
-        <v>0.167656</v>
+        <v>7.3007000000000002E-2</v>
       </c>
       <c r="O6">
-        <v>0.166376</v>
+        <v>7.0616999999999999E-2</v>
       </c>
       <c r="P6">
-        <v>0.16428300000000001</v>
+        <v>6.9291000000000005E-2</v>
       </c>
       <c r="Q6">
-        <v>0.16458600000000001</v>
+        <v>5.1804000000000003E-2</v>
       </c>
       <c r="R6">
-        <v>0.16480400000000001</v>
+        <v>3.1766000000000003E-2</v>
       </c>
       <c r="S6">
-        <v>0.16352800000000001</v>
+        <v>0.118731</v>
       </c>
       <c r="T6">
-        <v>0.16322600000000001</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.173017</v>
+        <v>0.124489</v>
       </c>
       <c r="B7">
-        <v>0.17537800000000001</v>
+        <v>0.12589900000000001</v>
       </c>
       <c r="C7">
-        <v>0.177428</v>
+        <v>0.123085</v>
       </c>
       <c r="D7">
-        <v>0.177343</v>
+        <v>0.121654</v>
       </c>
       <c r="E7">
-        <v>0.17758199999999999</v>
+        <v>0.118146</v>
       </c>
       <c r="F7">
-        <v>0.17916899999999999</v>
+        <v>0.11452900000000001</v>
       </c>
       <c r="G7">
-        <v>0.17838799999999999</v>
+        <v>0.10942499999999999</v>
       </c>
       <c r="H7">
-        <v>0.178956</v>
+        <v>0.108181</v>
       </c>
       <c r="I7">
-        <v>0.18049499999999999</v>
+        <v>0.104947</v>
       </c>
       <c r="J7">
-        <v>0.18010200000000001</v>
+        <v>0.100619</v>
       </c>
       <c r="K7">
-        <v>0.18088599999999999</v>
+        <v>9.4602000000000006E-2</v>
       </c>
       <c r="L7">
-        <v>0.17940900000000001</v>
+        <v>8.6772000000000002E-2</v>
       </c>
       <c r="M7">
-        <v>0.177344</v>
+        <v>7.8338000000000005E-2</v>
       </c>
       <c r="N7">
-        <v>0.17346700000000001</v>
+        <v>7.0419999999999996E-2</v>
       </c>
       <c r="O7">
-        <v>0.17286899999999999</v>
+        <v>6.7418000000000006E-2</v>
       </c>
       <c r="P7">
-        <v>0.170567</v>
+        <v>6.4814999999999998E-2</v>
       </c>
       <c r="Q7">
-        <v>0.17205899999999999</v>
+        <v>4.8253999999999998E-2</v>
       </c>
       <c r="R7">
-        <v>0.17283799999999999</v>
+        <v>3.0242999999999999E-2</v>
       </c>
       <c r="S7">
-        <v>0.17169300000000001</v>
+        <v>0.117282</v>
       </c>
       <c r="T7">
-        <v>0.17230500000000001</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.173987</v>
+        <v>0.125578</v>
       </c>
       <c r="B8">
-        <v>0.17585600000000001</v>
+        <v>0.12733800000000001</v>
       </c>
       <c r="C8">
-        <v>0.17674400000000001</v>
+        <v>0.12508</v>
       </c>
       <c r="D8">
-        <v>0.176812</v>
+        <v>0.12435499999999999</v>
       </c>
       <c r="E8">
-        <v>0.17693</v>
+        <v>0.121572</v>
       </c>
       <c r="F8">
-        <v>0.178759</v>
+        <v>0.11914</v>
       </c>
       <c r="G8">
-        <v>0.17827799999999999</v>
+        <v>0.114413</v>
       </c>
       <c r="H8">
-        <v>0.17929899999999999</v>
+        <v>0.11372699999999999</v>
       </c>
       <c r="I8">
-        <v>0.18113299999999999</v>
+        <v>0.11093500000000001</v>
       </c>
       <c r="J8">
-        <v>0.18168000000000001</v>
+        <v>0.10561</v>
       </c>
       <c r="K8">
-        <v>0.182308</v>
+        <v>9.9252000000000007E-2</v>
       </c>
       <c r="L8">
-        <v>0.180481</v>
+        <v>9.1026999999999997E-2</v>
       </c>
       <c r="M8">
-        <v>0.178674</v>
+        <v>8.2267999999999994E-2</v>
       </c>
       <c r="N8">
-        <v>0.17494399999999999</v>
+        <v>7.7380000000000004E-2</v>
       </c>
       <c r="O8">
-        <v>0.17402100000000001</v>
+        <v>7.3574000000000001E-2</v>
       </c>
       <c r="P8">
-        <v>0.17177300000000001</v>
+        <v>6.7368999999999998E-2</v>
       </c>
       <c r="Q8">
-        <v>0.17138200000000001</v>
+        <v>4.9201000000000002E-2</v>
       </c>
       <c r="R8">
-        <v>0.17211000000000001</v>
+        <v>3.3812000000000002E-2</v>
       </c>
       <c r="S8">
-        <v>0.17042399999999999</v>
+        <v>0.115802</v>
       </c>
       <c r="T8">
-        <v>0.17247799999999999</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.17402000000000001</v>
+        <v>0.123111</v>
       </c>
       <c r="B9">
-        <v>0.175451</v>
+        <v>0.12506600000000001</v>
       </c>
       <c r="C9">
-        <v>0.17643500000000001</v>
+        <v>0.12230199999999999</v>
       </c>
       <c r="D9">
-        <v>0.17701800000000001</v>
+        <v>0.122723</v>
       </c>
       <c r="E9">
-        <v>0.17657400000000001</v>
+        <v>0.120741</v>
       </c>
       <c r="F9">
-        <v>0.177729</v>
+        <v>0.118173</v>
       </c>
       <c r="G9">
-        <v>0.17790500000000001</v>
+        <v>0.11436300000000001</v>
       </c>
       <c r="H9">
-        <v>0.17885200000000001</v>
+        <v>0.116381</v>
       </c>
       <c r="I9">
-        <v>0.179753</v>
+        <v>0.111639</v>
       </c>
       <c r="J9">
-        <v>0.18092900000000001</v>
+        <v>0.10571700000000001</v>
       </c>
       <c r="K9">
-        <v>0.182171</v>
+        <v>0.100596</v>
       </c>
       <c r="L9">
-        <v>0.18035100000000001</v>
+        <v>9.2147000000000007E-2</v>
       </c>
       <c r="M9">
-        <v>0.17882100000000001</v>
+        <v>8.2679000000000002E-2</v>
       </c>
       <c r="N9">
-        <v>0.17501700000000001</v>
+        <v>7.8331999999999999E-2</v>
       </c>
       <c r="O9">
-        <v>0.174318</v>
+        <v>7.8577999999999995E-2</v>
       </c>
       <c r="P9">
-        <v>0.17253599999999999</v>
+        <v>6.8862000000000007E-2</v>
       </c>
       <c r="Q9">
-        <v>0.17136000000000001</v>
+        <v>4.9895000000000002E-2</v>
       </c>
       <c r="R9">
-        <v>0.174567</v>
+        <v>3.2057000000000002E-2</v>
       </c>
       <c r="S9">
-        <v>0.17179</v>
+        <v>0.114302</v>
       </c>
       <c r="T9">
-        <v>0.172014</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.181649</v>
+        <v>0.125776</v>
       </c>
       <c r="B10">
-        <v>0.18212200000000001</v>
+        <v>0.128166</v>
       </c>
       <c r="C10">
-        <v>0.18273600000000001</v>
+        <v>0.126109</v>
       </c>
       <c r="D10">
-        <v>0.18296799999999999</v>
+        <v>0.128723</v>
       </c>
       <c r="E10">
-        <v>0.18359600000000001</v>
+        <v>0.12826899999999999</v>
       </c>
       <c r="F10">
-        <v>0.18496199999999999</v>
+        <v>0.12345299999999999</v>
       </c>
       <c r="G10">
-        <v>0.183203</v>
+        <v>0.11906700000000001</v>
       </c>
       <c r="H10">
-        <v>0.18354200000000001</v>
+        <v>0.11640300000000001</v>
       </c>
       <c r="I10">
-        <v>0.184445</v>
+        <v>0.112859</v>
       </c>
       <c r="J10">
-        <v>0.185616</v>
+        <v>0.105989</v>
       </c>
       <c r="K10">
-        <v>0.18601699999999999</v>
+        <v>0.100504</v>
       </c>
       <c r="L10">
-        <v>0.18341299999999999</v>
+        <v>9.3276999999999999E-2</v>
       </c>
       <c r="M10">
-        <v>0.180811</v>
+        <v>8.5202E-2</v>
       </c>
       <c r="N10">
-        <v>0.17711499999999999</v>
+        <v>8.4375000000000006E-2</v>
       </c>
       <c r="O10">
-        <v>0.175812</v>
+        <v>8.0597000000000002E-2</v>
       </c>
       <c r="P10">
-        <v>0.175286</v>
+        <v>7.3410000000000003E-2</v>
       </c>
       <c r="Q10">
-        <v>0.174261</v>
+        <v>5.6756000000000001E-2</v>
       </c>
       <c r="R10">
-        <v>0.17754600000000001</v>
+        <v>3.7429999999999998E-2</v>
       </c>
       <c r="S10">
-        <v>0.17655899999999999</v>
+        <v>0.114302</v>
       </c>
       <c r="T10">
-        <v>0.17641799999999999</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.184002</v>
+        <v>0.111239</v>
       </c>
       <c r="B11">
-        <v>0.18321100000000001</v>
+        <v>0.11292000000000001</v>
       </c>
       <c r="C11">
-        <v>0.18412100000000001</v>
+        <v>0.111612</v>
       </c>
       <c r="D11">
-        <v>0.18310699999999999</v>
+        <v>0.113023</v>
       </c>
       <c r="E11">
-        <v>0.183478</v>
+        <v>0.111497</v>
       </c>
       <c r="F11">
-        <v>0.18450900000000001</v>
+        <v>0.107569</v>
       </c>
       <c r="G11">
-        <v>0.18401999999999999</v>
+        <v>0.10391</v>
       </c>
       <c r="H11">
-        <v>0.18328900000000001</v>
+        <v>0.10288</v>
       </c>
       <c r="I11">
-        <v>0.184337</v>
+        <v>9.9833000000000005E-2</v>
       </c>
       <c r="J11">
-        <v>0.18595800000000001</v>
+        <v>9.3778E-2</v>
       </c>
       <c r="K11">
-        <v>0.18553900000000001</v>
+        <v>9.0225E-2</v>
       </c>
       <c r="L11">
-        <v>0.18357699999999999</v>
+        <v>8.4278000000000006E-2</v>
       </c>
       <c r="M11">
-        <v>0.18187800000000001</v>
+        <v>7.7385999999999996E-2</v>
       </c>
       <c r="N11">
-        <v>0.17769399999999999</v>
+        <v>7.8395000000000006E-2</v>
       </c>
       <c r="O11">
-        <v>0.176174</v>
+        <v>7.2525000000000006E-2</v>
       </c>
       <c r="P11">
-        <v>0.177288</v>
+        <v>6.6243999999999997E-2</v>
       </c>
       <c r="Q11">
-        <v>0.17484</v>
+        <v>5.2431999999999999E-2</v>
       </c>
       <c r="R11">
-        <v>0.17602799999999999</v>
+        <v>3.4826000000000003E-2</v>
       </c>
       <c r="S11">
-        <v>0.17500299999999999</v>
+        <v>0.111261</v>
       </c>
       <c r="T11">
-        <v>0.174789</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.17954100000000001</v>
+        <v>0.105723</v>
       </c>
       <c r="B12">
-        <v>0.178505</v>
+        <v>0.106825</v>
       </c>
       <c r="C12">
-        <v>0.17901400000000001</v>
+        <v>0.10699</v>
       </c>
       <c r="D12">
-        <v>0.17849100000000001</v>
+        <v>0.108041</v>
       </c>
       <c r="E12">
-        <v>0.179313</v>
+        <v>0.10520400000000001</v>
       </c>
       <c r="F12">
-        <v>0.181169</v>
+        <v>0.102052</v>
       </c>
       <c r="G12">
-        <v>0.18038899999999999</v>
+        <v>9.9223000000000006E-2</v>
       </c>
       <c r="H12">
-        <v>0.18053900000000001</v>
+        <v>9.5314999999999997E-2</v>
       </c>
       <c r="I12">
-        <v>0.181312</v>
+        <v>9.3174000000000007E-2</v>
       </c>
       <c r="J12">
-        <v>0.183055</v>
+        <v>8.8363999999999998E-2</v>
       </c>
       <c r="K12">
-        <v>0.181279</v>
+        <v>8.4533999999999998E-2</v>
       </c>
       <c r="L12">
-        <v>0.178702</v>
+        <v>8.0810999999999994E-2</v>
       </c>
       <c r="M12">
-        <v>0.177841</v>
+        <v>7.2502999999999998E-2</v>
       </c>
       <c r="N12">
-        <v>0.17349500000000001</v>
+        <v>7.7169000000000001E-2</v>
       </c>
       <c r="O12">
-        <v>0.172623</v>
+        <v>7.0607000000000003E-2</v>
       </c>
       <c r="P12">
-        <v>0.173707</v>
+        <v>6.9348999999999994E-2</v>
       </c>
       <c r="Q12">
-        <v>0.170823</v>
+        <v>5.1445999999999999E-2</v>
       </c>
       <c r="R12">
-        <v>0.17338999999999999</v>
+        <v>3.0513999999999999E-2</v>
       </c>
       <c r="S12">
-        <v>0.17408799999999999</v>
+        <v>0.106541</v>
       </c>
       <c r="T12">
-        <v>0.17411299999999999</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.18137300000000001</v>
+        <v>9.5824999999999994E-2</v>
       </c>
       <c r="B13">
-        <v>0.17884800000000001</v>
+        <v>9.5739000000000005E-2</v>
       </c>
       <c r="C13">
-        <v>0.17922299999999999</v>
+        <v>9.4843999999999998E-2</v>
       </c>
       <c r="D13">
-        <v>0.179118</v>
+        <v>9.4343999999999997E-2</v>
       </c>
       <c r="E13">
-        <v>0.18026800000000001</v>
+        <v>9.2071E-2</v>
       </c>
       <c r="F13">
-        <v>0.18214900000000001</v>
+        <v>9.0333999999999998E-2</v>
       </c>
       <c r="G13">
-        <v>0.18082999999999999</v>
+        <v>8.8419999999999999E-2</v>
       </c>
       <c r="H13">
-        <v>0.18051600000000001</v>
+        <v>8.5415000000000005E-2</v>
       </c>
       <c r="I13">
-        <v>0.182647</v>
+        <v>8.5142999999999996E-2</v>
       </c>
       <c r="J13">
-        <v>0.18069199999999999</v>
+        <v>8.1714999999999996E-2</v>
       </c>
       <c r="K13">
-        <v>0.179754</v>
+        <v>8.0625000000000002E-2</v>
       </c>
       <c r="L13">
-        <v>0.177759</v>
+        <v>7.6680999999999999E-2</v>
       </c>
       <c r="M13">
-        <v>0.175068</v>
+        <v>7.1443999999999994E-2</v>
       </c>
       <c r="N13">
-        <v>0.170982</v>
+        <v>7.3355000000000004E-2</v>
       </c>
       <c r="O13">
-        <v>0.17106199999999999</v>
+        <v>7.0445999999999995E-2</v>
       </c>
       <c r="P13">
-        <v>0.17238899999999999</v>
+        <v>6.8903000000000006E-2</v>
       </c>
       <c r="Q13">
-        <v>0.17019599999999999</v>
+        <v>4.4420000000000001E-2</v>
       </c>
       <c r="R13">
-        <v>0.17131199999999999</v>
+        <v>2.6641999999999999E-2</v>
       </c>
       <c r="S13">
-        <v>0.17168800000000001</v>
+        <v>9.9890000000000007E-2</v>
       </c>
       <c r="T13">
-        <v>0.168985</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.17490800000000001</v>
+        <v>8.1816E-2</v>
       </c>
       <c r="B14">
-        <v>0.17253399999999999</v>
+        <v>8.2632999999999998E-2</v>
       </c>
       <c r="C14">
-        <v>0.17350599999999999</v>
+        <v>8.0627000000000004E-2</v>
       </c>
       <c r="D14">
-        <v>0.174209</v>
+        <v>8.0972000000000002E-2</v>
       </c>
       <c r="E14">
-        <v>0.176175</v>
+        <v>7.9841999999999996E-2</v>
       </c>
       <c r="F14">
-        <v>0.177566</v>
+        <v>7.8989000000000004E-2</v>
       </c>
       <c r="G14">
-        <v>0.17662700000000001</v>
+        <v>7.8421000000000005E-2</v>
       </c>
       <c r="H14">
-        <v>0.177207</v>
+        <v>7.6854000000000006E-2</v>
       </c>
       <c r="I14">
-        <v>0.17944199999999999</v>
+        <v>7.5920000000000001E-2</v>
       </c>
       <c r="J14">
-        <v>0.176539</v>
+        <v>7.3782E-2</v>
       </c>
       <c r="K14">
-        <v>0.17192099999999999</v>
+        <v>7.5133000000000005E-2</v>
       </c>
       <c r="L14">
-        <v>0.168933</v>
+        <v>6.8900000000000003E-2</v>
       </c>
       <c r="M14">
-        <v>0.166853</v>
+        <v>6.5135999999999999E-2</v>
       </c>
       <c r="N14">
-        <v>0.16314899999999999</v>
+        <v>6.7128999999999994E-2</v>
       </c>
       <c r="O14">
-        <v>0.164016</v>
+        <v>6.2267999999999997E-2</v>
       </c>
       <c r="P14">
-        <v>0.167217</v>
+        <v>6.5265000000000004E-2</v>
       </c>
       <c r="Q14">
-        <v>0.16601199999999999</v>
+        <v>4.2224999999999999E-2</v>
       </c>
       <c r="R14">
-        <v>0.16456399999999999</v>
+        <v>2.1894E-2</v>
       </c>
       <c r="S14">
-        <v>0.164052</v>
+        <v>9.6394999999999995E-2</v>
       </c>
       <c r="T14">
-        <v>0.163077</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.18417700000000001</v>
+        <v>7.3993000000000003E-2</v>
       </c>
       <c r="B15">
-        <v>0.181672</v>
+        <v>7.2764999999999996E-2</v>
       </c>
       <c r="C15">
-        <v>0.18427299999999999</v>
+        <v>7.1438000000000001E-2</v>
       </c>
       <c r="D15">
-        <v>0.183507</v>
+        <v>6.9777000000000006E-2</v>
       </c>
       <c r="E15">
-        <v>0.18418899999999999</v>
+        <v>6.8769999999999998E-2</v>
       </c>
       <c r="F15">
-        <v>0.18568499999999999</v>
+        <v>6.9995000000000002E-2</v>
       </c>
       <c r="G15">
-        <v>0.18541199999999999</v>
+        <v>7.0982000000000003E-2</v>
       </c>
       <c r="H15">
-        <v>0.18365400000000001</v>
+        <v>7.1539000000000005E-2</v>
       </c>
       <c r="I15">
-        <v>0.18440000000000001</v>
+        <v>7.4985999999999997E-2</v>
       </c>
       <c r="J15">
-        <v>0.182059</v>
+        <v>7.7812999999999993E-2</v>
       </c>
       <c r="K15">
-        <v>0.177284</v>
+        <v>8.3415000000000003E-2</v>
       </c>
       <c r="L15">
-        <v>0.17541000000000001</v>
+        <v>7.6966999999999994E-2</v>
       </c>
       <c r="M15">
-        <v>0.174175</v>
+        <v>6.8529999999999994E-2</v>
       </c>
       <c r="N15">
-        <v>0.171569</v>
+        <v>0.102437</v>
       </c>
       <c r="O15">
-        <v>0.17444399999999999</v>
+        <v>8.7326000000000001E-2</v>
       </c>
       <c r="P15">
-        <v>0.179282</v>
+        <v>6.5648999999999999E-2</v>
       </c>
       <c r="Q15">
-        <v>0.18024399999999999</v>
+        <v>4.4255999999999997E-2</v>
       </c>
       <c r="R15">
-        <v>0.18082799999999999</v>
+        <v>2.5762E-2</v>
       </c>
       <c r="S15">
-        <v>0.177375</v>
+        <v>8.7028999999999995E-2</v>
       </c>
       <c r="T15">
-        <v>0.17672399999999999</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.18728900000000001</v>
+        <v>5.3775999999999997E-2</v>
       </c>
       <c r="B16">
-        <v>0.184696</v>
+        <v>5.2877E-2</v>
       </c>
       <c r="C16">
-        <v>0.187334</v>
+        <v>5.1847999999999998E-2</v>
       </c>
       <c r="D16">
-        <v>0.18754799999999999</v>
+        <v>5.0516999999999999E-2</v>
       </c>
       <c r="E16">
-        <v>0.189996</v>
+        <v>4.9764999999999997E-2</v>
       </c>
       <c r="F16">
-        <v>0.190278</v>
+        <v>4.8411000000000003E-2</v>
       </c>
       <c r="G16">
-        <v>0.19097900000000001</v>
+        <v>5.1451999999999998E-2</v>
       </c>
       <c r="H16">
-        <v>0.187834</v>
+        <v>4.7876000000000002E-2</v>
       </c>
       <c r="I16">
-        <v>0.184389</v>
+        <v>5.3720999999999998E-2</v>
       </c>
       <c r="J16">
-        <v>0.18007300000000001</v>
+        <v>5.1158000000000002E-2</v>
       </c>
       <c r="K16">
-        <v>0.175624</v>
+        <v>4.9424999999999997E-2</v>
       </c>
       <c r="L16">
-        <v>0.17242399999999999</v>
+        <v>4.7329999999999997E-2</v>
       </c>
       <c r="M16">
-        <v>0.17227700000000001</v>
+        <v>4.3268000000000001E-2</v>
       </c>
       <c r="N16">
-        <v>0.170573</v>
+        <v>6.5139000000000002E-2</v>
       </c>
       <c r="O16">
-        <v>0.17291899999999999</v>
+        <v>5.6957000000000001E-2</v>
       </c>
       <c r="P16">
-        <v>0.177898</v>
+        <v>4.1867000000000001E-2</v>
       </c>
       <c r="Q16">
-        <v>0.17699000000000001</v>
+        <v>2.7297999999999999E-2</v>
       </c>
       <c r="R16">
-        <v>0.18001500000000001</v>
+        <v>1.6379000000000001E-2</v>
       </c>
       <c r="S16">
-        <v>0.17394699999999999</v>
+        <v>7.6492000000000004E-2</v>
       </c>
       <c r="T16">
-        <v>0.17563999999999999</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.179759</v>
+        <v>3.1064000000000001E-2</v>
       </c>
       <c r="B17">
-        <v>0.177532</v>
+        <v>3.0588000000000001E-2</v>
       </c>
       <c r="C17">
-        <v>0.17838000000000001</v>
+        <v>2.9909000000000002E-2</v>
       </c>
       <c r="D17">
-        <v>0.17905399999999999</v>
+        <v>2.8514000000000001E-2</v>
       </c>
       <c r="E17">
-        <v>0.182807</v>
+        <v>2.8514000000000001E-2</v>
       </c>
       <c r="F17">
-        <v>0.18444099999999999</v>
+        <v>2.8514000000000001E-2</v>
       </c>
       <c r="G17">
-        <v>0.18620800000000001</v>
+        <v>3.9595999999999999E-2</v>
       </c>
       <c r="H17">
-        <v>0.18343799999999999</v>
+        <v>3.8935999999999998E-2</v>
       </c>
       <c r="I17">
-        <v>0.180006</v>
+        <v>0.19489500000000001</v>
       </c>
       <c r="J17">
-        <v>0.17605199999999999</v>
+        <v>0.18953100000000001</v>
       </c>
       <c r="K17">
-        <v>0.17189499999999999</v>
+        <v>0.184946</v>
       </c>
       <c r="L17">
-        <v>0.168818</v>
+        <v>0.18401100000000001</v>
       </c>
       <c r="M17">
-        <v>0.170154</v>
+        <v>0.17341899999999999</v>
       </c>
       <c r="N17">
-        <v>0.16639499999999999</v>
+        <v>0.16735900000000001</v>
       </c>
       <c r="O17">
-        <v>0.170651</v>
+        <v>0.157858</v>
       </c>
       <c r="P17">
-        <v>0.17978</v>
+        <v>0.13920099999999999</v>
       </c>
       <c r="Q17">
-        <v>0.175342</v>
+        <v>0.114826</v>
       </c>
       <c r="R17">
-        <v>0.17113600000000001</v>
+        <v>9.0917999999999999E-2</v>
       </c>
       <c r="S17">
-        <v>0.16633200000000001</v>
+        <v>5.8686000000000002E-2</v>
       </c>
       <c r="T17">
-        <v>0.17033699999999999</v>
+        <v>1.8574E-2</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.18624199999999999</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="B18">
-        <v>0.18398600000000001</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="C18">
-        <v>0.18732699999999999</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="D18">
-        <v>0.19053200000000001</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="E18">
-        <v>0.193745</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="F18">
-        <v>0.192577</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="G18">
-        <v>0.19738600000000001</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="H18">
-        <v>0.19495199999999999</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="I18">
-        <v>0.191584</v>
+        <v>9.1180999999999998E-2</v>
       </c>
       <c r="J18">
-        <v>0.187968</v>
+        <v>8.7316000000000005E-2</v>
       </c>
       <c r="K18">
-        <v>0.183918</v>
+        <v>8.7316000000000005E-2</v>
       </c>
       <c r="L18">
-        <v>0.18132100000000001</v>
+        <v>8.7316000000000005E-2</v>
       </c>
       <c r="M18">
-        <v>0.17908299999999999</v>
+        <v>8.5322999999999996E-2</v>
       </c>
       <c r="N18">
-        <v>0.175036</v>
+        <v>8.3277000000000004E-2</v>
       </c>
       <c r="O18">
-        <v>0.17749899999999999</v>
+        <v>7.9032000000000005E-2</v>
       </c>
       <c r="P18">
-        <v>0.187254</v>
+        <v>7.4538999999999994E-2</v>
       </c>
       <c r="Q18">
-        <v>0.18277099999999999</v>
+        <v>6.9418999999999995E-2</v>
       </c>
       <c r="R18">
-        <v>0.178782</v>
+        <v>5.8686000000000002E-2</v>
       </c>
       <c r="S18">
-        <v>0.17389099999999999</v>
+        <v>4.5442000000000003E-2</v>
       </c>
       <c r="T18">
-        <v>0.16769600000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.17171500000000001</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="B19">
-        <v>0.17013800000000001</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="C19">
-        <v>0.17508499999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="D19">
-        <v>0.17980199999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="E19">
-        <v>0.18471399999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="F19">
-        <v>0.18355399999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="G19">
-        <v>0.19031500000000001</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="H19">
-        <v>0.18837499999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="I19">
-        <v>0.18482799999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="J19">
-        <v>0.181808</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="K19">
-        <v>0.17860000000000001</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="L19">
-        <v>0.176562</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="M19">
-        <v>0.17458399999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="N19">
-        <v>0.17075299999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="O19">
-        <v>0.17577300000000001</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="P19">
-        <v>0.18207599999999999</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="Q19">
-        <v>0.17765600000000001</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="R19">
-        <v>0.17394100000000001</v>
+        <v>2.6249000000000001E-2</v>
       </c>
       <c r="S19">
-        <v>0.16939199999999999</v>
+        <v>1.8574E-2</v>
       </c>
       <c r="T19">
-        <v>0.16358900000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.16586300000000001</v>
+        <v>0</v>
       </c>
       <c r="B20">
-        <v>0.16420699999999999</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0.17268</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0.18195800000000001</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.19275900000000001</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0.191223</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>0.206037</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>0.20393500000000001</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0.20077300000000001</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.19775499999999999</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>0.19494500000000001</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>0.19353899999999999</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>0.19170899999999999</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>0.18771699999999999</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>0.204343</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>0.22800899999999999</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>0.22181999999999999</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>0.21857099999999999</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>0.21432799999999999</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>0.20757500000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C7C32-ECA6-462B-8C84-ED0F8BB462F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF9CB33-ED8C-4F40-8329-BF95A8756971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,61 +349,61 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.13115499999999999</v>
+        <v>0.126836</v>
       </c>
       <c r="B1">
-        <v>0.131435</v>
+        <v>0.12683900000000001</v>
       </c>
       <c r="C1">
-        <v>0.128385</v>
+        <v>0.123778</v>
       </c>
       <c r="D1">
-        <v>0.12818299999999999</v>
+        <v>0.12414</v>
       </c>
       <c r="E1">
-        <v>0.12562499999999999</v>
+        <v>0.122253</v>
       </c>
       <c r="F1">
-        <v>0.12212199999999999</v>
+        <v>0.118853</v>
       </c>
       <c r="G1">
-        <v>0.118257</v>
+        <v>0.11512</v>
       </c>
       <c r="H1">
-        <v>0.117072</v>
+        <v>0.113764</v>
       </c>
       <c r="I1">
-        <v>0.11175499999999999</v>
+        <v>0.108198</v>
       </c>
       <c r="J1">
-        <v>0.106253</v>
+        <v>0.102716</v>
       </c>
       <c r="K1">
-        <v>0.101923</v>
+        <v>9.9201999999999999E-2</v>
       </c>
       <c r="L1">
-        <v>9.1844999999999996E-2</v>
+        <v>8.9091000000000004E-2</v>
       </c>
       <c r="M1">
-        <v>8.4185999999999997E-2</v>
+        <v>8.2268999999999995E-2</v>
       </c>
       <c r="N1">
-        <v>7.7727000000000004E-2</v>
+        <v>7.5625999999999999E-2</v>
       </c>
       <c r="O1">
-        <v>7.3246000000000006E-2</v>
+        <v>7.0820999999999995E-2</v>
       </c>
       <c r="P1">
-        <v>6.6646999999999998E-2</v>
+        <v>6.3869999999999996E-2</v>
       </c>
       <c r="Q1">
-        <v>5.1582000000000003E-2</v>
+        <v>5.2115000000000002E-2</v>
       </c>
       <c r="R1">
-        <v>3.0883000000000001E-2</v>
+        <v>3.1486E-2</v>
       </c>
       <c r="S1">
-        <v>0.124391</v>
+        <v>0.125754</v>
       </c>
       <c r="T1">
         <v>1.8574E-2</v>
@@ -411,61 +411,61 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.13359699999999999</v>
+        <v>0.12901799999999999</v>
       </c>
       <c r="B2">
-        <v>0.13400599999999999</v>
+        <v>0.12882199999999999</v>
       </c>
       <c r="C2">
-        <v>0.13126699999999999</v>
+        <v>0.12615699999999999</v>
       </c>
       <c r="D2">
-        <v>0.13061300000000001</v>
+        <v>0.125858</v>
       </c>
       <c r="E2">
-        <v>0.12659400000000001</v>
+        <v>0.122872</v>
       </c>
       <c r="F2">
-        <v>0.12256</v>
+        <v>0.11902799999999999</v>
       </c>
       <c r="G2">
-        <v>0.11859699999999999</v>
+        <v>0.115296</v>
       </c>
       <c r="H2">
-        <v>0.116566</v>
+        <v>0.113272</v>
       </c>
       <c r="I2">
-        <v>0.111931</v>
+        <v>0.108388</v>
       </c>
       <c r="J2">
-        <v>0.107139</v>
+        <v>0.103573</v>
       </c>
       <c r="K2">
-        <v>0.102336</v>
+        <v>9.9143999999999996E-2</v>
       </c>
       <c r="L2">
-        <v>9.2462000000000003E-2</v>
+        <v>8.9194999999999997E-2</v>
       </c>
       <c r="M2">
-        <v>8.5751999999999995E-2</v>
+        <v>8.3288000000000001E-2</v>
       </c>
       <c r="N2">
-        <v>7.8516000000000002E-2</v>
+        <v>7.5983999999999996E-2</v>
       </c>
       <c r="O2">
-        <v>7.2931999999999997E-2</v>
+        <v>7.0171999999999998E-2</v>
       </c>
       <c r="P2">
-        <v>6.5568000000000001E-2</v>
+        <v>6.2691999999999998E-2</v>
       </c>
       <c r="Q2">
-        <v>5.1156E-2</v>
+        <v>5.1581000000000002E-2</v>
       </c>
       <c r="R2">
-        <v>3.0733E-2</v>
+        <v>3.1336000000000003E-2</v>
       </c>
       <c r="S2">
-        <v>0.12300800000000001</v>
+        <v>0.124391</v>
       </c>
       <c r="T2">
         <v>1.8574E-2</v>
@@ -473,61 +473,61 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.13300899999999999</v>
+        <v>0.12811500000000001</v>
       </c>
       <c r="B3">
-        <v>0.133158</v>
+        <v>0.12772700000000001</v>
       </c>
       <c r="C3">
-        <v>0.13031200000000001</v>
+        <v>0.125057</v>
       </c>
       <c r="D3">
-        <v>0.12970400000000001</v>
+        <v>0.124447</v>
       </c>
       <c r="E3">
-        <v>0.12612100000000001</v>
+        <v>0.122033</v>
       </c>
       <c r="F3">
-        <v>0.122174</v>
+        <v>0.118309</v>
       </c>
       <c r="G3">
-        <v>0.117077</v>
+        <v>0.11361599999999999</v>
       </c>
       <c r="H3">
-        <v>0.115769</v>
+        <v>0.112304</v>
       </c>
       <c r="I3">
-        <v>0.111887</v>
+        <v>0.108094</v>
       </c>
       <c r="J3">
-        <v>0.106965</v>
+        <v>0.10331700000000001</v>
       </c>
       <c r="K3">
-        <v>0.102344</v>
+        <v>9.8488000000000006E-2</v>
       </c>
       <c r="L3">
-        <v>9.2979999999999993E-2</v>
+        <v>8.9014999999999997E-2</v>
       </c>
       <c r="M3">
-        <v>8.5539000000000004E-2</v>
+        <v>8.2581000000000002E-2</v>
       </c>
       <c r="N3">
-        <v>7.7709E-2</v>
+        <v>7.4758000000000005E-2</v>
       </c>
       <c r="O3">
-        <v>7.3654999999999998E-2</v>
+        <v>7.0306999999999994E-2</v>
       </c>
       <c r="P3">
-        <v>6.8163000000000001E-2</v>
+        <v>6.4583000000000002E-2</v>
       </c>
       <c r="Q3">
-        <v>5.2863E-2</v>
+        <v>5.3199000000000003E-2</v>
       </c>
       <c r="R3">
-        <v>3.4133999999999998E-2</v>
+        <v>3.4638000000000002E-2</v>
       </c>
       <c r="S3">
-        <v>0.12300800000000001</v>
+        <v>0.124391</v>
       </c>
       <c r="T3">
         <v>1.8574E-2</v>
@@ -535,61 +535,61 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.132051</v>
+        <v>0.12712100000000001</v>
       </c>
       <c r="B4">
-        <v>0.13305900000000001</v>
+        <v>0.12751699999999999</v>
       </c>
       <c r="C4">
-        <v>0.13018199999999999</v>
+        <v>0.124878</v>
       </c>
       <c r="D4">
-        <v>0.129579</v>
+        <v>0.12432799999999999</v>
       </c>
       <c r="E4">
-        <v>0.12507299999999999</v>
+        <v>0.121297</v>
       </c>
       <c r="F4">
-        <v>0.120991</v>
+        <v>0.11754299999999999</v>
       </c>
       <c r="G4">
-        <v>0.11633300000000001</v>
+        <v>0.113333</v>
       </c>
       <c r="H4">
-        <v>0.113862</v>
+        <v>0.110489</v>
       </c>
       <c r="I4">
-        <v>0.110753</v>
+        <v>0.10702299999999999</v>
       </c>
       <c r="J4">
-        <v>0.10556699999999999</v>
+        <v>0.102101</v>
       </c>
       <c r="K4">
-        <v>0.101036</v>
+        <v>9.7470000000000001E-2</v>
       </c>
       <c r="L4">
-        <v>9.1856999999999994E-2</v>
+        <v>8.8202000000000003E-2</v>
       </c>
       <c r="M4">
-        <v>8.5481000000000001E-2</v>
+        <v>8.2974000000000006E-2</v>
       </c>
       <c r="N4">
-        <v>7.5638999999999998E-2</v>
+        <v>7.3492000000000002E-2</v>
       </c>
       <c r="O4">
-        <v>7.1233000000000005E-2</v>
+        <v>6.8015999999999993E-2</v>
       </c>
       <c r="P4">
-        <v>6.6725000000000007E-2</v>
+        <v>6.3229999999999995E-2</v>
       </c>
       <c r="Q4">
-        <v>5.2047000000000003E-2</v>
+        <v>5.2381999999999998E-2</v>
       </c>
       <c r="R4">
-        <v>3.3626999999999997E-2</v>
+        <v>3.4131000000000002E-2</v>
       </c>
       <c r="S4">
-        <v>0.121598</v>
+        <v>0.12299599999999999</v>
       </c>
       <c r="T4">
         <v>1.8574E-2</v>
@@ -597,61 +597,61 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.128244</v>
+        <v>0.12457</v>
       </c>
       <c r="B5">
-        <v>0.12921199999999999</v>
+        <v>0.12507799999999999</v>
       </c>
       <c r="C5">
-        <v>0.12692400000000001</v>
+        <v>0.123076</v>
       </c>
       <c r="D5">
-        <v>0.12554799999999999</v>
+        <v>0.121462</v>
       </c>
       <c r="E5">
-        <v>0.12179</v>
+        <v>0.118662</v>
       </c>
       <c r="F5">
-        <v>0.11823699999999999</v>
+        <v>0.115449</v>
       </c>
       <c r="G5">
-        <v>0.113564</v>
+        <v>0.111289</v>
       </c>
       <c r="H5">
-        <v>0.11102099999999999</v>
+        <v>0.108461</v>
       </c>
       <c r="I5">
-        <v>0.10851</v>
+        <v>0.105604</v>
       </c>
       <c r="J5">
-        <v>0.10312200000000001</v>
+        <v>0.100679</v>
       </c>
       <c r="K5">
-        <v>9.8204E-2</v>
+        <v>9.5880000000000007E-2</v>
       </c>
       <c r="L5">
-        <v>8.9446999999999999E-2</v>
+        <v>8.7082999999999994E-2</v>
       </c>
       <c r="M5">
-        <v>8.3731E-2</v>
+        <v>8.1845000000000001E-2</v>
       </c>
       <c r="N5">
-        <v>7.4958999999999998E-2</v>
+        <v>7.2577000000000003E-2</v>
       </c>
       <c r="O5">
-        <v>7.2523000000000004E-2</v>
+        <v>6.8722000000000005E-2</v>
       </c>
       <c r="P5">
-        <v>6.9056999999999993E-2</v>
+        <v>6.4804E-2</v>
       </c>
       <c r="Q5">
-        <v>5.0244999999999998E-2</v>
+        <v>5.0581000000000001E-2</v>
       </c>
       <c r="R5">
-        <v>3.2443E-2</v>
+        <v>3.2946999999999997E-2</v>
       </c>
       <c r="S5">
-        <v>0.118731</v>
+        <v>0.120162</v>
       </c>
       <c r="T5">
         <v>1.8574E-2</v>
@@ -659,61 +659,61 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.12686700000000001</v>
+        <v>0.122811</v>
       </c>
       <c r="B6">
-        <v>0.12735099999999999</v>
+        <v>0.122876</v>
       </c>
       <c r="C6">
-        <v>0.12546299999999999</v>
+        <v>0.12127499999999999</v>
       </c>
       <c r="D6">
-        <v>0.124851</v>
+        <v>0.11970500000000001</v>
       </c>
       <c r="E6">
-        <v>0.12078999999999999</v>
+        <v>0.116841</v>
       </c>
       <c r="F6">
-        <v>0.11649</v>
+        <v>0.113008</v>
       </c>
       <c r="G6">
-        <v>0.111665</v>
+        <v>0.10877199999999999</v>
       </c>
       <c r="H6">
-        <v>0.110192</v>
+        <v>0.106917</v>
       </c>
       <c r="I6">
-        <v>0.10680000000000001</v>
+        <v>0.10323499999999999</v>
       </c>
       <c r="J6">
-        <v>0.10179299999999999</v>
+        <v>9.8726999999999995E-2</v>
       </c>
       <c r="K6">
-        <v>9.7928000000000001E-2</v>
+        <v>9.5029000000000002E-2</v>
       </c>
       <c r="L6">
-        <v>9.0295E-2</v>
+        <v>8.7258000000000002E-2</v>
       </c>
       <c r="M6">
-        <v>8.2007999999999998E-2</v>
+        <v>7.9728999999999994E-2</v>
       </c>
       <c r="N6">
-        <v>7.3007000000000002E-2</v>
+        <v>7.0305000000000006E-2</v>
       </c>
       <c r="O6">
-        <v>7.0616999999999999E-2</v>
+        <v>6.6463999999999995E-2</v>
       </c>
       <c r="P6">
-        <v>6.9291000000000005E-2</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="Q6">
-        <v>5.1804000000000003E-2</v>
+        <v>5.2041999999999998E-2</v>
       </c>
       <c r="R6">
-        <v>3.1766000000000003E-2</v>
+        <v>3.2101999999999999E-2</v>
       </c>
       <c r="S6">
-        <v>0.118731</v>
+        <v>0.120162</v>
       </c>
       <c r="T6">
         <v>1.8574E-2</v>
@@ -721,61 +721,61 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.124489</v>
+        <v>0.121263</v>
       </c>
       <c r="B7">
-        <v>0.12589900000000001</v>
+        <v>0.122269</v>
       </c>
       <c r="C7">
-        <v>0.123085</v>
+        <v>0.119307</v>
       </c>
       <c r="D7">
-        <v>0.121654</v>
+        <v>0.116978</v>
       </c>
       <c r="E7">
-        <v>0.118146</v>
+        <v>0.114842</v>
       </c>
       <c r="F7">
-        <v>0.11452900000000001</v>
+        <v>0.11172799999999999</v>
       </c>
       <c r="G7">
-        <v>0.10942499999999999</v>
+        <v>0.107326</v>
       </c>
       <c r="H7">
-        <v>0.108181</v>
+        <v>0.105785</v>
       </c>
       <c r="I7">
-        <v>0.104947</v>
+        <v>0.10236199999999999</v>
       </c>
       <c r="J7">
-        <v>0.100619</v>
+        <v>9.8665000000000003E-2</v>
       </c>
       <c r="K7">
-        <v>9.4602000000000006E-2</v>
+        <v>9.3198000000000003E-2</v>
       </c>
       <c r="L7">
-        <v>8.6772000000000002E-2</v>
+        <v>8.5333999999999993E-2</v>
       </c>
       <c r="M7">
-        <v>7.8338000000000005E-2</v>
+        <v>7.6823000000000002E-2</v>
       </c>
       <c r="N7">
-        <v>7.0419999999999996E-2</v>
+        <v>6.8569000000000005E-2</v>
       </c>
       <c r="O7">
-        <v>6.7418000000000006E-2</v>
+        <v>6.4612000000000003E-2</v>
       </c>
       <c r="P7">
-        <v>6.4814999999999998E-2</v>
+        <v>6.2688999999999995E-2</v>
       </c>
       <c r="Q7">
-        <v>4.8253999999999998E-2</v>
+        <v>4.8492E-2</v>
       </c>
       <c r="R7">
-        <v>3.0242999999999999E-2</v>
+        <v>3.058E-2</v>
       </c>
       <c r="S7">
-        <v>0.117282</v>
+        <v>0.118731</v>
       </c>
       <c r="T7">
         <v>1.8574E-2</v>
@@ -783,61 +783,61 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.125578</v>
+        <v>0.12207</v>
       </c>
       <c r="B8">
-        <v>0.12733800000000001</v>
+        <v>0.12336800000000001</v>
       </c>
       <c r="C8">
-        <v>0.12508</v>
+        <v>0.120924</v>
       </c>
       <c r="D8">
-        <v>0.12435499999999999</v>
+        <v>0.119051</v>
       </c>
       <c r="E8">
-        <v>0.121572</v>
+        <v>0.117949</v>
       </c>
       <c r="F8">
-        <v>0.11914</v>
+        <v>0.11611200000000001</v>
       </c>
       <c r="G8">
-        <v>0.114413</v>
+        <v>0.111333</v>
       </c>
       <c r="H8">
-        <v>0.11372699999999999</v>
+        <v>0.11015</v>
       </c>
       <c r="I8">
-        <v>0.11093500000000001</v>
+        <v>0.107057</v>
       </c>
       <c r="J8">
-        <v>0.10561</v>
+        <v>0.1027</v>
       </c>
       <c r="K8">
-        <v>9.9252000000000007E-2</v>
+        <v>9.7174999999999997E-2</v>
       </c>
       <c r="L8">
-        <v>9.1026999999999997E-2</v>
+        <v>8.8914000000000007E-2</v>
       </c>
       <c r="M8">
-        <v>8.2267999999999994E-2</v>
+        <v>8.0074000000000006E-2</v>
       </c>
       <c r="N8">
-        <v>7.7380000000000004E-2</v>
+        <v>7.4549000000000004E-2</v>
       </c>
       <c r="O8">
-        <v>7.3574000000000001E-2</v>
+        <v>6.9513000000000005E-2</v>
       </c>
       <c r="P8">
-        <v>6.7368999999999998E-2</v>
+        <v>6.4699999999999994E-2</v>
       </c>
       <c r="Q8">
-        <v>4.9201000000000002E-2</v>
+        <v>4.9454999999999999E-2</v>
       </c>
       <c r="R8">
-        <v>3.3812000000000002E-2</v>
+        <v>3.4199E-2</v>
       </c>
       <c r="S8">
-        <v>0.115802</v>
+        <v>0.117269</v>
       </c>
       <c r="T8">
         <v>1.8574E-2</v>
@@ -845,61 +845,61 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.123111</v>
+        <v>0.12034</v>
       </c>
       <c r="B9">
-        <v>0.12506600000000001</v>
+        <v>0.121901</v>
       </c>
       <c r="C9">
-        <v>0.12230199999999999</v>
+        <v>0.119056</v>
       </c>
       <c r="D9">
-        <v>0.122723</v>
+        <v>0.11808100000000001</v>
       </c>
       <c r="E9">
-        <v>0.120741</v>
+        <v>0.117008</v>
       </c>
       <c r="F9">
-        <v>0.118173</v>
+        <v>0.114276</v>
       </c>
       <c r="G9">
-        <v>0.11436300000000001</v>
+        <v>0.110335</v>
       </c>
       <c r="H9">
-        <v>0.116381</v>
+        <v>0.111418</v>
       </c>
       <c r="I9">
-        <v>0.111639</v>
+        <v>0.106573</v>
       </c>
       <c r="J9">
-        <v>0.10571700000000001</v>
+        <v>0.10197100000000001</v>
       </c>
       <c r="K9">
-        <v>0.100596</v>
+        <v>9.7753999999999994E-2</v>
       </c>
       <c r="L9">
-        <v>9.2147000000000007E-2</v>
+        <v>8.9375999999999997E-2</v>
       </c>
       <c r="M9">
-        <v>8.2679000000000002E-2</v>
+        <v>7.9963999999999993E-2</v>
       </c>
       <c r="N9">
-        <v>7.8331999999999999E-2</v>
+        <v>7.4831999999999996E-2</v>
       </c>
       <c r="O9">
-        <v>7.8577999999999995E-2</v>
+        <v>7.2783E-2</v>
       </c>
       <c r="P9">
-        <v>6.8862000000000007E-2</v>
+        <v>6.5457000000000001E-2</v>
       </c>
       <c r="Q9">
-        <v>4.9895000000000002E-2</v>
+        <v>5.0167999999999997E-2</v>
       </c>
       <c r="R9">
-        <v>3.2057000000000002E-2</v>
+        <v>3.2444000000000001E-2</v>
       </c>
       <c r="S9">
-        <v>0.114302</v>
+        <v>0.115789</v>
       </c>
       <c r="T9">
         <v>1.8574E-2</v>
@@ -907,61 +907,61 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.125776</v>
+        <v>0.12279</v>
       </c>
       <c r="B10">
-        <v>0.128166</v>
+        <v>0.12472999999999999</v>
       </c>
       <c r="C10">
-        <v>0.126109</v>
+        <v>0.122505</v>
       </c>
       <c r="D10">
-        <v>0.128723</v>
+        <v>0.12300800000000001</v>
       </c>
       <c r="E10">
-        <v>0.12826899999999999</v>
+        <v>0.123833</v>
       </c>
       <c r="F10">
-        <v>0.12345299999999999</v>
+        <v>0.119078</v>
       </c>
       <c r="G10">
-        <v>0.11906700000000001</v>
+        <v>0.114622</v>
       </c>
       <c r="H10">
-        <v>0.11640300000000001</v>
+        <v>0.111606</v>
       </c>
       <c r="I10">
-        <v>0.112859</v>
+        <v>0.107875</v>
       </c>
       <c r="J10">
-        <v>0.105989</v>
+        <v>0.102927</v>
       </c>
       <c r="K10">
-        <v>0.100504</v>
+        <v>9.6790000000000001E-2</v>
       </c>
       <c r="L10">
-        <v>9.3276999999999999E-2</v>
+        <v>8.9521000000000003E-2</v>
       </c>
       <c r="M10">
-        <v>8.5202E-2</v>
+        <v>8.1360000000000002E-2</v>
       </c>
       <c r="N10">
-        <v>8.4375000000000006E-2</v>
+        <v>7.893E-2</v>
       </c>
       <c r="O10">
-        <v>8.0597000000000002E-2</v>
+        <v>7.3280999999999999E-2</v>
       </c>
       <c r="P10">
-        <v>7.3410000000000003E-2</v>
+        <v>6.8361000000000005E-2</v>
       </c>
       <c r="Q10">
-        <v>5.6756000000000001E-2</v>
+        <v>5.6922E-2</v>
       </c>
       <c r="R10">
-        <v>3.7429999999999998E-2</v>
+        <v>3.7664999999999997E-2</v>
       </c>
       <c r="S10">
-        <v>0.114302</v>
+        <v>0.115789</v>
       </c>
       <c r="T10">
         <v>1.8574E-2</v>
@@ -969,61 +969,61 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.111239</v>
+        <v>0.110775</v>
       </c>
       <c r="B11">
-        <v>0.11292000000000001</v>
+        <v>0.112312</v>
       </c>
       <c r="C11">
-        <v>0.111612</v>
+        <v>0.110911</v>
       </c>
       <c r="D11">
-        <v>0.113023</v>
+        <v>0.11062</v>
       </c>
       <c r="E11">
-        <v>0.111497</v>
+        <v>0.11060499999999999</v>
       </c>
       <c r="F11">
-        <v>0.107569</v>
+        <v>0.106696</v>
       </c>
       <c r="G11">
-        <v>0.10391</v>
+        <v>0.102933</v>
       </c>
       <c r="H11">
-        <v>0.10288</v>
+        <v>0.10177899999999999</v>
       </c>
       <c r="I11">
-        <v>9.9833000000000005E-2</v>
+        <v>9.8676E-2</v>
       </c>
       <c r="J11">
-        <v>9.3778E-2</v>
+        <v>9.2610999999999999E-2</v>
       </c>
       <c r="K11">
-        <v>9.0225E-2</v>
+        <v>8.8619000000000003E-2</v>
       </c>
       <c r="L11">
-        <v>8.4278000000000006E-2</v>
+        <v>8.2635E-2</v>
       </c>
       <c r="M11">
-        <v>7.7385999999999996E-2</v>
+        <v>7.5641E-2</v>
       </c>
       <c r="N11">
-        <v>7.8395000000000006E-2</v>
+        <v>7.5662999999999994E-2</v>
       </c>
       <c r="O11">
-        <v>7.2525000000000006E-2</v>
+        <v>6.9097000000000006E-2</v>
       </c>
       <c r="P11">
-        <v>6.6243999999999997E-2</v>
+        <v>6.6515000000000005E-2</v>
       </c>
       <c r="Q11">
-        <v>5.2431999999999999E-2</v>
+        <v>5.2597999999999999E-2</v>
       </c>
       <c r="R11">
-        <v>3.4826000000000003E-2</v>
+        <v>3.5062000000000003E-2</v>
       </c>
       <c r="S11">
-        <v>0.111261</v>
+        <v>0.112787</v>
       </c>
       <c r="T11">
         <v>1.8574E-2</v>
@@ -1031,49 +1031,49 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.105723</v>
+        <v>0.104641</v>
       </c>
       <c r="B12">
-        <v>0.106825</v>
+        <v>0.105572</v>
       </c>
       <c r="C12">
-        <v>0.10699</v>
+        <v>0.105563</v>
       </c>
       <c r="D12">
-        <v>0.108041</v>
+        <v>0.104517</v>
       </c>
       <c r="E12">
-        <v>0.10520400000000001</v>
+        <v>0.103617</v>
       </c>
       <c r="F12">
-        <v>0.102052</v>
+        <v>0.100455</v>
       </c>
       <c r="G12">
-        <v>9.9223000000000006E-2</v>
+        <v>9.7539000000000001E-2</v>
       </c>
       <c r="H12">
-        <v>9.5314999999999997E-2</v>
+        <v>9.3632000000000007E-2</v>
       </c>
       <c r="I12">
-        <v>9.3174000000000007E-2</v>
+        <v>9.1363E-2</v>
       </c>
       <c r="J12">
-        <v>8.8363999999999998E-2</v>
+        <v>8.6494000000000001E-2</v>
       </c>
       <c r="K12">
-        <v>8.4533999999999998E-2</v>
+        <v>8.2357E-2</v>
       </c>
       <c r="L12">
-        <v>8.0810999999999994E-2</v>
+        <v>7.8463000000000005E-2</v>
       </c>
       <c r="M12">
-        <v>7.2502999999999998E-2</v>
+        <v>7.0262000000000005E-2</v>
       </c>
       <c r="N12">
-        <v>7.7169000000000001E-2</v>
+        <v>7.3302000000000006E-2</v>
       </c>
       <c r="O12">
-        <v>7.0607000000000003E-2</v>
+        <v>6.6156000000000006E-2</v>
       </c>
       <c r="P12">
         <v>6.9348999999999994E-2</v>
@@ -1093,43 +1093,43 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>9.5824999999999994E-2</v>
+        <v>9.6056000000000002E-2</v>
       </c>
       <c r="B13">
-        <v>9.5739000000000005E-2</v>
+        <v>9.5976000000000006E-2</v>
       </c>
       <c r="C13">
-        <v>9.4843999999999998E-2</v>
+        <v>9.5086000000000004E-2</v>
       </c>
       <c r="D13">
-        <v>9.4343999999999997E-2</v>
+        <v>9.4591999999999996E-2</v>
       </c>
       <c r="E13">
-        <v>9.2071E-2</v>
+        <v>9.2244000000000007E-2</v>
       </c>
       <c r="F13">
-        <v>9.0333999999999998E-2</v>
+        <v>9.0511999999999995E-2</v>
       </c>
       <c r="G13">
-        <v>8.8419999999999999E-2</v>
+        <v>8.8603000000000001E-2</v>
       </c>
       <c r="H13">
-        <v>8.5415000000000005E-2</v>
+        <v>8.5602999999999999E-2</v>
       </c>
       <c r="I13">
-        <v>8.5142999999999996E-2</v>
+        <v>8.5343000000000002E-2</v>
       </c>
       <c r="J13">
-        <v>8.1714999999999996E-2</v>
+        <v>8.1921999999999995E-2</v>
       </c>
       <c r="K13">
-        <v>8.0625000000000002E-2</v>
+        <v>8.0721000000000001E-2</v>
       </c>
       <c r="L13">
-        <v>7.6680999999999999E-2</v>
+        <v>7.6781000000000002E-2</v>
       </c>
       <c r="M13">
-        <v>7.1443999999999994E-2</v>
+        <v>7.1550000000000002E-2</v>
       </c>
       <c r="N13">
         <v>7.3355000000000004E-2</v>
@@ -1155,43 +1155,43 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>8.1816E-2</v>
+        <v>8.1977999999999995E-2</v>
       </c>
       <c r="B14">
-        <v>8.2632999999999998E-2</v>
+        <v>8.2801E-2</v>
       </c>
       <c r="C14">
-        <v>8.0627000000000004E-2</v>
+        <v>8.0794000000000005E-2</v>
       </c>
       <c r="D14">
-        <v>8.0972000000000002E-2</v>
+        <v>8.1144999999999995E-2</v>
       </c>
       <c r="E14">
-        <v>7.9841999999999996E-2</v>
+        <v>7.9929E-2</v>
       </c>
       <c r="F14">
-        <v>7.8989000000000004E-2</v>
+        <v>7.9078999999999997E-2</v>
       </c>
       <c r="G14">
-        <v>7.8421000000000005E-2</v>
+        <v>7.8512999999999999E-2</v>
       </c>
       <c r="H14">
-        <v>7.6854000000000006E-2</v>
+        <v>7.6950000000000005E-2</v>
       </c>
       <c r="I14">
-        <v>7.5920000000000001E-2</v>
+        <v>7.6021000000000005E-2</v>
       </c>
       <c r="J14">
-        <v>7.3782E-2</v>
+        <v>7.3886999999999994E-2</v>
       </c>
       <c r="K14">
-        <v>7.5133000000000005E-2</v>
+        <v>7.5249999999999997E-2</v>
       </c>
       <c r="L14">
-        <v>6.8900000000000003E-2</v>
+        <v>6.9017999999999996E-2</v>
       </c>
       <c r="M14">
-        <v>6.5135999999999999E-2</v>
+        <v>6.5262000000000001E-2</v>
       </c>
       <c r="N14">
         <v>6.7128999999999994E-2</v>
@@ -1217,16 +1217,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>7.3993000000000003E-2</v>
+        <v>7.4103000000000002E-2</v>
       </c>
       <c r="B15">
-        <v>7.2764999999999996E-2</v>
+        <v>7.2875999999999996E-2</v>
       </c>
       <c r="C15">
-        <v>7.1438000000000001E-2</v>
+        <v>7.1550000000000002E-2</v>
       </c>
       <c r="D15">
-        <v>6.9777000000000006E-2</v>
+        <v>6.9889000000000007E-2</v>
       </c>
       <c r="E15">
         <v>6.8769999999999998E-2</v>
@@ -1279,16 +1279,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>5.3775999999999997E-2</v>
+        <v>5.3926000000000002E-2</v>
       </c>
       <c r="B16">
-        <v>5.2877E-2</v>
+        <v>5.3025999999999997E-2</v>
       </c>
       <c r="C16">
-        <v>5.1847999999999998E-2</v>
+        <v>5.1997000000000002E-2</v>
       </c>
       <c r="D16">
-        <v>5.0516999999999999E-2</v>
+        <v>5.0666999999999997E-2</v>
       </c>
       <c r="E16">
         <v>4.9764999999999997E-2</v>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07A01E4-54BC-424D-8CE9-9D96FF47DEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9B7C1E-776E-4ADB-A8E4-F8475B51F7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,1927 +355,1927 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>0.58459700000000003</v>
+        <v>0.62027500000000002</v>
       </c>
       <c r="B1" s="1">
-        <v>0.58746699999999996</v>
+        <v>0.62541199999999997</v>
       </c>
       <c r="C1" s="1">
-        <v>0.59151299999999996</v>
+        <v>0.63125399999999998</v>
       </c>
       <c r="D1" s="1">
-        <v>0.59581200000000001</v>
+        <v>0.63727900000000004</v>
       </c>
       <c r="E1" s="1">
-        <v>0.59834100000000001</v>
+        <v>0.64118200000000003</v>
       </c>
       <c r="F1" s="1">
-        <v>0.60366600000000004</v>
+        <v>0.64634599999999998</v>
       </c>
       <c r="G1" s="1">
-        <v>0.61132799999999998</v>
+        <v>0.65215500000000004</v>
       </c>
       <c r="H1" s="1">
-        <v>0.61632900000000002</v>
+        <v>0.662578</v>
       </c>
       <c r="I1" s="1">
-        <v>0.62323899999999999</v>
+        <v>0.67023600000000005</v>
       </c>
       <c r="J1" s="1">
-        <v>0.630853</v>
+        <v>0.67572699999999997</v>
       </c>
       <c r="K1" s="1">
-        <v>0.63833200000000001</v>
+        <v>0.680531</v>
       </c>
       <c r="L1" s="1">
-        <v>0.64413399999999998</v>
+        <v>0.68674400000000002</v>
       </c>
       <c r="M1" s="1">
-        <v>0.65000100000000005</v>
+        <v>0.69255199999999995</v>
       </c>
       <c r="N1" s="1">
-        <v>0.65602899999999997</v>
+        <v>0.69889199999999996</v>
       </c>
       <c r="O1" s="1">
-        <v>0.66631799999999997</v>
+        <v>0.70687100000000003</v>
       </c>
       <c r="P1" s="1">
-        <v>0.67574000000000001</v>
+        <v>0.71584400000000004</v>
       </c>
       <c r="Q1" s="1">
-        <v>0.68259300000000001</v>
+        <v>0.71933400000000003</v>
       </c>
       <c r="R1" s="1">
-        <v>0.69422600000000001</v>
+        <v>0.72343800000000003</v>
       </c>
       <c r="S1" s="1">
-        <v>0.70304599999999995</v>
+        <v>0.72945400000000005</v>
       </c>
       <c r="T1" s="1">
-        <v>0.71220499999999998</v>
+        <v>0.74185299999999998</v>
       </c>
       <c r="U1" s="1">
-        <v>0.72039900000000001</v>
+        <v>0.74719000000000002</v>
       </c>
       <c r="V1" s="1">
-        <v>0.74954699999999996</v>
+        <v>0.75383299999999998</v>
       </c>
       <c r="W1" s="1">
-        <v>0.756911</v>
+        <v>0.759544</v>
       </c>
       <c r="X1" s="1">
-        <v>0.74138899999999996</v>
+        <v>0.76107100000000005</v>
       </c>
       <c r="Y1" s="1">
-        <v>0.76375099999999996</v>
+        <v>0.69873300000000005</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
-        <v>0.58661399999999997</v>
+        <v>0.61995599999999995</v>
       </c>
       <c r="B2" s="1">
-        <v>0.58950400000000003</v>
+        <v>0.62448800000000004</v>
       </c>
       <c r="C2" s="1">
-        <v>0.59346699999999997</v>
+        <v>0.63013300000000005</v>
       </c>
       <c r="D2" s="1">
-        <v>0.597387</v>
+        <v>0.636382</v>
       </c>
       <c r="E2" s="1">
-        <v>0.60013399999999995</v>
+        <v>0.64039699999999999</v>
       </c>
       <c r="F2" s="1">
-        <v>0.60555899999999996</v>
+        <v>0.64598</v>
       </c>
       <c r="G2" s="1">
-        <v>0.61368</v>
+        <v>0.651999</v>
       </c>
       <c r="H2" s="1">
-        <v>0.61868800000000002</v>
+        <v>0.66241300000000003</v>
       </c>
       <c r="I2" s="1">
-        <v>0.62534199999999995</v>
+        <v>0.67025500000000005</v>
       </c>
       <c r="J2" s="1">
-        <v>0.63363599999999998</v>
+        <v>0.67538699999999996</v>
       </c>
       <c r="K2" s="1">
-        <v>0.64135500000000001</v>
+        <v>0.68046399999999996</v>
       </c>
       <c r="L2" s="1">
-        <v>0.64676400000000001</v>
+        <v>0.68660699999999997</v>
       </c>
       <c r="M2" s="1">
-        <v>0.65322999999999998</v>
+        <v>0.69230100000000006</v>
       </c>
       <c r="N2" s="1">
-        <v>0.658829</v>
+        <v>0.69841299999999995</v>
       </c>
       <c r="O2" s="1">
-        <v>0.66867699999999997</v>
+        <v>0.70577400000000001</v>
       </c>
       <c r="P2" s="1">
-        <v>0.67722899999999997</v>
+        <v>0.71523999999999999</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.68438200000000005</v>
+        <v>0.71939399999999998</v>
       </c>
       <c r="R2" s="1">
-        <v>0.69539200000000001</v>
+        <v>0.72343800000000003</v>
       </c>
       <c r="S2" s="1">
-        <v>0.70502100000000001</v>
+        <v>0.72933499999999996</v>
       </c>
       <c r="T2" s="1">
-        <v>0.71427700000000005</v>
+        <v>0.74201799999999996</v>
       </c>
       <c r="U2" s="1">
-        <v>0.72547099999999998</v>
+        <v>0.74690100000000004</v>
       </c>
       <c r="V2" s="1">
-        <v>0.75443000000000005</v>
+        <v>0.75270000000000004</v>
       </c>
       <c r="W2" s="1">
-        <v>0.76275700000000002</v>
+        <v>0.75723300000000004</v>
       </c>
       <c r="X2" s="1">
-        <v>0.74820600000000004</v>
+        <v>0.75709800000000005</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.77636000000000005</v>
+        <v>0.69670799999999999</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
-        <v>0.58791400000000005</v>
+        <v>0.62256699999999998</v>
       </c>
       <c r="B3" s="1">
-        <v>0.59072199999999997</v>
+        <v>0.62697800000000004</v>
       </c>
       <c r="C3" s="1">
-        <v>0.594557</v>
+        <v>0.63283400000000001</v>
       </c>
       <c r="D3" s="1">
-        <v>0.59828400000000004</v>
+        <v>0.63908699999999996</v>
       </c>
       <c r="E3" s="1">
-        <v>0.60094800000000004</v>
+        <v>0.64338399999999996</v>
       </c>
       <c r="F3" s="1">
-        <v>0.60651200000000005</v>
+        <v>0.64858199999999999</v>
       </c>
       <c r="G3" s="1">
-        <v>0.61527799999999999</v>
+        <v>0.65486599999999995</v>
       </c>
       <c r="H3" s="1">
-        <v>0.62053100000000005</v>
+        <v>0.66497899999999999</v>
       </c>
       <c r="I3" s="1">
-        <v>0.62732100000000002</v>
+        <v>0.67334499999999997</v>
       </c>
       <c r="J3" s="1">
-        <v>0.63603799999999999</v>
+        <v>0.67820599999999998</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64353499999999997</v>
+        <v>0.68372900000000003</v>
       </c>
       <c r="L3" s="1">
-        <v>0.64914000000000005</v>
+        <v>0.690438</v>
       </c>
       <c r="M3" s="1">
-        <v>0.656026</v>
+        <v>0.69642700000000002</v>
       </c>
       <c r="N3" s="1">
-        <v>0.66195300000000001</v>
+        <v>0.70258699999999996</v>
       </c>
       <c r="O3" s="1">
-        <v>0.67227800000000004</v>
+        <v>0.70914600000000005</v>
       </c>
       <c r="P3" s="1">
-        <v>0.68048399999999998</v>
+        <v>0.71827300000000005</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.68760200000000005</v>
+        <v>0.72153500000000004</v>
       </c>
       <c r="R3" s="1">
-        <v>0.69922300000000004</v>
+        <v>0.72665800000000003</v>
       </c>
       <c r="S3" s="1">
-        <v>0.70938900000000005</v>
+        <v>0.73048500000000005</v>
       </c>
       <c r="T3" s="1">
-        <v>0.71825300000000003</v>
+        <v>0.74304000000000003</v>
       </c>
       <c r="U3" s="1">
-        <v>0.728495</v>
+        <v>0.74881799999999998</v>
       </c>
       <c r="V3" s="1">
-        <v>0.75393500000000002</v>
+        <v>0.75539800000000001</v>
       </c>
       <c r="W3" s="2">
-        <v>0.76336599999999999</v>
+        <v>0.75944400000000001</v>
       </c>
       <c r="X3" s="1">
-        <v>0.74866500000000002</v>
+        <v>0.76213299999999995</v>
       </c>
       <c r="Y3" s="1">
-        <v>0.77309700000000003</v>
+        <v>0.70177699999999998</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
-        <v>0.58816199999999996</v>
+        <v>0.62445200000000001</v>
       </c>
       <c r="B4" s="1">
-        <v>0.59099000000000002</v>
+        <v>0.62849900000000003</v>
       </c>
       <c r="C4" s="1">
-        <v>0.59520399999999996</v>
+        <v>0.63427599999999995</v>
       </c>
       <c r="D4" s="1">
-        <v>0.59899000000000002</v>
+        <v>0.64091500000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>0.60127299999999995</v>
+        <v>0.645146</v>
       </c>
       <c r="F4" s="1">
-        <v>0.60669700000000004</v>
+        <v>0.65052100000000002</v>
       </c>
       <c r="G4" s="1">
-        <v>0.61501399999999995</v>
+        <v>0.65739899999999996</v>
       </c>
       <c r="H4" s="1">
-        <v>0.62025399999999997</v>
+        <v>0.66643600000000003</v>
       </c>
       <c r="I4" s="1">
-        <v>0.62627299999999997</v>
+        <v>0.67502099999999998</v>
       </c>
       <c r="J4" s="1">
-        <v>0.63506300000000004</v>
+        <v>0.68005099999999996</v>
       </c>
       <c r="K4" s="1">
-        <v>0.64176900000000003</v>
+        <v>0.68522899999999998</v>
       </c>
       <c r="L4" s="1">
-        <v>0.64735699999999996</v>
+        <v>0.69140299999999999</v>
       </c>
       <c r="M4" s="1">
-        <v>0.65358899999999998</v>
+        <v>0.69777999999999996</v>
       </c>
       <c r="N4" s="1">
-        <v>0.65939300000000001</v>
+        <v>0.70313400000000004</v>
       </c>
       <c r="O4" s="1">
-        <v>0.67040500000000003</v>
+        <v>0.70934200000000003</v>
       </c>
       <c r="P4" s="1">
-        <v>0.67815300000000001</v>
+        <v>0.71790600000000004</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.68545199999999995</v>
+        <v>0.720356</v>
       </c>
       <c r="R4" s="1">
-        <v>0.69776099999999996</v>
+        <v>0.72550700000000001</v>
       </c>
       <c r="S4" s="1">
-        <v>0.70644899999999999</v>
+        <v>0.73001499999999997</v>
       </c>
       <c r="T4" s="1">
-        <v>0.71514999999999995</v>
+        <v>0.74229400000000001</v>
       </c>
       <c r="U4" s="1">
-        <v>0.72592999999999996</v>
+        <v>0.74814800000000004</v>
       </c>
       <c r="V4" s="1">
-        <v>0.75116400000000005</v>
+        <v>0.75584099999999999</v>
       </c>
       <c r="W4" s="1">
-        <v>0.76118600000000003</v>
+        <v>0.75958700000000001</v>
       </c>
       <c r="X4" s="1">
-        <v>0.74877300000000002</v>
+        <v>0.76069900000000001</v>
       </c>
       <c r="Y4" s="1">
-        <v>0.78584200000000004</v>
+        <v>0.69922899999999999</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
-        <v>0.58887999999999996</v>
+        <v>0.62708299999999995</v>
       </c>
       <c r="B5" s="1">
-        <v>0.59143999999999997</v>
+        <v>0.630938</v>
       </c>
       <c r="C5" s="1">
-        <v>0.59564799999999996</v>
+        <v>0.637216</v>
       </c>
       <c r="D5" s="1">
-        <v>0.59966200000000003</v>
+        <v>0.64409799999999995</v>
       </c>
       <c r="E5" s="1">
-        <v>0.60228999999999999</v>
+        <v>0.64846000000000004</v>
       </c>
       <c r="F5" s="1">
-        <v>0.60736900000000005</v>
+        <v>0.65377600000000002</v>
       </c>
       <c r="G5" s="1">
-        <v>0.61545099999999997</v>
+        <v>0.66068099999999996</v>
       </c>
       <c r="H5" s="1">
-        <v>0.62058999999999997</v>
+        <v>0.66913999999999996</v>
       </c>
       <c r="I5" s="1">
-        <v>0.62672399999999995</v>
+        <v>0.67731300000000005</v>
       </c>
       <c r="J5" s="1">
-        <v>0.63585199999999997</v>
+        <v>0.68120000000000003</v>
       </c>
       <c r="K5" s="1">
-        <v>0.64275899999999997</v>
+        <v>0.68610099999999996</v>
       </c>
       <c r="L5" s="1">
-        <v>0.64840699999999996</v>
+        <v>0.69244300000000003</v>
       </c>
       <c r="M5" s="1">
-        <v>0.65559500000000004</v>
+        <v>0.69871300000000003</v>
       </c>
       <c r="N5" s="1">
-        <v>0.66179200000000005</v>
+        <v>0.70303499999999997</v>
       </c>
       <c r="O5" s="1">
-        <v>0.67261700000000002</v>
+        <v>0.709063</v>
       </c>
       <c r="P5" s="1">
-        <v>0.68021900000000002</v>
+        <v>0.71823499999999996</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.68749899999999997</v>
+        <v>0.72085100000000002</v>
       </c>
       <c r="R5" s="1">
-        <v>0.70025899999999996</v>
+        <v>0.72548299999999999</v>
       </c>
       <c r="S5" s="1">
-        <v>0.70874899999999996</v>
+        <v>0.73076600000000003</v>
       </c>
       <c r="T5" s="1">
-        <v>0.71711499999999995</v>
+        <v>0.74214899999999995</v>
       </c>
       <c r="U5" s="1">
-        <v>0.72869300000000004</v>
+        <v>0.74715699999999996</v>
       </c>
       <c r="V5" s="1">
-        <v>0.75371900000000003</v>
+        <v>0.75300999999999996</v>
       </c>
       <c r="W5" s="1">
-        <v>0.76103500000000002</v>
+        <v>0.75931800000000005</v>
       </c>
       <c r="X5" s="1">
-        <v>0.747525</v>
+        <v>0.75958099999999995</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.79158399999999995</v>
+        <v>0.69997100000000001</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
-        <v>0.590777</v>
+        <v>0.62847399999999998</v>
       </c>
       <c r="B6" s="1">
-        <v>0.59351600000000004</v>
+        <v>0.63260099999999997</v>
       </c>
       <c r="C6" s="1">
-        <v>0.59768500000000002</v>
+        <v>0.63965700000000003</v>
       </c>
       <c r="D6" s="1">
-        <v>0.60145199999999999</v>
+        <v>0.646536</v>
       </c>
       <c r="E6" s="1">
-        <v>0.60403600000000002</v>
+        <v>0.64994799999999997</v>
       </c>
       <c r="F6" s="1">
-        <v>0.60849200000000003</v>
+        <v>0.65559800000000001</v>
       </c>
       <c r="G6" s="1">
-        <v>0.61637200000000003</v>
+        <v>0.66170600000000002</v>
       </c>
       <c r="H6" s="1">
-        <v>0.62051400000000001</v>
+        <v>0.67003100000000004</v>
       </c>
       <c r="I6" s="1">
-        <v>0.62577199999999999</v>
+        <v>0.67799900000000002</v>
       </c>
       <c r="J6" s="1">
-        <v>0.63425799999999999</v>
+        <v>0.681612</v>
       </c>
       <c r="K6" s="1">
-        <v>0.64096699999999995</v>
+        <v>0.68620700000000001</v>
       </c>
       <c r="L6" s="1">
-        <v>0.64659900000000003</v>
+        <v>0.691886</v>
       </c>
       <c r="M6" s="1">
-        <v>0.65427900000000005</v>
+        <v>0.69917499999999999</v>
       </c>
       <c r="N6" s="1">
-        <v>0.66078899999999996</v>
+        <v>0.70277299999999998</v>
       </c>
       <c r="O6" s="1">
-        <v>0.67149400000000004</v>
+        <v>0.70918999999999999</v>
       </c>
       <c r="P6" s="1">
-        <v>0.677925</v>
+        <v>0.71915899999999999</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.68607499999999999</v>
+        <v>0.72170500000000004</v>
       </c>
       <c r="R6" s="1">
-        <v>0.69778799999999996</v>
+        <v>0.72757300000000003</v>
       </c>
       <c r="S6" s="1">
-        <v>0.70626900000000004</v>
+        <v>0.73190599999999995</v>
       </c>
       <c r="T6" s="1">
-        <v>0.71493099999999998</v>
+        <v>0.74307900000000005</v>
       </c>
       <c r="U6" s="1">
-        <v>0.72870800000000002</v>
+        <v>0.74742900000000001</v>
       </c>
       <c r="V6" s="1">
-        <v>0.75189799999999996</v>
+        <v>0.75307599999999997</v>
       </c>
       <c r="W6" s="1">
-        <v>0.75933200000000001</v>
+        <v>0.75512900000000005</v>
       </c>
       <c r="X6" s="1">
-        <v>0.74119900000000005</v>
+        <v>0.75799000000000005</v>
       </c>
       <c r="Y6" s="1">
-        <v>0.78714499999999998</v>
+        <v>0.70047000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
-        <v>0.59230000000000005</v>
+        <v>0.63053499999999996</v>
       </c>
       <c r="B7" s="1">
-        <v>0.59420499999999998</v>
+        <v>0.634274</v>
       </c>
       <c r="C7" s="1">
-        <v>0.59814400000000001</v>
+        <v>0.64080199999999998</v>
       </c>
       <c r="D7" s="1">
-        <v>0.60219800000000001</v>
+        <v>0.64810900000000005</v>
       </c>
       <c r="E7" s="1">
-        <v>0.60408799999999996</v>
+        <v>0.65215400000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>0.60810900000000001</v>
+        <v>0.657887</v>
       </c>
       <c r="G7" s="1">
-        <v>0.616012</v>
+        <v>0.66417400000000004</v>
       </c>
       <c r="H7" s="1">
-        <v>0.62073299999999998</v>
+        <v>0.67142800000000002</v>
       </c>
       <c r="I7" s="1">
-        <v>0.62573699999999999</v>
+        <v>0.67998400000000003</v>
       </c>
       <c r="J7" s="1">
-        <v>0.63410299999999997</v>
+        <v>0.68332300000000001</v>
       </c>
       <c r="K7" s="1">
-        <v>0.64065399999999995</v>
+        <v>0.68818400000000002</v>
       </c>
       <c r="L7" s="1">
-        <v>0.64613200000000004</v>
+        <v>0.69347700000000001</v>
       </c>
       <c r="M7" s="1">
-        <v>0.65320699999999998</v>
+        <v>0.70034200000000002</v>
       </c>
       <c r="N7" s="1">
-        <v>0.65865200000000002</v>
+        <v>0.70295700000000005</v>
       </c>
       <c r="O7" s="1">
-        <v>0.66968899999999998</v>
+        <v>0.71022700000000005</v>
       </c>
       <c r="P7" s="1">
-        <v>0.67597799999999997</v>
+        <v>0.71989300000000001</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.68329600000000001</v>
+        <v>0.72187299999999999</v>
       </c>
       <c r="R7" s="1">
-        <v>0.69506999999999997</v>
+        <v>0.72707599999999994</v>
       </c>
       <c r="S7" s="1">
-        <v>0.70337499999999997</v>
+        <v>0.73126800000000003</v>
       </c>
       <c r="T7" s="1">
-        <v>0.71153100000000002</v>
+        <v>0.74210399999999999</v>
       </c>
       <c r="U7" s="1">
-        <v>0.72502500000000003</v>
+        <v>0.74754799999999999</v>
       </c>
       <c r="V7" s="1">
-        <v>0.74875000000000003</v>
+        <v>0.75178500000000004</v>
       </c>
       <c r="W7" s="1">
-        <v>0.75534999999999997</v>
+        <v>0.75243000000000004</v>
       </c>
       <c r="X7" s="1">
-        <v>0.73794999999999999</v>
+        <v>0.75530200000000003</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.78290099999999996</v>
+        <v>0.69600600000000001</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>0.59590600000000005</v>
+        <v>0.63342900000000002</v>
       </c>
       <c r="B8" s="1">
-        <v>0.59780500000000003</v>
+        <v>0.63675899999999996</v>
       </c>
       <c r="C8" s="1">
-        <v>0.60184599999999999</v>
+        <v>0.64264399999999999</v>
       </c>
       <c r="D8" s="1">
-        <v>0.60557700000000003</v>
+        <v>0.64936499999999997</v>
       </c>
       <c r="E8" s="1">
-        <v>0.60778799999999999</v>
+        <v>0.653115</v>
       </c>
       <c r="F8" s="1">
-        <v>0.611174</v>
+        <v>0.65914600000000001</v>
       </c>
       <c r="G8" s="1">
-        <v>0.61805600000000005</v>
+        <v>0.66617300000000002</v>
       </c>
       <c r="H8" s="1">
-        <v>0.62231499999999995</v>
+        <v>0.67366800000000004</v>
       </c>
       <c r="I8" s="1">
-        <v>0.62739400000000001</v>
+        <v>0.68183800000000006</v>
       </c>
       <c r="J8" s="1">
-        <v>0.63461199999999995</v>
+        <v>0.68488800000000005</v>
       </c>
       <c r="K8" s="1">
-        <v>0.64069600000000004</v>
+        <v>0.689863</v>
       </c>
       <c r="L8" s="1">
-        <v>0.64602099999999996</v>
+        <v>0.69537700000000002</v>
       </c>
       <c r="M8" s="1">
-        <v>0.65330600000000005</v>
+        <v>0.70227200000000001</v>
       </c>
       <c r="N8" s="1">
-        <v>0.65915299999999999</v>
+        <v>0.70433299999999999</v>
       </c>
       <c r="O8" s="1">
-        <v>0.66971499999999995</v>
+        <v>0.71091300000000002</v>
       </c>
       <c r="P8" s="1">
-        <v>0.67626900000000001</v>
+        <v>0.71964300000000003</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.68398999999999999</v>
+        <v>0.72174499999999997</v>
       </c>
       <c r="R8" s="1">
-        <v>0.69637400000000005</v>
+        <v>0.72762099999999996</v>
       </c>
       <c r="S8" s="1">
-        <v>0.70303800000000005</v>
+        <v>0.73143599999999998</v>
       </c>
       <c r="T8" s="1">
-        <v>0.70899699999999999</v>
+        <v>0.74317299999999997</v>
       </c>
       <c r="U8" s="1">
-        <v>0.723665</v>
+        <v>0.74883900000000003</v>
       </c>
       <c r="V8" s="1">
-        <v>0.74709999999999999</v>
+        <v>0.75444299999999997</v>
       </c>
       <c r="W8" s="1">
-        <v>0.75369600000000003</v>
+        <v>0.75370000000000004</v>
       </c>
       <c r="X8" s="1">
-        <v>0.73467099999999996</v>
+        <v>0.75740799999999997</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.77858499999999997</v>
+        <v>0.69242599999999999</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
-        <v>0.59841599999999995</v>
+        <v>0.63418600000000003</v>
       </c>
       <c r="B9" s="1">
-        <v>0.60014599999999996</v>
+        <v>0.63748000000000005</v>
       </c>
       <c r="C9" s="1">
-        <v>0.60471299999999995</v>
+        <v>0.64307099999999995</v>
       </c>
       <c r="D9" s="1">
-        <v>0.60877099999999995</v>
+        <v>0.64968000000000004</v>
       </c>
       <c r="E9" s="1">
-        <v>0.61126899999999995</v>
+        <v>0.65242199999999995</v>
       </c>
       <c r="F9" s="1">
-        <v>0.61478500000000003</v>
+        <v>0.65801299999999996</v>
       </c>
       <c r="G9" s="1">
-        <v>0.62214700000000001</v>
+        <v>0.66429800000000006</v>
       </c>
       <c r="H9" s="1">
-        <v>0.62667499999999998</v>
+        <v>0.67183999999999999</v>
       </c>
       <c r="I9" s="1">
-        <v>0.63213399999999997</v>
+        <v>0.68057100000000004</v>
       </c>
       <c r="J9" s="1">
-        <v>0.63813699999999995</v>
+        <v>0.68325899999999995</v>
       </c>
       <c r="K9" s="1">
-        <v>0.64305199999999996</v>
+        <v>0.68721900000000002</v>
       </c>
       <c r="L9" s="1">
-        <v>0.64864699999999997</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="M9" s="1">
-        <v>0.65648700000000004</v>
+        <v>0.69843200000000005</v>
       </c>
       <c r="N9" s="1">
-        <v>0.66311399999999998</v>
+        <v>0.70117499999999999</v>
       </c>
       <c r="O9" s="1">
-        <v>0.67294200000000004</v>
+        <v>0.70797500000000002</v>
       </c>
       <c r="P9" s="1">
-        <v>0.67926299999999995</v>
+        <v>0.71740499999999996</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.68867599999999995</v>
+        <v>0.72055899999999995</v>
       </c>
       <c r="R9" s="1">
-        <v>0.69825899999999996</v>
+        <v>0.72634299999999996</v>
       </c>
       <c r="S9" s="1">
-        <v>0.70351900000000001</v>
+        <v>0.73160800000000004</v>
       </c>
       <c r="T9" s="1">
-        <v>0.71046399999999998</v>
+        <v>0.74355499999999997</v>
       </c>
       <c r="U9" s="1">
-        <v>0.72547399999999995</v>
+        <v>0.74770199999999998</v>
       </c>
       <c r="V9" s="1">
-        <v>0.75193699999999997</v>
+        <v>0.75473999999999997</v>
       </c>
       <c r="W9" s="1">
-        <v>0.754216</v>
+        <v>0.75181299999999995</v>
       </c>
       <c r="X9" s="1">
-        <v>0.738201</v>
+        <v>0.75447399999999998</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.77300400000000002</v>
+        <v>0.68889199999999995</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
-        <v>0.59920200000000001</v>
+        <v>0.63893100000000003</v>
       </c>
       <c r="B10" s="1">
-        <v>0.60080500000000003</v>
+        <v>0.64263800000000004</v>
       </c>
       <c r="C10" s="1">
-        <v>0.60526000000000002</v>
+        <v>0.64705199999999996</v>
       </c>
       <c r="D10" s="1">
-        <v>0.60884400000000005</v>
+        <v>0.65386599999999995</v>
       </c>
       <c r="E10" s="1">
-        <v>0.61194000000000004</v>
+        <v>0.65688100000000005</v>
       </c>
       <c r="F10" s="1">
-        <v>0.615263</v>
+        <v>0.66193900000000006</v>
       </c>
       <c r="G10" s="1">
-        <v>0.62156900000000004</v>
+        <v>0.66824300000000003</v>
       </c>
       <c r="H10" s="1">
-        <v>0.62645899999999999</v>
+        <v>0.67619899999999999</v>
       </c>
       <c r="I10" s="1">
-        <v>0.63130600000000003</v>
+        <v>0.68498800000000004</v>
       </c>
       <c r="J10" s="1">
-        <v>0.63789499999999999</v>
+        <v>0.68731200000000003</v>
       </c>
       <c r="K10" s="1">
-        <v>0.64271400000000001</v>
+        <v>0.69122499999999998</v>
       </c>
       <c r="L10" s="1">
-        <v>0.64849000000000001</v>
+        <v>0.69777</v>
       </c>
       <c r="M10" s="1">
-        <v>0.655389</v>
+        <v>0.70276799999999995</v>
       </c>
       <c r="N10" s="1">
-        <v>0.66093299999999999</v>
+        <v>0.70491300000000001</v>
       </c>
       <c r="O10" s="1">
-        <v>0.67045600000000005</v>
+        <v>0.711561</v>
       </c>
       <c r="P10" s="1">
-        <v>0.676983</v>
+        <v>0.72100299999999995</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.68546700000000005</v>
+        <v>0.72410399999999997</v>
       </c>
       <c r="R10" s="1">
-        <v>0.69472299999999998</v>
+        <v>0.73139900000000002</v>
       </c>
       <c r="S10" s="1">
-        <v>0.70155999999999996</v>
+        <v>0.73610500000000001</v>
       </c>
       <c r="T10" s="1">
-        <v>0.70807699999999996</v>
+        <v>0.74704300000000001</v>
       </c>
       <c r="U10" s="1">
-        <v>0.72344600000000003</v>
+        <v>0.75116899999999998</v>
       </c>
       <c r="V10" s="1">
-        <v>0.751054</v>
+        <v>0.759436</v>
       </c>
       <c r="W10" s="1">
-        <v>0.75407400000000002</v>
+        <v>0.75359200000000004</v>
       </c>
       <c r="X10" s="1">
-        <v>0.74457399999999996</v>
+        <v>0.75641899999999995</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.76756899999999995</v>
+        <v>0.69138100000000002</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
-        <v>0.60030300000000003</v>
+        <v>0.64188599999999996</v>
       </c>
       <c r="B11" s="1">
-        <v>0.60197400000000001</v>
+        <v>0.64571400000000001</v>
       </c>
       <c r="C11" s="1">
-        <v>0.60658500000000004</v>
+        <v>0.64961100000000005</v>
       </c>
       <c r="D11" s="1">
-        <v>0.61046500000000004</v>
+        <v>0.65549599999999997</v>
       </c>
       <c r="E11" s="1">
-        <v>0.614035</v>
+        <v>0.65883700000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>0.61742699999999995</v>
+        <v>0.663775</v>
       </c>
       <c r="G11" s="1">
-        <v>0.62226300000000001</v>
+        <v>0.66999699999999995</v>
       </c>
       <c r="H11" s="1">
-        <v>0.62564900000000001</v>
+        <v>0.67861000000000005</v>
       </c>
       <c r="I11" s="1">
-        <v>0.629409</v>
+        <v>0.68629899999999999</v>
       </c>
       <c r="J11" s="1">
-        <v>0.63625600000000004</v>
+        <v>0.68790200000000001</v>
       </c>
       <c r="K11" s="1">
-        <v>0.64123799999999997</v>
+        <v>0.69116999999999995</v>
       </c>
       <c r="L11" s="1">
-        <v>0.64633700000000005</v>
+        <v>0.69801299999999999</v>
       </c>
       <c r="M11" s="1">
-        <v>0.65349400000000002</v>
+        <v>0.70317399999999997</v>
       </c>
       <c r="N11" s="1">
-        <v>0.65875700000000004</v>
+        <v>0.70643500000000004</v>
       </c>
       <c r="O11" s="1">
-        <v>0.66890099999999997</v>
+        <v>0.71261300000000005</v>
       </c>
       <c r="P11" s="1">
-        <v>0.67377900000000002</v>
+        <v>0.72044399999999997</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.68258399999999997</v>
+        <v>0.72423999999999999</v>
       </c>
       <c r="R11" s="1">
-        <v>0.69106500000000004</v>
+        <v>0.73176799999999997</v>
       </c>
       <c r="S11" s="1">
-        <v>0.69855299999999998</v>
+        <v>0.736294</v>
       </c>
       <c r="T11" s="1">
-        <v>0.70465100000000003</v>
+        <v>0.74604899999999996</v>
       </c>
       <c r="U11" s="1">
-        <v>0.71931599999999996</v>
+        <v>0.74805200000000005</v>
       </c>
       <c r="V11" s="1">
-        <v>0.74682499999999996</v>
+        <v>0.75529599999999997</v>
       </c>
       <c r="W11" s="1">
-        <v>0.75072799999999995</v>
+        <v>0.75017800000000001</v>
       </c>
       <c r="X11" s="1">
-        <v>0.74165300000000001</v>
+        <v>0.75205699999999998</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.76179200000000002</v>
+        <v>0.689967</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
-        <v>0.59911599999999998</v>
+        <v>0.64620699999999998</v>
       </c>
       <c r="B12" s="1">
-        <v>0.60105799999999998</v>
+        <v>0.65034800000000004</v>
       </c>
       <c r="C12" s="1">
-        <v>0.60581200000000002</v>
+        <v>0.65374299999999996</v>
       </c>
       <c r="D12" s="1">
-        <v>0.60993799999999998</v>
+        <v>0.65865799999999997</v>
       </c>
       <c r="E12" s="1">
-        <v>0.61428400000000005</v>
+        <v>0.66120900000000005</v>
       </c>
       <c r="F12" s="1">
-        <v>0.618313</v>
+        <v>0.66596900000000003</v>
       </c>
       <c r="G12" s="1">
-        <v>0.62329599999999996</v>
+        <v>0.67202300000000004</v>
       </c>
       <c r="H12" s="1">
-        <v>0.62673900000000005</v>
+        <v>0.67915899999999996</v>
       </c>
       <c r="I12" s="1">
-        <v>0.63049299999999997</v>
+        <v>0.68623599999999996</v>
       </c>
       <c r="J12" s="1">
-        <v>0.636185</v>
+        <v>0.68785200000000002</v>
       </c>
       <c r="K12" s="1">
-        <v>0.64055099999999998</v>
+        <v>0.69104100000000002</v>
       </c>
       <c r="L12" s="1">
-        <v>0.64536000000000004</v>
+        <v>0.69803400000000004</v>
       </c>
       <c r="M12" s="1">
-        <v>0.65305599999999997</v>
+        <v>0.70252300000000001</v>
       </c>
       <c r="N12" s="1">
-        <v>0.65984900000000002</v>
+        <v>0.70684899999999995</v>
       </c>
       <c r="O12" s="1">
-        <v>0.67040200000000005</v>
+        <v>0.712947</v>
       </c>
       <c r="P12" s="1">
-        <v>0.675701</v>
+        <v>0.72062000000000004</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.68243900000000002</v>
+        <v>0.72417600000000004</v>
       </c>
       <c r="R12" s="1">
-        <v>0.69125400000000004</v>
+        <v>0.73258900000000005</v>
       </c>
       <c r="S12" s="1">
-        <v>0.69543699999999997</v>
+        <v>0.73675500000000005</v>
       </c>
       <c r="T12" s="1">
-        <v>0.70195200000000002</v>
+        <v>0.745251</v>
       </c>
       <c r="U12" s="1">
-        <v>0.716839</v>
+        <v>0.74723300000000004</v>
       </c>
       <c r="V12" s="1">
-        <v>0.74210100000000001</v>
+        <v>0.75409099999999996</v>
       </c>
       <c r="W12" s="1">
-        <v>0.74823300000000004</v>
+        <v>0.75134999999999996</v>
       </c>
       <c r="X12" s="1">
-        <v>0.73987199999999997</v>
+        <v>0.75123899999999999</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.77075800000000005</v>
+        <v>0.68858900000000001</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
-        <v>0.59758500000000003</v>
+        <v>0.64516300000000004</v>
       </c>
       <c r="B13" s="1">
-        <v>0.59965100000000005</v>
+        <v>0.648312</v>
       </c>
       <c r="C13" s="1">
-        <v>0.60395399999999999</v>
+        <v>0.65190999999999999</v>
       </c>
       <c r="D13" s="1">
-        <v>0.60780999999999996</v>
+        <v>0.65661400000000003</v>
       </c>
       <c r="E13" s="1">
-        <v>0.61214900000000005</v>
+        <v>0.65846899999999997</v>
       </c>
       <c r="F13" s="1">
-        <v>0.61685999999999996</v>
+        <v>0.66190700000000002</v>
       </c>
       <c r="G13" s="1">
-        <v>0.62041800000000003</v>
+        <v>0.66783999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>0.62377300000000002</v>
+        <v>0.67537000000000003</v>
       </c>
       <c r="I13" s="1">
-        <v>0.62792999999999999</v>
+        <v>0.68155399999999999</v>
       </c>
       <c r="J13" s="1">
-        <v>0.63286699999999996</v>
+        <v>0.68381999999999998</v>
       </c>
       <c r="K13" s="1">
-        <v>0.63855399999999995</v>
+        <v>0.68569199999999997</v>
       </c>
       <c r="L13" s="1">
-        <v>0.64337900000000003</v>
+        <v>0.69209900000000002</v>
       </c>
       <c r="M13" s="1">
-        <v>0.65124700000000002</v>
+        <v>0.69662900000000005</v>
       </c>
       <c r="N13" s="1">
-        <v>0.65821200000000002</v>
+        <v>0.70036600000000004</v>
       </c>
       <c r="O13" s="1">
-        <v>0.66934700000000003</v>
+        <v>0.70778099999999999</v>
       </c>
       <c r="P13" s="1">
-        <v>0.67596800000000001</v>
+        <v>0.71464000000000005</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.68218500000000004</v>
+        <v>0.71860100000000005</v>
       </c>
       <c r="R13" s="1">
-        <v>0.69106900000000004</v>
+        <v>0.72664499999999999</v>
       </c>
       <c r="S13" s="1">
-        <v>0.69285099999999999</v>
+        <v>0.73055099999999995</v>
       </c>
       <c r="T13" s="1">
-        <v>0.70115700000000003</v>
+        <v>0.740255</v>
       </c>
       <c r="U13" s="1">
-        <v>0.71286099999999997</v>
+        <v>0.73970599999999997</v>
       </c>
       <c r="V13" s="1">
-        <v>0.73663500000000004</v>
+        <v>0.74435700000000005</v>
       </c>
       <c r="W13" s="1">
-        <v>0.74758500000000006</v>
+        <v>0.74382400000000004</v>
       </c>
       <c r="X13" s="1">
-        <v>0.73651999999999995</v>
+        <v>0.74620799999999998</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.76229400000000003</v>
+        <v>0.68563799999999997</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
-        <v>0.59448699999999999</v>
+        <v>0.64013799999999998</v>
       </c>
       <c r="B14" s="1">
-        <v>0.59667000000000003</v>
+        <v>0.64337800000000001</v>
       </c>
       <c r="C14" s="1">
-        <v>0.60077899999999995</v>
+        <v>0.64657399999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.60501499999999997</v>
+        <v>0.65188400000000002</v>
       </c>
       <c r="E14" s="1">
-        <v>0.60951</v>
+        <v>0.65334899999999996</v>
       </c>
       <c r="F14" s="1">
-        <v>0.61424100000000004</v>
+        <v>0.65709499999999998</v>
       </c>
       <c r="G14" s="1">
-        <v>0.61688600000000005</v>
+        <v>0.66276599999999997</v>
       </c>
       <c r="H14" s="1">
-        <v>0.62090500000000004</v>
+        <v>0.66979500000000003</v>
       </c>
       <c r="I14" s="1">
-        <v>0.62510900000000003</v>
+        <v>0.67536499999999999</v>
       </c>
       <c r="J14" s="1">
-        <v>0.63013799999999998</v>
+        <v>0.67885099999999998</v>
       </c>
       <c r="K14" s="1">
-        <v>0.63455700000000004</v>
+        <v>0.68116299999999996</v>
       </c>
       <c r="L14" s="1">
-        <v>0.63904300000000003</v>
+        <v>0.68722899999999998</v>
       </c>
       <c r="M14" s="1">
-        <v>0.64774699999999996</v>
+        <v>0.69280900000000001</v>
       </c>
       <c r="N14" s="1">
-        <v>0.65544899999999995</v>
+        <v>0.69624900000000001</v>
       </c>
       <c r="O14" s="1">
-        <v>0.66809099999999999</v>
+        <v>0.70465500000000003</v>
       </c>
       <c r="P14" s="1">
-        <v>0.67526299999999995</v>
+        <v>0.71296999999999999</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.68043100000000001</v>
+        <v>0.71595900000000001</v>
       </c>
       <c r="R14" s="1">
-        <v>0.68865900000000002</v>
+        <v>0.72342399999999996</v>
       </c>
       <c r="S14" s="1">
-        <v>0.68903199999999998</v>
+        <v>0.72756600000000005</v>
       </c>
       <c r="T14" s="1">
-        <v>0.69701100000000005</v>
+        <v>0.73540000000000005</v>
       </c>
       <c r="U14" s="1">
-        <v>0.71122300000000005</v>
+        <v>0.73458599999999996</v>
       </c>
       <c r="V14" s="1">
-        <v>0.73629900000000004</v>
+        <v>0.74077499999999996</v>
       </c>
       <c r="W14" s="1">
-        <v>0.74361200000000005</v>
+        <v>0.73870000000000002</v>
       </c>
       <c r="X14" s="1">
-        <v>0.73003300000000004</v>
+        <v>0.74199000000000004</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.75322500000000003</v>
+        <v>0.69367400000000001</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
-        <v>0.59606000000000003</v>
+        <v>0.63384300000000005</v>
       </c>
       <c r="B15" s="1">
-        <v>0.59757099999999996</v>
+        <v>0.63655099999999998</v>
       </c>
       <c r="C15" s="1">
-        <v>0.60122900000000001</v>
+        <v>0.64001300000000005</v>
       </c>
       <c r="D15" s="1">
-        <v>0.60452700000000004</v>
+        <v>0.64486299999999996</v>
       </c>
       <c r="E15" s="1">
-        <v>0.60950599999999999</v>
+        <v>0.646451</v>
       </c>
       <c r="F15" s="1">
-        <v>0.61369899999999999</v>
+        <v>0.64996299999999996</v>
       </c>
       <c r="G15" s="1">
-        <v>0.61713899999999999</v>
+        <v>0.65573400000000004</v>
       </c>
       <c r="H15" s="1">
-        <v>0.62153000000000003</v>
+        <v>0.66311799999999999</v>
       </c>
       <c r="I15" s="1">
-        <v>0.62610200000000005</v>
+        <v>0.66829700000000003</v>
       </c>
       <c r="J15" s="1">
-        <v>0.630444</v>
+        <v>0.67095700000000003</v>
       </c>
       <c r="K15" s="1">
-        <v>0.63665400000000005</v>
+        <v>0.67361800000000005</v>
       </c>
       <c r="L15" s="1">
-        <v>0.64102400000000004</v>
+        <v>0.67940900000000004</v>
       </c>
       <c r="M15" s="1">
-        <v>0.64918600000000004</v>
+        <v>0.68518199999999996</v>
       </c>
       <c r="N15" s="1">
-        <v>0.65751700000000002</v>
+        <v>0.68792500000000001</v>
       </c>
       <c r="O15" s="1">
-        <v>0.67102700000000004</v>
+        <v>0.69761300000000004</v>
       </c>
       <c r="P15" s="1">
-        <v>0.67726799999999998</v>
+        <v>0.70506500000000005</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.68214600000000003</v>
+        <v>0.70865699999999998</v>
       </c>
       <c r="R15" s="1">
-        <v>0.68976000000000004</v>
+        <v>0.71525300000000003</v>
       </c>
       <c r="S15" s="1">
-        <v>0.69169999999999998</v>
+        <v>0.71596899999999997</v>
       </c>
       <c r="T15" s="1">
-        <v>0.69823299999999999</v>
+        <v>0.72438100000000005</v>
       </c>
       <c r="U15" s="1">
-        <v>0.70977900000000005</v>
+        <v>0.72555000000000003</v>
       </c>
       <c r="V15" s="1">
-        <v>0.73912299999999997</v>
+        <v>0.73209100000000005</v>
       </c>
       <c r="W15" s="1">
-        <v>0.74954699999999996</v>
+        <v>0.72714800000000002</v>
       </c>
       <c r="X15" s="1">
-        <v>0.73359799999999997</v>
+        <v>0.73303099999999999</v>
       </c>
       <c r="Y15" s="1">
-        <v>0.742259</v>
+        <v>0.68755500000000003</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
-        <v>0.59706099999999995</v>
+        <v>0.63593699999999997</v>
       </c>
       <c r="B16" s="1">
-        <v>0.59882500000000005</v>
+        <v>0.63929100000000005</v>
       </c>
       <c r="C16" s="1">
-        <v>0.60172999999999999</v>
+        <v>0.64212000000000002</v>
       </c>
       <c r="D16" s="1">
-        <v>0.60498700000000005</v>
+        <v>0.647011</v>
       </c>
       <c r="E16" s="1">
-        <v>0.60949299999999995</v>
+        <v>0.64860600000000002</v>
       </c>
       <c r="F16" s="1">
-        <v>0.61312199999999994</v>
+        <v>0.65268599999999999</v>
       </c>
       <c r="G16" s="1">
-        <v>0.61694099999999996</v>
+        <v>0.65855600000000003</v>
       </c>
       <c r="H16" s="1">
-        <v>0.62130200000000002</v>
+        <v>0.66590000000000005</v>
       </c>
       <c r="I16" s="1">
-        <v>0.62701099999999999</v>
+        <v>0.67013699999999998</v>
       </c>
       <c r="J16" s="1">
-        <v>0.63034800000000002</v>
+        <v>0.67329000000000006</v>
       </c>
       <c r="K16" s="1">
-        <v>0.63732200000000006</v>
+        <v>0.67673099999999997</v>
       </c>
       <c r="L16" s="1">
-        <v>0.64216300000000004</v>
+        <v>0.682176</v>
       </c>
       <c r="M16" s="1">
-        <v>0.65072700000000006</v>
+        <v>0.68927700000000003</v>
       </c>
       <c r="N16" s="1">
-        <v>0.65861999999999998</v>
+        <v>0.69261300000000003</v>
       </c>
       <c r="O16" s="1">
-        <v>0.67226600000000003</v>
+        <v>0.70119799999999999</v>
       </c>
       <c r="P16" s="1">
-        <v>0.67719099999999999</v>
+        <v>0.70739399999999997</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.68306999999999995</v>
+        <v>0.70986400000000005</v>
       </c>
       <c r="R16" s="1">
-        <v>0.69303400000000004</v>
+        <v>0.71797699999999998</v>
       </c>
       <c r="S16" s="1">
-        <v>0.69415199999999999</v>
+        <v>0.72101599999999999</v>
       </c>
       <c r="T16" s="1">
-        <v>0.70464199999999999</v>
+        <v>0.73005100000000001</v>
       </c>
       <c r="U16" s="1">
-        <v>0.71746699999999997</v>
+        <v>0.73221800000000004</v>
       </c>
       <c r="V16" s="1">
-        <v>0.74437799999999998</v>
+        <v>0.73542700000000005</v>
       </c>
       <c r="W16" s="1">
-        <v>0.75443800000000005</v>
+        <v>0.72661200000000004</v>
       </c>
       <c r="X16" s="1">
-        <v>0.74323700000000004</v>
+        <v>0.73356100000000002</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.74736800000000003</v>
+        <v>0.68074500000000004</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
-        <v>0.59617299999999995</v>
+        <v>0.63168599999999997</v>
       </c>
       <c r="B17" s="1">
-        <v>0.59850000000000003</v>
+        <v>0.63491600000000004</v>
       </c>
       <c r="C17" s="1">
-        <v>0.60124500000000003</v>
+        <v>0.636965</v>
       </c>
       <c r="D17" s="1">
-        <v>0.60443899999999995</v>
+        <v>0.64132900000000004</v>
       </c>
       <c r="E17" s="1">
-        <v>0.60959099999999999</v>
+        <v>0.64315800000000001</v>
       </c>
       <c r="F17" s="1">
-        <v>0.61244500000000002</v>
+        <v>0.64628799999999997</v>
       </c>
       <c r="G17" s="1">
-        <v>0.61480999999999997</v>
+        <v>0.65281199999999995</v>
       </c>
       <c r="H17" s="1">
-        <v>0.618923</v>
+        <v>0.659856</v>
       </c>
       <c r="I17" s="1">
-        <v>0.62543400000000005</v>
+        <v>0.66423600000000005</v>
       </c>
       <c r="J17" s="1">
-        <v>0.62894799999999995</v>
+        <v>0.66774500000000003</v>
       </c>
       <c r="K17" s="1">
-        <v>0.63542600000000005</v>
+        <v>0.67136099999999999</v>
       </c>
       <c r="L17" s="1">
-        <v>0.63980499999999996</v>
+        <v>0.67540900000000004</v>
       </c>
       <c r="M17" s="1">
-        <v>0.64722299999999999</v>
+        <v>0.68123900000000004</v>
       </c>
       <c r="N17" s="1">
-        <v>0.65541400000000005</v>
+        <v>0.68402799999999997</v>
       </c>
       <c r="O17" s="1">
-        <v>0.66852400000000001</v>
+        <v>0.69266899999999998</v>
       </c>
       <c r="P17" s="1">
-        <v>0.67218</v>
+        <v>0.69915899999999997</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.67549700000000001</v>
+        <v>0.70165</v>
       </c>
       <c r="R17" s="1">
-        <v>0.68726100000000001</v>
+        <v>0.71091499999999996</v>
       </c>
       <c r="S17" s="1">
-        <v>0.69022799999999995</v>
+        <v>0.71325799999999995</v>
       </c>
       <c r="T17" s="1">
-        <v>0.69688099999999997</v>
+        <v>0.72500900000000001</v>
       </c>
       <c r="U17" s="1">
-        <v>0.71022700000000005</v>
+        <v>0.72580900000000004</v>
       </c>
       <c r="V17" s="1">
-        <v>0.73891600000000002</v>
+        <v>0.72770800000000002</v>
       </c>
       <c r="W17" s="1">
-        <v>0.74546199999999996</v>
+        <v>0.71916199999999997</v>
       </c>
       <c r="X17" s="1">
-        <v>0.74047099999999999</v>
+        <v>0.72331500000000004</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.75047399999999997</v>
+        <v>0.67249899999999996</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
-        <v>0.59514999999999996</v>
+        <v>0.62998900000000002</v>
       </c>
       <c r="B18" s="1">
-        <v>0.59736900000000004</v>
+        <v>0.63286699999999996</v>
       </c>
       <c r="C18" s="1">
-        <v>0.599607</v>
+        <v>0.63560799999999995</v>
       </c>
       <c r="D18" s="1">
-        <v>0.60287400000000002</v>
+        <v>0.63955399999999996</v>
       </c>
       <c r="E18" s="1">
-        <v>0.60775100000000004</v>
+        <v>0.64101300000000005</v>
       </c>
       <c r="F18" s="1">
-        <v>0.61180599999999996</v>
+        <v>0.64375499999999997</v>
       </c>
       <c r="G18" s="1">
-        <v>0.614622</v>
+        <v>0.64955799999999997</v>
       </c>
       <c r="H18" s="1">
-        <v>0.61883600000000005</v>
+        <v>0.654999</v>
       </c>
       <c r="I18" s="1">
-        <v>0.62415900000000002</v>
+        <v>0.65973199999999999</v>
       </c>
       <c r="J18" s="1">
-        <v>0.62784399999999996</v>
+        <v>0.66301500000000002</v>
       </c>
       <c r="K18" s="1">
-        <v>0.63565300000000002</v>
+        <v>0.66772100000000001</v>
       </c>
       <c r="L18" s="1">
-        <v>0.64102700000000001</v>
+        <v>0.67089600000000005</v>
       </c>
       <c r="M18" s="1">
-        <v>0.65014099999999997</v>
+        <v>0.67663499999999999</v>
       </c>
       <c r="N18" s="1">
-        <v>0.65920500000000004</v>
+        <v>0.67908999999999997</v>
       </c>
       <c r="O18" s="1">
-        <v>0.67158499999999999</v>
+        <v>0.68679599999999996</v>
       </c>
       <c r="P18" s="1">
-        <v>0.674454</v>
+        <v>0.69340800000000002</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.67753699999999994</v>
+        <v>0.69425099999999995</v>
       </c>
       <c r="R18" s="1">
-        <v>0.69080299999999994</v>
+        <v>0.69930000000000003</v>
       </c>
       <c r="S18" s="1">
-        <v>0.69500399999999996</v>
+        <v>0.70004100000000002</v>
       </c>
       <c r="T18" s="1">
-        <v>0.701233</v>
+        <v>0.70998899999999998</v>
       </c>
       <c r="U18" s="1">
-        <v>0.71266499999999999</v>
+        <v>0.71327399999999996</v>
       </c>
       <c r="V18" s="1">
-        <v>0.7389</v>
+        <v>0.71736699999999998</v>
       </c>
       <c r="W18" s="1">
-        <v>0.74492400000000003</v>
+        <v>0.70527899999999999</v>
       </c>
       <c r="X18" s="1">
-        <v>0.73543400000000003</v>
+        <v>0.71464499999999997</v>
       </c>
       <c r="Y18" s="1">
-        <v>0.74056100000000002</v>
+        <v>0.66834499999999997</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
-        <v>0.59034900000000001</v>
+        <v>0.63003100000000001</v>
       </c>
       <c r="B19" s="1">
-        <v>0.59280100000000002</v>
+        <v>0.63334800000000002</v>
       </c>
       <c r="C19" s="1">
-        <v>0.59368699999999996</v>
+        <v>0.63491200000000003</v>
       </c>
       <c r="D19" s="1">
-        <v>0.59590699999999996</v>
+        <v>0.63851400000000003</v>
       </c>
       <c r="E19" s="1">
-        <v>0.60137399999999996</v>
+        <v>0.63971199999999995</v>
       </c>
       <c r="F19" s="1">
-        <v>0.60562199999999999</v>
+        <v>0.64308399999999999</v>
       </c>
       <c r="G19" s="1">
-        <v>0.60977700000000001</v>
+        <v>0.64937299999999998</v>
       </c>
       <c r="H19" s="1">
-        <v>0.61400600000000005</v>
+        <v>0.65510500000000005</v>
       </c>
       <c r="I19" s="1">
-        <v>0.62130200000000002</v>
+        <v>0.65924899999999997</v>
       </c>
       <c r="J19" s="1">
-        <v>0.62534900000000004</v>
+        <v>0.66354400000000002</v>
       </c>
       <c r="K19" s="1">
-        <v>0.63393200000000005</v>
+        <v>0.66770099999999999</v>
       </c>
       <c r="L19" s="1">
-        <v>0.63834000000000002</v>
+        <v>0.67189900000000002</v>
       </c>
       <c r="M19" s="1">
-        <v>0.64781999999999995</v>
+        <v>0.67783000000000004</v>
       </c>
       <c r="N19" s="1">
-        <v>0.65643799999999997</v>
+        <v>0.68092600000000003</v>
       </c>
       <c r="O19" s="1">
-        <v>0.66989799999999999</v>
+        <v>0.68917700000000004</v>
       </c>
       <c r="P19" s="1">
-        <v>0.66969900000000004</v>
+        <v>0.696932</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.67233600000000004</v>
+        <v>0.69894500000000004</v>
       </c>
       <c r="R19" s="1">
-        <v>0.68944000000000005</v>
+        <v>0.70559400000000005</v>
       </c>
       <c r="S19" s="1">
-        <v>0.69295700000000005</v>
+        <v>0.70762999999999998</v>
       </c>
       <c r="T19" s="1">
-        <v>0.69846200000000003</v>
+        <v>0.71616800000000003</v>
       </c>
       <c r="U19" s="1">
-        <v>0.70757099999999995</v>
+        <v>0.72244900000000001</v>
       </c>
       <c r="V19" s="1">
-        <v>0.73208099999999998</v>
+        <v>0.73364099999999999</v>
       </c>
       <c r="W19" s="1">
-        <v>0.73633800000000005</v>
+        <v>0.71018800000000004</v>
       </c>
       <c r="X19" s="1">
-        <v>0.71965800000000002</v>
+        <v>0.71877999999999997</v>
       </c>
       <c r="Y19" s="1">
-        <v>0.72774300000000003</v>
+        <v>0.68623999999999996</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
-        <v>0.583229</v>
+        <v>0.62872700000000004</v>
       </c>
       <c r="B20" s="1">
-        <v>0.58606199999999997</v>
+        <v>0.63309599999999999</v>
       </c>
       <c r="C20" s="1">
-        <v>0.58759399999999995</v>
+        <v>0.63459200000000004</v>
       </c>
       <c r="D20" s="1">
-        <v>0.58962999999999999</v>
+        <v>0.63689300000000004</v>
       </c>
       <c r="E20" s="1">
-        <v>0.593468</v>
+        <v>0.63792599999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>0.59731999999999996</v>
+        <v>0.641204</v>
       </c>
       <c r="G20" s="1">
-        <v>0.60146100000000002</v>
+        <v>0.64607999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>0.60583299999999995</v>
+        <v>0.64990199999999998</v>
       </c>
       <c r="I20" s="1">
-        <v>0.61300299999999996</v>
+        <v>0.65334800000000004</v>
       </c>
       <c r="J20" s="1">
-        <v>0.61715500000000001</v>
+        <v>0.65798599999999996</v>
       </c>
       <c r="K20" s="1">
-        <v>0.62521599999999999</v>
+        <v>0.66269599999999995</v>
       </c>
       <c r="L20" s="1">
-        <v>0.62853300000000001</v>
+        <v>0.66808699999999999</v>
       </c>
       <c r="M20" s="1">
-        <v>0.64103600000000005</v>
+        <v>0.67543900000000001</v>
       </c>
       <c r="N20" s="1">
-        <v>0.65092799999999995</v>
+        <v>0.67745</v>
       </c>
       <c r="O20" s="1">
-        <v>0.66328799999999999</v>
+        <v>0.68623599999999996</v>
       </c>
       <c r="P20" s="1">
-        <v>0.66358600000000001</v>
+        <v>0.69296000000000002</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.66300400000000004</v>
+        <v>0.69586300000000001</v>
       </c>
       <c r="R20" s="1">
-        <v>0.67909399999999998</v>
+        <v>0.70274800000000004</v>
       </c>
       <c r="S20" s="1">
-        <v>0.68470600000000004</v>
+        <v>0.70548599999999995</v>
       </c>
       <c r="T20" s="1">
-        <v>0.69496999999999998</v>
+        <v>0.714086</v>
       </c>
       <c r="U20" s="1">
-        <v>0.69855999999999996</v>
+        <v>0.71833800000000003</v>
       </c>
       <c r="V20" s="1">
-        <v>0.72559899999999999</v>
+        <v>0.72850499999999996</v>
       </c>
       <c r="W20" s="1">
-        <v>0.73248000000000002</v>
+        <v>0.70649300000000004</v>
       </c>
       <c r="X20" s="1">
-        <v>0.71696499999999996</v>
+        <v>0.70965500000000004</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.70908400000000005</v>
+        <v>0.68183800000000006</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
-        <v>0.57758100000000001</v>
+        <v>0.61733300000000002</v>
       </c>
       <c r="B21" s="1">
-        <v>0.58083700000000005</v>
+        <v>0.62050099999999997</v>
       </c>
       <c r="C21" s="1">
-        <v>0.58189000000000002</v>
+        <v>0.62285500000000005</v>
       </c>
       <c r="D21" s="1">
-        <v>0.58597299999999997</v>
+        <v>0.62604400000000004</v>
       </c>
       <c r="E21" s="1">
-        <v>0.58757499999999996</v>
+        <v>0.62653099999999995</v>
       </c>
       <c r="F21" s="1">
-        <v>0.59154600000000002</v>
+        <v>0.63031099999999995</v>
       </c>
       <c r="G21" s="1">
-        <v>0.59589199999999998</v>
+        <v>0.63371599999999995</v>
       </c>
       <c r="H21" s="1">
-        <v>0.60133999999999999</v>
+        <v>0.63852900000000001</v>
       </c>
       <c r="I21" s="1">
-        <v>0.607429</v>
+        <v>0.64153899999999997</v>
       </c>
       <c r="J21" s="1">
-        <v>0.60953199999999996</v>
+        <v>0.64733499999999999</v>
       </c>
       <c r="K21" s="1">
-        <v>0.61872000000000005</v>
+        <v>0.65238799999999997</v>
       </c>
       <c r="L21" s="1">
-        <v>0.61909999999999998</v>
+        <v>0.65640799999999999</v>
       </c>
       <c r="M21" s="1">
-        <v>0.62812699999999999</v>
+        <v>0.66197600000000001</v>
       </c>
       <c r="N21" s="1">
-        <v>0.63702999999999999</v>
+        <v>0.66651499999999997</v>
       </c>
       <c r="O21" s="1">
-        <v>0.64736899999999997</v>
+        <v>0.67277399999999998</v>
       </c>
       <c r="P21" s="1">
-        <v>0.64824899999999996</v>
+        <v>0.68357299999999999</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.64860200000000001</v>
+        <v>0.68444700000000003</v>
       </c>
       <c r="R21" s="1">
-        <v>0.66415500000000005</v>
+        <v>0.69050699999999998</v>
       </c>
       <c r="S21" s="1">
-        <v>0.66807899999999998</v>
+        <v>0.69155500000000003</v>
       </c>
       <c r="T21" s="1">
-        <v>0.67474000000000001</v>
+        <v>0.69930000000000003</v>
       </c>
       <c r="U21" s="1">
-        <v>0.67768499999999998</v>
+        <v>0.706762</v>
       </c>
       <c r="V21" s="1">
-        <v>0.71039300000000005</v>
+        <v>0.71732700000000005</v>
       </c>
       <c r="W21" s="1">
-        <v>0.71612500000000001</v>
+        <v>0.70157800000000003</v>
       </c>
       <c r="X21" s="1">
-        <v>0.69806999999999997</v>
+        <v>0.69876499999999997</v>
       </c>
       <c r="Y21" s="1">
-        <v>0.68462599999999996</v>
+        <v>0.66268300000000002</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
-        <v>0.56272</v>
+        <v>0.594947</v>
       </c>
       <c r="B22" s="1">
-        <v>0.56476000000000004</v>
+        <v>0.59777899999999995</v>
       </c>
       <c r="C22" s="1">
-        <v>0.56687600000000005</v>
+        <v>0.59878900000000002</v>
       </c>
       <c r="D22" s="1">
-        <v>0.570604</v>
+        <v>0.60259399999999996</v>
       </c>
       <c r="E22" s="1">
-        <v>0.57247099999999995</v>
+        <v>0.60333099999999995</v>
       </c>
       <c r="F22" s="1">
-        <v>0.57576099999999997</v>
+        <v>0.605217</v>
       </c>
       <c r="G22" s="1">
-        <v>0.57991999999999999</v>
+        <v>0.60854399999999997</v>
       </c>
       <c r="H22" s="1">
-        <v>0.58454600000000001</v>
+        <v>0.61513099999999998</v>
       </c>
       <c r="I22" s="1">
-        <v>0.58573299999999995</v>
+        <v>0.62010699999999996</v>
       </c>
       <c r="J22" s="1">
-        <v>0.58950100000000005</v>
+        <v>0.62536199999999997</v>
       </c>
       <c r="K22" s="1">
-        <v>0.598993</v>
+        <v>0.63</v>
       </c>
       <c r="L22" s="1">
-        <v>0.59804100000000004</v>
+        <v>0.63340399999999997</v>
       </c>
       <c r="M22" s="1">
-        <v>0.60528999999999999</v>
+        <v>0.63847500000000001</v>
       </c>
       <c r="N22" s="1">
-        <v>0.612591</v>
+        <v>0.64371900000000004</v>
       </c>
       <c r="O22" s="1">
-        <v>0.62279899999999999</v>
+        <v>0.65165799999999996</v>
       </c>
       <c r="P22" s="1">
-        <v>0.62599800000000005</v>
+        <v>0.65857500000000002</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.62509899999999996</v>
+        <v>0.66045100000000001</v>
       </c>
       <c r="R22" s="1">
-        <v>0.64022000000000001</v>
+        <v>0.66456899999999997</v>
       </c>
       <c r="S22" s="1">
-        <v>0.64335100000000001</v>
+        <v>0.66796599999999995</v>
       </c>
       <c r="T22" s="1">
-        <v>0.65138700000000005</v>
+        <v>0.67114700000000005</v>
       </c>
       <c r="U22" s="1">
-        <v>0.65433799999999998</v>
+        <v>0.68559899999999996</v>
       </c>
       <c r="V22" s="1">
-        <v>0.68577200000000005</v>
+        <v>0.696631</v>
       </c>
       <c r="W22" s="1">
-        <v>0.69386800000000004</v>
+        <v>0.67801199999999995</v>
       </c>
       <c r="X22" s="1">
-        <v>0.69070299999999996</v>
+        <v>0.67417700000000003</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.66694900000000001</v>
+        <v>0.63190599999999997</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
-        <v>0.54009600000000002</v>
+        <v>0.59044300000000005</v>
       </c>
       <c r="B23" s="1">
-        <v>0.53871500000000005</v>
+        <v>0.59054799999999996</v>
       </c>
       <c r="C23" s="1">
-        <v>0.54121900000000001</v>
+        <v>0.59041399999999999</v>
       </c>
       <c r="D23" s="1">
-        <v>0.54345200000000005</v>
+        <v>0.59241900000000003</v>
       </c>
       <c r="E23" s="1">
-        <v>0.54571599999999998</v>
+        <v>0.59340199999999999</v>
       </c>
       <c r="F23" s="1">
-        <v>0.54771700000000001</v>
+        <v>0.595028</v>
       </c>
       <c r="G23" s="1">
-        <v>0.55028999999999995</v>
+        <v>0.59992999999999996</v>
       </c>
       <c r="H23" s="1">
-        <v>0.55472600000000005</v>
+        <v>0.60418300000000003</v>
       </c>
       <c r="I23" s="1">
-        <v>0.55776899999999996</v>
+        <v>0.61136199999999996</v>
       </c>
       <c r="J23" s="1">
-        <v>0.56162199999999995</v>
+        <v>0.61260199999999998</v>
       </c>
       <c r="K23" s="1">
-        <v>0.573353</v>
+        <v>0.61795100000000003</v>
       </c>
       <c r="L23" s="1">
-        <v>0.57287900000000003</v>
+        <v>0.61901799999999996</v>
       </c>
       <c r="M23" s="1">
-        <v>0.57867599999999997</v>
+        <v>0.62195500000000004</v>
       </c>
       <c r="N23" s="1">
-        <v>0.58906700000000001</v>
+        <v>0.62673900000000005</v>
       </c>
       <c r="O23" s="1">
-        <v>0.59806199999999998</v>
+        <v>0.62973500000000004</v>
       </c>
       <c r="P23" s="1">
-        <v>0.604711</v>
+        <v>0.63911799999999996</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.60830899999999999</v>
+        <v>0.64432100000000003</v>
       </c>
       <c r="R23" s="1">
-        <v>0.62812299999999999</v>
+        <v>0.64730600000000005</v>
       </c>
       <c r="S23" s="1">
-        <v>0.62899300000000002</v>
+        <v>0.65582799999999997</v>
       </c>
       <c r="T23" s="1">
-        <v>0.63364900000000002</v>
+        <v>0.66033500000000001</v>
       </c>
       <c r="U23" s="1">
-        <v>0.63695299999999999</v>
+        <v>0.67239099999999996</v>
       </c>
       <c r="V23" s="1">
-        <v>0.65385099999999996</v>
+        <v>0.67542999999999997</v>
       </c>
       <c r="W23" s="1">
-        <v>0.65455300000000005</v>
+        <v>0.66457200000000005</v>
       </c>
       <c r="X23" s="1">
-        <v>0.64964200000000005</v>
+        <v>0.65776699999999999</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.62698900000000002</v>
+        <v>0.64354800000000001</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
-        <v>0.520038</v>
+        <v>0.527729</v>
       </c>
       <c r="B24" s="1">
-        <v>0.51923600000000003</v>
+        <v>0.52715999999999996</v>
       </c>
       <c r="C24" s="1">
-        <v>0.52051000000000003</v>
+        <v>0.52788100000000004</v>
       </c>
       <c r="D24" s="1">
-        <v>0.51966100000000004</v>
+        <v>0.52973599999999998</v>
       </c>
       <c r="E24" s="1">
-        <v>0.51882300000000003</v>
+        <v>0.530362</v>
       </c>
       <c r="F24" s="1">
-        <v>0.51952299999999996</v>
+        <v>0.53225999999999996</v>
       </c>
       <c r="G24" s="1">
-        <v>0.51873499999999995</v>
+        <v>0.53486599999999995</v>
       </c>
       <c r="H24" s="1">
-        <v>0.52083999999999997</v>
+        <v>0.53841300000000003</v>
       </c>
       <c r="I24" s="1">
-        <v>0.52088400000000001</v>
+        <v>0.54214899999999999</v>
       </c>
       <c r="J24" s="1">
-        <v>0.52503299999999997</v>
+        <v>0.54178999999999999</v>
       </c>
       <c r="K24" s="1">
-        <v>0.53816799999999998</v>
+        <v>0.547261</v>
       </c>
       <c r="L24" s="1">
-        <v>0.53555799999999998</v>
+        <v>0.54889600000000005</v>
       </c>
       <c r="M24" s="1">
-        <v>0.54006399999999999</v>
+        <v>0.55136499999999999</v>
       </c>
       <c r="N24" s="1">
-        <v>0.54659199999999997</v>
+        <v>0.55600799999999995</v>
       </c>
       <c r="O24" s="1">
-        <v>0.55566599999999999</v>
+        <v>0.55865200000000004</v>
       </c>
       <c r="P24" s="1">
-        <v>0.56417300000000004</v>
+        <v>0.56875500000000001</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.56340900000000005</v>
+        <v>0.57606999999999997</v>
       </c>
       <c r="R24" s="1">
-        <v>0.57951600000000003</v>
+        <v>0.57401199999999997</v>
       </c>
       <c r="S24" s="1">
-        <v>0.58269800000000005</v>
+        <v>0.58270299999999997</v>
       </c>
       <c r="T24" s="1">
-        <v>0.58689899999999995</v>
+        <v>0.58080500000000002</v>
       </c>
       <c r="U24" s="1">
-        <v>0.59623099999999996</v>
+        <v>0.59309699999999999</v>
       </c>
       <c r="V24" s="1">
-        <v>0.60846699999999998</v>
+        <v>0.59602500000000003</v>
       </c>
       <c r="W24" s="1">
-        <v>0.62043599999999999</v>
+        <v>0.58820700000000004</v>
       </c>
       <c r="X24" s="1">
-        <v>0.60803099999999999</v>
+        <v>0.60105799999999998</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.60630899999999999</v>
+        <v>0.60319999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
-        <v>0.43770799999999999</v>
+        <v>0.44573299999999999</v>
       </c>
       <c r="B25" s="1">
-        <v>0.43729099999999999</v>
+        <v>0.44565300000000002</v>
       </c>
       <c r="C25" s="1">
-        <v>0.437143</v>
+        <v>0.44516299999999998</v>
       </c>
       <c r="D25" s="1">
-        <v>0.436836</v>
+        <v>0.44772200000000001</v>
       </c>
       <c r="E25" s="1">
-        <v>0.43653900000000001</v>
+        <v>0.44720399999999999</v>
       </c>
       <c r="F25" s="1">
-        <v>0.43556400000000001</v>
+        <v>0.44631999999999999</v>
       </c>
       <c r="G25" s="1">
-        <v>0.43510199999999999</v>
+        <v>0.44590999999999997</v>
       </c>
       <c r="H25" s="1">
-        <v>0.43773200000000001</v>
+        <v>0.44829599999999997</v>
       </c>
       <c r="I25" s="1">
-        <v>0.43640600000000002</v>
+        <v>0.44769300000000001</v>
       </c>
       <c r="J25" s="1">
-        <v>0.43946400000000002</v>
+        <v>0.44647599999999998</v>
       </c>
       <c r="K25" s="1">
-        <v>0.45988699999999999</v>
+        <v>0.44888899999999998</v>
       </c>
       <c r="L25" s="1">
-        <v>0.458063</v>
+        <v>0.45123400000000002</v>
       </c>
       <c r="M25" s="1">
-        <v>0.46142300000000003</v>
+        <v>0.45622499999999999</v>
       </c>
       <c r="N25" s="1">
-        <v>0.47479199999999999</v>
+        <v>0.45838899999999999</v>
       </c>
       <c r="O25" s="1">
-        <v>0.47268500000000002</v>
+        <v>0.45674199999999998</v>
       </c>
       <c r="P25" s="1">
-        <v>0.47549799999999998</v>
+        <v>0.46098499999999998</v>
       </c>
       <c r="Q25" s="1">
-        <v>0.47135500000000002</v>
+        <v>0.46078799999999998</v>
       </c>
       <c r="R25" s="1">
-        <v>0.47878599999999999</v>
+        <v>0.46606500000000001</v>
       </c>
       <c r="S25" s="1">
-        <v>0.47942899999999999</v>
+        <v>0.46917399999999998</v>
       </c>
       <c r="T25" s="1">
-        <v>0.47691</v>
+        <v>0.46686499999999997</v>
       </c>
       <c r="U25" s="1">
-        <v>0.47678300000000001</v>
+        <v>0.47557899999999997</v>
       </c>
       <c r="V25" s="1">
-        <v>0.47422599999999998</v>
+        <v>0.48630800000000002</v>
       </c>
       <c r="W25" s="1">
-        <v>0.44709300000000002</v>
+        <v>0.49148599999999998</v>
       </c>
       <c r="X25" s="1">
-        <v>0.46081899999999998</v>
+        <v>0.50405</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.45347100000000001</v>
+        <v>0.47830299999999998</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9B7C1E-776E-4ADB-A8E4-F8475B51F7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F906D4-FCD1-48D5-93BF-B037D40E67BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,1927 +355,1927 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>0.62027500000000002</v>
+        <v>0.572272</v>
       </c>
       <c r="B1" s="1">
-        <v>0.62541199999999997</v>
+        <v>0.57640899999999995</v>
       </c>
       <c r="C1" s="1">
-        <v>0.63125399999999998</v>
+        <v>0.579175</v>
       </c>
       <c r="D1" s="1">
-        <v>0.63727900000000004</v>
+        <v>0.58387699999999998</v>
       </c>
       <c r="E1" s="1">
-        <v>0.64118200000000003</v>
+        <v>0.58683300000000005</v>
       </c>
       <c r="F1" s="1">
-        <v>0.64634599999999998</v>
+        <v>0.59157099999999996</v>
       </c>
       <c r="G1" s="1">
-        <v>0.65215500000000004</v>
+        <v>0.595024</v>
       </c>
       <c r="H1" s="1">
-        <v>0.662578</v>
+        <v>0.59992199999999996</v>
       </c>
       <c r="I1" s="1">
-        <v>0.67023600000000005</v>
+        <v>0.60562000000000005</v>
       </c>
       <c r="J1" s="1">
-        <v>0.67572699999999997</v>
+        <v>0.60960199999999998</v>
       </c>
       <c r="K1" s="1">
-        <v>0.680531</v>
+        <v>0.61582599999999998</v>
       </c>
       <c r="L1" s="1">
-        <v>0.68674400000000002</v>
+        <v>0.61981900000000001</v>
       </c>
       <c r="M1" s="1">
-        <v>0.69255199999999995</v>
+        <v>0.62619499999999995</v>
       </c>
       <c r="N1" s="1">
-        <v>0.69889199999999996</v>
+        <v>0.63338499999999998</v>
       </c>
       <c r="O1" s="1">
-        <v>0.70687100000000003</v>
+        <v>0.64135900000000001</v>
       </c>
       <c r="P1" s="1">
-        <v>0.71584400000000004</v>
+        <v>0.65266800000000003</v>
       </c>
       <c r="Q1" s="1">
-        <v>0.71933400000000003</v>
+        <v>0.65827599999999997</v>
       </c>
       <c r="R1" s="1">
-        <v>0.72343800000000003</v>
+        <v>0.66335699999999997</v>
       </c>
       <c r="S1" s="1">
-        <v>0.72945400000000005</v>
+        <v>0.67405599999999999</v>
       </c>
       <c r="T1" s="1">
-        <v>0.74185299999999998</v>
+        <v>0.69075399999999998</v>
       </c>
       <c r="U1" s="1">
-        <v>0.74719000000000002</v>
+        <v>0.69638900000000004</v>
       </c>
       <c r="V1" s="1">
-        <v>0.75383299999999998</v>
+        <v>0.70747000000000004</v>
       </c>
       <c r="W1" s="1">
-        <v>0.759544</v>
+        <v>0.73358000000000001</v>
       </c>
       <c r="X1" s="1">
-        <v>0.76107100000000005</v>
+        <v>0.74151199999999995</v>
       </c>
       <c r="Y1" s="1">
-        <v>0.69873300000000005</v>
+        <v>0.72225099999999998</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
-        <v>0.61995599999999995</v>
+        <v>0.57383499999999998</v>
       </c>
       <c r="B2" s="1">
-        <v>0.62448800000000004</v>
+        <v>0.57784000000000002</v>
       </c>
       <c r="C2" s="1">
-        <v>0.63013300000000005</v>
+        <v>0.58047300000000002</v>
       </c>
       <c r="D2" s="1">
-        <v>0.636382</v>
+        <v>0.58530499999999996</v>
       </c>
       <c r="E2" s="1">
-        <v>0.64039699999999999</v>
+        <v>0.58852800000000005</v>
       </c>
       <c r="F2" s="1">
-        <v>0.64598</v>
+        <v>0.59351500000000001</v>
       </c>
       <c r="G2" s="1">
-        <v>0.651999</v>
+        <v>0.59693200000000002</v>
       </c>
       <c r="H2" s="1">
-        <v>0.66241300000000003</v>
+        <v>0.60220399999999996</v>
       </c>
       <c r="I2" s="1">
-        <v>0.67025500000000005</v>
+        <v>0.607348</v>
       </c>
       <c r="J2" s="1">
-        <v>0.67538699999999996</v>
+        <v>0.61121199999999998</v>
       </c>
       <c r="K2" s="1">
-        <v>0.68046399999999996</v>
+        <v>0.61769700000000005</v>
       </c>
       <c r="L2" s="1">
-        <v>0.68660699999999997</v>
+        <v>0.62219400000000002</v>
       </c>
       <c r="M2" s="1">
-        <v>0.69230100000000006</v>
+        <v>0.62817699999999999</v>
       </c>
       <c r="N2" s="1">
-        <v>0.69841299999999995</v>
+        <v>0.63425900000000002</v>
       </c>
       <c r="O2" s="1">
-        <v>0.70577400000000001</v>
+        <v>0.64139999999999997</v>
       </c>
       <c r="P2" s="1">
-        <v>0.71523999999999999</v>
+        <v>0.65310999999999997</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.71939399999999998</v>
+        <v>0.65864699999999998</v>
       </c>
       <c r="R2" s="1">
-        <v>0.72343800000000003</v>
+        <v>0.664022</v>
       </c>
       <c r="S2" s="1">
-        <v>0.72933499999999996</v>
+        <v>0.67466499999999996</v>
       </c>
       <c r="T2" s="1">
-        <v>0.74201799999999996</v>
+        <v>0.69103199999999998</v>
       </c>
       <c r="U2" s="1">
-        <v>0.74690100000000004</v>
+        <v>0.69780799999999998</v>
       </c>
       <c r="V2" s="1">
-        <v>0.75270000000000004</v>
+        <v>0.71012200000000003</v>
       </c>
       <c r="W2" s="1">
-        <v>0.75723300000000004</v>
+        <v>0.73428599999999999</v>
       </c>
       <c r="X2" s="1">
-        <v>0.75709800000000005</v>
+        <v>0.73932200000000003</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.69670799999999999</v>
+        <v>0.72215200000000002</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
-        <v>0.62256699999999998</v>
+        <v>0.57494299999999998</v>
       </c>
       <c r="B3" s="1">
-        <v>0.62697800000000004</v>
+        <v>0.57898400000000005</v>
       </c>
       <c r="C3" s="1">
-        <v>0.63283400000000001</v>
+        <v>0.58203300000000002</v>
       </c>
       <c r="D3" s="1">
-        <v>0.63908699999999996</v>
+        <v>0.58662700000000001</v>
       </c>
       <c r="E3" s="1">
-        <v>0.64338399999999996</v>
+        <v>0.58976700000000004</v>
       </c>
       <c r="F3" s="1">
-        <v>0.64858199999999999</v>
+        <v>0.59455499999999994</v>
       </c>
       <c r="G3" s="1">
-        <v>0.65486599999999995</v>
+        <v>0.59784899999999996</v>
       </c>
       <c r="H3" s="1">
-        <v>0.66497899999999999</v>
+        <v>0.60282800000000003</v>
       </c>
       <c r="I3" s="1">
-        <v>0.67334499999999997</v>
+        <v>0.60810799999999998</v>
       </c>
       <c r="J3" s="1">
-        <v>0.67820599999999998</v>
+        <v>0.61237399999999997</v>
       </c>
       <c r="K3" s="1">
-        <v>0.68372900000000003</v>
+        <v>0.618394</v>
       </c>
       <c r="L3" s="1">
-        <v>0.690438</v>
+        <v>0.62281699999999995</v>
       </c>
       <c r="M3" s="1">
-        <v>0.69642700000000002</v>
+        <v>0.628695</v>
       </c>
       <c r="N3" s="1">
-        <v>0.70258699999999996</v>
+        <v>0.63514199999999998</v>
       </c>
       <c r="O3" s="1">
-        <v>0.70914600000000005</v>
+        <v>0.64186399999999999</v>
       </c>
       <c r="P3" s="1">
-        <v>0.71827300000000005</v>
+        <v>0.65336700000000003</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.72153500000000004</v>
+        <v>0.65844499999999995</v>
       </c>
       <c r="R3" s="1">
-        <v>0.72665800000000003</v>
+        <v>0.66425000000000001</v>
       </c>
       <c r="S3" s="1">
-        <v>0.73048500000000005</v>
+        <v>0.67444400000000004</v>
       </c>
       <c r="T3" s="1">
-        <v>0.74304000000000003</v>
+        <v>0.68989100000000003</v>
       </c>
       <c r="U3" s="1">
-        <v>0.74881799999999998</v>
+        <v>0.697106</v>
       </c>
       <c r="V3" s="1">
-        <v>0.75539800000000001</v>
+        <v>0.70942400000000005</v>
       </c>
       <c r="W3" s="2">
-        <v>0.75944400000000001</v>
+        <v>0.735205</v>
       </c>
       <c r="X3" s="1">
-        <v>0.76213299999999995</v>
+        <v>0.739456</v>
       </c>
       <c r="Y3" s="1">
-        <v>0.70177699999999998</v>
+        <v>0.721607</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
-        <v>0.62445200000000001</v>
+        <v>0.57752300000000001</v>
       </c>
       <c r="B4" s="1">
-        <v>0.62849900000000003</v>
+        <v>0.581677</v>
       </c>
       <c r="C4" s="1">
-        <v>0.63427599999999995</v>
+        <v>0.584511</v>
       </c>
       <c r="D4" s="1">
-        <v>0.64091500000000001</v>
+        <v>0.58893600000000002</v>
       </c>
       <c r="E4" s="1">
-        <v>0.645146</v>
+        <v>0.59207799999999999</v>
       </c>
       <c r="F4" s="1">
-        <v>0.65052100000000002</v>
+        <v>0.59681099999999998</v>
       </c>
       <c r="G4" s="1">
-        <v>0.65739899999999996</v>
+        <v>0.60037399999999996</v>
       </c>
       <c r="H4" s="1">
-        <v>0.66643600000000003</v>
+        <v>0.60524699999999998</v>
       </c>
       <c r="I4" s="1">
-        <v>0.67502099999999998</v>
+        <v>0.61061100000000001</v>
       </c>
       <c r="J4" s="1">
-        <v>0.68005099999999996</v>
+        <v>0.61499700000000002</v>
       </c>
       <c r="K4" s="1">
-        <v>0.68522899999999998</v>
+        <v>0.62058199999999997</v>
       </c>
       <c r="L4" s="1">
-        <v>0.69140299999999999</v>
+        <v>0.62477899999999997</v>
       </c>
       <c r="M4" s="1">
-        <v>0.69777999999999996</v>
+        <v>0.63079399999999997</v>
       </c>
       <c r="N4" s="1">
-        <v>0.70313400000000004</v>
+        <v>0.63732900000000003</v>
       </c>
       <c r="O4" s="1">
-        <v>0.70934200000000003</v>
+        <v>0.64384799999999998</v>
       </c>
       <c r="P4" s="1">
-        <v>0.71790600000000004</v>
+        <v>0.65604399999999996</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.720356</v>
+        <v>0.66139199999999998</v>
       </c>
       <c r="R4" s="1">
-        <v>0.72550700000000001</v>
+        <v>0.66703900000000005</v>
       </c>
       <c r="S4" s="1">
-        <v>0.73001499999999997</v>
+        <v>0.67732700000000001</v>
       </c>
       <c r="T4" s="1">
-        <v>0.74229400000000001</v>
+        <v>0.69377599999999995</v>
       </c>
       <c r="U4" s="1">
-        <v>0.74814800000000004</v>
+        <v>0.70106500000000005</v>
       </c>
       <c r="V4" s="1">
-        <v>0.75584099999999999</v>
+        <v>0.71055699999999999</v>
       </c>
       <c r="W4" s="1">
-        <v>0.75958700000000001</v>
+        <v>0.73526499999999995</v>
       </c>
       <c r="X4" s="1">
-        <v>0.76069900000000001</v>
+        <v>0.74108399999999996</v>
       </c>
       <c r="Y4" s="1">
-        <v>0.69922899999999999</v>
+        <v>0.71930799999999995</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
-        <v>0.62708299999999995</v>
+        <v>0.57824200000000003</v>
       </c>
       <c r="B5" s="1">
-        <v>0.630938</v>
+        <v>0.58252499999999996</v>
       </c>
       <c r="C5" s="1">
-        <v>0.637216</v>
+        <v>0.58508599999999999</v>
       </c>
       <c r="D5" s="1">
-        <v>0.64409799999999995</v>
+        <v>0.58960800000000002</v>
       </c>
       <c r="E5" s="1">
-        <v>0.64846000000000004</v>
+        <v>0.59262800000000004</v>
       </c>
       <c r="F5" s="1">
-        <v>0.65377600000000002</v>
+        <v>0.59697100000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>0.66068099999999996</v>
+        <v>0.60035799999999995</v>
       </c>
       <c r="H5" s="1">
-        <v>0.66913999999999996</v>
+        <v>0.60526800000000003</v>
       </c>
       <c r="I5" s="1">
-        <v>0.67731300000000005</v>
+        <v>0.61070100000000005</v>
       </c>
       <c r="J5" s="1">
-        <v>0.68120000000000003</v>
+        <v>0.61483600000000005</v>
       </c>
       <c r="K5" s="1">
-        <v>0.68610099999999996</v>
+        <v>0.620556</v>
       </c>
       <c r="L5" s="1">
-        <v>0.69244300000000003</v>
+        <v>0.624394</v>
       </c>
       <c r="M5" s="1">
-        <v>0.69871300000000003</v>
+        <v>0.63085599999999997</v>
       </c>
       <c r="N5" s="1">
-        <v>0.70303499999999997</v>
+        <v>0.63710800000000001</v>
       </c>
       <c r="O5" s="1">
-        <v>0.709063</v>
+        <v>0.64406799999999997</v>
       </c>
       <c r="P5" s="1">
-        <v>0.71823499999999996</v>
+        <v>0.65617800000000004</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.72085100000000002</v>
+        <v>0.661659</v>
       </c>
       <c r="R5" s="1">
-        <v>0.72548299999999999</v>
+        <v>0.66708999999999996</v>
       </c>
       <c r="S5" s="1">
-        <v>0.73076600000000003</v>
+        <v>0.67729899999999998</v>
       </c>
       <c r="T5" s="1">
-        <v>0.74214899999999995</v>
+        <v>0.69351799999999997</v>
       </c>
       <c r="U5" s="1">
-        <v>0.74715699999999996</v>
+        <v>0.70158399999999999</v>
       </c>
       <c r="V5" s="1">
-        <v>0.75300999999999996</v>
+        <v>0.71016599999999996</v>
       </c>
       <c r="W5" s="1">
-        <v>0.75931800000000005</v>
+        <v>0.73428899999999997</v>
       </c>
       <c r="X5" s="1">
-        <v>0.75958099999999995</v>
+        <v>0.74022399999999999</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.69997100000000001</v>
+        <v>0.71889700000000001</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
-        <v>0.62847399999999998</v>
+        <v>0.58206899999999995</v>
       </c>
       <c r="B6" s="1">
-        <v>0.63260099999999997</v>
+        <v>0.58631599999999995</v>
       </c>
       <c r="C6" s="1">
-        <v>0.63965700000000003</v>
+        <v>0.58881300000000003</v>
       </c>
       <c r="D6" s="1">
-        <v>0.646536</v>
+        <v>0.59318700000000002</v>
       </c>
       <c r="E6" s="1">
-        <v>0.64994799999999997</v>
+        <v>0.59632099999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>0.65559800000000001</v>
+        <v>0.60065000000000002</v>
       </c>
       <c r="G6" s="1">
-        <v>0.66170600000000002</v>
+        <v>0.60388299999999995</v>
       </c>
       <c r="H6" s="1">
-        <v>0.67003100000000004</v>
+        <v>0.60933400000000004</v>
       </c>
       <c r="I6" s="1">
-        <v>0.67799900000000002</v>
+        <v>0.61495999999999995</v>
       </c>
       <c r="J6" s="1">
-        <v>0.681612</v>
+        <v>0.61905600000000005</v>
       </c>
       <c r="K6" s="1">
-        <v>0.68620700000000001</v>
+        <v>0.62450499999999998</v>
       </c>
       <c r="L6" s="1">
-        <v>0.691886</v>
+        <v>0.62836700000000001</v>
       </c>
       <c r="M6" s="1">
-        <v>0.69917499999999999</v>
+        <v>0.63453099999999996</v>
       </c>
       <c r="N6" s="1">
-        <v>0.70277299999999998</v>
+        <v>0.64136000000000004</v>
       </c>
       <c r="O6" s="1">
-        <v>0.70918999999999999</v>
+        <v>0.64820100000000003</v>
       </c>
       <c r="P6" s="1">
-        <v>0.71915899999999999</v>
+        <v>0.66035500000000003</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.72170500000000004</v>
+        <v>0.66575200000000001</v>
       </c>
       <c r="R6" s="1">
-        <v>0.72757300000000003</v>
+        <v>0.67041300000000004</v>
       </c>
       <c r="S6" s="1">
-        <v>0.73190599999999995</v>
+        <v>0.68197399999999997</v>
       </c>
       <c r="T6" s="1">
-        <v>0.74307900000000005</v>
+        <v>0.69790399999999997</v>
       </c>
       <c r="U6" s="1">
-        <v>0.74742900000000001</v>
+        <v>0.70640800000000004</v>
       </c>
       <c r="V6" s="1">
-        <v>0.75307599999999997</v>
+        <v>0.71633899999999995</v>
       </c>
       <c r="W6" s="1">
-        <v>0.75512900000000005</v>
+        <v>0.73579899999999998</v>
       </c>
       <c r="X6" s="1">
-        <v>0.75799000000000005</v>
+        <v>0.73814199999999996</v>
       </c>
       <c r="Y6" s="1">
-        <v>0.70047000000000004</v>
+        <v>0.71828499999999995</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
-        <v>0.63053499999999996</v>
+        <v>0.58379300000000001</v>
       </c>
       <c r="B7" s="1">
-        <v>0.634274</v>
+        <v>0.588256</v>
       </c>
       <c r="C7" s="1">
-        <v>0.64080199999999998</v>
+        <v>0.59087599999999996</v>
       </c>
       <c r="D7" s="1">
-        <v>0.64810900000000005</v>
+        <v>0.59529900000000002</v>
       </c>
       <c r="E7" s="1">
-        <v>0.65215400000000001</v>
+        <v>0.59813799999999995</v>
       </c>
       <c r="F7" s="1">
-        <v>0.657887</v>
+        <v>0.60246299999999997</v>
       </c>
       <c r="G7" s="1">
-        <v>0.66417400000000004</v>
+        <v>0.60578500000000002</v>
       </c>
       <c r="H7" s="1">
-        <v>0.67142800000000002</v>
+        <v>0.61121499999999995</v>
       </c>
       <c r="I7" s="1">
-        <v>0.67998400000000003</v>
+        <v>0.61634</v>
       </c>
       <c r="J7" s="1">
-        <v>0.68332300000000001</v>
+        <v>0.62057899999999999</v>
       </c>
       <c r="K7" s="1">
-        <v>0.68818400000000002</v>
+        <v>0.62616899999999998</v>
       </c>
       <c r="L7" s="1">
-        <v>0.69347700000000001</v>
+        <v>0.62974699999999995</v>
       </c>
       <c r="M7" s="1">
-        <v>0.70034200000000002</v>
+        <v>0.63623099999999999</v>
       </c>
       <c r="N7" s="1">
-        <v>0.70295700000000005</v>
+        <v>0.64247799999999999</v>
       </c>
       <c r="O7" s="1">
-        <v>0.71022700000000005</v>
+        <v>0.64943200000000001</v>
       </c>
       <c r="P7" s="1">
-        <v>0.71989300000000001</v>
+        <v>0.66146300000000002</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.72187299999999999</v>
+        <v>0.66659599999999997</v>
       </c>
       <c r="R7" s="1">
-        <v>0.72707599999999994</v>
+        <v>0.67163300000000004</v>
       </c>
       <c r="S7" s="1">
-        <v>0.73126800000000003</v>
+        <v>0.68392399999999998</v>
       </c>
       <c r="T7" s="1">
-        <v>0.74210399999999999</v>
+        <v>0.69816999999999996</v>
       </c>
       <c r="U7" s="1">
-        <v>0.74754799999999999</v>
+        <v>0.70588799999999996</v>
       </c>
       <c r="V7" s="1">
-        <v>0.75178500000000004</v>
+        <v>0.71623300000000001</v>
       </c>
       <c r="W7" s="1">
-        <v>0.75243000000000004</v>
+        <v>0.735626</v>
       </c>
       <c r="X7" s="1">
-        <v>0.75530200000000003</v>
+        <v>0.73562899999999998</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.69600600000000001</v>
+        <v>0.71958500000000003</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>0.63342900000000002</v>
+        <v>0.58699299999999999</v>
       </c>
       <c r="B8" s="1">
-        <v>0.63675899999999996</v>
+        <v>0.59092</v>
       </c>
       <c r="C8" s="1">
-        <v>0.64264399999999999</v>
+        <v>0.59360999999999997</v>
       </c>
       <c r="D8" s="1">
-        <v>0.64936499999999997</v>
+        <v>0.59778299999999995</v>
       </c>
       <c r="E8" s="1">
-        <v>0.653115</v>
+        <v>0.60035099999999997</v>
       </c>
       <c r="F8" s="1">
-        <v>0.65914600000000001</v>
+        <v>0.60433099999999995</v>
       </c>
       <c r="G8" s="1">
-        <v>0.66617300000000002</v>
+        <v>0.60790200000000005</v>
       </c>
       <c r="H8" s="1">
-        <v>0.67366800000000004</v>
+        <v>0.61304800000000004</v>
       </c>
       <c r="I8" s="1">
-        <v>0.68183800000000006</v>
+        <v>0.61793600000000004</v>
       </c>
       <c r="J8" s="1">
-        <v>0.68488800000000005</v>
+        <v>0.62238599999999999</v>
       </c>
       <c r="K8" s="1">
-        <v>0.689863</v>
+        <v>0.62761900000000004</v>
       </c>
       <c r="L8" s="1">
-        <v>0.69537700000000002</v>
+        <v>0.63158999999999998</v>
       </c>
       <c r="M8" s="1">
-        <v>0.70227200000000001</v>
+        <v>0.63788500000000004</v>
       </c>
       <c r="N8" s="1">
-        <v>0.70433299999999999</v>
+        <v>0.64456100000000005</v>
       </c>
       <c r="O8" s="1">
-        <v>0.71091300000000002</v>
+        <v>0.65161199999999997</v>
       </c>
       <c r="P8" s="1">
-        <v>0.71964300000000003</v>
+        <v>0.664663</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.72174499999999997</v>
+        <v>0.67100599999999999</v>
       </c>
       <c r="R8" s="1">
-        <v>0.72762099999999996</v>
+        <v>0.67638799999999999</v>
       </c>
       <c r="S8" s="1">
-        <v>0.73143599999999998</v>
+        <v>0.68783700000000003</v>
       </c>
       <c r="T8" s="1">
-        <v>0.74317299999999997</v>
+        <v>0.70270100000000002</v>
       </c>
       <c r="U8" s="1">
-        <v>0.74883900000000003</v>
+        <v>0.70950100000000005</v>
       </c>
       <c r="V8" s="1">
-        <v>0.75444299999999997</v>
+        <v>0.71950199999999997</v>
       </c>
       <c r="W8" s="1">
-        <v>0.75370000000000004</v>
+        <v>0.73977599999999999</v>
       </c>
       <c r="X8" s="1">
-        <v>0.75740799999999997</v>
+        <v>0.73868400000000001</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.69242599999999999</v>
+        <v>0.71996099999999996</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
-        <v>0.63418600000000003</v>
+        <v>0.58843100000000004</v>
       </c>
       <c r="B9" s="1">
-        <v>0.63748000000000005</v>
+        <v>0.59230099999999997</v>
       </c>
       <c r="C9" s="1">
-        <v>0.64307099999999995</v>
+        <v>0.59543500000000005</v>
       </c>
       <c r="D9" s="1">
-        <v>0.64968000000000004</v>
+        <v>0.59938800000000003</v>
       </c>
       <c r="E9" s="1">
-        <v>0.65242199999999995</v>
+        <v>0.60174499999999997</v>
       </c>
       <c r="F9" s="1">
-        <v>0.65801299999999996</v>
+        <v>0.60557799999999995</v>
       </c>
       <c r="G9" s="1">
-        <v>0.66429800000000006</v>
+        <v>0.60923700000000003</v>
       </c>
       <c r="H9" s="1">
-        <v>0.67183999999999999</v>
+        <v>0.61398299999999995</v>
       </c>
       <c r="I9" s="1">
-        <v>0.68057100000000004</v>
+        <v>0.61870800000000004</v>
       </c>
       <c r="J9" s="1">
-        <v>0.68325899999999995</v>
+        <v>0.62296200000000002</v>
       </c>
       <c r="K9" s="1">
-        <v>0.68721900000000002</v>
+        <v>0.62803200000000003</v>
       </c>
       <c r="L9" s="1">
-        <v>0.69299999999999995</v>
+        <v>0.63144199999999995</v>
       </c>
       <c r="M9" s="1">
-        <v>0.69843200000000005</v>
+        <v>0.63781200000000005</v>
       </c>
       <c r="N9" s="1">
-        <v>0.70117499999999999</v>
+        <v>0.64439900000000006</v>
       </c>
       <c r="O9" s="1">
-        <v>0.70797500000000002</v>
+        <v>0.65168000000000004</v>
       </c>
       <c r="P9" s="1">
-        <v>0.71740499999999996</v>
+        <v>0.66472799999999999</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.72055899999999995</v>
+        <v>0.67122300000000001</v>
       </c>
       <c r="R9" s="1">
-        <v>0.72634299999999996</v>
+        <v>0.67665699999999995</v>
       </c>
       <c r="S9" s="1">
-        <v>0.73160800000000004</v>
+        <v>0.68720000000000003</v>
       </c>
       <c r="T9" s="1">
-        <v>0.74355499999999997</v>
+        <v>0.70257999999999998</v>
       </c>
       <c r="U9" s="1">
-        <v>0.74770199999999998</v>
+        <v>0.71021900000000004</v>
       </c>
       <c r="V9" s="1">
-        <v>0.75473999999999997</v>
+        <v>0.71807100000000001</v>
       </c>
       <c r="W9" s="1">
-        <v>0.75181299999999995</v>
+        <v>0.73891499999999999</v>
       </c>
       <c r="X9" s="1">
-        <v>0.75447399999999998</v>
+        <v>0.73724599999999996</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.68889199999999995</v>
+        <v>0.71634299999999995</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
-        <v>0.63893100000000003</v>
+        <v>0.59074300000000002</v>
       </c>
       <c r="B10" s="1">
-        <v>0.64263800000000004</v>
+        <v>0.59414400000000001</v>
       </c>
       <c r="C10" s="1">
-        <v>0.64705199999999996</v>
+        <v>0.59711400000000003</v>
       </c>
       <c r="D10" s="1">
-        <v>0.65386599999999995</v>
+        <v>0.60150899999999996</v>
       </c>
       <c r="E10" s="1">
-        <v>0.65688100000000005</v>
+        <v>0.60336500000000004</v>
       </c>
       <c r="F10" s="1">
-        <v>0.66193900000000006</v>
+        <v>0.60742399999999996</v>
       </c>
       <c r="G10" s="1">
-        <v>0.66824300000000003</v>
+        <v>0.61124900000000004</v>
       </c>
       <c r="H10" s="1">
-        <v>0.67619899999999999</v>
+        <v>0.61606499999999997</v>
       </c>
       <c r="I10" s="1">
-        <v>0.68498800000000004</v>
+        <v>0.62093200000000004</v>
       </c>
       <c r="J10" s="1">
-        <v>0.68731200000000003</v>
+        <v>0.62429999999999997</v>
       </c>
       <c r="K10" s="1">
-        <v>0.69122499999999998</v>
+        <v>0.62909499999999996</v>
       </c>
       <c r="L10" s="1">
-        <v>0.69777</v>
+        <v>0.63276699999999997</v>
       </c>
       <c r="M10" s="1">
-        <v>0.70276799999999995</v>
+        <v>0.63860799999999995</v>
       </c>
       <c r="N10" s="1">
-        <v>0.70491300000000001</v>
+        <v>0.64541999999999999</v>
       </c>
       <c r="O10" s="1">
-        <v>0.711561</v>
+        <v>0.65278700000000001</v>
       </c>
       <c r="P10" s="1">
-        <v>0.72100299999999995</v>
+        <v>0.66583300000000001</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.72410399999999997</v>
+        <v>0.67208199999999996</v>
       </c>
       <c r="R10" s="1">
-        <v>0.73139900000000002</v>
+        <v>0.678396</v>
       </c>
       <c r="S10" s="1">
-        <v>0.73610500000000001</v>
+        <v>0.68861799999999995</v>
       </c>
       <c r="T10" s="1">
-        <v>0.74704300000000001</v>
+        <v>0.70259099999999997</v>
       </c>
       <c r="U10" s="1">
-        <v>0.75116899999999998</v>
+        <v>0.71066600000000002</v>
       </c>
       <c r="V10" s="1">
-        <v>0.759436</v>
+        <v>0.71765900000000005</v>
       </c>
       <c r="W10" s="1">
-        <v>0.75359200000000004</v>
+        <v>0.73916000000000004</v>
       </c>
       <c r="X10" s="1">
-        <v>0.75641899999999995</v>
+        <v>0.73618600000000001</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.69138100000000002</v>
+        <v>0.71413599999999999</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
-        <v>0.64188599999999996</v>
+        <v>0.59173399999999998</v>
       </c>
       <c r="B11" s="1">
-        <v>0.64571400000000001</v>
+        <v>0.59523499999999996</v>
       </c>
       <c r="C11" s="1">
-        <v>0.64961100000000005</v>
+        <v>0.59865400000000002</v>
       </c>
       <c r="D11" s="1">
-        <v>0.65549599999999997</v>
+        <v>0.603186</v>
       </c>
       <c r="E11" s="1">
-        <v>0.65883700000000001</v>
+        <v>0.60524199999999995</v>
       </c>
       <c r="F11" s="1">
-        <v>0.663775</v>
+        <v>0.608765</v>
       </c>
       <c r="G11" s="1">
-        <v>0.66999699999999995</v>
+        <v>0.61220399999999997</v>
       </c>
       <c r="H11" s="1">
-        <v>0.67861000000000005</v>
+        <v>0.61683200000000005</v>
       </c>
       <c r="I11" s="1">
-        <v>0.68629899999999999</v>
+        <v>0.62228099999999997</v>
       </c>
       <c r="J11" s="1">
-        <v>0.68790200000000001</v>
+        <v>0.62598399999999998</v>
       </c>
       <c r="K11" s="1">
-        <v>0.69116999999999995</v>
+        <v>0.63112699999999999</v>
       </c>
       <c r="L11" s="1">
-        <v>0.69801299999999999</v>
+        <v>0.63497300000000001</v>
       </c>
       <c r="M11" s="1">
-        <v>0.70317399999999997</v>
+        <v>0.64112800000000003</v>
       </c>
       <c r="N11" s="1">
-        <v>0.70643500000000004</v>
+        <v>0.64767699999999995</v>
       </c>
       <c r="O11" s="1">
-        <v>0.71261300000000005</v>
+        <v>0.65484200000000004</v>
       </c>
       <c r="P11" s="1">
-        <v>0.72044399999999997</v>
+        <v>0.66805999999999999</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.72423999999999999</v>
+        <v>0.67396800000000001</v>
       </c>
       <c r="R11" s="1">
-        <v>0.73176799999999997</v>
+        <v>0.679898</v>
       </c>
       <c r="S11" s="1">
-        <v>0.736294</v>
+        <v>0.69011999999999996</v>
       </c>
       <c r="T11" s="1">
-        <v>0.74604899999999996</v>
+        <v>0.70358100000000001</v>
       </c>
       <c r="U11" s="1">
-        <v>0.74805200000000005</v>
+        <v>0.71241200000000005</v>
       </c>
       <c r="V11" s="1">
-        <v>0.75529599999999997</v>
+        <v>0.71859700000000004</v>
       </c>
       <c r="W11" s="1">
-        <v>0.75017800000000001</v>
+        <v>0.73910399999999998</v>
       </c>
       <c r="X11" s="1">
-        <v>0.75205699999999998</v>
+        <v>0.735348</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.689967</v>
+        <v>0.71248900000000004</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
-        <v>0.64620699999999998</v>
+        <v>0.59537399999999996</v>
       </c>
       <c r="B12" s="1">
-        <v>0.65034800000000004</v>
+        <v>0.59864200000000001</v>
       </c>
       <c r="C12" s="1">
-        <v>0.65374299999999996</v>
+        <v>0.60191399999999995</v>
       </c>
       <c r="D12" s="1">
-        <v>0.65865799999999997</v>
+        <v>0.60647899999999999</v>
       </c>
       <c r="E12" s="1">
-        <v>0.66120900000000005</v>
+        <v>0.60885500000000004</v>
       </c>
       <c r="F12" s="1">
-        <v>0.66596900000000003</v>
+        <v>0.61265499999999995</v>
       </c>
       <c r="G12" s="1">
-        <v>0.67202300000000004</v>
+        <v>0.61596300000000004</v>
       </c>
       <c r="H12" s="1">
-        <v>0.67915899999999996</v>
+        <v>0.62011099999999997</v>
       </c>
       <c r="I12" s="1">
-        <v>0.68623599999999996</v>
+        <v>0.62550600000000001</v>
       </c>
       <c r="J12" s="1">
-        <v>0.68785200000000002</v>
+        <v>0.62944900000000004</v>
       </c>
       <c r="K12" s="1">
-        <v>0.69104100000000002</v>
+        <v>0.63463400000000003</v>
       </c>
       <c r="L12" s="1">
-        <v>0.69803400000000004</v>
+        <v>0.63885800000000004</v>
       </c>
       <c r="M12" s="1">
-        <v>0.70252300000000001</v>
+        <v>0.64414300000000002</v>
       </c>
       <c r="N12" s="1">
-        <v>0.70684899999999995</v>
+        <v>0.65081299999999997</v>
       </c>
       <c r="O12" s="1">
-        <v>0.712947</v>
+        <v>0.65802099999999997</v>
       </c>
       <c r="P12" s="1">
-        <v>0.72062000000000004</v>
+        <v>0.67168399999999995</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.72417600000000004</v>
+        <v>0.67761499999999997</v>
       </c>
       <c r="R12" s="1">
-        <v>0.73258900000000005</v>
+        <v>0.68147999999999997</v>
       </c>
       <c r="S12" s="1">
-        <v>0.73675500000000005</v>
+        <v>0.69183899999999998</v>
       </c>
       <c r="T12" s="1">
-        <v>0.745251</v>
+        <v>0.70455800000000002</v>
       </c>
       <c r="U12" s="1">
-        <v>0.74723300000000004</v>
+        <v>0.71378699999999995</v>
       </c>
       <c r="V12" s="1">
-        <v>0.75409099999999996</v>
+        <v>0.71856299999999995</v>
       </c>
       <c r="W12" s="1">
-        <v>0.75134999999999996</v>
+        <v>0.73924199999999995</v>
       </c>
       <c r="X12" s="1">
-        <v>0.75123899999999999</v>
+        <v>0.73866299999999996</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.68858900000000001</v>
+        <v>0.71284599999999998</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
-        <v>0.64516300000000004</v>
+        <v>0.59828599999999998</v>
       </c>
       <c r="B13" s="1">
-        <v>0.648312</v>
+        <v>0.60180900000000004</v>
       </c>
       <c r="C13" s="1">
-        <v>0.65190999999999999</v>
+        <v>0.60507299999999997</v>
       </c>
       <c r="D13" s="1">
-        <v>0.65661400000000003</v>
+        <v>0.60873299999999997</v>
       </c>
       <c r="E13" s="1">
-        <v>0.65846899999999997</v>
+        <v>0.61165000000000003</v>
       </c>
       <c r="F13" s="1">
-        <v>0.66190700000000002</v>
+        <v>0.61475599999999997</v>
       </c>
       <c r="G13" s="1">
-        <v>0.66783999999999999</v>
+        <v>0.61746299999999998</v>
       </c>
       <c r="H13" s="1">
-        <v>0.67537000000000003</v>
+        <v>0.62093799999999999</v>
       </c>
       <c r="I13" s="1">
-        <v>0.68155399999999999</v>
+        <v>0.62605200000000005</v>
       </c>
       <c r="J13" s="1">
-        <v>0.68381999999999998</v>
+        <v>0.63039900000000004</v>
       </c>
       <c r="K13" s="1">
-        <v>0.68569199999999997</v>
+        <v>0.63585100000000006</v>
       </c>
       <c r="L13" s="1">
-        <v>0.69209900000000002</v>
+        <v>0.64058800000000005</v>
       </c>
       <c r="M13" s="1">
-        <v>0.69662900000000005</v>
+        <v>0.64629800000000004</v>
       </c>
       <c r="N13" s="1">
-        <v>0.70036600000000004</v>
+        <v>0.65208500000000003</v>
       </c>
       <c r="O13" s="1">
-        <v>0.70778099999999999</v>
+        <v>0.65826499999999999</v>
       </c>
       <c r="P13" s="1">
-        <v>0.71464000000000005</v>
+        <v>0.67220500000000005</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.71860100000000005</v>
+        <v>0.679342</v>
       </c>
       <c r="R13" s="1">
-        <v>0.72664499999999999</v>
+        <v>0.68096800000000002</v>
       </c>
       <c r="S13" s="1">
-        <v>0.73055099999999995</v>
+        <v>0.69309600000000005</v>
       </c>
       <c r="T13" s="1">
-        <v>0.740255</v>
+        <v>0.70667000000000002</v>
       </c>
       <c r="U13" s="1">
-        <v>0.73970599999999997</v>
+        <v>0.71292</v>
       </c>
       <c r="V13" s="1">
-        <v>0.74435700000000005</v>
+        <v>0.71919699999999998</v>
       </c>
       <c r="W13" s="1">
-        <v>0.74382400000000004</v>
+        <v>0.73838199999999998</v>
       </c>
       <c r="X13" s="1">
-        <v>0.74620799999999998</v>
+        <v>0.73726100000000006</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.68563799999999997</v>
+        <v>0.71015499999999998</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
-        <v>0.64013799999999998</v>
+        <v>0.60033099999999995</v>
       </c>
       <c r="B14" s="1">
-        <v>0.64337800000000001</v>
+        <v>0.60367499999999996</v>
       </c>
       <c r="C14" s="1">
-        <v>0.64657399999999998</v>
+        <v>0.60630499999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.65188400000000002</v>
+        <v>0.60833899999999996</v>
       </c>
       <c r="E14" s="1">
-        <v>0.65334899999999996</v>
+        <v>0.61131599999999997</v>
       </c>
       <c r="F14" s="1">
-        <v>0.65709499999999998</v>
+        <v>0.61463500000000004</v>
       </c>
       <c r="G14" s="1">
-        <v>0.66276599999999997</v>
+        <v>0.61708399999999997</v>
       </c>
       <c r="H14" s="1">
-        <v>0.66979500000000003</v>
+        <v>0.62039</v>
       </c>
       <c r="I14" s="1">
-        <v>0.67536499999999999</v>
+        <v>0.62490100000000004</v>
       </c>
       <c r="J14" s="1">
-        <v>0.67885099999999998</v>
+        <v>0.62880000000000003</v>
       </c>
       <c r="K14" s="1">
-        <v>0.68116299999999996</v>
+        <v>0.63336400000000004</v>
       </c>
       <c r="L14" s="1">
-        <v>0.68722899999999998</v>
+        <v>0.63785800000000004</v>
       </c>
       <c r="M14" s="1">
-        <v>0.69280900000000001</v>
+        <v>0.64346000000000003</v>
       </c>
       <c r="N14" s="1">
-        <v>0.69624900000000001</v>
+        <v>0.64939000000000002</v>
       </c>
       <c r="O14" s="1">
-        <v>0.70465500000000003</v>
+        <v>0.654999</v>
       </c>
       <c r="P14" s="1">
-        <v>0.71296999999999999</v>
+        <v>0.66910899999999995</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.71595900000000001</v>
+        <v>0.67488700000000001</v>
       </c>
       <c r="R14" s="1">
-        <v>0.72342399999999996</v>
+        <v>0.67618599999999995</v>
       </c>
       <c r="S14" s="1">
-        <v>0.72756600000000005</v>
+        <v>0.68837599999999999</v>
       </c>
       <c r="T14" s="1">
-        <v>0.73540000000000005</v>
+        <v>0.70181400000000005</v>
       </c>
       <c r="U14" s="1">
-        <v>0.73458599999999996</v>
+        <v>0.71105799999999997</v>
       </c>
       <c r="V14" s="1">
-        <v>0.74077499999999996</v>
+        <v>0.71610499999999999</v>
       </c>
       <c r="W14" s="1">
-        <v>0.73870000000000002</v>
+        <v>0.73232699999999995</v>
       </c>
       <c r="X14" s="1">
-        <v>0.74199000000000004</v>
+        <v>0.73340899999999998</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.69367400000000001</v>
+        <v>0.70784599999999998</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
-        <v>0.63384300000000005</v>
+        <v>0.60203499999999999</v>
       </c>
       <c r="B15" s="1">
-        <v>0.63655099999999998</v>
+        <v>0.60555999999999999</v>
       </c>
       <c r="C15" s="1">
-        <v>0.64001300000000005</v>
+        <v>0.608074</v>
       </c>
       <c r="D15" s="1">
-        <v>0.64486299999999996</v>
+        <v>0.61060999999999999</v>
       </c>
       <c r="E15" s="1">
-        <v>0.646451</v>
+        <v>0.61377199999999998</v>
       </c>
       <c r="F15" s="1">
-        <v>0.64996299999999996</v>
+        <v>0.61743099999999995</v>
       </c>
       <c r="G15" s="1">
-        <v>0.65573400000000004</v>
+        <v>0.61976399999999998</v>
       </c>
       <c r="H15" s="1">
-        <v>0.66311799999999999</v>
+        <v>0.62293399999999999</v>
       </c>
       <c r="I15" s="1">
-        <v>0.66829700000000003</v>
+        <v>0.62724400000000002</v>
       </c>
       <c r="J15" s="1">
-        <v>0.67095700000000003</v>
+        <v>0.63033399999999995</v>
       </c>
       <c r="K15" s="1">
-        <v>0.67361800000000005</v>
+        <v>0.63465899999999997</v>
       </c>
       <c r="L15" s="1">
-        <v>0.67940900000000004</v>
+        <v>0.63977600000000001</v>
       </c>
       <c r="M15" s="1">
-        <v>0.68518199999999996</v>
+        <v>0.64508100000000002</v>
       </c>
       <c r="N15" s="1">
-        <v>0.68792500000000001</v>
+        <v>0.65174600000000005</v>
       </c>
       <c r="O15" s="1">
-        <v>0.69761300000000004</v>
+        <v>0.657134</v>
       </c>
       <c r="P15" s="1">
-        <v>0.70506500000000005</v>
+        <v>0.670871</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.70865699999999998</v>
+        <v>0.67700400000000005</v>
       </c>
       <c r="R15" s="1">
-        <v>0.71525300000000003</v>
+        <v>0.67848600000000003</v>
       </c>
       <c r="S15" s="1">
-        <v>0.71596899999999997</v>
+        <v>0.69243699999999997</v>
       </c>
       <c r="T15" s="1">
-        <v>0.72438100000000005</v>
+        <v>0.70273799999999997</v>
       </c>
       <c r="U15" s="1">
-        <v>0.72555000000000003</v>
+        <v>0.71359700000000004</v>
       </c>
       <c r="V15" s="1">
-        <v>0.73209100000000005</v>
+        <v>0.72121800000000003</v>
       </c>
       <c r="W15" s="1">
-        <v>0.72714800000000002</v>
+        <v>0.73610600000000004</v>
       </c>
       <c r="X15" s="1">
-        <v>0.73303099999999999</v>
+        <v>0.73000299999999996</v>
       </c>
       <c r="Y15" s="1">
-        <v>0.68755500000000003</v>
+        <v>0.70624399999999998</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
-        <v>0.63593699999999997</v>
+        <v>0.60493200000000003</v>
       </c>
       <c r="B16" s="1">
-        <v>0.63929100000000005</v>
+        <v>0.60833599999999999</v>
       </c>
       <c r="C16" s="1">
-        <v>0.64212000000000002</v>
+        <v>0.61139200000000005</v>
       </c>
       <c r="D16" s="1">
-        <v>0.647011</v>
+        <v>0.61403399999999997</v>
       </c>
       <c r="E16" s="1">
-        <v>0.64860600000000002</v>
+        <v>0.61773299999999998</v>
       </c>
       <c r="F16" s="1">
-        <v>0.65268599999999999</v>
+        <v>0.62121899999999997</v>
       </c>
       <c r="G16" s="1">
-        <v>0.65855600000000003</v>
+        <v>0.62406899999999998</v>
       </c>
       <c r="H16" s="1">
-        <v>0.66590000000000005</v>
+        <v>0.62746199999999996</v>
       </c>
       <c r="I16" s="1">
-        <v>0.67013699999999998</v>
+        <v>0.63181399999999999</v>
       </c>
       <c r="J16" s="1">
-        <v>0.67329000000000006</v>
+        <v>0.63444599999999995</v>
       </c>
       <c r="K16" s="1">
-        <v>0.67673099999999997</v>
+        <v>0.639432</v>
       </c>
       <c r="L16" s="1">
-        <v>0.682176</v>
+        <v>0.64395599999999997</v>
       </c>
       <c r="M16" s="1">
-        <v>0.68927700000000003</v>
+        <v>0.64881299999999997</v>
       </c>
       <c r="N16" s="1">
-        <v>0.69261300000000003</v>
+        <v>0.65507099999999996</v>
       </c>
       <c r="O16" s="1">
-        <v>0.70119799999999999</v>
+        <v>0.66066000000000003</v>
       </c>
       <c r="P16" s="1">
-        <v>0.70739399999999997</v>
+        <v>0.67441700000000004</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.70986400000000005</v>
+        <v>0.68106199999999995</v>
       </c>
       <c r="R16" s="1">
-        <v>0.71797699999999998</v>
+        <v>0.68135500000000004</v>
       </c>
       <c r="S16" s="1">
-        <v>0.72101599999999999</v>
+        <v>0.69446399999999997</v>
       </c>
       <c r="T16" s="1">
-        <v>0.73005100000000001</v>
+        <v>0.70690600000000003</v>
       </c>
       <c r="U16" s="1">
-        <v>0.73221800000000004</v>
+        <v>0.71661900000000001</v>
       </c>
       <c r="V16" s="1">
-        <v>0.73542700000000005</v>
+        <v>0.72017399999999998</v>
       </c>
       <c r="W16" s="1">
-        <v>0.72661200000000004</v>
+        <v>0.73042399999999996</v>
       </c>
       <c r="X16" s="1">
-        <v>0.73356100000000002</v>
+        <v>0.72658299999999998</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.68074500000000004</v>
+        <v>0.70104</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
-        <v>0.63168599999999997</v>
+        <v>0.605572</v>
       </c>
       <c r="B17" s="1">
-        <v>0.63491600000000004</v>
+        <v>0.60861100000000001</v>
       </c>
       <c r="C17" s="1">
-        <v>0.636965</v>
+        <v>0.61152200000000001</v>
       </c>
       <c r="D17" s="1">
-        <v>0.64132900000000004</v>
+        <v>0.61452099999999998</v>
       </c>
       <c r="E17" s="1">
-        <v>0.64315800000000001</v>
+        <v>0.61818899999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>0.64628799999999997</v>
+        <v>0.62138599999999999</v>
       </c>
       <c r="G17" s="1">
-        <v>0.65281199999999995</v>
+        <v>0.62445200000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>0.659856</v>
+        <v>0.62879700000000005</v>
       </c>
       <c r="I17" s="1">
-        <v>0.66423600000000005</v>
+        <v>0.63359100000000002</v>
       </c>
       <c r="J17" s="1">
-        <v>0.66774500000000003</v>
+        <v>0.63606799999999997</v>
       </c>
       <c r="K17" s="1">
-        <v>0.67136099999999999</v>
+        <v>0.64141599999999999</v>
       </c>
       <c r="L17" s="1">
-        <v>0.67540900000000004</v>
+        <v>0.64522299999999999</v>
       </c>
       <c r="M17" s="1">
-        <v>0.68123900000000004</v>
+        <v>0.65023399999999998</v>
       </c>
       <c r="N17" s="1">
-        <v>0.68402799999999997</v>
+        <v>0.65542900000000004</v>
       </c>
       <c r="O17" s="1">
-        <v>0.69266899999999998</v>
+        <v>0.66133699999999995</v>
       </c>
       <c r="P17" s="1">
-        <v>0.69915899999999997</v>
+        <v>0.67409600000000003</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.70165</v>
+        <v>0.68037000000000003</v>
       </c>
       <c r="R17" s="1">
-        <v>0.71091499999999996</v>
+        <v>0.68130900000000005</v>
       </c>
       <c r="S17" s="1">
-        <v>0.71325799999999995</v>
+        <v>0.69323299999999999</v>
       </c>
       <c r="T17" s="1">
-        <v>0.72500900000000001</v>
+        <v>0.70170900000000003</v>
       </c>
       <c r="U17" s="1">
-        <v>0.72580900000000004</v>
+        <v>0.71221299999999998</v>
       </c>
       <c r="V17" s="1">
-        <v>0.72770800000000002</v>
+        <v>0.71529399999999999</v>
       </c>
       <c r="W17" s="1">
-        <v>0.71916199999999997</v>
+        <v>0.72519</v>
       </c>
       <c r="X17" s="1">
-        <v>0.72331500000000004</v>
+        <v>0.72385200000000005</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.67249899999999996</v>
+        <v>0.70520000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
-        <v>0.62998900000000002</v>
+        <v>0.60140800000000005</v>
       </c>
       <c r="B18" s="1">
-        <v>0.63286699999999996</v>
+        <v>0.60355099999999995</v>
       </c>
       <c r="C18" s="1">
-        <v>0.63560799999999995</v>
+        <v>0.60679899999999998</v>
       </c>
       <c r="D18" s="1">
-        <v>0.63955399999999996</v>
+        <v>0.61021000000000003</v>
       </c>
       <c r="E18" s="1">
-        <v>0.64101300000000005</v>
+        <v>0.61338099999999995</v>
       </c>
       <c r="F18" s="1">
-        <v>0.64375499999999997</v>
+        <v>0.61735099999999998</v>
       </c>
       <c r="G18" s="1">
-        <v>0.64955799999999997</v>
+        <v>0.62063800000000002</v>
       </c>
       <c r="H18" s="1">
-        <v>0.654999</v>
+        <v>0.62421599999999999</v>
       </c>
       <c r="I18" s="1">
-        <v>0.65973199999999999</v>
+        <v>0.62876500000000002</v>
       </c>
       <c r="J18" s="1">
-        <v>0.66301500000000002</v>
+        <v>0.63126000000000004</v>
       </c>
       <c r="K18" s="1">
-        <v>0.66772100000000001</v>
+        <v>0.63666999999999996</v>
       </c>
       <c r="L18" s="1">
-        <v>0.67089600000000005</v>
+        <v>0.63989600000000002</v>
       </c>
       <c r="M18" s="1">
-        <v>0.67663499999999999</v>
+        <v>0.64497400000000005</v>
       </c>
       <c r="N18" s="1">
-        <v>0.67908999999999997</v>
+        <v>0.65091299999999996</v>
       </c>
       <c r="O18" s="1">
-        <v>0.68679599999999996</v>
+        <v>0.65646300000000002</v>
       </c>
       <c r="P18" s="1">
-        <v>0.69340800000000002</v>
+        <v>0.67102399999999995</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.69425099999999995</v>
+        <v>0.67579</v>
       </c>
       <c r="R18" s="1">
-        <v>0.69930000000000003</v>
+        <v>0.67718800000000001</v>
       </c>
       <c r="S18" s="1">
-        <v>0.70004100000000002</v>
+        <v>0.68795399999999995</v>
       </c>
       <c r="T18" s="1">
-        <v>0.70998899999999998</v>
+        <v>0.69659300000000002</v>
       </c>
       <c r="U18" s="1">
-        <v>0.71327399999999996</v>
+        <v>0.70737300000000003</v>
       </c>
       <c r="V18" s="1">
-        <v>0.71736699999999998</v>
+        <v>0.70910099999999998</v>
       </c>
       <c r="W18" s="1">
-        <v>0.70527899999999999</v>
+        <v>0.71523199999999998</v>
       </c>
       <c r="X18" s="1">
-        <v>0.71464499999999997</v>
+        <v>0.718449</v>
       </c>
       <c r="Y18" s="1">
-        <v>0.66834499999999997</v>
+        <v>0.70308099999999996</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
-        <v>0.63003100000000001</v>
+        <v>0.60002100000000003</v>
       </c>
       <c r="B19" s="1">
-        <v>0.63334800000000002</v>
+        <v>0.60244299999999995</v>
       </c>
       <c r="C19" s="1">
-        <v>0.63491200000000003</v>
+        <v>0.60502599999999995</v>
       </c>
       <c r="D19" s="1">
-        <v>0.63851400000000003</v>
+        <v>0.60775599999999996</v>
       </c>
       <c r="E19" s="1">
-        <v>0.63971199999999995</v>
+        <v>0.61119100000000004</v>
       </c>
       <c r="F19" s="1">
-        <v>0.64308399999999999</v>
+        <v>0.61521899999999996</v>
       </c>
       <c r="G19" s="1">
-        <v>0.64937299999999998</v>
+        <v>0.61864699999999995</v>
       </c>
       <c r="H19" s="1">
-        <v>0.65510500000000005</v>
+        <v>0.62188500000000002</v>
       </c>
       <c r="I19" s="1">
-        <v>0.65924899999999997</v>
+        <v>0.62534999999999996</v>
       </c>
       <c r="J19" s="1">
-        <v>0.66354400000000002</v>
+        <v>0.62795100000000004</v>
       </c>
       <c r="K19" s="1">
-        <v>0.66770099999999999</v>
+        <v>0.63407999999999998</v>
       </c>
       <c r="L19" s="1">
-        <v>0.67189900000000002</v>
+        <v>0.63590899999999995</v>
       </c>
       <c r="M19" s="1">
-        <v>0.67783000000000004</v>
+        <v>0.63978500000000005</v>
       </c>
       <c r="N19" s="1">
-        <v>0.68092600000000003</v>
+        <v>0.64579600000000004</v>
       </c>
       <c r="O19" s="1">
-        <v>0.68917700000000004</v>
+        <v>0.652667</v>
       </c>
       <c r="P19" s="1">
-        <v>0.696932</v>
+        <v>0.66946899999999998</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.69894500000000004</v>
+        <v>0.671292</v>
       </c>
       <c r="R19" s="1">
-        <v>0.70559400000000005</v>
+        <v>0.67136700000000005</v>
       </c>
       <c r="S19" s="1">
-        <v>0.70762999999999998</v>
+        <v>0.68281499999999995</v>
       </c>
       <c r="T19" s="1">
-        <v>0.71616800000000003</v>
+        <v>0.68965299999999996</v>
       </c>
       <c r="U19" s="1">
-        <v>0.72244900000000001</v>
+        <v>0.70399599999999996</v>
       </c>
       <c r="V19" s="1">
-        <v>0.73364099999999999</v>
+        <v>0.704426</v>
       </c>
       <c r="W19" s="1">
-        <v>0.71018800000000004</v>
+        <v>0.70770100000000002</v>
       </c>
       <c r="X19" s="1">
-        <v>0.71877999999999997</v>
+        <v>0.70577999999999996</v>
       </c>
       <c r="Y19" s="1">
-        <v>0.68623999999999996</v>
+        <v>0.70014799999999999</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
-        <v>0.62872700000000004</v>
+        <v>0.59628599999999998</v>
       </c>
       <c r="B20" s="1">
-        <v>0.63309599999999999</v>
+        <v>0.59862300000000002</v>
       </c>
       <c r="C20" s="1">
-        <v>0.63459200000000004</v>
+        <v>0.60141800000000001</v>
       </c>
       <c r="D20" s="1">
-        <v>0.63689300000000004</v>
+        <v>0.60408899999999999</v>
       </c>
       <c r="E20" s="1">
-        <v>0.63792599999999999</v>
+        <v>0.60706599999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>0.641204</v>
+        <v>0.61027100000000001</v>
       </c>
       <c r="G20" s="1">
-        <v>0.64607999999999999</v>
+        <v>0.61346500000000004</v>
       </c>
       <c r="H20" s="1">
-        <v>0.64990199999999998</v>
+        <v>0.61678999999999995</v>
       </c>
       <c r="I20" s="1">
-        <v>0.65334800000000004</v>
+        <v>0.62044500000000002</v>
       </c>
       <c r="J20" s="1">
-        <v>0.65798599999999996</v>
+        <v>0.62335700000000005</v>
       </c>
       <c r="K20" s="1">
-        <v>0.66269599999999995</v>
+        <v>0.62822199999999995</v>
       </c>
       <c r="L20" s="1">
-        <v>0.66808699999999999</v>
+        <v>0.63005699999999998</v>
       </c>
       <c r="M20" s="1">
-        <v>0.67543900000000001</v>
+        <v>0.63404400000000005</v>
       </c>
       <c r="N20" s="1">
-        <v>0.67745</v>
+        <v>0.63844500000000004</v>
       </c>
       <c r="O20" s="1">
-        <v>0.68623599999999996</v>
+        <v>0.64599399999999996</v>
       </c>
       <c r="P20" s="1">
-        <v>0.69296000000000002</v>
+        <v>0.66308100000000003</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.69586300000000001</v>
+        <v>0.66463399999999995</v>
       </c>
       <c r="R20" s="1">
-        <v>0.70274800000000004</v>
+        <v>0.66417300000000001</v>
       </c>
       <c r="S20" s="1">
-        <v>0.70548599999999995</v>
+        <v>0.67736099999999999</v>
       </c>
       <c r="T20" s="1">
-        <v>0.714086</v>
+        <v>0.68218299999999998</v>
       </c>
       <c r="U20" s="1">
-        <v>0.71833800000000003</v>
+        <v>0.69382900000000003</v>
       </c>
       <c r="V20" s="1">
-        <v>0.72850499999999996</v>
+        <v>0.694743</v>
       </c>
       <c r="W20" s="1">
-        <v>0.70649300000000004</v>
+        <v>0.69928800000000002</v>
       </c>
       <c r="X20" s="1">
-        <v>0.70965500000000004</v>
+        <v>0.69237899999999997</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.68183800000000006</v>
+        <v>0.68878600000000001</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
-        <v>0.61733300000000002</v>
+        <v>0.58871399999999996</v>
       </c>
       <c r="B21" s="1">
-        <v>0.62050099999999997</v>
+        <v>0.59072999999999998</v>
       </c>
       <c r="C21" s="1">
-        <v>0.62285500000000005</v>
+        <v>0.592746</v>
       </c>
       <c r="D21" s="1">
-        <v>0.62604400000000004</v>
+        <v>0.59532799999999997</v>
       </c>
       <c r="E21" s="1">
-        <v>0.62653099999999995</v>
+        <v>0.598024</v>
       </c>
       <c r="F21" s="1">
-        <v>0.63031099999999995</v>
+        <v>0.60062599999999999</v>
       </c>
       <c r="G21" s="1">
-        <v>0.63371599999999995</v>
+        <v>0.60347200000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>0.63852900000000001</v>
+        <v>0.607159</v>
       </c>
       <c r="I21" s="1">
-        <v>0.64153899999999997</v>
+        <v>0.61086200000000002</v>
       </c>
       <c r="J21" s="1">
-        <v>0.64733499999999999</v>
+        <v>0.61453599999999997</v>
       </c>
       <c r="K21" s="1">
-        <v>0.65238799999999997</v>
+        <v>0.61942399999999997</v>
       </c>
       <c r="L21" s="1">
-        <v>0.65640799999999999</v>
+        <v>0.62288699999999997</v>
       </c>
       <c r="M21" s="1">
-        <v>0.66197600000000001</v>
+        <v>0.62744599999999995</v>
       </c>
       <c r="N21" s="1">
-        <v>0.66651499999999997</v>
+        <v>0.631019</v>
       </c>
       <c r="O21" s="1">
-        <v>0.67277399999999998</v>
+        <v>0.63843899999999998</v>
       </c>
       <c r="P21" s="1">
-        <v>0.68357299999999999</v>
+        <v>0.65527199999999997</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.68444700000000003</v>
+        <v>0.65792600000000001</v>
       </c>
       <c r="R21" s="1">
-        <v>0.69050699999999998</v>
+        <v>0.65520100000000003</v>
       </c>
       <c r="S21" s="1">
-        <v>0.69155500000000003</v>
+        <v>0.66975600000000002</v>
       </c>
       <c r="T21" s="1">
-        <v>0.69930000000000003</v>
+        <v>0.67712700000000003</v>
       </c>
       <c r="U21" s="1">
-        <v>0.706762</v>
+        <v>0.69010800000000005</v>
       </c>
       <c r="V21" s="1">
-        <v>0.71732700000000005</v>
+        <v>0.68900600000000001</v>
       </c>
       <c r="W21" s="1">
-        <v>0.70157800000000003</v>
+        <v>0.69621299999999997</v>
       </c>
       <c r="X21" s="1">
-        <v>0.69876499999999997</v>
+        <v>0.69568799999999997</v>
       </c>
       <c r="Y21" s="1">
-        <v>0.66268300000000002</v>
+        <v>0.68352900000000005</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
-        <v>0.594947</v>
+        <v>0.579179</v>
       </c>
       <c r="B22" s="1">
-        <v>0.59777899999999995</v>
+        <v>0.57987699999999998</v>
       </c>
       <c r="C22" s="1">
-        <v>0.59878900000000002</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="D22" s="1">
-        <v>0.60259399999999996</v>
+        <v>0.582758</v>
       </c>
       <c r="E22" s="1">
-        <v>0.60333099999999995</v>
+        <v>0.58629500000000001</v>
       </c>
       <c r="F22" s="1">
-        <v>0.605217</v>
+        <v>0.58843299999999998</v>
       </c>
       <c r="G22" s="1">
-        <v>0.60854399999999997</v>
+        <v>0.59175500000000003</v>
       </c>
       <c r="H22" s="1">
-        <v>0.61513099999999998</v>
+        <v>0.59442200000000001</v>
       </c>
       <c r="I22" s="1">
-        <v>0.62010699999999996</v>
+        <v>0.59584899999999996</v>
       </c>
       <c r="J22" s="1">
-        <v>0.62536199999999997</v>
+        <v>0.60074700000000003</v>
       </c>
       <c r="K22" s="1">
-        <v>0.63</v>
+        <v>0.60523300000000002</v>
       </c>
       <c r="L22" s="1">
-        <v>0.63340399999999997</v>
+        <v>0.60885299999999998</v>
       </c>
       <c r="M22" s="1">
-        <v>0.63847500000000001</v>
+        <v>0.61213200000000001</v>
       </c>
       <c r="N22" s="1">
-        <v>0.64371900000000004</v>
+        <v>0.61361100000000002</v>
       </c>
       <c r="O22" s="1">
-        <v>0.65165799999999996</v>
+        <v>0.61924900000000005</v>
       </c>
       <c r="P22" s="1">
-        <v>0.65857500000000002</v>
+        <v>0.63950899999999999</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.66045100000000001</v>
+        <v>0.64305699999999999</v>
       </c>
       <c r="R22" s="1">
-        <v>0.66456899999999997</v>
+        <v>0.64105299999999998</v>
       </c>
       <c r="S22" s="1">
-        <v>0.66796599999999995</v>
+        <v>0.65521399999999996</v>
       </c>
       <c r="T22" s="1">
-        <v>0.67114700000000005</v>
+        <v>0.65830599999999995</v>
       </c>
       <c r="U22" s="1">
-        <v>0.68559899999999996</v>
+        <v>0.66946700000000003</v>
       </c>
       <c r="V22" s="1">
-        <v>0.696631</v>
+        <v>0.66558499999999998</v>
       </c>
       <c r="W22" s="1">
-        <v>0.67801199999999995</v>
+        <v>0.67602700000000004</v>
       </c>
       <c r="X22" s="1">
-        <v>0.67417700000000003</v>
+        <v>0.67044400000000004</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.63190599999999997</v>
+        <v>0.64542299999999997</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
-        <v>0.59044300000000005</v>
+        <v>0.57812300000000005</v>
       </c>
       <c r="B23" s="1">
-        <v>0.59054799999999996</v>
+        <v>0.57925599999999999</v>
       </c>
       <c r="C23" s="1">
-        <v>0.59041399999999999</v>
+        <v>0.57955400000000001</v>
       </c>
       <c r="D23" s="1">
-        <v>0.59241900000000003</v>
+        <v>0.58165</v>
       </c>
       <c r="E23" s="1">
-        <v>0.59340199999999999</v>
+        <v>0.58247000000000004</v>
       </c>
       <c r="F23" s="1">
-        <v>0.595028</v>
+        <v>0.584229</v>
       </c>
       <c r="G23" s="1">
-        <v>0.59992999999999996</v>
+        <v>0.58643800000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>0.60418300000000003</v>
+        <v>0.58765400000000001</v>
       </c>
       <c r="I23" s="1">
-        <v>0.61136199999999996</v>
+        <v>0.58885100000000001</v>
       </c>
       <c r="J23" s="1">
-        <v>0.61260199999999998</v>
+        <v>0.59280100000000002</v>
       </c>
       <c r="K23" s="1">
-        <v>0.61795100000000003</v>
+        <v>0.59321500000000005</v>
       </c>
       <c r="L23" s="1">
-        <v>0.61901799999999996</v>
+        <v>0.59709299999999998</v>
       </c>
       <c r="M23" s="1">
-        <v>0.62195500000000004</v>
+        <v>0.60289199999999998</v>
       </c>
       <c r="N23" s="1">
-        <v>0.62673900000000005</v>
+        <v>0.60536800000000002</v>
       </c>
       <c r="O23" s="1">
-        <v>0.62973500000000004</v>
+        <v>0.611097</v>
       </c>
       <c r="P23" s="1">
-        <v>0.63911799999999996</v>
+        <v>0.62923499999999999</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.64432100000000003</v>
+        <v>0.63039699999999999</v>
       </c>
       <c r="R23" s="1">
-        <v>0.64730600000000005</v>
+        <v>0.62801399999999996</v>
       </c>
       <c r="S23" s="1">
-        <v>0.65582799999999997</v>
+        <v>0.63702599999999998</v>
       </c>
       <c r="T23" s="1">
-        <v>0.66033500000000001</v>
+        <v>0.63748000000000005</v>
       </c>
       <c r="U23" s="1">
-        <v>0.67239099999999996</v>
+        <v>0.64151999999999998</v>
       </c>
       <c r="V23" s="1">
-        <v>0.67542999999999997</v>
+        <v>0.63853599999999999</v>
       </c>
       <c r="W23" s="1">
-        <v>0.66457200000000005</v>
+        <v>0.64940500000000001</v>
       </c>
       <c r="X23" s="1">
-        <v>0.65776699999999999</v>
+        <v>0.645262</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.64354800000000001</v>
+        <v>0.619834</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
-        <v>0.527729</v>
+        <v>0.57340599999999997</v>
       </c>
       <c r="B24" s="1">
-        <v>0.52715999999999996</v>
+        <v>0.575206</v>
       </c>
       <c r="C24" s="1">
-        <v>0.52788100000000004</v>
+        <v>0.57546200000000003</v>
       </c>
       <c r="D24" s="1">
-        <v>0.52973599999999998</v>
+        <v>0.57948999999999995</v>
       </c>
       <c r="E24" s="1">
-        <v>0.530362</v>
+        <v>0.58090799999999998</v>
       </c>
       <c r="F24" s="1">
-        <v>0.53225999999999996</v>
+        <v>0.58006000000000002</v>
       </c>
       <c r="G24" s="1">
-        <v>0.53486599999999995</v>
+        <v>0.58388700000000004</v>
       </c>
       <c r="H24" s="1">
-        <v>0.53841300000000003</v>
+        <v>0.58643900000000004</v>
       </c>
       <c r="I24" s="1">
-        <v>0.54214899999999999</v>
+        <v>0.58914200000000005</v>
       </c>
       <c r="J24" s="1">
-        <v>0.54178999999999999</v>
+        <v>0.59154799999999996</v>
       </c>
       <c r="K24" s="1">
-        <v>0.547261</v>
+        <v>0.58960299999999999</v>
       </c>
       <c r="L24" s="1">
-        <v>0.54889600000000005</v>
+        <v>0.59009400000000001</v>
       </c>
       <c r="M24" s="1">
-        <v>0.55136499999999999</v>
+        <v>0.59283200000000003</v>
       </c>
       <c r="N24" s="1">
-        <v>0.55600799999999995</v>
+        <v>0.59631900000000004</v>
       </c>
       <c r="O24" s="1">
-        <v>0.55865200000000004</v>
+        <v>0.60074899999999998</v>
       </c>
       <c r="P24" s="1">
-        <v>0.56875500000000001</v>
+        <v>0.61074899999999999</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.57606999999999997</v>
+        <v>0.61193799999999998</v>
       </c>
       <c r="R24" s="1">
-        <v>0.57401199999999997</v>
+        <v>0.60665800000000003</v>
       </c>
       <c r="S24" s="1">
-        <v>0.58270299999999997</v>
+        <v>0.61629199999999995</v>
       </c>
       <c r="T24" s="1">
-        <v>0.58080500000000002</v>
+        <v>0.61656500000000003</v>
       </c>
       <c r="U24" s="1">
-        <v>0.59309699999999999</v>
+        <v>0.62118700000000004</v>
       </c>
       <c r="V24" s="1">
-        <v>0.59602500000000003</v>
+        <v>0.61916099999999996</v>
       </c>
       <c r="W24" s="1">
-        <v>0.58820700000000004</v>
+        <v>0.64156800000000003</v>
       </c>
       <c r="X24" s="1">
-        <v>0.60105799999999998</v>
+        <v>0.64440600000000003</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.60319999999999996</v>
+        <v>0.61796300000000004</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
-        <v>0.44573299999999999</v>
+        <v>0.50444900000000004</v>
       </c>
       <c r="B25" s="1">
-        <v>0.44565300000000002</v>
+        <v>0.50394899999999998</v>
       </c>
       <c r="C25" s="1">
-        <v>0.44516299999999998</v>
+        <v>0.50322199999999995</v>
       </c>
       <c r="D25" s="1">
-        <v>0.44772200000000001</v>
+        <v>0.50278400000000001</v>
       </c>
       <c r="E25" s="1">
-        <v>0.44720399999999999</v>
+        <v>0.50236000000000003</v>
       </c>
       <c r="F25" s="1">
-        <v>0.44631999999999999</v>
+        <v>0.50170099999999995</v>
       </c>
       <c r="G25" s="1">
-        <v>0.44590999999999997</v>
+        <v>0.50077199999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>0.44829599999999997</v>
+        <v>0.50268299999999999</v>
       </c>
       <c r="I25" s="1">
-        <v>0.44769300000000001</v>
+        <v>0.50160800000000005</v>
       </c>
       <c r="J25" s="1">
-        <v>0.44647599999999998</v>
+        <v>0.50651400000000002</v>
       </c>
       <c r="K25" s="1">
-        <v>0.44888899999999998</v>
+        <v>0.50525799999999998</v>
       </c>
       <c r="L25" s="1">
-        <v>0.45123400000000002</v>
+        <v>0.51023499999999999</v>
       </c>
       <c r="M25" s="1">
-        <v>0.45622499999999999</v>
+        <v>0.51452399999999998</v>
       </c>
       <c r="N25" s="1">
-        <v>0.45838899999999999</v>
+        <v>0.51322599999999996</v>
       </c>
       <c r="O25" s="1">
-        <v>0.45674199999999998</v>
+        <v>0.52746099999999996</v>
       </c>
       <c r="P25" s="1">
-        <v>0.46098499999999998</v>
+        <v>0.53505400000000003</v>
       </c>
       <c r="Q25" s="1">
-        <v>0.46078799999999998</v>
+        <v>0.53544999999999998</v>
       </c>
       <c r="R25" s="1">
-        <v>0.46606500000000001</v>
+        <v>0.53142100000000003</v>
       </c>
       <c r="S25" s="1">
-        <v>0.46917399999999998</v>
+        <v>0.54202600000000001</v>
       </c>
       <c r="T25" s="1">
-        <v>0.46686499999999997</v>
+        <v>0.53917199999999998</v>
       </c>
       <c r="U25" s="1">
-        <v>0.47557899999999997</v>
+        <v>0.53331700000000004</v>
       </c>
       <c r="V25" s="1">
-        <v>0.48630800000000002</v>
+        <v>0.52821300000000004</v>
       </c>
       <c r="W25" s="1">
-        <v>0.49148599999999998</v>
+        <v>0.55374599999999996</v>
       </c>
       <c r="X25" s="1">
-        <v>0.50405</v>
+        <v>0.54732400000000003</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.47830299999999998</v>
+        <v>0.53135100000000002</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_large.xlsx
+++ b/TMVA/FOM_large.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F906D4-FCD1-48D5-93BF-B037D40E67BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85C998F-0F37-4F53-8A5D-BBA52CF84B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,1927 +355,1927 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>0.572272</v>
+        <v>0.57933000000000001</v>
       </c>
       <c r="B1" s="1">
-        <v>0.57640899999999995</v>
+        <v>0.58215399999999995</v>
       </c>
       <c r="C1" s="1">
-        <v>0.579175</v>
+        <v>0.58509199999999995</v>
       </c>
       <c r="D1" s="1">
-        <v>0.58387699999999998</v>
+        <v>0.58939900000000001</v>
       </c>
       <c r="E1" s="1">
-        <v>0.58683300000000005</v>
+        <v>0.59335499999999997</v>
       </c>
       <c r="F1" s="1">
-        <v>0.59157099999999996</v>
+        <v>0.59760100000000005</v>
       </c>
       <c r="G1" s="1">
-        <v>0.595024</v>
+        <v>0.60028499999999996</v>
       </c>
       <c r="H1" s="1">
-        <v>0.59992199999999996</v>
+        <v>0.604688</v>
       </c>
       <c r="I1" s="1">
-        <v>0.60562000000000005</v>
+        <v>0.60995100000000002</v>
       </c>
       <c r="J1" s="1">
-        <v>0.60960199999999998</v>
+        <v>0.61321000000000003</v>
       </c>
       <c r="K1" s="1">
-        <v>0.61582599999999998</v>
+        <v>0.616784</v>
       </c>
       <c r="L1" s="1">
-        <v>0.61981900000000001</v>
+        <v>0.62447900000000001</v>
       </c>
       <c r="M1" s="1">
-        <v>0.62619499999999995</v>
+        <v>0.629386</v>
       </c>
       <c r="N1" s="1">
-        <v>0.63338499999999998</v>
+        <v>0.63611799999999996</v>
       </c>
       <c r="O1" s="1">
-        <v>0.64135900000000001</v>
+        <v>0.64751199999999998</v>
       </c>
       <c r="P1" s="1">
-        <v>0.65266800000000003</v>
+        <v>0.65600599999999998</v>
       </c>
       <c r="Q1" s="1">
-        <v>0.65827599999999997</v>
+        <v>0.66536899999999999</v>
       </c>
       <c r="R1" s="1">
-        <v>0.66335699999999997</v>
+        <v>0.67693499999999995</v>
       </c>
       <c r="S1" s="1">
-        <v>0.67405599999999999</v>
+        <v>0.68998199999999998</v>
       </c>
       <c r="T1" s="1">
-        <v>0.69075399999999998</v>
+        <v>0.698847</v>
       </c>
       <c r="U1" s="1">
-        <v>0.69638900000000004</v>
+        <v>0.71392199999999995</v>
       </c>
       <c r="V1" s="1">
-        <v>0.70747000000000004</v>
+        <v>0.73026999999999997</v>
       </c>
       <c r="W1" s="1">
-        <v>0.73358000000000001</v>
+        <v>0.74621899999999997</v>
       </c>
       <c r="X1" s="1">
-        <v>0.74151199999999995</v>
+        <v>0.76762900000000001</v>
       </c>
       <c r="Y1" s="1">
-        <v>0.72225099999999998</v>
+        <v>0.73156600000000005</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
-        <v>0.57383499999999998</v>
+        <v>0.58126699999999998</v>
       </c>
       <c r="B2" s="1">
-        <v>0.57784000000000002</v>
+        <v>0.583839</v>
       </c>
       <c r="C2" s="1">
-        <v>0.58047300000000002</v>
+        <v>0.58669400000000005</v>
       </c>
       <c r="D2" s="1">
-        <v>0.58530499999999996</v>
+        <v>0.59081499999999998</v>
       </c>
       <c r="E2" s="1">
-        <v>0.58852800000000005</v>
+        <v>0.59491899999999998</v>
       </c>
       <c r="F2" s="1">
-        <v>0.59351500000000001</v>
+        <v>0.59905399999999998</v>
       </c>
       <c r="G2" s="1">
-        <v>0.59693200000000002</v>
+        <v>0.60120600000000002</v>
       </c>
       <c r="H2" s="1">
-        <v>0.60220399999999996</v>
+        <v>0.60578100000000001</v>
       </c>
       <c r="I2" s="1">
-        <v>0.607348</v>
+        <v>0.61065599999999998</v>
       </c>
       <c r="J2" s="1">
-        <v>0.61121199999999998</v>
+        <v>0.61381799999999997</v>
       </c>
       <c r="K2" s="1">
-        <v>0.61769700000000005</v>
+        <v>0.61723899999999998</v>
       </c>
       <c r="L2" s="1">
-        <v>0.62219400000000002</v>
+        <v>0.62453800000000004</v>
       </c>
       <c r="M2" s="1">
-        <v>0.62817699999999999</v>
+        <v>0.62967799999999996</v>
       </c>
       <c r="N2" s="1">
-        <v>0.63425900000000002</v>
+        <v>0.63610599999999995</v>
       </c>
       <c r="O2" s="1">
-        <v>0.64139999999999997</v>
+        <v>0.64691600000000005</v>
       </c>
       <c r="P2" s="1">
-        <v>0.65310999999999997</v>
+        <v>0.65575799999999995</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.65864699999999998</v>
+        <v>0.66529000000000005</v>
       </c>
       <c r="R2" s="1">
-        <v>0.664022</v>
+        <v>0.67689699999999997</v>
       </c>
       <c r="S2" s="1">
-        <v>0.67466499999999996</v>
+        <v>0.68934099999999998</v>
       </c>
       <c r="T2" s="1">
-        <v>0.69103199999999998</v>
+        <v>0.69789900000000005</v>
       </c>
       <c r="U2" s="1">
-        <v>0.69780799999999998</v>
+        <v>0.71266799999999997</v>
       </c>
       <c r="V2" s="1">
-        <v>0.71012200000000003</v>
+        <v>0.72914999999999996</v>
       </c>
       <c r="W2" s="1">
-        <v>0.73428599999999999</v>
+        <v>0.74469099999999999</v>
       </c>
       <c r="X2" s="1">
-        <v>0.73932200000000003</v>
+        <v>0.76561100000000004</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.72215200000000002</v>
+        <v>0.72997900000000004</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
-        <v>0.57494299999999998</v>
+        <v>0.58355900000000005</v>
       </c>
       <c r="B3" s="1">
-        <v>0.57898400000000005</v>
+        <v>0.58626299999999998</v>
       </c>
       <c r="C3" s="1">
-        <v>0.58203300000000002</v>
+        <v>0.58919500000000002</v>
       </c>
       <c r="D3" s="1">
-        <v>0.58662700000000001</v>
+        <v>0.59346500000000002</v>
       </c>
       <c r="E3" s="1">
-        <v>0.58976700000000004</v>
+        <v>0.59748100000000004</v>
       </c>
       <c r="F3" s="1">
-        <v>0.59455499999999994</v>
+        <v>0.60175800000000002</v>
       </c>
       <c r="G3" s="1">
-        <v>0.59784899999999996</v>
+        <v>0.60374399999999995</v>
       </c>
       <c r="H3" s="1">
-        <v>0.60282800000000003</v>
+        <v>0.60836900000000005</v>
       </c>
       <c r="I3" s="1">
-        <v>0.60810799999999998</v>
+        <v>0.61335499999999998</v>
       </c>
       <c r="J3" s="1">
-        <v>0.61237399999999997</v>
+        <v>0.61639100000000002</v>
       </c>
       <c r="K3" s="1">
-        <v>0.618394</v>
+        <v>0.62016899999999997</v>
       </c>
       <c r="L3" s="1">
-        <v>0.62281699999999995</v>
+        <v>0.62750399999999995</v>
       </c>
       <c r="M3" s="1">
-        <v>0.628695</v>
+        <v>0.63298500000000002</v>
       </c>
       <c r="N3" s="1">
-        <v>0.63514199999999998</v>
+        <v>0.63893699999999998</v>
       </c>
       <c r="O3" s="1">
-        <v>0.64186399999999999</v>
+        <v>0.65025999999999995</v>
       </c>
       <c r="P3" s="1">
-        <v>0.65336700000000003</v>
+        <v>0.65908299999999997</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.65844499999999995</v>
+        <v>0.66755600000000004</v>
       </c>
       <c r="R3" s="1">
-        <v>0.66425000000000001</v>
+        <v>0.67999799999999999</v>
       </c>
       <c r="S3" s="1">
-        <v>0.67444400000000004</v>
+        <v>0.69303400000000004</v>
       </c>
       <c r="T3" s="1">
-        <v>0.68989100000000003</v>
+        <v>0.70124699999999995</v>
       </c>
       <c r="U3" s="1">
-        <v>0.697106</v>
+        <v>0.71513599999999999</v>
       </c>
       <c r="V3" s="1">
-        <v>0.70942400000000005</v>
+        <v>0.72882899999999995</v>
       </c>
       <c r="W3" s="2">
-        <v>0.735205</v>
+        <v>0.74541800000000003</v>
       </c>
       <c r="X3" s="1">
-        <v>0.739456</v>
+        <v>0.766401</v>
       </c>
       <c r="Y3" s="1">
-        <v>0.721607</v>
+        <v>0.72969899999999999</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
-        <v>0.57752300000000001</v>
+        <v>0.58613300000000002</v>
       </c>
       <c r="B4" s="1">
-        <v>0.581677</v>
+        <v>0.58877900000000005</v>
       </c>
       <c r="C4" s="1">
-        <v>0.584511</v>
+        <v>0.59202500000000002</v>
       </c>
       <c r="D4" s="1">
-        <v>0.58893600000000002</v>
+        <v>0.59651100000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>0.59207799999999999</v>
+        <v>0.60055999999999998</v>
       </c>
       <c r="F4" s="1">
-        <v>0.59681099999999998</v>
+        <v>0.60480699999999998</v>
       </c>
       <c r="G4" s="1">
-        <v>0.60037399999999996</v>
+        <v>0.60638400000000003</v>
       </c>
       <c r="H4" s="1">
-        <v>0.60524699999999998</v>
+        <v>0.61148100000000005</v>
       </c>
       <c r="I4" s="1">
-        <v>0.61061100000000001</v>
+        <v>0.61567300000000003</v>
       </c>
       <c r="J4" s="1">
-        <v>0.61499700000000002</v>
+        <v>0.61869499999999999</v>
       </c>
       <c r="K4" s="1">
-        <v>0.62058199999999997</v>
+        <v>0.62260400000000005</v>
       </c>
       <c r="L4" s="1">
-        <v>0.62477899999999997</v>
+        <v>0.62959900000000002</v>
       </c>
       <c r="M4" s="1">
-        <v>0.63079399999999997</v>
+        <v>0.63510299999999997</v>
       </c>
       <c r="N4" s="1">
-        <v>0.63732900000000003</v>
+        <v>0.64160099999999998</v>
       </c>
       <c r="O4" s="1">
-        <v>0.64384799999999998</v>
+        <v>0.65210500000000005</v>
       </c>
       <c r="P4" s="1">
-        <v>0.65604399999999996</v>
+        <v>0.66095899999999996</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.66139199999999998</v>
+        <v>0.66918699999999998</v>
       </c>
       <c r="R4" s="1">
-        <v>0.66703900000000005</v>
+        <v>0.68101400000000001</v>
       </c>
       <c r="S4" s="1">
-        <v>0.67732700000000001</v>
+        <v>0.69444600000000001</v>
       </c>
       <c r="T4" s="1">
-        <v>0.69377599999999995</v>
+        <v>0.70198300000000002</v>
       </c>
       <c r="U4" s="1">
-        <v>0.70106500000000005</v>
+        <v>0.71594100000000005</v>
       </c>
       <c r="V4" s="1">
-        <v>0.71055699999999999</v>
+        <v>0.73089999999999999</v>
       </c>
       <c r="W4" s="1">
-        <v>0.73526499999999995</v>
+        <v>0.74648599999999998</v>
       </c>
       <c r="X4" s="1">
-        <v>0.74108399999999996</v>
+        <v>0.76640600000000003</v>
       </c>
       <c r="Y4" s="1">
-        <v>0.71930799999999995</v>
+        <v>0.72877499999999995</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
-        <v>0.57824200000000003</v>
+        <v>0.58961399999999997</v>
       </c>
       <c r="B5" s="1">
-        <v>0.58252499999999996</v>
+        <v>0.59245999999999999</v>
       </c>
       <c r="C5" s="1">
-        <v>0.58508599999999999</v>
+        <v>0.59547499999999998</v>
       </c>
       <c r="D5" s="1">
-        <v>0.58960800000000002</v>
+        <v>0.599823</v>
       </c>
       <c r="E5" s="1">
-        <v>0.59262800000000004</v>
+        <v>0.60385299999999997</v>
       </c>
       <c r="F5" s="1">
-        <v>0.59697100000000003</v>
+        <v>0.60805900000000002</v>
       </c>
       <c r="G5" s="1">
-        <v>0.60035799999999995</v>
+        <v>0.60952200000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>0.60526800000000003</v>
+        <v>0.61430200000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>0.61070100000000005</v>
+        <v>0.61820299999999995</v>
       </c>
       <c r="J5" s="1">
-        <v>0.61483600000000005</v>
+        <v>0.62092599999999998</v>
       </c>
       <c r="K5" s="1">
-        <v>0.620556</v>
+        <v>0.62494000000000005</v>
       </c>
       <c r="L5" s="1">
-        <v>0.624394</v>
+        <v>0.63172200000000001</v>
       </c>
       <c r="M5" s="1">
-        <v>0.63085599999999997</v>
+        <v>0.63736400000000004</v>
       </c>
       <c r="N5" s="1">
-        <v>0.63710800000000001</v>
+        <v>0.64428099999999999</v>
       </c>
       <c r="O5" s="1">
-        <v>0.64406799999999997</v>
+        <v>0.65441899999999997</v>
       </c>
       <c r="P5" s="1">
-        <v>0.65617800000000004</v>
+        <v>0.66344899999999996</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.661659</v>
+        <v>0.67215599999999998</v>
       </c>
       <c r="R5" s="1">
-        <v>0.66708999999999996</v>
+        <v>0.68412200000000001</v>
       </c>
       <c r="S5" s="1">
-        <v>0.67729899999999998</v>
+        <v>0.69639099999999998</v>
       </c>
       <c r="T5" s="1">
-        <v>0.69351799999999997</v>
+        <v>0.703596</v>
       </c>
       <c r="U5" s="1">
-        <v>0.70158399999999999</v>
+        <v>0.71921299999999999</v>
       </c>
       <c r="V5" s="1">
-        <v>0.71016599999999996</v>
+        <v>0.73261200000000004</v>
       </c>
       <c r="W5" s="1">
-        <v>0.73428899999999997</v>
+        <v>0.74734299999999998</v>
       </c>
       <c r="X5" s="1">
-        <v>0.74022399999999999</v>
+        <v>0.76585300000000001</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.71889700000000001</v>
+        <v>0.72674399999999995</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
-        <v>0.58206899999999995</v>
+        <v>0.59243299999999999</v>
       </c>
       <c r="B6" s="1">
-        <v>0.58631599999999995</v>
+        <v>0.59525700000000004</v>
       </c>
       <c r="C6" s="1">
-        <v>0.58881300000000003</v>
+        <v>0.59752700000000003</v>
       </c>
       <c r="D6" s="1">
-        <v>0.59318700000000002</v>
+        <v>0.601738</v>
       </c>
       <c r="E6" s="1">
-        <v>0.59632099999999999</v>
+        <v>0.60580999999999996</v>
       </c>
       <c r="F6" s="1">
-        <v>0.60065000000000002</v>
+        <v>0.60937399999999997</v>
       </c>
       <c r="G6" s="1">
-        <v>0.60388299999999995</v>
+        <v>0.61092400000000002</v>
       </c>
       <c r="H6" s="1">
-        <v>0.60933400000000004</v>
+        <v>0.61518399999999995</v>
       </c>
       <c r="I6" s="1">
-        <v>0.61495999999999995</v>
+        <v>0.61890000000000001</v>
       </c>
       <c r="J6" s="1">
-        <v>0.61905600000000005</v>
+        <v>0.62129900000000005</v>
       </c>
       <c r="K6" s="1">
-        <v>0.62450499999999998</v>
+        <v>0.62547399999999997</v>
       </c>
       <c r="L6" s="1">
-        <v>0.62836700000000001</v>
+        <v>0.63247200000000003</v>
       </c>
       <c r="M6" s="1">
-        <v>0.63453099999999996</v>
+        <v>0.637486</v>
       </c>
       <c r="N6" s="1">
-        <v>0.64136000000000004</v>
+        <v>0.64391600000000004</v>
       </c>
       <c r="O6" s="1">
-        <v>0.64820100000000003</v>
+        <v>0.65449100000000004</v>
       </c>
       <c r="P6" s="1">
-        <v>0.66035500000000003</v>
+        <v>0.663991</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.66575200000000001</v>
+        <v>0.67330599999999996</v>
       </c>
       <c r="R6" s="1">
-        <v>0.67041300000000004</v>
+        <v>0.68518800000000002</v>
       </c>
       <c r="S6" s="1">
-        <v>0.68197399999999997</v>
+        <v>0.69708199999999998</v>
       </c>
       <c r="T6" s="1">
-        <v>0.69790399999999997</v>
+        <v>0.70327899999999999</v>
       </c>
       <c r="U6" s="1">
-        <v>0.70640800000000004</v>
+        <v>0.71854099999999999</v>
       </c>
       <c r="V6" s="1">
-        <v>0.71633899999999995</v>
+        <v>0.73117600000000005</v>
       </c>
       <c r="W6" s="1">
-        <v>0.73579899999999998</v>
+        <v>0.74753199999999997</v>
       </c>
       <c r="X6" s="1">
-        <v>0.73814199999999996</v>
+        <v>0.76593900000000004</v>
       </c>
       <c r="Y6" s="1">
-        <v>0.71828499999999995</v>
+        <v>0.72599000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
-        <v>0.58379300000000001</v>
+        <v>0.59497199999999995</v>
       </c>
       <c r="B7" s="1">
-        <v>0.588256</v>
+        <v>0.59808899999999998</v>
       </c>
       <c r="C7" s="1">
-        <v>0.59087599999999996</v>
+        <v>0.60041800000000001</v>
       </c>
       <c r="D7" s="1">
-        <v>0.59529900000000002</v>
+        <v>0.604271</v>
       </c>
       <c r="E7" s="1">
-        <v>0.59813799999999995</v>
+        <v>0.60783900000000002</v>
       </c>
       <c r="F7" s="1">
-        <v>0.60246299999999997</v>
+        <v>0.611483</v>
       </c>
       <c r="G7" s="1">
-        <v>0.60578500000000002</v>
+        <v>0.61269200000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>0.61121499999999995</v>
+        <v>0.61728899999999998</v>
       </c>
       <c r="I7" s="1">
-        <v>0.61634</v>
+        <v>0.62061699999999997</v>
       </c>
       <c r="J7" s="1">
-        <v>0.62057899999999999</v>
+        <v>0.62359600000000004</v>
       </c>
       <c r="K7" s="1">
-        <v>0.62616899999999998</v>
+        <v>0.62739299999999998</v>
       </c>
       <c r="L7" s="1">
-        <v>0.62974699999999995</v>
+        <v>0.63386200000000004</v>
       </c>
       <c r="M7" s="1">
-        <v>0.63623099999999999</v>
+        <v>0.63920900000000003</v>
       </c>
       <c r="N7" s="1">
-        <v>0.64247799999999999</v>
+        <v>0.644729</v>
       </c>
       <c r="O7" s="1">
-        <v>0.64943200000000001</v>
+        <v>0.65486200000000006</v>
       </c>
       <c r="P7" s="1">
-        <v>0.66146300000000002</v>
+        <v>0.66431499999999999</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.66659599999999997</v>
+        <v>0.67396400000000001</v>
       </c>
       <c r="R7" s="1">
-        <v>0.67163300000000004</v>
+        <v>0.68618699999999999</v>
       </c>
       <c r="S7" s="1">
-        <v>0.68392399999999998</v>
+        <v>0.69754799999999995</v>
       </c>
       <c r="T7" s="1">
-        <v>0.69816999999999996</v>
+        <v>0.70386599999999999</v>
       </c>
       <c r="U7" s="1">
-        <v>0.70588799999999996</v>
+        <v>0.718198</v>
       </c>
       <c r="V7" s="1">
-        <v>0.71623300000000001</v>
+        <v>0.73156200000000005</v>
       </c>
       <c r="W7" s="1">
-        <v>0.735626</v>
+        <v>0.74975499999999995</v>
       </c>
       <c r="X7" s="1">
-        <v>0.73562899999999998</v>
+        <v>0.767903</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.71958500000000003</v>
+        <v>0.72748299999999999</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>0.58699299999999999</v>
+        <v>0.59786799999999996</v>
       </c>
       <c r="B8" s="1">
-        <v>0.59092</v>
+        <v>0.60092599999999996</v>
       </c>
       <c r="C8" s="1">
-        <v>0.59360999999999997</v>
+        <v>0.60295299999999996</v>
       </c>
       <c r="D8" s="1">
-        <v>0.59778299999999995</v>
+        <v>0.60666100000000001</v>
       </c>
       <c r="E8" s="1">
-        <v>0.60035099999999997</v>
+        <v>0.61021700000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>0.60433099999999995</v>
+        <v>0.61364099999999999</v>
       </c>
       <c r="G8" s="1">
-        <v>0.60790200000000005</v>
+        <v>0.61514400000000002</v>
       </c>
       <c r="H8" s="1">
-        <v>0.61304800000000004</v>
+        <v>0.61940200000000001</v>
       </c>
       <c r="I8" s="1">
-        <v>0.61793600000000004</v>
+        <v>0.62294400000000005</v>
       </c>
       <c r="J8" s="1">
-        <v>0.62238599999999999</v>
+        <v>0.62582400000000005</v>
       </c>
       <c r="K8" s="1">
-        <v>0.62761900000000004</v>
+        <v>0.62937100000000001</v>
       </c>
       <c r="L8" s="1">
-        <v>0.63158999999999998</v>
+        <v>0.63628099999999999</v>
       </c>
       <c r="M8" s="1">
-        <v>0.63788500000000004</v>
+        <v>0.64197300000000002</v>
       </c>
       <c r="N8" s="1">
-        <v>0.64456100000000005</v>
+        <v>0.64780800000000005</v>
       </c>
       <c r="O8" s="1">
-        <v>0.65161199999999997</v>
+        <v>0.65812999999999999</v>
       </c>
       <c r="P8" s="1">
-        <v>0.664663</v>
+        <v>0.66800400000000004</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.67100599999999999</v>
+        <v>0.67783199999999999</v>
       </c>
       <c r="R8" s="1">
-        <v>0.67638799999999999</v>
+        <v>0.69004900000000002</v>
       </c>
       <c r="S8" s="1">
-        <v>0.68783700000000003</v>
+        <v>0.70160599999999995</v>
       </c>
       <c r="T8" s="1">
-        <v>0.70270100000000002</v>
+        <v>0.70800200000000002</v>
       </c>
       <c r="U8" s="1">
-        <v>0.70950100000000005</v>
+        <v>0.72218899999999997</v>
       </c>
       <c r="V8" s="1">
-        <v>0.71950199999999997</v>
+        <v>0.73456100000000002</v>
       </c>
       <c r="W8" s="1">
-        <v>0.73977599999999999</v>
+        <v>0.75390000000000001</v>
       </c>
       <c r="X8" s="1">
-        <v>0.73868400000000001</v>
+        <v>0.77088400000000001</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.71996099999999996</v>
+        <v>0.73068900000000003</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
-        <v>0.58843100000000004</v>
+        <v>0.59980199999999995</v>
       </c>
       <c r="B9" s="1">
-        <v>0.59230099999999997</v>
+        <v>0.602877</v>
       </c>
       <c r="C9" s="1">
-        <v>0.59543500000000005</v>
+        <v>0.60475900000000005</v>
       </c>
       <c r="D9" s="1">
-        <v>0.59938800000000003</v>
+        <v>0.60853699999999999</v>
       </c>
       <c r="E9" s="1">
-        <v>0.60174499999999997</v>
+        <v>0.61162000000000005</v>
       </c>
       <c r="F9" s="1">
-        <v>0.60557799999999995</v>
+        <v>0.61523000000000005</v>
       </c>
       <c r="G9" s="1">
-        <v>0.60923700000000003</v>
+        <v>0.61691700000000005</v>
       </c>
       <c r="H9" s="1">
-        <v>0.61398299999999995</v>
+        <v>0.621479</v>
       </c>
       <c r="I9" s="1">
-        <v>0.61870800000000004</v>
+        <v>0.62448999999999999</v>
       </c>
       <c r="J9" s="1">
-        <v>0.62296200000000002</v>
+        <v>0.62770000000000004</v>
       </c>
       <c r="K9" s="1">
-        <v>0.62803200000000003</v>
+        <v>0.63149299999999997</v>
       </c>
       <c r="L9" s="1">
-        <v>0.63144199999999995</v>
+        <v>0.63875300000000002</v>
       </c>
       <c r="M9" s="1">
-        <v>0.63781200000000005</v>
+        <v>0.64358099999999996</v>
       </c>
       <c r="N9" s="1">
-        <v>0.64439900000000006</v>
+        <v>0.64995800000000004</v>
       </c>
       <c r="O9" s="1">
-        <v>0.65168000000000004</v>
+        <v>0.660694</v>
       </c>
       <c r="P9" s="1">
-        <v>0.66472799999999999</v>
+        <v>0.67026699999999995</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.67122300000000001</v>
+        <v>0.68078700000000003</v>
       </c>
       <c r="R9" s="1">
-        <v>0.67665699999999995</v>
+        <v>0.69407600000000003</v>
       </c>
       <c r="S9" s="1">
-        <v>0.68720000000000003</v>
+        <v>0.70470299999999997</v>
       </c>
       <c r="T9" s="1">
-        <v>0.70257999999999998</v>
+        <v>0.71199599999999996</v>
       </c>
       <c r="U9" s="1">
-        <v>0.71021900000000004</v>
+        <v>0.72491499999999998</v>
       </c>
       <c r="V9" s="1">
-        <v>0.71807100000000001</v>
+        <v>0.73695299999999997</v>
       </c>
       <c r="W9" s="1">
-        <v>0.73891499999999999</v>
+        <v>0.75603500000000001</v>
       </c>
       <c r="X9" s="1">
-        <v>0.73724599999999996</v>
+        <v>0.769177</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.71634299999999995</v>
+        <v>0.72867000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
-        <v>0.59074300000000002</v>
+        <v>0.60309400000000002</v>
       </c>
       <c r="B10" s="1">
-        <v>0.59414400000000001</v>
+        <v>0.60635300000000003</v>
       </c>
       <c r="C10" s="1">
-        <v>0.59711400000000003</v>
+        <v>0.60777199999999998</v>
       </c>
       <c r="D10" s="1">
-        <v>0.60150899999999996</v>
+        <v>0.61134699999999997</v>
       </c>
       <c r="E10" s="1">
-        <v>0.60336500000000004</v>
+        <v>0.61438199999999998</v>
       </c>
       <c r="F10" s="1">
-        <v>0.60742399999999996</v>
+        <v>0.61778999999999995</v>
       </c>
       <c r="G10" s="1">
-        <v>0.61124900000000004</v>
+        <v>0.61956100000000003</v>
       </c>
       <c r="H10" s="1">
-        <v>0.61606499999999997</v>
+        <v>0.62333300000000003</v>
       </c>
       <c r="I10" s="1">
-        <v>0.62093200000000004</v>
+        <v>0.62626099999999996</v>
       </c>
       <c r="J10" s="1">
-        <v>0.62429999999999997</v>
+        <v>0.62961199999999995</v>
       </c>
       <c r="K10" s="1">
-        <v>0.62909499999999996</v>
+        <v>0.63291299999999995</v>
       </c>
       <c r="L10" s="1">
-        <v>0.63276699999999997</v>
+        <v>0.64052100000000001</v>
       </c>
       <c r="M10" s="1">
-        <v>0.63860799999999995</v>
+        <v>0.64488100000000004</v>
       </c>
       <c r="N10" s="1">
-        <v>0.64541999999999999</v>
+        <v>0.65110400000000002</v>
       </c>
       <c r="O10" s="1">
-        <v>0.65278700000000001</v>
+        <v>0.66130199999999995</v>
       </c>
       <c r="P10" s="1">
-        <v>0.66583300000000001</v>
+        <v>0.67114300000000005</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.67208199999999996</v>
+        <v>0.68146200000000001</v>
       </c>
       <c r="R10" s="1">
-        <v>0.678396</v>
+        <v>0.69376599999999999</v>
       </c>
       <c r="S10" s="1">
-        <v>0.68861799999999995</v>
+        <v>0.70392299999999997</v>
       </c>
       <c r="T10" s="1">
-        <v>0.70259099999999997</v>
+        <v>0.71180299999999996</v>
       </c>
       <c r="U10" s="1">
-        <v>0.71066600000000002</v>
+        <v>0.72506499999999996</v>
       </c>
       <c r="V10" s="1">
-        <v>0.71765900000000005</v>
+        <v>0.73661100000000002</v>
       </c>
       <c r="W10" s="1">
-        <v>0.73916000000000004</v>
+        <v>0.75340099999999999</v>
       </c>
       <c r="X10" s="1">
-        <v>0.73618600000000001</v>
+        <v>0.76749599999999996</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.71413599999999999</v>
+        <v>0.73025099999999998</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
-        <v>0.59173399999999998</v>
+        <v>0.603912</v>
       </c>
       <c r="B11" s="1">
-        <v>0.59523499999999996</v>
+        <v>0.60723000000000005</v>
       </c>
       <c r="C11" s="1">
-        <v>0.59865400000000002</v>
+        <v>0.60872400000000004</v>
       </c>
       <c r="D11" s="1">
-        <v>0.603186</v>
+        <v>0.61224500000000004</v>
       </c>
       <c r="E11" s="1">
-        <v>0.60524199999999995</v>
+        <v>0.61488900000000002</v>
       </c>
       <c r="F11" s="1">
-        <v>0.608765</v>
+        <v>0.61757300000000004</v>
       </c>
       <c r="G11" s="1">
-        <v>0.61220399999999997</v>
+        <v>0.61947099999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>0.61683200000000005</v>
+        <v>0.62315100000000001</v>
       </c>
       <c r="I11" s="1">
-        <v>0.62228099999999997</v>
+        <v>0.62522599999999995</v>
       </c>
       <c r="J11" s="1">
-        <v>0.62598399999999998</v>
+        <v>0.62846100000000005</v>
       </c>
       <c r="K11" s="1">
-        <v>0.63112699999999999</v>
+        <v>0.63202700000000001</v>
       </c>
       <c r="L11" s="1">
-        <v>0.63497300000000001</v>
+        <v>0.63959299999999997</v>
       </c>
       <c r="M11" s="1">
-        <v>0.64112800000000003</v>
+        <v>0.64375199999999999</v>
       </c>
       <c r="N11" s="1">
-        <v>0.64767699999999995</v>
+        <v>0.64926300000000003</v>
       </c>
       <c r="O11" s="1">
-        <v>0.65484200000000004</v>
+        <v>0.65956700000000001</v>
       </c>
       <c r="P11" s="1">
-        <v>0.66805999999999999</v>
+        <v>0.66913599999999995</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.67396800000000001</v>
+        <v>0.67918100000000003</v>
       </c>
       <c r="R11" s="1">
-        <v>0.679898</v>
+        <v>0.69093899999999997</v>
       </c>
       <c r="S11" s="1">
-        <v>0.69011999999999996</v>
+        <v>0.70027899999999998</v>
       </c>
       <c r="T11" s="1">
-        <v>0.70358100000000001</v>
+        <v>0.70794900000000005</v>
       </c>
       <c r="U11" s="1">
-        <v>0.71241200000000005</v>
+        <v>0.72170699999999999</v>
       </c>
       <c r="V11" s="1">
-        <v>0.71859700000000004</v>
+        <v>0.73363199999999995</v>
       </c>
       <c r="W11" s="1">
-        <v>0.73910399999999998</v>
+        <v>0.75025799999999998</v>
       </c>
       <c r="X11" s="1">
-        <v>0.735348</v>
+        <v>0.76283800000000002</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.71248900000000004</v>
+        <v>0.72442700000000004</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
-        <v>0.59537399999999996</v>
+        <v>0.60383500000000001</v>
       </c>
       <c r="B12" s="1">
-        <v>0.59864200000000001</v>
+        <v>0.60718000000000005</v>
       </c>
       <c r="C12" s="1">
-        <v>0.60191399999999995</v>
+        <v>0.60895600000000005</v>
       </c>
       <c r="D12" s="1">
-        <v>0.60647899999999999</v>
+        <v>0.61248899999999995</v>
       </c>
       <c r="E12" s="1">
-        <v>0.60885500000000004</v>
+        <v>0.615147</v>
       </c>
       <c r="F12" s="1">
-        <v>0.61265499999999995</v>
+        <v>0.61801700000000004</v>
       </c>
       <c r="G12" s="1">
-        <v>0.61596300000000004</v>
+        <v>0.62053800000000003</v>
       </c>
       <c r="H12" s="1">
-        <v>0.62011099999999997</v>
+        <v>0.62388200000000005</v>
       </c>
       <c r="I12" s="1">
-        <v>0.62550600000000001</v>
+        <v>0.62589499999999998</v>
       </c>
       <c r="J12" s="1">
-        <v>0.62944900000000004</v>
+        <v>0.62876799999999999</v>
       </c>
       <c r="K12" s="1">
-        <v>0.63463400000000003</v>
+        <v>0.63229400000000002</v>
       </c>
       <c r="L12" s="1">
-        <v>0.63885800000000004</v>
+        <v>0.63930900000000002</v>
       </c>
       <c r="M12" s="1">
-        <v>0.64414300000000002</v>
+        <v>0.64355200000000001</v>
       </c>
       <c r="N12" s="1">
-        <v>0.65081299999999997</v>
+        <v>0.64902700000000002</v>
       </c>
       <c r="O12" s="1">
-        <v>0.65802099999999997</v>
+        <v>0.65876100000000004</v>
       </c>
       <c r="P12" s="1">
-        <v>0.67168399999999995</v>
+        <v>0.66807300000000003</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.67761499999999997</v>
+        <v>0.677732</v>
       </c>
       <c r="R12" s="1">
-        <v>0.68147999999999997</v>
+        <v>0.68943200000000004</v>
       </c>
       <c r="S12" s="1">
-        <v>0.69183899999999998</v>
+        <v>0.69926600000000005</v>
       </c>
       <c r="T12" s="1">
-        <v>0.70455800000000002</v>
+        <v>0.70470900000000003</v>
       </c>
       <c r="U12" s="1">
-        <v>0.71378699999999995</v>
+        <v>0.71849099999999999</v>
       </c>
       <c r="V12" s="1">
-        <v>0.71856299999999995</v>
+        <v>0.73239500000000002</v>
       </c>
       <c r="W12" s="1">
-        <v>0.73924199999999995</v>
+        <v>0.74889899999999998</v>
       </c>
       <c r="X12" s="1">
-        <v>0.73866299999999996</v>
+        <v>0.76139100000000004</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.71284599999999998</v>
+        <v>0.72076099999999999</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
-        <v>0.59828599999999998</v>
+        <v>0.60597400000000001</v>
       </c>
       <c r="B13" s="1">
-        <v>0.60180900000000004</v>
+        <v>0.60930600000000001</v>
       </c>
       <c r="C13" s="1">
-        <v>0.60507299999999997</v>
+        <v>0.61098799999999998</v>
       </c>
       <c r="D13" s="1">
-        <v>0.60873299999999997</v>
+        <v>0.614232</v>
       </c>
       <c r="E13" s="1">
-        <v>0.61165000000000003</v>
+        <v>0.61678699999999997</v>
       </c>
       <c r="F13" s="1">
-        <v>0.61475599999999997</v>
+        <v>0.61957799999999996</v>
       </c>
       <c r="G13" s="1">
-        <v>0.61746299999999998</v>
+        <v>0.62257200000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>0.62093799999999999</v>
+        <v>0.62583900000000003</v>
       </c>
       <c r="I13" s="1">
-        <v>0.62605200000000005</v>
+        <v>0.62779399999999996</v>
       </c>
       <c r="J13" s="1">
-        <v>0.63039900000000004</v>
+        <v>0.63017199999999995</v>
       </c>
       <c r="K13" s="1">
-        <v>0.63585100000000006</v>
+        <v>0.63346999999999998</v>
       </c>
       <c r="L13" s="1">
-        <v>0.64058800000000005</v>
+        <v>0.64075499999999996</v>
       </c>
       <c r="M13" s="1">
-        <v>0.64629800000000004</v>
+        <v>0.64466800000000002</v>
       </c>
       <c r="N13" s="1">
-        <v>0.65208500000000003</v>
+        <v>0.65117800000000003</v>
       </c>
       <c r="O13" s="1">
-        <v>0.65826499999999999</v>
+        <v>0.66071100000000005</v>
       </c>
       <c r="P13" s="1">
-        <v>0.67220500000000005</v>
+        <v>0.66973499999999997</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.679342</v>
+        <v>0.68022700000000003</v>
       </c>
       <c r="R13" s="1">
-        <v>0.68096800000000002</v>
+        <v>0.69050199999999995</v>
       </c>
       <c r="S13" s="1">
-        <v>0.69309600000000005</v>
+        <v>0.69890799999999997</v>
       </c>
       <c r="T13" s="1">
-        <v>0.70667000000000002</v>
+        <v>0.70353600000000005</v>
       </c>
       <c r="U13" s="1">
-        <v>0.71292</v>
+        <v>0.71684000000000003</v>
       </c>
       <c r="V13" s="1">
-        <v>0.71919699999999998</v>
+        <v>0.73197100000000004</v>
       </c>
       <c r="W13" s="1">
-        <v>0.73838199999999998</v>
+        <v>0.74500500000000003</v>
       </c>
       <c r="X13" s="1">
-        <v>0.73726100000000006</v>
+        <v>0.75911099999999998</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.71015499999999998</v>
+        <v>0.72203600000000001</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
-        <v>0.60033099999999995</v>
+        <v>0.60991600000000001</v>
       </c>
       <c r="B14" s="1">
-        <v>0.60367499999999996</v>
+        <v>0.61276200000000003</v>
       </c>
       <c r="C14" s="1">
-        <v>0.60630499999999998</v>
+        <v>0.61485900000000004</v>
       </c>
       <c r="D14" s="1">
-        <v>0.60833899999999996</v>
+        <v>0.61772700000000003</v>
       </c>
       <c r="E14" s="1">
-        <v>0.61131599999999997</v>
+        <v>0.62027600000000005</v>
       </c>
       <c r="F14" s="1">
-        <v>0.61463500000000004</v>
+        <v>0.62179799999999996</v>
       </c>
       <c r="G14" s="1">
-        <v>0.61708399999999997</v>
+        <v>0.62422299999999997</v>
       </c>
       <c r="H14" s="1">
-        <v>0.62039</v>
+        <v>0.62729900000000005</v>
       </c>
       <c r="I14" s="1">
-        <v>0.62490100000000004</v>
+        <v>0.62911899999999998</v>
       </c>
       <c r="J14" s="1">
-        <v>0.62880000000000003</v>
+        <v>0.63138499999999997</v>
       </c>
       <c r="K14" s="1">
-        <v>0.63336400000000004</v>
+        <v>0.63451000000000002</v>
       </c>
       <c r="L14" s="1">
-        <v>0.63785800000000004</v>
+        <v>0.64182700000000004</v>
       </c>
       <c r="M14" s="1">
-        <v>0.64346000000000003</v>
+        <v>0.64619000000000004</v>
       </c>
       <c r="N14" s="1">
-        <v>0.64939000000000002</v>
+        <v>0.65371999999999997</v>
       </c>
       <c r="O14" s="1">
-        <v>0.654999</v>
+        <v>0.66333200000000003</v>
       </c>
       <c r="P14" s="1">
-        <v>0.66910899999999995</v>
+        <v>0.67295700000000003</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.67488700000000001</v>
+        <v>0.68354300000000001</v>
       </c>
       <c r="R14" s="1">
-        <v>0.67618599999999995</v>
+        <v>0.69461300000000004</v>
       </c>
       <c r="S14" s="1">
-        <v>0.68837599999999999</v>
+        <v>0.70278799999999997</v>
       </c>
       <c r="T14" s="1">
-        <v>0.70181400000000005</v>
+        <v>0.70805200000000001</v>
       </c>
       <c r="U14" s="1">
-        <v>0.71105799999999997</v>
+        <v>0.71957700000000002</v>
       </c>
       <c r="V14" s="1">
-        <v>0.71610499999999999</v>
+        <v>0.73251500000000003</v>
       </c>
       <c r="W14" s="1">
-        <v>0.73232699999999995</v>
+        <v>0.74681399999999998</v>
       </c>
       <c r="X14" s="1">
-        <v>0.73340899999999998</v>
+        <v>0.75911600000000001</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.70784599999999998</v>
+        <v>0.72321599999999997</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
-        <v>0.60203499999999999</v>
+        <v>0.61368599999999995</v>
       </c>
       <c r="B15" s="1">
-        <v>0.60555999999999999</v>
+        <v>0.61622500000000002</v>
       </c>
       <c r="C15" s="1">
-        <v>0.608074</v>
+        <v>0.618282</v>
       </c>
       <c r="D15" s="1">
-        <v>0.61060999999999999</v>
+        <v>0.62114400000000003</v>
       </c>
       <c r="E15" s="1">
-        <v>0.61377199999999998</v>
+        <v>0.62401499999999999</v>
       </c>
       <c r="F15" s="1">
-        <v>0.61743099999999995</v>
+        <v>0.62516000000000005</v>
       </c>
       <c r="G15" s="1">
-        <v>0.61976399999999998</v>
+        <v>0.62739100000000003</v>
       </c>
       <c r="H15" s="1">
-        <v>0.62293399999999999</v>
+        <v>0.63049500000000003</v>
       </c>
       <c r="I15" s="1">
-        <v>0.62724400000000002</v>
+        <v>0.63238499999999997</v>
       </c>
       <c r="J15" s="1">
-        <v>0.63033399999999995</v>
+        <v>0.63484300000000005</v>
       </c>
       <c r="K15" s="1">
-        <v>0.63465899999999997</v>
+        <v>0.63820900000000003</v>
       </c>
       <c r="L15" s="1">
-        <v>0.63977600000000001</v>
+        <v>0.64454</v>
       </c>
       <c r="M15" s="1">
-        <v>0.64508100000000002</v>
+        <v>0.64997700000000003</v>
       </c>
       <c r="N15" s="1">
-        <v>0.65174600000000005</v>
+        <v>0.657196</v>
       </c>
       <c r="O15" s="1">
-        <v>0.657134</v>
+        <v>0.666107</v>
       </c>
       <c r="P15" s="1">
-        <v>0.670871</v>
+        <v>0.67561599999999999</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.67700400000000005</v>
+        <v>0.68572999999999995</v>
       </c>
       <c r="R15" s="1">
-        <v>0.67848600000000003</v>
+        <v>0.69499599999999995</v>
       </c>
       <c r="S15" s="1">
-        <v>0.69243699999999997</v>
+        <v>0.70336200000000004</v>
       </c>
       <c r="T15" s="1">
-        <v>0.70273799999999997</v>
+        <v>0.70838999999999996</v>
       </c>
       <c r="U15" s="1">
-        <v>0.71359700000000004</v>
+        <v>0.71989400000000003</v>
       </c>
       <c r="V15" s="1">
-        <v>0.72121800000000003</v>
+        <v>0.73165999999999998</v>
       </c>
       <c r="W15" s="1">
-        <v>0.73610600000000004</v>
+        <v>0.74811000000000005</v>
       </c>
       <c r="X15" s="1">
-        <v>0.73000299999999996</v>
+        <v>0.75645200000000001</v>
       </c>
       <c r="Y15" s="1">
-        <v>0.70624399999999998</v>
+        <v>0.72647899999999999</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
-        <v>0.60493200000000003</v>
+        <v>0.613178</v>
       </c>
       <c r="B16" s="1">
-        <v>0.60833599999999999</v>
+        <v>0.615788</v>
       </c>
       <c r="C16" s="1">
-        <v>0.61139200000000005</v>
+        <v>0.61772899999999997</v>
       </c>
       <c r="D16" s="1">
-        <v>0.61403399999999997</v>
+        <v>0.62068999999999996</v>
       </c>
       <c r="E16" s="1">
-        <v>0.61773299999999998</v>
+        <v>0.62384600000000001</v>
       </c>
       <c r="F16" s="1">
-        <v>0.62121899999999997</v>
+        <v>0.62447299999999994</v>
       </c>
       <c r="G16" s="1">
-        <v>0.62406899999999998</v>
+        <v>0.62503600000000004</v>
       </c>
       <c r="H16" s="1">
-        <v>0.62746199999999996</v>
+        <v>0.628224</v>
       </c>
       <c r="I16" s="1">
-        <v>0.63181399999999999</v>
+        <v>0.62970000000000004</v>
       </c>
       <c r="J16" s="1">
-        <v>0.63444599999999995</v>
+        <v>0.63119000000000003</v>
       </c>
       <c r="K16" s="1">
-        <v>0.639432</v>
+        <v>0.63401099999999999</v>
       </c>
       <c r="L16" s="1">
-        <v>0.64395599999999997</v>
+        <v>0.63975400000000004</v>
       </c>
       <c r="M16" s="1">
-        <v>0.64881299999999997</v>
+        <v>0.64451999999999998</v>
       </c>
       <c r="N16" s="1">
-        <v>0.65507099999999996</v>
+        <v>0.65238600000000002</v>
       </c>
       <c r="O16" s="1">
-        <v>0.66066000000000003</v>
+        <v>0.66201900000000002</v>
       </c>
       <c r="P16" s="1">
-        <v>0.67441700000000004</v>
+        <v>0.67146399999999995</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.68106199999999995</v>
+        <v>0.68345299999999998</v>
       </c>
       <c r="R16" s="1">
-        <v>0.68135500000000004</v>
+        <v>0.69163300000000005</v>
       </c>
       <c r="S16" s="1">
-        <v>0.69446399999999997</v>
+        <v>0.70013599999999998</v>
       </c>
       <c r="T16" s="1">
-        <v>0.70690600000000003</v>
+        <v>0.70382100000000003</v>
       </c>
       <c r="U16" s="1">
-        <v>0.71661900000000001</v>
+        <v>0.71697599999999995</v>
       </c>
       <c r="V16" s="1">
-        <v>0.72017399999999998</v>
+        <v>0.72766900000000001</v>
       </c>
       <c r="W16" s="1">
-        <v>0.73042399999999996</v>
+        <v>0.74164099999999999</v>
       </c>
       <c r="X16" s="1">
-        <v>0.72658299999999998</v>
+        <v>0.74819500000000005</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.70104</v>
+        <v>0.718194</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
-        <v>0.605572</v>
+        <v>0.61365400000000003</v>
       </c>
       <c r="B17" s="1">
-        <v>0.60861100000000001</v>
+        <v>0.61582000000000003</v>
       </c>
       <c r="C17" s="1">
-        <v>0.61152200000000001</v>
+        <v>0.61771600000000004</v>
       </c>
       <c r="D17" s="1">
-        <v>0.61452099999999998</v>
+        <v>0.62005100000000002</v>
       </c>
       <c r="E17" s="1">
-        <v>0.61818899999999999</v>
+        <v>0.62332100000000001</v>
       </c>
       <c r="F17" s="1">
-        <v>0.62138599999999999</v>
+        <v>0.62336400000000003</v>
       </c>
       <c r="G17" s="1">
-        <v>0.62445200000000001</v>
+        <v>0.62293200000000004</v>
       </c>
       <c r="H17" s="1">
-        <v>0.62879700000000005</v>
+        <v>0.626475</v>
       </c>
       <c r="I17" s="1">
-        <v>0.63359100000000002</v>
+        <v>0.62728799999999996</v>
       </c>
       <c r="J17" s="1">
-        <v>0.63606799999999997</v>
+        <v>0.62915699999999997</v>
       </c>
       <c r="K17" s="1">
-        <v>0.64141599999999999</v>
+        <v>0.63236999999999999</v>
       </c>
       <c r="L17" s="1">
-        <v>0.64522299999999999</v>
+        <v>0.63816700000000004</v>
       </c>
       <c r="M17" s="1">
-        <v>0.65023399999999998</v>
+        <v>0.64133799999999996</v>
       </c>
       <c r="N17" s="1">
-        <v>0.65542900000000004</v>
+        <v>0.649648</v>
       </c>
       <c r="O17" s="1">
-        <v>0.66133699999999995</v>
+        <v>0.65926399999999996</v>
       </c>
       <c r="P17" s="1">
-        <v>0.67409600000000003</v>
+        <v>0.66981800000000002</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.68037000000000003</v>
+        <v>0.68288499999999996</v>
       </c>
       <c r="R17" s="1">
-        <v>0.68130900000000005</v>
+        <v>0.69220300000000001</v>
       </c>
       <c r="S17" s="1">
-        <v>0.69323299999999999</v>
+        <v>0.70179899999999995</v>
       </c>
       <c r="T17" s="1">
-        <v>0.70170900000000003</v>
+        <v>0.70463399999999998</v>
       </c>
       <c r="U17" s="1">
-        <v>0.71221299999999998</v>
+        <v>0.71537799999999996</v>
       </c>
       <c r="V17" s="1">
-        <v>0.71529399999999999</v>
+        <v>0.726047</v>
       </c>
       <c r="W17" s="1">
-        <v>0.72519</v>
+        <v>0.73460599999999998</v>
       </c>
       <c r="X17" s="1">
-        <v>0.72385200000000005</v>
+        <v>0.738869</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.70520000000000005</v>
+        <v>0.71088200000000001</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
-        <v>0.60140800000000005</v>
+        <v>0.61405200000000004</v>
       </c>
       <c r="B18" s="1">
-        <v>0.60355099999999995</v>
+        <v>0.61654100000000001</v>
       </c>
       <c r="C18" s="1">
-        <v>0.60679899999999998</v>
+        <v>0.61826099999999995</v>
       </c>
       <c r="D18" s="1">
-        <v>0.61021000000000003</v>
+        <v>0.62048000000000003</v>
       </c>
       <c r="E18" s="1">
-        <v>0.61338099999999995</v>
+        <v>0.623081</v>
       </c>
       <c r="F18" s="1">
-        <v>0.61735099999999998</v>
+        <v>0.62383699999999997</v>
       </c>
       <c r="G18" s="1">
-        <v>0.62063800000000002</v>
+        <v>0.62435700000000005</v>
       </c>
       <c r="H18" s="1">
-        <v>0.62421599999999999</v>
+        <v>0.62755700000000003</v>
       </c>
       <c r="I18" s="1">
-        <v>0.62876500000000002</v>
+        <v>0.627834</v>
       </c>
       <c r="J18" s="1">
-        <v>0.63126000000000004</v>
+        <v>0.63030799999999998</v>
       </c>
       <c r="K18" s="1">
-        <v>0.63666999999999996</v>
+        <v>0.63272600000000001</v>
       </c>
       <c r="L18" s="1">
-        <v>0.63989600000000002</v>
+        <v>0.63871599999999995</v>
       </c>
       <c r="M18" s="1">
-        <v>0.64497400000000005</v>
+        <v>0.64268999999999998</v>
       </c>
       <c r="N18" s="1">
-        <v>0.65091299999999996</v>
+        <v>0.64942200000000005</v>
       </c>
       <c r="O18" s="1">
-        <v>0.65646300000000002</v>
+        <v>0.66004600000000002</v>
       </c>
       <c r="P18" s="1">
-        <v>0.67102399999999995</v>
+        <v>0.67113500000000004</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.67579</v>
+        <v>0.68370299999999995</v>
       </c>
       <c r="R18" s="1">
-        <v>0.67718800000000001</v>
+        <v>0.69149099999999997</v>
       </c>
       <c r="S18" s="1">
-        <v>0.68795399999999995</v>
+        <v>0.70212300000000005</v>
       </c>
       <c r="T18" s="1">
-        <v>0.69659300000000002</v>
+        <v>0.70641699999999996</v>
       </c>
       <c r="U18" s="1">
-        <v>0.70737300000000003</v>
+        <v>0.714395</v>
       </c>
       <c r="V18" s="1">
-        <v>0.70910099999999998</v>
+        <v>0.72226699999999999</v>
       </c>
       <c r="W18" s="1">
-        <v>0.71523199999999998</v>
+        <v>0.72954799999999997</v>
       </c>
       <c r="X18" s="1">
-        <v>0.718449</v>
+        <v>0.72966299999999995</v>
       </c>
       <c r="Y18" s="1">
-        <v>0.70308099999999996</v>
+        <v>0.70729399999999998</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
-        <v>0.60002100000000003</v>
+        <v>0.61291099999999998</v>
       </c>
       <c r="B19" s="1">
-        <v>0.60244299999999995</v>
+        <v>0.61547700000000005</v>
       </c>
       <c r="C19" s="1">
-        <v>0.60502599999999995</v>
+        <v>0.61715100000000001</v>
       </c>
       <c r="D19" s="1">
-        <v>0.60775599999999996</v>
+        <v>0.61861100000000002</v>
       </c>
       <c r="E19" s="1">
-        <v>0.61119100000000004</v>
+        <v>0.62222</v>
       </c>
       <c r="F19" s="1">
-        <v>0.61521899999999996</v>
+        <v>0.622695</v>
       </c>
       <c r="G19" s="1">
-        <v>0.61864699999999995</v>
+        <v>0.62303699999999995</v>
       </c>
       <c r="H19" s="1">
-        <v>0.62188500000000002</v>
+        <v>0.62696799999999997</v>
       </c>
       <c r="I19" s="1">
-        <v>0.62534999999999996</v>
+        <v>0.62816799999999995</v>
       </c>
       <c r="J19" s="1">
-        <v>0.62795100000000004</v>
+        <v>0.63104199999999999</v>
       </c>
       <c r="K19" s="1">
-        <v>0.63407999999999998</v>
+        <v>0.63313200000000003</v>
       </c>
       <c r="L19" s="1">
-        <v>0.63590899999999995</v>
+        <v>0.63918399999999997</v>
       </c>
       <c r="M19" s="1">
-        <v>0.63978500000000005</v>
+        <v>0.64363099999999995</v>
       </c>
       <c r="N19" s="1">
-        <v>0.64579600000000004</v>
+        <v>0.64983000000000002</v>
       </c>
       <c r="O19" s="1">
-        <v>0.652667</v>
+        <v>0.66193900000000006</v>
       </c>
       <c r="P19" s="1">
-        <v>0.66946899999999998</v>
+        <v>0.672682</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.671292</v>
+        <v>0.68265200000000004</v>
       </c>
       <c r="R19" s="1">
-        <v>0.67136700000000005</v>
+        <v>0.69086700000000001</v>
       </c>
       <c r="S19" s="1">
-        <v>0.68281499999999995</v>
+        <v>0.70117499999999999</v>
       </c>
       <c r="T19" s="1">
-        <v>0.68965299999999996</v>
+        <v>0.70627099999999998</v>
       </c>
       <c r="U19" s="1">
-        <v>0.70399599999999996</v>
+        <v>0.71290799999999999</v>
       </c>
       <c r="V19" s="1">
-        <v>0.704426</v>
+        <v>0.72367700000000001</v>
       </c>
       <c r="W19" s="1">
-        <v>0.70770100000000002</v>
+        <v>0.73380400000000001</v>
       </c>
       <c r="X19" s="1">
-        <v>0.70577999999999996</v>
+        <v>0.73478900000000003</v>
       </c>
       <c r="Y19" s="1">
-        <v>0.70014799999999999</v>
+        <v>0.72123400000000004</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
-        <v>0.59628599999999998</v>
+        <v>0.60728400000000005</v>
       </c>
       <c r="B20" s="1">
-        <v>0.59862300000000002</v>
+        <v>0.60890699999999998</v>
       </c>
       <c r="C20" s="1">
-        <v>0.60141800000000001</v>
+        <v>0.61155800000000005</v>
       </c>
       <c r="D20" s="1">
-        <v>0.60408899999999999</v>
+        <v>0.61257200000000001</v>
       </c>
       <c r="E20" s="1">
-        <v>0.60706599999999999</v>
+        <v>0.61490800000000001</v>
       </c>
       <c r="F20" s="1">
-        <v>0.61027100000000001</v>
+        <v>0.61570000000000003</v>
       </c>
       <c r="G20" s="1">
-        <v>0.61346500000000004</v>
+        <v>0.61558199999999996</v>
       </c>
       <c r="H20" s="1">
-        <v>0.61678999999999995</v>
+        <v>0.61979099999999998</v>
       </c>
       <c r="I20" s="1">
-        <v>0.62044500000000002</v>
+        <v>0.62139800000000001</v>
       </c>
       <c r="J20" s="1">
-        <v>0.62335700000000005</v>
+        <v>0.62375700000000001</v>
       </c>
       <c r="K20" s="1">
-        <v>0.62822199999999995</v>
+        <v>0.62629100000000004</v>
       </c>
       <c r="L20" s="1">
-        <v>0.63005699999999998</v>
+        <v>0.63191600000000003</v>
       </c>
       <c r="M20" s="1">
-        <v>0.63404400000000005</v>
+        <v>0.63677300000000003</v>
       </c>
       <c r="N20" s="1">
-        <v>0.63844500000000004</v>
+        <v>0.64231400000000005</v>
       </c>
       <c r="O20" s="1">
-        <v>0.64599399999999996</v>
+        <v>0.65468700000000002</v>
       </c>
       <c r="P20" s="1">
-        <v>0.66308100000000003</v>
+        <v>0.66690899999999997</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.66463399999999995</v>
+        <v>0.67618199999999995</v>
       </c>
       <c r="R20" s="1">
-        <v>0.66417300000000001</v>
+        <v>0.68282299999999996</v>
       </c>
       <c r="S20" s="1">
-        <v>0.67736099999999999</v>
+        <v>0.69549099999999997</v>
       </c>
       <c r="T20" s="1">
-        <v>0.68218299999999998</v>
+        <v>0.70358399999999999</v>
       </c>
       <c r="U20" s="1">
-        <v>0.69382900000000003</v>
+        <v>0.71011400000000002</v>
       </c>
       <c r="V20" s="1">
-        <v>0.694743</v>
+        <v>0.72008799999999995</v>
       </c>
       <c r="W20" s="1">
-        <v>0.69928800000000002</v>
+        <v>0.72588200000000003</v>
       </c>
       <c r="X20" s="1">
-        <v>0.69237899999999997</v>
+        <v>0.72597500000000004</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.68878600000000001</v>
+        <v>0.71697900000000003</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
-        <v>0.58871399999999996</v>
+        <v>0.60893299999999995</v>
       </c>
       <c r="B21" s="1">
-        <v>0.59072999999999998</v>
+        <v>0.61122699999999996</v>
       </c>
       <c r="C21" s="1">
-        <v>0.592746</v>
+        <v>0.61267099999999997</v>
       </c>
       <c r="D21" s="1">
-        <v>0.59532799999999997</v>
+        <v>0.613147</v>
       </c>
       <c r="E21" s="1">
-        <v>0.598024</v>
+        <v>0.616232</v>
       </c>
       <c r="F21" s="1">
-        <v>0.60062599999999999</v>
+        <v>0.61687099999999995</v>
       </c>
       <c r="G21" s="1">
-        <v>0.60347200000000001</v>
+        <v>0.61759600000000003</v>
       </c>
       <c r="H21" s="1">
-        <v>0.607159</v>
+        <v>0.62071299999999996</v>
       </c>
       <c r="I21" s="1">
-        <v>0.61086200000000002</v>
+        <v>0.62271799999999999</v>
       </c>
       <c r="J21" s="1">
-        <v>0.61453599999999997</v>
+        <v>0.62511300000000003</v>
       </c>
       <c r="K21" s="1">
-        <v>0.61942399999999997</v>
+        <v>0.62814899999999996</v>
       </c>
       <c r="L21" s="1">
-        <v>0.62288699999999997</v>
+        <v>0.63191299999999995</v>
       </c>
       <c r="M21" s="1">
-        <v>0.62744599999999995</v>
+        <v>0.63911399999999996</v>
       </c>
       <c r="N21" s="1">
-        <v>0.631019</v>
+        <v>0.64454</v>
       </c>
       <c r="O21" s="1">
-        <v>0.63843899999999998</v>
+        <v>0.65600999999999998</v>
       </c>
       <c r="P21" s="1">
-        <v>0.65527199999999997</v>
+        <v>0.66788000000000003</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.65792600000000001</v>
+        <v>0.678956</v>
       </c>
       <c r="R21" s="1">
-        <v>0.65520100000000003</v>
+        <v>0.68709200000000004</v>
       </c>
       <c r="S21" s="1">
-        <v>0.66975600000000002</v>
+        <v>0.70019100000000001</v>
       </c>
       <c r="T21" s="1">
-        <v>0.67712700000000003</v>
+        <v>0.70699000000000001</v>
       </c>
       <c r="U21" s="1">
-        <v>0.69010800000000005</v>
+        <v>0.71317799999999998</v>
       </c>
       <c r="V21" s="1">
-        <v>0.68900600000000001</v>
+        <v>0.71861600000000003</v>
       </c>
       <c r="W21" s="1">
-        <v>0.69621299999999997</v>
+        <v>0.724379</v>
       </c>
       <c r="X21" s="1">
-        <v>0.69568799999999997</v>
+        <v>0.72158199999999995</v>
       </c>
       <c r="Y21" s="1">
-        <v>0.68352900000000005</v>
+        <v>0.72070699999999999</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
-        <v>0.579179</v>
+        <v>0.59996700000000003</v>
       </c>
       <c r="B22" s="1">
-        <v>0.57987699999999998</v>
+        <v>0.60250499999999996</v>
       </c>
       <c r="C22" s="1">
-        <v>0.58040000000000003</v>
+        <v>0.60333499999999995</v>
       </c>
       <c r="D22" s="1">
-        <v>0.582758</v>
+        <v>0.60394599999999998</v>
       </c>
       <c r="E22" s="1">
-        <v>0.58629500000000001</v>
+        <v>0.60753299999999999</v>
       </c>
       <c r="F22" s="1">
-        <v>0.58843299999999998</v>
+        <v>0.60670999999999997</v>
       </c>
       <c r="G22" s="1">
-        <v>0.59175500000000003</v>
+        <v>0.60776399999999997</v>
       </c>
       <c r="H22" s="1">
-        <v>0.59442200000000001</v>
+        <v>0.61249299999999995</v>
       </c>
       <c r="I22" s="1">
-        <v>0.59584899999999996</v>
+        <v>0.614201</v>
       </c>
       <c r="J22" s="1">
-        <v>0.60074700000000003</v>
+        <v>0.61556699999999998</v>
       </c>
       <c r="K22" s="1">
-        <v>0.60523300000000002</v>
+        <v>0.61677999999999999</v>
       </c>
       <c r="L22" s="1">
-        <v>0.60885299999999998</v>
+        <v>0.62001899999999999</v>
       </c>
       <c r="M22" s="1">
-        <v>0.61213200000000001</v>
+        <v>0.62575700000000001</v>
       </c>
       <c r="N22" s="1">
-        <v>0.61361100000000002</v>
+        <v>0.63304499999999997</v>
       </c>
       <c r="O22" s="1">
-        <v>0.61924900000000005</v>
+        <v>0.64489799999999997</v>
       </c>
       <c r="P22" s="1">
-        <v>0.63950899999999999</v>
+        <v>0.657416</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.64305699999999999</v>
+        <v>0.66415199999999996</v>
       </c>
       <c r="R22" s="1">
-        <v>0.64105299999999998</v>
+        <v>0.67328699999999997</v>
       </c>
       <c r="S22" s="1">
-        <v>0.65521399999999996</v>
+        <v>0.68629200000000001</v>
       </c>
       <c r="T22" s="1">
-        <v>0.65830599999999995</v>
+        <v>0.69570900000000002</v>
       </c>
       <c r="U22" s="1">
-        <v>0.66946700000000003</v>
+        <v>0.70074000000000003</v>
       </c>
       <c r="V22" s="1">
-        <v>0.66558499999999998</v>
+        <v>0.70323500000000005</v>
       </c>
       <c r="W22" s="1">
-        <v>0.67602700000000004</v>
+        <v>0.71179400000000004</v>
       </c>
       <c r="X22" s="1">
-        <v>0.67044400000000004</v>
+        <v>0.71469899999999997</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.64542299999999997</v>
+        <v>0.70670200000000005</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
-        <v>0.57812300000000005</v>
+        <v>0.58248500000000003</v>
       </c>
       <c r="B23" s="1">
-        <v>0.57925599999999999</v>
+        <v>0.58385600000000004</v>
       </c>
       <c r="C23" s="1">
-        <v>0.57955400000000001</v>
+        <v>0.58501700000000001</v>
       </c>
       <c r="D23" s="1">
-        <v>0.58165</v>
+        <v>0.58515399999999995</v>
       </c>
       <c r="E23" s="1">
-        <v>0.58247000000000004</v>
+        <v>0.58696999999999999</v>
       </c>
       <c r="F23" s="1">
-        <v>0.584229</v>
+        <v>0.58622200000000002</v>
       </c>
       <c r="G23" s="1">
-        <v>0.58643800000000001</v>
+        <v>0.58591000000000004</v>
       </c>
       <c r="H23" s="1">
-        <v>0.58765400000000001</v>
+        <v>0.59011199999999997</v>
       </c>
       <c r="I23" s="1">
-        <v>0.58885100000000001</v>
+        <v>0.59340499999999996</v>
       </c>
       <c r="J23" s="1">
-        <v>0.59280100000000002</v>
+        <v>0.59529299999999996</v>
       </c>
       <c r="K23" s="1">
-        <v>0.59321500000000005</v>
+        <v>0.59855899999999995</v>
       </c>
       <c r="L23" s="1">
-        <v>0.59709299999999998</v>
+        <v>0.60363800000000001</v>
       </c>
       <c r="M23" s="1">
-        <v>0.60289199999999998</v>
+        <v>0.61126199999999997</v>
       </c>
       <c r="N23" s="1">
-        <v>0.60536800000000002</v>
+        <v>0.61763999999999997</v>
       </c>
       <c r="O23" s="1">
-        <v>0.611097</v>
+        <v>0.62534199999999995</v>
       </c>
       <c r="P23" s="1">
-        <v>0.62923499999999999</v>
+        <v>0.63747200000000004</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.63039699999999999</v>
+        <v>0.64188100000000003</v>
       </c>
       <c r="R23" s="1">
-        <v>0.62801399999999996</v>
+        <v>0.646034</v>
       </c>
       <c r="S23" s="1">
-        <v>0.63702599999999998</v>
+        <v>0.663659</v>
       </c>
       <c r="T23" s="1">
-        <v>0.63748000000000005</v>
+        <v>0.66594200000000003</v>
       </c>
       <c r="U23" s="1">
-        <v>0.64151999999999998</v>
+        <v>0.66916699999999996</v>
       </c>
       <c r="V23" s="1">
-        <v>0.63853599999999999</v>
+        <v>0.67398999999999998</v>
       </c>
       <c r="W23" s="1">
-        <v>0.64940500000000001</v>
+        <v>0.68276899999999996</v>
       </c>
       <c r="X23" s="1">
-        <v>0.645262</v>
+        <v>0.68116600000000005</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.619834</v>
+        <v>0.66919700000000004</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
-        <v>0.57340599999999997</v>
+        <v>0.582237</v>
       </c>
       <c r="B24" s="1">
-        <v>0.575206</v>
+        <v>0.58237700000000003</v>
       </c>
       <c r="C24" s="1">
-        <v>0.57546200000000003</v>
+        <v>0.58302299999999996</v>
       </c>
       <c r="D24" s="1">
-        <v>0.57948999999999995</v>
+        <v>0.583341</v>
       </c>
       <c r="E24" s="1">
-        <v>0.58090799999999998</v>
+        <v>0.58888099999999999</v>
       </c>
       <c r="F24" s="1">
-        <v>0.58006000000000002</v>
+        <v>0.58758299999999997</v>
       </c>
       <c r="G24" s="1">
-        <v>0.58388700000000004</v>
+        <v>0.58904999999999996</v>
       </c>
       <c r="H24" s="1">
-        <v>0.58643900000000004</v>
+        <v>0.59187699999999999</v>
       </c>
       <c r="I24" s="1">
-        <v>0.58914200000000005</v>
+        <v>0.59295699999999996</v>
       </c>
       <c r="J24" s="1">
-        <v>0.59154799999999996</v>
+        <v>0.594468</v>
       </c>
       <c r="K24" s="1">
-        <v>0.58960299999999999</v>
+        <v>0.59693700000000005</v>
       </c>
       <c r="L24" s="1">
-        <v>0.59009400000000001</v>
+        <v>0.60207900000000003</v>
       </c>
       <c r="M24" s="1">
-        <v>0.59283200000000003</v>
+        <v>0.60524</v>
       </c>
       <c r="N24" s="1">
-        <v>0.59631900000000004</v>
+        <v>0.61126599999999998</v>
       </c>
       <c r="O24" s="1">
-        <v>0.60074899999999998</v>
+        <v>0.61686799999999997</v>
       </c>
       <c r="P24" s="1">
-        <v>0.61074899999999999</v>
+        <v>0.62632200000000005</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.61193799999999998</v>
+        <v>0.62809899999999996</v>
       </c>
       <c r="R24" s="1">
-        <v>0.60665800000000003</v>
+        <v>0.634216</v>
       </c>
       <c r="S24" s="1">
-        <v>0.61629199999999995</v>
+        <v>0.64655300000000004</v>
       </c>
       <c r="T24" s="1">
-        <v>0.61656500000000003</v>
+        <v>0.64397099999999996</v>
       </c>
       <c r="U24" s="1">
-        <v>0.62118700000000004</v>
+        <v>0.65647500000000003</v>
       </c>
       <c r="V24" s="1">
-        <v>0.61916099999999996</v>
+        <v>0.66148399999999996</v>
       </c>
       <c r="W24" s="1">
-        <v>0.64156800000000003</v>
+        <v>0.66699299999999995</v>
       </c>
       <c r="X24" s="1">
-        <v>0.64440600000000003</v>
+        <v>0.68498800000000004</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.61796300000000004</v>
+        <v>0.67397700000000005</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
-        <v>0.50444900000000004</v>
+        <v>0.51012199999999996</v>
       </c>
       <c r="B25" s="1">
-        <v>0.50394899999999998</v>
+        <v>0.50929999999999997</v>
       </c>
       <c r="C25" s="1">
-        <v>0.50322199999999995</v>
+        <v>0.50873800000000002</v>
       </c>
       <c r="D25" s="1">
-        <v>0.50278400000000001</v>
+        <v>0.50818300000000005</v>
       </c>
       <c r="E25" s="1">
-        <v>0.50236000000000003</v>
+        <v>0.50754900000000003</v>
       </c>
       <c r="F25" s="1">
-        <v>0.50170099999999995</v>
+        <v>0.50703799999999999</v>
       </c>
       <c r="G25" s="1">
-        <v>0.50077199999999999</v>
+        <v>0.50656999999999996</v>
       </c>
       <c r="H25" s="1">
-        <v>0.50268299999999999</v>
+        <v>0.50838799999999995</v>
       </c>
       <c r="I25" s="1">
-        <v>0.50160800000000005</v>
+        <v>0.50759500000000002</v>
       </c>
       <c r="J25" s="1">
-        <v>0.50651400000000002</v>
+        <v>0.50686100000000001</v>
       </c>
       <c r="K25" s="1">
-        <v>0.50525799999999998</v>
+        <v>0.50551199999999996</v>
       </c>
       <c r="L25" s="1">
-        <v>0.51023499999999999</v>
+        <v>0.50746999999999998</v>
       </c>
       <c r="M25" s="1">
-        <v>0.51452399999999998</v>
+        <v>0.50659399999999999</v>
       </c>
       <c r="N25" s="1">
-        <v>0.51322599999999996</v>
+        <v>0.51284700000000005</v>
       </c>
       <c r="O25" s="1">
-        <v>0.52746099999999996</v>
+        <v>0.51597599999999999</v>
       </c>
       <c r="P25" s="1">
-        <v>0.53505400000000003</v>
+        <v>0.51983900000000005</v>
       </c>
       <c r="Q25" s="1">
-        <v>0.53544999999999998</v>
+        <v>0.51727800000000002</v>
       </c>
       <c r="R25" s="1">
-        <v>0.53142100000000003</v>
+        <v>0.52332400000000001</v>
       </c>
       <c r="S25" s="1">
-        <v>0.54202600000000001</v>
+        <v>0.53810599999999997</v>
       </c>
       <c r="T25" s="1">
-        <v>0.53917199999999998</v>
+        <v>0.546516</v>
       </c>
       <c r="U25" s="1">
-        <v>0.53331700000000004</v>
+        <v>0.55033600000000005</v>
       </c>
       <c r="V25" s="1">
-        <v>0.52821300000000004</v>
+        <v>0.55755100000000002</v>
       </c>
       <c r="W25" s="1">
-        <v>0.55374599999999996</v>
+        <v>0.56774800000000003</v>
       </c>
       <c r="X25" s="1">
-        <v>0.54732400000000003</v>
+        <v>0.57280299999999995</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.53135100000000002</v>
+        <v>0.55491599999999996</v>
       </c>
     </row>
   </sheetData>
